--- a/Tickers_Info.xlsx
+++ b/Tickers_Info.xlsx
@@ -5,21 +5,21 @@
   <workbookPr defaultThemeVersion="153222"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Dropbox\+Trading\AlgorithmicTrading\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Dropbox\+Trading\AlgorithmicTrading\StockScreener\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="16392" windowHeight="5784"/>
   </bookViews>
   <sheets>
-    <sheet name="Canada" sheetId="1" r:id="rId1"/>
+    <sheet name="TSX" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="152511"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="689" uniqueCount="554">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="686" uniqueCount="551">
   <si>
     <t>Name</t>
   </si>
@@ -222,15 +222,6 @@
     <t>IFC.TO</t>
   </si>
   <si>
-    <t>lululemon athletica</t>
-  </si>
-  <si>
-    <t>LULU</t>
-  </si>
-  <si>
-    <t>LULU.TO</t>
-  </si>
-  <si>
     <t>Wheaton Precious Metals</t>
   </si>
   <si>
@@ -540,12 +531,6 @@
     <t>Descartes Systems Group</t>
   </si>
   <si>
-    <t>DSGX</t>
-  </si>
-  <si>
-    <t>DSGX.TO</t>
-  </si>
-  <si>
     <t>Lundin Gold</t>
   </si>
   <si>
@@ -1681,6 +1666,12 @@
   </si>
   <si>
     <t>SIS.TO</t>
+  </si>
+  <si>
+    <t>DSG</t>
+  </si>
+  <si>
+    <t>DSG.TO</t>
   </si>
 </sst>
 </file>
@@ -2241,8 +2232,11 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:E229" totalsRowShown="0">
-  <autoFilter ref="A1:E229"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:E228" totalsRowShown="0">
+  <autoFilter ref="A1:E228"/>
+  <sortState ref="A2:E228">
+    <sortCondition ref="E2"/>
+  </sortState>
   <tableColumns count="5">
     <tableColumn id="1" name="Name"/>
     <tableColumn id="2" name="Symbol" dataDxfId="3"/>
@@ -2517,7 +2511,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E229"/>
+  <dimension ref="A1:E228"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="34" bestFit="1" customWidth="1"/>
@@ -2546,2985 +2540,2985 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>5</v>
+        <v>482</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>6</v>
+        <v>483</v>
       </c>
       <c r="C2" s="1">
-        <v>171.63</v>
+        <v>1.35</v>
       </c>
       <c r="D2" s="1">
-        <v>120.86</v>
+        <v>3.9136799999999998</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>7</v>
+        <v>483</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>491</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>9</v>
+        <v>492</v>
       </c>
       <c r="C3" s="1">
-        <v>136.30000000000001</v>
+        <v>1.29</v>
       </c>
       <c r="D3" s="1">
-        <v>104.34</v>
+        <v>7.7057399999999996</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>10</v>
+        <v>492</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>11</v>
+        <v>243</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>12</v>
+        <v>244</v>
       </c>
       <c r="C4" s="1">
-        <v>111.37</v>
+        <v>4.47</v>
       </c>
       <c r="D4" s="1">
-        <v>63.28</v>
+        <v>13.1434</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>13</v>
+        <v>244</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>14</v>
+        <v>259</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>15</v>
+        <v>260</v>
       </c>
       <c r="C5" s="1">
-        <v>97.75</v>
+        <v>4</v>
       </c>
       <c r="D5" s="1">
-        <v>44.55</v>
+        <v>35.595199999999998</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>16</v>
+        <v>260</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>17</v>
+        <v>49</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>18</v>
+        <v>50</v>
       </c>
       <c r="C6" s="1">
-        <v>94.52</v>
+        <v>53.87</v>
       </c>
       <c r="D6" s="1">
-        <v>57.47</v>
+        <v>106.46</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>19</v>
+        <v>51</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>20</v>
+        <v>320</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>21</v>
+        <v>321</v>
       </c>
       <c r="C7" s="1">
-        <v>90.82</v>
+        <v>2.83</v>
       </c>
       <c r="D7" s="1">
-        <v>58.7</v>
+        <v>5.83</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>22</v>
+        <v>322</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>23</v>
+        <v>161</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>24</v>
+        <v>162</v>
       </c>
       <c r="C8" s="1">
-        <v>83.63</v>
+        <v>10.52</v>
       </c>
       <c r="D8" s="1">
-        <v>184.75</v>
+        <v>24.88</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>25</v>
+        <v>163</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>26</v>
+        <v>413</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>27</v>
+        <v>414</v>
       </c>
       <c r="C9" s="1">
-        <v>77.78</v>
+        <v>1.81</v>
       </c>
       <c r="D9" s="1">
-        <v>3670.43</v>
+        <v>40.188600000000001</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>27</v>
+        <v>414</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>28</v>
+        <v>191</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>29</v>
+        <v>192</v>
       </c>
       <c r="C10" s="1">
-        <v>73.819999999999993</v>
+        <v>8.02</v>
       </c>
       <c r="D10" s="1">
-        <v>101.46</v>
+        <v>26.8019</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>30</v>
+        <v>192</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>31</v>
+        <v>453</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>32</v>
+        <v>454</v>
       </c>
       <c r="C11" s="1">
-        <v>71.64</v>
+        <v>1.5</v>
       </c>
       <c r="D11" s="1">
-        <v>76.599999999999994</v>
+        <v>38.306899999999999</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>33</v>
+        <v>454</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>34</v>
+        <v>446</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>35</v>
+        <v>447</v>
       </c>
       <c r="C12" s="1">
-        <v>66.290000000000006</v>
+        <v>1.52</v>
       </c>
       <c r="D12" s="1">
-        <v>31.42</v>
+        <v>10.875299999999999</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>36</v>
+        <v>447</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>37</v>
+        <v>245</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>38</v>
+        <v>246</v>
       </c>
       <c r="C13" s="1">
-        <v>66.010000000000005</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="D13" s="1">
-        <v>104.7</v>
+        <v>5.71</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>39</v>
+        <v>247</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>40</v>
+        <v>151</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>41</v>
+        <v>152</v>
       </c>
       <c r="C14" s="1">
-        <v>63.35</v>
+        <v>11.56</v>
       </c>
       <c r="D14" s="1">
-        <v>50.55</v>
+        <v>19.761600000000001</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>42</v>
+        <v>152</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="C15" s="1">
-        <v>60.16</v>
+        <v>47.15</v>
       </c>
       <c r="D15" s="1">
-        <v>63.68</v>
+        <v>49.7331</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>45</v>
+        <v>56</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>46</v>
+        <v>418</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>47</v>
+        <v>419</v>
       </c>
       <c r="C16" s="1">
-        <v>54.59</v>
+        <v>1.78</v>
       </c>
       <c r="D16" s="1">
-        <v>31.6</v>
+        <v>3.4772400000000001</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>48</v>
+        <v>419</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>49</v>
+        <v>172</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>50</v>
+        <v>173</v>
       </c>
       <c r="C17" s="1">
-        <v>53.87</v>
+        <v>9.31</v>
       </c>
       <c r="D17" s="1">
-        <v>106.46</v>
+        <v>53.2318</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>51</v>
+        <v>173</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>52</v>
+        <v>341</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>53</v>
+        <v>342</v>
       </c>
       <c r="C18" s="1">
-        <v>50.27</v>
+        <v>2.65</v>
       </c>
       <c r="D18" s="1">
-        <v>48.12</v>
+        <v>26.97</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>54</v>
+        <v>343</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>55</v>
+        <v>232</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>56</v>
+        <v>233</v>
       </c>
       <c r="C19" s="1">
-        <v>47.15</v>
+        <v>5.29</v>
       </c>
       <c r="D19" s="1">
-        <v>49.7331</v>
+        <v>46.2273</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>56</v>
+        <v>233</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>57</v>
+        <v>523</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>58</v>
+        <v>524</v>
       </c>
       <c r="C20" s="1">
-        <v>45.76</v>
+        <v>1.1100000000000001</v>
       </c>
       <c r="D20" s="1">
-        <v>153.03399999999999</v>
+        <v>8.1199999999999992</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>58</v>
+        <v>525</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>59</v>
+        <v>17</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>60</v>
+        <v>18</v>
       </c>
       <c r="C21" s="1">
-        <v>44.38</v>
+        <v>94.52</v>
       </c>
       <c r="D21" s="1">
-        <v>35.869999999999997</v>
+        <v>57.47</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>61</v>
+        <v>19</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>62</v>
+        <v>370</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>63</v>
+        <v>371</v>
       </c>
       <c r="C22" s="1">
-        <v>37.07</v>
+        <v>2.3199999999999998</v>
       </c>
       <c r="D22" s="1">
-        <v>72.47</v>
+        <v>3.88</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>64</v>
+        <v>372</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>65</v>
+        <v>219</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>66</v>
+        <v>220</v>
       </c>
       <c r="C23" s="1">
-        <v>37.049999999999997</v>
+        <v>6.3</v>
       </c>
       <c r="D23" s="1">
-        <v>207.76900000000001</v>
+        <v>64.364699999999999</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>66</v>
+        <v>220</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>67</v>
+        <v>119</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>68</v>
+        <v>119</v>
       </c>
       <c r="C24" s="1">
-        <v>36.549999999999997</v>
+        <v>20.88</v>
       </c>
       <c r="D24" s="1">
-        <v>304.2</v>
+        <v>22.56</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>69</v>
+        <v>120</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>70</v>
+        <v>530</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>71</v>
+        <v>531</v>
       </c>
       <c r="C25" s="1">
-        <v>35.979999999999997</v>
+        <v>1.06</v>
       </c>
       <c r="D25" s="1">
-        <v>78.98</v>
+        <v>31.266500000000001</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>72</v>
+        <v>531</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>73</v>
+        <v>356</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>74</v>
+        <v>357</v>
       </c>
       <c r="C26" s="1">
-        <v>35.590000000000003</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="D26" s="1">
-        <v>62.46</v>
+        <v>47.915799999999997</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>75</v>
+        <v>357</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>76</v>
+        <v>415</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>77</v>
+        <v>416</v>
       </c>
       <c r="C27" s="1">
-        <v>35.270000000000003</v>
+        <v>1.78</v>
       </c>
       <c r="D27" s="1">
-        <v>90.165000000000006</v>
+        <v>4.78</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>77</v>
+        <v>417</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>78</v>
+        <v>499</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>79</v>
+        <v>500</v>
       </c>
       <c r="C28" s="1">
-        <v>35.24</v>
+        <v>1.25</v>
       </c>
       <c r="D28" s="1">
-        <v>1574.78</v>
+        <v>4.5790800000000003</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>79</v>
+        <v>500</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>80</v>
+        <v>251</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>81</v>
+        <v>252</v>
       </c>
       <c r="C29" s="1">
-        <v>34.159999999999997</v>
+        <v>4.2</v>
       </c>
       <c r="D29" s="1">
-        <v>36.675600000000003</v>
+        <v>11.89</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>81</v>
+        <v>253</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>82</v>
+        <v>365</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>83</v>
+        <v>366</v>
       </c>
       <c r="C30" s="1">
-        <v>32.869999999999997</v>
+        <v>2.34</v>
       </c>
       <c r="D30" s="1">
-        <v>118.562</v>
+        <v>22.730799999999999</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>83</v>
+        <v>366</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>84</v>
+        <v>28</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>85</v>
+        <v>29</v>
       </c>
       <c r="C31" s="1">
-        <v>32.590000000000003</v>
+        <v>73.819999999999993</v>
       </c>
       <c r="D31" s="1">
-        <v>18.86</v>
+        <v>101.46</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>86</v>
+        <v>30</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>87</v>
+        <v>20</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="C32" s="1">
-        <v>31.4</v>
+        <v>90.82</v>
       </c>
       <c r="D32" s="1">
-        <v>68.790000000000006</v>
+        <v>58.7</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>89</v>
+        <v>22</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>90</v>
+        <v>40</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>91</v>
+        <v>41</v>
       </c>
       <c r="C33" s="1">
-        <v>30.73</v>
+        <v>63.35</v>
       </c>
       <c r="D33" s="1">
-        <v>158.66999999999999</v>
+        <v>50.55</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>92</v>
+        <v>42</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>93</v>
+        <v>479</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>94</v>
+        <v>480</v>
       </c>
       <c r="C34" s="1">
-        <v>27.61</v>
+        <v>1.36</v>
       </c>
       <c r="D34" s="1">
-        <v>56.2</v>
+        <v>1.75</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>95</v>
+        <v>481</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>96</v>
+        <v>267</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>97</v>
+        <v>268</v>
       </c>
       <c r="C35" s="1">
-        <v>25.15</v>
+        <v>3.93</v>
       </c>
       <c r="D35" s="1">
-        <v>13.71</v>
+        <v>2.96</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>98</v>
+        <v>269</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>99</v>
+        <v>302</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>100</v>
+        <v>303</v>
       </c>
       <c r="C36" s="1">
-        <v>24.3</v>
+        <v>3.26</v>
       </c>
       <c r="D36" s="1">
-        <v>107.89</v>
+        <v>152.06800000000001</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>101</v>
+        <v>303</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>102</v>
+        <v>181</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>103</v>
+        <v>181</v>
       </c>
       <c r="C37" s="1">
-        <v>24.29</v>
+        <v>8.5</v>
       </c>
       <c r="D37" s="1">
-        <v>186.14699999999999</v>
+        <v>26.45</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>103</v>
+        <v>182</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>104</v>
+        <v>241</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>105</v>
+        <v>242</v>
       </c>
       <c r="C38" s="1">
-        <v>24.2</v>
+        <v>4.8499999999999996</v>
       </c>
       <c r="D38" s="1">
-        <v>15.93</v>
+        <v>29.8857</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>106</v>
+        <v>242</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>107</v>
+        <v>390</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>108</v>
+        <v>391</v>
       </c>
       <c r="C39" s="1">
-        <v>23.86</v>
+        <v>2.04</v>
       </c>
       <c r="D39" s="1">
-        <v>184.53700000000001</v>
+        <v>48.445300000000003</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>108</v>
+        <v>391</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="C40" s="1">
-        <v>23.55</v>
+        <v>22.37</v>
       </c>
       <c r="D40" s="1">
-        <v>46.74</v>
+        <v>51.16</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>112</v>
+        <v>167</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>113</v>
+        <v>168</v>
       </c>
       <c r="C41" s="1">
-        <v>22.92</v>
+        <v>9.8800000000000008</v>
       </c>
       <c r="D41" s="1">
-        <v>36.060299999999998</v>
+        <v>56.093800000000002</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>113</v>
+        <v>168</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>114</v>
+        <v>519</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>115</v>
+        <v>520</v>
       </c>
       <c r="C42" s="1">
-        <v>22.37</v>
+        <v>1.1599999999999999</v>
       </c>
       <c r="D42" s="1">
-        <v>51.16</v>
+        <v>9.8020999999999994</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>116</v>
+        <v>520</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>117</v>
+        <v>474</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>118</v>
+        <v>475</v>
       </c>
       <c r="C43" s="1">
-        <v>21.6</v>
+        <v>1.38</v>
       </c>
       <c r="D43" s="1">
-        <v>37.03</v>
+        <v>6.64</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>119</v>
+        <v>476</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>120</v>
+        <v>350</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>121</v>
+        <v>351</v>
       </c>
       <c r="C44" s="1">
-        <v>21.36</v>
+        <v>2.61</v>
       </c>
       <c r="D44" s="1">
-        <v>35.638100000000001</v>
+        <v>6.5752800000000002</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>121</v>
+        <v>351</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>122</v>
+        <v>195</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>122</v>
+        <v>196</v>
       </c>
       <c r="C45" s="1">
-        <v>20.88</v>
+        <v>7.71</v>
       </c>
       <c r="D45" s="1">
-        <v>22.56</v>
+        <v>10.6464</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>123</v>
+        <v>196</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>124</v>
+        <v>214</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>125</v>
+        <v>215</v>
       </c>
       <c r="C46" s="1">
-        <v>19.47</v>
+        <v>6.58</v>
       </c>
       <c r="D46" s="1">
-        <v>104.17</v>
+        <v>129.09</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>126</v>
+        <v>216</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>127</v>
+        <v>532</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>128</v>
+        <v>533</v>
       </c>
       <c r="C47" s="1">
-        <v>18.850000000000001</v>
+        <v>1.06</v>
       </c>
       <c r="D47" s="1">
-        <v>37.67</v>
+        <v>67.985100000000003</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>129</v>
+        <v>533</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>130</v>
+        <v>148</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>131</v>
+        <v>149</v>
       </c>
       <c r="C48" s="1">
-        <v>17.850000000000001</v>
+        <v>11.58</v>
       </c>
       <c r="D48" s="1">
-        <v>48.68</v>
+        <v>100.32</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>132</v>
+        <v>150</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>133</v>
+        <v>43</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>134</v>
+        <v>44</v>
       </c>
       <c r="C49" s="1">
-        <v>17.07</v>
+        <v>60.16</v>
       </c>
       <c r="D49" s="1">
-        <v>45.569000000000003</v>
+        <v>63.68</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>134</v>
+        <v>45</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>135</v>
+        <v>37</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>136</v>
+        <v>38</v>
       </c>
       <c r="C50" s="1">
-        <v>16.899999999999999</v>
+        <v>66.010000000000005</v>
       </c>
       <c r="D50" s="1">
-        <v>13.7</v>
+        <v>104.7</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>137</v>
+        <v>39</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>138</v>
+        <v>34</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>139</v>
+        <v>35</v>
       </c>
       <c r="C51" s="1">
-        <v>16.12</v>
+        <v>66.290000000000006</v>
       </c>
       <c r="D51" s="1">
-        <v>73.444199999999995</v>
+        <v>31.42</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>139</v>
+        <v>36</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>140</v>
+        <v>31</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>141</v>
+        <v>32</v>
       </c>
       <c r="C52" s="1">
-        <v>14.3</v>
+        <v>71.64</v>
       </c>
       <c r="D52" s="1">
-        <v>25.77</v>
+        <v>76.599999999999994</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>142</v>
+        <v>33</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>143</v>
+        <v>226</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>144</v>
+        <v>227</v>
       </c>
       <c r="C53" s="1">
-        <v>13.98</v>
+        <v>5.94</v>
       </c>
       <c r="D53" s="1">
-        <v>10.3316</v>
+        <v>38.385599999999997</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>144</v>
+        <v>227</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>145</v>
+        <v>400</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>146</v>
+        <v>401</v>
       </c>
       <c r="C54" s="1">
-        <v>13.51</v>
+        <v>1.9</v>
       </c>
       <c r="D54" s="1">
-        <v>14.703099999999999</v>
+        <v>10.3101</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>146</v>
+        <v>401</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>147</v>
+        <v>352</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>148</v>
+        <v>353</v>
       </c>
       <c r="C55" s="1">
-        <v>12.83</v>
+        <v>2.61</v>
       </c>
       <c r="D55" s="1">
-        <v>43.086300000000001</v>
+        <v>10.9826</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>148</v>
+        <v>353</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>149</v>
+        <v>270</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>150</v>
+        <v>271</v>
       </c>
       <c r="C56" s="1">
-        <v>12.04</v>
+        <v>3.9</v>
       </c>
       <c r="D56" s="1">
-        <v>14.4313</v>
+        <v>5.1156899999999998</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>150</v>
+        <v>271</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>151</v>
+        <v>292</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>152</v>
+        <v>293</v>
       </c>
       <c r="C57" s="1">
-        <v>11.58</v>
+        <v>3.32</v>
       </c>
       <c r="D57" s="1">
-        <v>100.32</v>
+        <v>10.911099999999999</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>153</v>
+        <v>293</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>154</v>
+        <v>286</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>155</v>
+        <v>287</v>
       </c>
       <c r="C58" s="1">
-        <v>11.56</v>
+        <v>3.56</v>
       </c>
       <c r="D58" s="1">
-        <v>19.761600000000001</v>
+        <v>12.8858</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>155</v>
+        <v>287</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>156</v>
+        <v>26</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>157</v>
+        <v>27</v>
       </c>
       <c r="C59" s="1">
-        <v>10.93</v>
+        <v>77.78</v>
       </c>
       <c r="D59" s="1">
-        <v>39.308599999999998</v>
+        <v>3670.43</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>157</v>
+        <v>27</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>158</v>
+        <v>217</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>159</v>
+        <v>218</v>
       </c>
       <c r="C60" s="1">
-        <v>10.7</v>
+        <v>6.31</v>
       </c>
       <c r="D60" s="1">
-        <v>93.48</v>
+        <v>163.845</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>160</v>
+        <v>218</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>161</v>
+        <v>228</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>162</v>
+        <v>229</v>
       </c>
       <c r="C61" s="1">
-        <v>10.58</v>
+        <v>5.38</v>
       </c>
       <c r="D61" s="1">
-        <v>127.413</v>
+        <v>26.236699999999999</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>163</v>
+        <v>229</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>164</v>
+        <v>93</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>165</v>
+        <v>94</v>
       </c>
       <c r="C62" s="1">
-        <v>10.52</v>
+        <v>25.15</v>
       </c>
       <c r="D62" s="1">
-        <v>24.88</v>
+        <v>13.71</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>166</v>
+        <v>95</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>167</v>
+        <v>409</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>168</v>
+        <v>410</v>
       </c>
       <c r="C63" s="1">
-        <v>10.29</v>
+        <v>1.82</v>
       </c>
       <c r="D63" s="1">
-        <v>36.35</v>
+        <v>2.1321400000000001</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>169</v>
+        <v>410</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>170</v>
+        <v>514</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>171</v>
+        <v>515</v>
       </c>
       <c r="C64" s="1">
-        <v>9.8800000000000008</v>
+        <v>1.17</v>
       </c>
       <c r="D64" s="1">
-        <v>56.093800000000002</v>
+        <v>53.589599999999997</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>171</v>
+        <v>515</v>
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>172</v>
+        <v>471</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>173</v>
+        <v>472</v>
       </c>
       <c r="C65" s="1">
-        <v>9.7200000000000006</v>
+        <v>1.39</v>
       </c>
       <c r="D65" s="1">
-        <v>113.17</v>
+        <v>4.2571199999999996</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>174</v>
+        <v>473</v>
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>175</v>
+        <v>237</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>176</v>
+        <v>238</v>
       </c>
       <c r="C66" s="1">
-        <v>9.6300000000000008</v>
+        <v>5.24</v>
       </c>
       <c r="D66" s="1">
-        <v>39.988300000000002</v>
+        <v>46.005499999999998</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>176</v>
+        <v>238</v>
       </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>177</v>
+        <v>379</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>178</v>
+        <v>380</v>
       </c>
       <c r="C67" s="1">
-        <v>9.31</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="D67" s="1">
-        <v>53.2318</v>
+        <v>7.54833</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>178</v>
+        <v>380</v>
       </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>179</v>
+        <v>465</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>180</v>
+        <v>466</v>
       </c>
       <c r="C68" s="1">
-        <v>9.16</v>
+        <v>1.4</v>
       </c>
       <c r="D68" s="1">
-        <v>34.3431</v>
+        <v>1.54</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>181</v>
+        <v>467</v>
       </c>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>182</v>
+        <v>497</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>183</v>
+        <v>498</v>
       </c>
       <c r="C69" s="1">
-        <v>9.1300000000000008</v>
+        <v>1.26</v>
       </c>
       <c r="D69" s="1">
-        <v>97.834999999999994</v>
+        <v>6.3892499999999997</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>183</v>
+        <v>498</v>
       </c>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>184</v>
+        <v>79</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>185</v>
+        <v>80</v>
       </c>
       <c r="C70" s="1">
-        <v>8.9499999999999993</v>
+        <v>32.869999999999997</v>
       </c>
       <c r="D70" s="1">
-        <v>22.280100000000001</v>
+        <v>118.562</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>185</v>
+        <v>80</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>186</v>
+        <v>331</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>186</v>
+        <v>332</v>
       </c>
       <c r="C71" s="1">
-        <v>8.5</v>
+        <v>2.73</v>
       </c>
       <c r="D71" s="1">
-        <v>26.45</v>
+        <v>37.200000000000003</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>187</v>
+        <v>333</v>
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>188</v>
+        <v>373</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>189</v>
+        <v>374</v>
       </c>
       <c r="C72" s="1">
-        <v>8.42</v>
+        <v>2.27</v>
       </c>
       <c r="D72" s="1">
-        <v>35.995899999999999</v>
+        <v>13.522600000000001</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>189</v>
+        <v>374</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>190</v>
+        <v>169</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>191</v>
+        <v>549</v>
       </c>
       <c r="C73" s="1">
-        <v>8.3000000000000007</v>
+        <v>9.7200000000000006</v>
       </c>
       <c r="D73" s="1">
-        <v>22.82</v>
+        <v>113.17</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>192</v>
+        <v>550</v>
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>193</v>
+        <v>455</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>194</v>
+        <v>456</v>
       </c>
       <c r="C74" s="1">
-        <v>8.0399999999999991</v>
+        <v>1.42</v>
       </c>
       <c r="D74" s="1">
-        <v>176.26</v>
+        <v>1.7743899999999999</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>195</v>
+        <v>456</v>
       </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>196</v>
+        <v>179</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>197</v>
+        <v>180</v>
       </c>
       <c r="C75" s="1">
-        <v>8.02</v>
+        <v>8.9499999999999993</v>
       </c>
       <c r="D75" s="1">
-        <v>26.8019</v>
+        <v>22.280100000000001</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>197</v>
+        <v>180</v>
       </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>198</v>
+        <v>281</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>199</v>
+        <v>282</v>
       </c>
       <c r="C76" s="1">
-        <v>7.87</v>
+        <v>3.69</v>
       </c>
       <c r="D76" s="1">
-        <v>18.623999999999999</v>
+        <v>17.87</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>199</v>
+        <v>283</v>
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>200</v>
+        <v>388</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>201</v>
+        <v>389</v>
       </c>
       <c r="C77" s="1">
-        <v>7.71</v>
+        <v>2.0499999999999998</v>
       </c>
       <c r="D77" s="1">
-        <v>10.6464</v>
+        <v>39.966799999999999</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>201</v>
+        <v>389</v>
       </c>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>202</v>
+        <v>290</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>203</v>
+        <v>291</v>
       </c>
       <c r="C78" s="1">
-        <v>7.62</v>
+        <v>3.53</v>
       </c>
       <c r="D78" s="1">
-        <v>8.9005899999999993</v>
+        <v>1019.56</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>203</v>
+        <v>291</v>
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>204</v>
+        <v>144</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>205</v>
+        <v>145</v>
       </c>
       <c r="C79" s="1">
-        <v>7.56</v>
+        <v>12.83</v>
       </c>
       <c r="D79" s="1">
-        <v>89.62</v>
+        <v>43.086300000000001</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>206</v>
+        <v>145</v>
       </c>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
-        <v>207</v>
+        <v>183</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>208</v>
+        <v>184</v>
       </c>
       <c r="C80" s="1">
-        <v>7.46</v>
+        <v>8.42</v>
       </c>
       <c r="D80" s="1">
-        <v>31.445399999999999</v>
+        <v>35.995899999999999</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>208</v>
+        <v>184</v>
       </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
-        <v>209</v>
+        <v>14</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>210</v>
+        <v>15</v>
       </c>
       <c r="C81" s="1">
-        <v>7.36</v>
+        <v>97.75</v>
       </c>
       <c r="D81" s="1">
-        <v>48.42</v>
+        <v>44.55</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>211</v>
+        <v>16</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
-        <v>212</v>
+        <v>541</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>213</v>
+        <v>542</v>
       </c>
       <c r="C82" s="1">
-        <v>7.27</v>
+        <v>1.02</v>
       </c>
       <c r="D82" s="1">
-        <v>27.94</v>
+        <v>18.566700000000001</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>214</v>
+        <v>542</v>
       </c>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
-        <v>215</v>
+        <v>344</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>216</v>
+        <v>345</v>
       </c>
       <c r="C83" s="1">
-        <v>7.12</v>
+        <v>2.64</v>
       </c>
       <c r="D83" s="1">
-        <v>31.080500000000001</v>
+        <v>68.772099999999995</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>216</v>
+        <v>345</v>
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
-        <v>217</v>
+        <v>323</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>218</v>
+        <v>324</v>
       </c>
       <c r="C84" s="1">
-        <v>6.79</v>
+        <v>2.82</v>
       </c>
       <c r="D84" s="1">
-        <v>83.539599999999993</v>
+        <v>6.14</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>218</v>
+        <v>325</v>
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
-        <v>219</v>
+        <v>457</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>220</v>
+        <v>458</v>
       </c>
       <c r="C85" s="1">
-        <v>6.58</v>
+        <v>1.41</v>
       </c>
       <c r="D85" s="1">
-        <v>129.09</v>
+        <v>13.62</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>221</v>
+        <v>459</v>
       </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
-        <v>222</v>
+        <v>348</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>223</v>
+        <v>349</v>
       </c>
       <c r="C86" s="1">
-        <v>6.31</v>
+        <v>2.61</v>
       </c>
       <c r="D86" s="1">
-        <v>163.845</v>
+        <v>12.277699999999999</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>223</v>
+        <v>349</v>
       </c>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
-        <v>224</v>
+        <v>75</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>225</v>
+        <v>76</v>
       </c>
       <c r="C87" s="1">
-        <v>6.3</v>
+        <v>35.24</v>
       </c>
       <c r="D87" s="1">
-        <v>64.364699999999999</v>
+        <v>1574.78</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>225</v>
+        <v>76</v>
       </c>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
-        <v>226</v>
+        <v>377</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>227</v>
+        <v>378</v>
       </c>
       <c r="C88" s="1">
-        <v>6.22</v>
+        <v>2.23</v>
       </c>
       <c r="D88" s="1">
-        <v>26.880600000000001</v>
+        <v>16.53</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>227</v>
+        <v>378</v>
       </c>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
-        <v>228</v>
+        <v>146</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>229</v>
+        <v>147</v>
       </c>
       <c r="C89" s="1">
-        <v>6.05</v>
+        <v>12.04</v>
       </c>
       <c r="D89" s="1">
-        <v>75.88</v>
+        <v>14.4313</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>230</v>
+        <v>147</v>
       </c>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
-        <v>231</v>
+        <v>431</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>232</v>
+        <v>432</v>
       </c>
       <c r="C90" s="1">
-        <v>5.94</v>
+        <v>1.64</v>
       </c>
       <c r="D90" s="1">
-        <v>38.385599999999997</v>
+        <v>27.266999999999999</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>232</v>
+        <v>432</v>
       </c>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
-        <v>233</v>
+        <v>87</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>234</v>
+        <v>88</v>
       </c>
       <c r="C91" s="1">
-        <v>5.38</v>
+        <v>30.73</v>
       </c>
       <c r="D91" s="1">
-        <v>26.236699999999999</v>
+        <v>158.66999999999999</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>234</v>
+        <v>89</v>
       </c>
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
-        <v>235</v>
+        <v>526</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>236</v>
+        <v>527</v>
       </c>
       <c r="C92" s="1">
-        <v>5.34</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="D92" s="1">
-        <v>75.740899999999996</v>
+        <v>2.61151</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>236</v>
+        <v>527</v>
       </c>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
-        <v>237</v>
+        <v>460</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>238</v>
+        <v>461</v>
       </c>
       <c r="C93" s="1">
-        <v>5.29</v>
+        <v>1.41</v>
       </c>
       <c r="D93" s="1">
-        <v>46.2273</v>
+        <v>8.5857799999999997</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>238</v>
+        <v>461</v>
       </c>
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
-        <v>239</v>
+        <v>422</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>240</v>
+        <v>423</v>
       </c>
       <c r="C94" s="1">
-        <v>5.27</v>
+        <v>1.72</v>
       </c>
       <c r="D94" s="1">
-        <v>25.15</v>
+        <v>5.55</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>241</v>
+        <v>424</v>
       </c>
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
-        <v>242</v>
+        <v>188</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>243</v>
+        <v>189</v>
       </c>
       <c r="C95" s="1">
-        <v>5.24</v>
+        <v>8.0399999999999991</v>
       </c>
       <c r="D95" s="1">
-        <v>46.005499999999998</v>
+        <v>176.26</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>243</v>
+        <v>190</v>
       </c>
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
-        <v>244</v>
+        <v>106</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>245</v>
+        <v>107</v>
       </c>
       <c r="C96" s="1">
-        <v>4.9000000000000004</v>
+        <v>23.55</v>
       </c>
       <c r="D96" s="1">
-        <v>28.075500000000002</v>
+        <v>46.74</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>245</v>
+        <v>108</v>
       </c>
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
-        <v>246</v>
+        <v>254</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>247</v>
+        <v>255</v>
       </c>
       <c r="C97" s="1">
-        <v>4.8499999999999996</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="D97" s="1">
-        <v>29.8857</v>
+        <v>30.379300000000001</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>247</v>
+        <v>255</v>
       </c>
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
-        <v>248</v>
+        <v>354</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>249</v>
+        <v>355</v>
       </c>
       <c r="C98" s="1">
-        <v>4.47</v>
+        <v>2.59</v>
       </c>
       <c r="D98" s="1">
-        <v>13.1434</v>
+        <v>15.826499999999999</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>249</v>
+        <v>355</v>
       </c>
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
-        <v>250</v>
+        <v>127</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>251</v>
+        <v>128</v>
       </c>
       <c r="C99" s="1">
-        <v>4.4000000000000004</v>
+        <v>17.850000000000001</v>
       </c>
       <c r="D99" s="1">
-        <v>5.71</v>
+        <v>48.68</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>252</v>
+        <v>129</v>
       </c>
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
-        <v>253</v>
+        <v>96</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>254</v>
+        <v>97</v>
       </c>
       <c r="C100" s="1">
-        <v>4.21</v>
+        <v>24.3</v>
       </c>
       <c r="D100" s="1">
-        <v>22.48</v>
+        <v>107.89</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>255</v>
+        <v>98</v>
       </c>
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
-        <v>256</v>
+        <v>204</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>257</v>
+        <v>205</v>
       </c>
       <c r="C101" s="1">
-        <v>4.2</v>
+        <v>7.36</v>
       </c>
       <c r="D101" s="1">
-        <v>11.89</v>
+        <v>48.42</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>258</v>
+        <v>206</v>
       </c>
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
-        <v>259</v>
+        <v>81</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>260</v>
+        <v>82</v>
       </c>
       <c r="C102" s="1">
-        <v>4.0999999999999996</v>
+        <v>32.590000000000003</v>
       </c>
       <c r="D102" s="1">
-        <v>30.379300000000001</v>
+        <v>18.86</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>260</v>
+        <v>83</v>
       </c>
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
-        <v>261</v>
+        <v>313</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>262</v>
+        <v>314</v>
       </c>
       <c r="C103" s="1">
-        <v>4.05</v>
+        <v>3</v>
       </c>
       <c r="D103" s="1">
-        <v>20.09</v>
+        <v>47.774999999999999</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>263</v>
+        <v>315</v>
       </c>
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
-        <v>264</v>
+        <v>425</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>265</v>
+        <v>426</v>
       </c>
       <c r="C104" s="1">
-        <v>4</v>
+        <v>1.69</v>
       </c>
       <c r="D104" s="1">
-        <v>35.595199999999998</v>
+        <v>104.11</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>265</v>
+        <v>426</v>
       </c>
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
-        <v>266</v>
+        <v>77</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>267</v>
+        <v>78</v>
       </c>
       <c r="C105" s="1">
-        <v>4</v>
+        <v>34.159999999999997</v>
       </c>
       <c r="D105" s="1">
-        <v>18.659800000000001</v>
+        <v>36.675600000000003</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>267</v>
+        <v>78</v>
       </c>
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
-        <v>268</v>
+        <v>117</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>269</v>
+        <v>118</v>
       </c>
       <c r="C106" s="1">
-        <v>3.99</v>
+        <v>21.36</v>
       </c>
       <c r="D106" s="1">
-        <v>16.9283</v>
+        <v>35.638100000000001</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>269</v>
+        <v>118</v>
       </c>
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
-        <v>270</v>
+        <v>294</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>271</v>
+        <v>295</v>
       </c>
       <c r="C107" s="1">
-        <v>3.96</v>
+        <v>3.31</v>
       </c>
       <c r="D107" s="1">
-        <v>141.072</v>
+        <v>8.33</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>271</v>
+        <v>296</v>
       </c>
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
-        <v>272</v>
+        <v>392</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>273</v>
+        <v>393</v>
       </c>
       <c r="C108" s="1">
-        <v>3.93</v>
+        <v>2</v>
       </c>
       <c r="D108" s="1">
-        <v>2.96</v>
+        <v>7.1333500000000001</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>274</v>
+        <v>393</v>
       </c>
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
-        <v>275</v>
+        <v>433</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>276</v>
+        <v>434</v>
       </c>
       <c r="C109" s="1">
-        <v>3.9</v>
+        <v>1.62</v>
       </c>
       <c r="D109" s="1">
-        <v>5.1156899999999998</v>
+        <v>15.52</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>276</v>
+        <v>435</v>
       </c>
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
-        <v>277</v>
+        <v>534</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>278</v>
+        <v>535</v>
       </c>
       <c r="C110" s="1">
-        <v>3.9</v>
+        <v>1.05</v>
       </c>
       <c r="D110" s="1">
-        <v>15.3185</v>
+        <v>4.4216800000000003</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>278</v>
+        <v>535</v>
       </c>
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
-        <v>279</v>
+        <v>177</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>280</v>
+        <v>178</v>
       </c>
       <c r="C111" s="1">
-        <v>3.72</v>
+        <v>9.1300000000000008</v>
       </c>
       <c r="D111" s="1">
-        <v>12.506600000000001</v>
+        <v>97.834999999999994</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>280</v>
+        <v>178</v>
       </c>
     </row>
     <row r="112" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="C112" s="1">
-        <v>3.7</v>
+        <v>3.63</v>
       </c>
       <c r="D112" s="1">
-        <v>6.01</v>
+        <v>6.29</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>283</v>
+        <v>178</v>
       </c>
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
-        <v>284</v>
+        <v>65</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>285</v>
+        <v>66</v>
       </c>
       <c r="C113" s="1">
-        <v>3.69</v>
+        <v>37.049999999999997</v>
       </c>
       <c r="D113" s="1">
-        <v>14.1236</v>
+        <v>207.76900000000001</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>285</v>
+        <v>66</v>
       </c>
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
-        <v>286</v>
+        <v>202</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>287</v>
+        <v>203</v>
       </c>
       <c r="C114" s="1">
-        <v>3.69</v>
+        <v>7.46</v>
       </c>
       <c r="D114" s="1">
-        <v>17.87</v>
+        <v>31.445399999999999</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>288</v>
+        <v>203</v>
       </c>
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
-        <v>289</v>
+        <v>503</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>290</v>
+        <v>504</v>
       </c>
       <c r="C115" s="1">
-        <v>3.63</v>
+        <v>1.21</v>
       </c>
       <c r="D115" s="1">
-        <v>6.29</v>
+        <v>8.1064100000000003</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>183</v>
+        <v>504</v>
       </c>
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
-        <v>291</v>
+        <v>468</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>292</v>
+        <v>469</v>
       </c>
       <c r="C116" s="1">
-        <v>3.56</v>
+        <v>1.39</v>
       </c>
       <c r="D116" s="1">
-        <v>12.8858</v>
+        <v>25.93</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>292</v>
+        <v>470</v>
       </c>
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
-        <v>293</v>
+        <v>62</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>294</v>
+        <v>63</v>
       </c>
       <c r="C117" s="1">
-        <v>3.55</v>
+        <v>37.07</v>
       </c>
       <c r="D117" s="1">
-        <v>6.0386600000000001</v>
+        <v>72.47</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>294</v>
+        <v>64</v>
       </c>
     </row>
     <row r="118" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
-        <v>295</v>
+        <v>394</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>296</v>
+        <v>395</v>
       </c>
       <c r="C118" s="1">
-        <v>3.53</v>
+        <v>1.97</v>
       </c>
       <c r="D118" s="1">
-        <v>1019.56</v>
+        <v>9.7591699999999992</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>296</v>
+        <v>395</v>
       </c>
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
-        <v>297</v>
+        <v>429</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>298</v>
+        <v>430</v>
       </c>
       <c r="C119" s="1">
-        <v>3.32</v>
+        <v>1.64</v>
       </c>
       <c r="D119" s="1">
-        <v>10.911099999999999</v>
+        <v>14.366899999999999</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>298</v>
+        <v>430</v>
       </c>
     </row>
     <row r="120" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
-        <v>299</v>
+        <v>140</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>300</v>
+        <v>141</v>
       </c>
       <c r="C120" s="1">
-        <v>3.31</v>
+        <v>13.98</v>
       </c>
       <c r="D120" s="1">
-        <v>8.33</v>
+        <v>10.3316</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>301</v>
+        <v>141</v>
       </c>
     </row>
     <row r="121" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
-        <v>302</v>
+        <v>545</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>303</v>
+        <v>546</v>
       </c>
       <c r="C121" s="1">
-        <v>3.27</v>
+        <v>1.02</v>
       </c>
       <c r="D121" s="1">
-        <v>18.366399999999999</v>
+        <v>24.254799999999999</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>303</v>
+        <v>546</v>
       </c>
     </row>
     <row r="122" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
-        <v>304</v>
+        <v>210</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>305</v>
+        <v>211</v>
       </c>
       <c r="C122" s="1">
-        <v>3.27</v>
+        <v>7.12</v>
       </c>
       <c r="D122" s="1">
-        <v>5.71</v>
+        <v>31.080500000000001</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>306</v>
+        <v>211</v>
       </c>
     </row>
     <row r="123" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
-        <v>307</v>
+        <v>132</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>308</v>
+        <v>133</v>
       </c>
       <c r="C123" s="1">
-        <v>3.26</v>
+        <v>16.899999999999999</v>
       </c>
       <c r="D123" s="1">
-        <v>152.06800000000001</v>
+        <v>13.7</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>308</v>
+        <v>134</v>
       </c>
     </row>
     <row r="124" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
-        <v>309</v>
+        <v>436</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>310</v>
+        <v>437</v>
       </c>
       <c r="C124" s="1">
-        <v>3.12</v>
+        <v>1.58</v>
       </c>
       <c r="D124" s="1">
-        <v>10.72</v>
+        <v>12.7141</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>311</v>
+        <v>437</v>
       </c>
     </row>
     <row r="125" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
-        <v>312</v>
+        <v>383</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>313</v>
+        <v>384</v>
       </c>
       <c r="C125" s="1">
-        <v>3.02</v>
+        <v>2.17</v>
       </c>
       <c r="D125" s="1">
-        <v>9.33</v>
+        <v>9.0508400000000009</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>314</v>
+        <v>384</v>
       </c>
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
-        <v>315</v>
+        <v>265</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>316</v>
+        <v>266</v>
       </c>
       <c r="C126" s="1">
-        <v>3.02</v>
+        <v>3.96</v>
       </c>
       <c r="D126" s="1">
-        <v>3.81</v>
+        <v>141.072</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>317</v>
+        <v>266</v>
       </c>
     </row>
     <row r="127" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
-        <v>318</v>
+        <v>57</v>
       </c>
       <c r="B127" s="1" t="s">
-        <v>319</v>
+        <v>58</v>
       </c>
       <c r="C127" s="1">
-        <v>3</v>
+        <v>45.76</v>
       </c>
       <c r="D127" s="1">
-        <v>47.774999999999999</v>
+        <v>153.03399999999999</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>320</v>
+        <v>58</v>
       </c>
     </row>
     <row r="128" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
-        <v>321</v>
+        <v>536</v>
       </c>
       <c r="B128" s="1" t="s">
-        <v>322</v>
+        <v>537</v>
       </c>
       <c r="C128" s="1">
-        <v>2.98</v>
+        <v>1.05</v>
       </c>
       <c r="D128" s="1">
-        <v>53.603900000000003</v>
+        <v>153.82900000000001</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>322</v>
+        <v>537</v>
       </c>
     </row>
     <row r="129" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
-        <v>323</v>
+        <v>487</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>324</v>
+        <v>488</v>
       </c>
       <c r="C129" s="1">
-        <v>2.88</v>
+        <v>1.29</v>
       </c>
       <c r="D129" s="1">
-        <v>4.1068600000000002</v>
+        <v>20.2195</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>324</v>
+        <v>488</v>
       </c>
     </row>
     <row r="130" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
-        <v>325</v>
+        <v>174</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>326</v>
+        <v>175</v>
       </c>
       <c r="C130" s="1">
-        <v>2.83</v>
+        <v>9.16</v>
       </c>
       <c r="D130" s="1">
-        <v>5.83</v>
+        <v>34.3431</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>327</v>
+        <v>176</v>
       </c>
     </row>
     <row r="131" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
-        <v>328</v>
+        <v>501</v>
       </c>
       <c r="B131" s="1" t="s">
-        <v>329</v>
+        <v>502</v>
       </c>
       <c r="C131" s="1">
-        <v>2.82</v>
+        <v>1.22</v>
       </c>
       <c r="D131" s="1">
-        <v>6.14</v>
+        <v>17.93</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>330</v>
+        <v>502</v>
       </c>
     </row>
     <row r="132" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
-        <v>331</v>
+        <v>346</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>332</v>
+        <v>347</v>
       </c>
       <c r="C132" s="1">
-        <v>2.75</v>
+        <v>2.63</v>
       </c>
       <c r="D132" s="1">
-        <v>35.85</v>
+        <v>43.673000000000002</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>333</v>
+        <v>347</v>
       </c>
     </row>
     <row r="133" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
-        <v>334</v>
+        <v>441</v>
       </c>
       <c r="B133" s="1" t="s">
-        <v>335</v>
+        <v>442</v>
       </c>
       <c r="C133" s="1">
-        <v>2.74</v>
+        <v>1.54</v>
       </c>
       <c r="D133" s="1">
-        <v>13.744400000000001</v>
+        <v>10.49</v>
       </c>
       <c r="E133" s="1" t="s">
-        <v>335</v>
+        <v>443</v>
       </c>
     </row>
     <row r="134" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
-        <v>336</v>
+        <v>170</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>337</v>
+        <v>171</v>
       </c>
       <c r="C134" s="1">
-        <v>2.73</v>
+        <v>9.6300000000000008</v>
       </c>
       <c r="D134" s="1">
-        <v>37.200000000000003</v>
+        <v>39.988300000000002</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>338</v>
+        <v>171</v>
       </c>
     </row>
     <row r="135" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
-        <v>339</v>
+        <v>197</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>340</v>
+        <v>198</v>
       </c>
       <c r="C135" s="1">
-        <v>2.72</v>
+        <v>7.62</v>
       </c>
       <c r="D135" s="1">
-        <v>17.715299999999999</v>
+        <v>8.9005899999999993</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>340</v>
+        <v>198</v>
       </c>
     </row>
     <row r="136" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
-        <v>341</v>
+        <v>404</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>342</v>
+        <v>405</v>
       </c>
       <c r="C136" s="1">
-        <v>2.71</v>
+        <v>1.87</v>
       </c>
       <c r="D136" s="1">
-        <v>60.637099999999997</v>
+        <v>17.95</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>342</v>
+        <v>406</v>
       </c>
     </row>
     <row r="137" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
-        <v>343</v>
+        <v>381</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>344</v>
+        <v>382</v>
       </c>
       <c r="C137" s="1">
-        <v>2.66</v>
+        <v>2.19</v>
       </c>
       <c r="D137" s="1">
-        <v>8.9</v>
+        <v>17.872699999999998</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>345</v>
+        <v>382</v>
       </c>
     </row>
     <row r="138" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
-        <v>346</v>
+        <v>272</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>347</v>
+        <v>273</v>
       </c>
       <c r="C138" s="1">
-        <v>2.65</v>
+        <v>3.9</v>
       </c>
       <c r="D138" s="1">
-        <v>26.97</v>
+        <v>15.3185</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>348</v>
+        <v>273</v>
       </c>
     </row>
     <row r="139" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
-        <v>349</v>
+        <v>367</v>
       </c>
       <c r="B139" s="1" t="s">
-        <v>350</v>
+        <v>368</v>
       </c>
       <c r="C139" s="1">
-        <v>2.64</v>
+        <v>2.33</v>
       </c>
       <c r="D139" s="1">
-        <v>68.772099999999995</v>
+        <v>34.479999999999997</v>
       </c>
       <c r="E139" s="1" t="s">
-        <v>350</v>
+        <v>369</v>
       </c>
     </row>
     <row r="140" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
-        <v>351</v>
+        <v>493</v>
       </c>
       <c r="B140" s="1" t="s">
-        <v>352</v>
+        <v>494</v>
       </c>
       <c r="C140" s="1">
-        <v>2.63</v>
+        <v>1.29</v>
       </c>
       <c r="D140" s="1">
-        <v>43.673000000000002</v>
+        <v>137.959</v>
       </c>
       <c r="E140" s="1" t="s">
-        <v>352</v>
+        <v>494</v>
       </c>
     </row>
     <row r="141" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
-        <v>353</v>
+        <v>46</v>
       </c>
       <c r="B141" s="1" t="s">
-        <v>354</v>
+        <v>47</v>
       </c>
       <c r="C141" s="1">
-        <v>2.61</v>
+        <v>54.59</v>
       </c>
       <c r="D141" s="1">
-        <v>12.277699999999999</v>
+        <v>31.6</v>
       </c>
       <c r="E141" s="1" t="s">
-        <v>354</v>
+        <v>48</v>
       </c>
     </row>
     <row r="142" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
-        <v>355</v>
+        <v>363</v>
       </c>
       <c r="B142" s="1" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="C142" s="1">
-        <v>2.61</v>
+        <v>2.39</v>
       </c>
       <c r="D142" s="1">
-        <v>6.5752800000000002</v>
+        <v>19.3108</v>
       </c>
       <c r="E142" s="1" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
     </row>
     <row r="143" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
-        <v>357</v>
+        <v>164</v>
       </c>
       <c r="B143" s="1" t="s">
-        <v>358</v>
+        <v>165</v>
       </c>
       <c r="C143" s="1">
-        <v>2.61</v>
+        <v>10.29</v>
       </c>
       <c r="D143" s="1">
-        <v>10.9826</v>
+        <v>36.35</v>
       </c>
       <c r="E143" s="1" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
     </row>
     <row r="144" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
-        <v>359</v>
+        <v>135</v>
       </c>
       <c r="B144" s="1" t="s">
-        <v>360</v>
+        <v>136</v>
       </c>
       <c r="C144" s="1">
-        <v>2.59</v>
+        <v>16.12</v>
       </c>
       <c r="D144" s="1">
-        <v>15.826499999999999</v>
+        <v>73.444199999999995</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>360</v>
+        <v>136</v>
       </c>
     </row>
     <row r="145" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
-        <v>361</v>
+        <v>73</v>
       </c>
       <c r="B145" s="1" t="s">
-        <v>362</v>
+        <v>74</v>
       </c>
       <c r="C145" s="1">
-        <v>2.5499999999999998</v>
+        <v>35.270000000000003</v>
       </c>
       <c r="D145" s="1">
-        <v>47.915799999999997</v>
+        <v>90.165000000000006</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>362</v>
+        <v>74</v>
       </c>
     </row>
     <row r="146" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
-        <v>363</v>
+        <v>505</v>
       </c>
       <c r="B146" s="1" t="s">
-        <v>364</v>
+        <v>506</v>
       </c>
       <c r="C146" s="1">
-        <v>2.52</v>
+        <v>1.21</v>
       </c>
       <c r="D146" s="1">
-        <v>29.256</v>
+        <v>10.167</v>
       </c>
       <c r="E146" s="1" t="s">
-        <v>364</v>
+        <v>506</v>
       </c>
     </row>
     <row r="147" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
-        <v>365</v>
+        <v>516</v>
       </c>
       <c r="B147" s="1" t="s">
-        <v>366</v>
+        <v>517</v>
       </c>
       <c r="C147" s="1">
-        <v>2.4</v>
+        <v>1.1599999999999999</v>
       </c>
       <c r="D147" s="1">
-        <v>8.16</v>
+        <v>3.46</v>
       </c>
       <c r="E147" s="1" t="s">
-        <v>367</v>
+        <v>518</v>
       </c>
     </row>
     <row r="148" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
-        <v>368</v>
+        <v>310</v>
       </c>
       <c r="B148" s="1" t="s">
-        <v>369</v>
+        <v>311</v>
       </c>
       <c r="C148" s="1">
-        <v>2.39</v>
+        <v>3.02</v>
       </c>
       <c r="D148" s="1">
-        <v>19.3108</v>
+        <v>3.81</v>
       </c>
       <c r="E148" s="1" t="s">
-        <v>369</v>
+        <v>312</v>
       </c>
     </row>
     <row r="149" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
-        <v>370</v>
+        <v>279</v>
       </c>
       <c r="B149" s="1" t="s">
-        <v>371</v>
+        <v>280</v>
       </c>
       <c r="C149" s="1">
-        <v>2.34</v>
+        <v>3.69</v>
       </c>
       <c r="D149" s="1">
-        <v>22.730799999999999</v>
+        <v>14.1236</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>371</v>
+        <v>280</v>
       </c>
     </row>
     <row r="150" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
-        <v>372</v>
+        <v>90</v>
       </c>
       <c r="B150" s="1" t="s">
-        <v>373</v>
+        <v>91</v>
       </c>
       <c r="C150" s="1">
-        <v>2.33</v>
+        <v>27.61</v>
       </c>
       <c r="D150" s="1">
-        <v>34.479999999999997</v>
+        <v>56.2</v>
       </c>
       <c r="E150" s="1" t="s">
-        <v>374</v>
+        <v>92</v>
       </c>
     </row>
     <row r="151" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
-        <v>375</v>
+        <v>396</v>
       </c>
       <c r="B151" s="1" t="s">
-        <v>376</v>
+        <v>397</v>
       </c>
       <c r="C151" s="1">
-        <v>2.3199999999999998</v>
+        <v>1.91</v>
       </c>
       <c r="D151" s="1">
-        <v>3.88</v>
+        <v>9.5015999999999998</v>
       </c>
       <c r="E151" s="1" t="s">
-        <v>377</v>
+        <v>397</v>
       </c>
     </row>
     <row r="152" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
-        <v>378</v>
+        <v>407</v>
       </c>
       <c r="B152" s="1" t="s">
-        <v>379</v>
+        <v>408</v>
       </c>
       <c r="C152" s="1">
-        <v>2.27</v>
+        <v>1.87</v>
       </c>
       <c r="D152" s="1">
-        <v>13.522600000000001</v>
+        <v>39.143999999999998</v>
       </c>
       <c r="E152" s="1" t="s">
-        <v>379</v>
+        <v>408</v>
       </c>
     </row>
     <row r="153" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
-        <v>380</v>
+        <v>299</v>
       </c>
       <c r="B153" s="1" t="s">
-        <v>381</v>
+        <v>300</v>
       </c>
       <c r="C153" s="1">
-        <v>2.23</v>
+        <v>3.27</v>
       </c>
       <c r="D153" s="1">
-        <v>9.6590000000000007</v>
+        <v>5.71</v>
       </c>
       <c r="E153" s="1" t="s">
-        <v>381</v>
+        <v>301</v>
       </c>
     </row>
     <row r="154" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
-        <v>382</v>
+        <v>318</v>
       </c>
       <c r="B154" s="1" t="s">
-        <v>383</v>
+        <v>319</v>
       </c>
       <c r="C154" s="1">
-        <v>2.23</v>
+        <v>2.88</v>
       </c>
       <c r="D154" s="1">
-        <v>16.53</v>
+        <v>4.1068600000000002</v>
       </c>
       <c r="E154" s="1" t="s">
-        <v>383</v>
+        <v>319</v>
       </c>
     </row>
     <row r="155" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
-        <v>384</v>
+        <v>230</v>
       </c>
       <c r="B155" s="1" t="s">
-        <v>385</v>
+        <v>231</v>
       </c>
       <c r="C155" s="1">
-        <v>2.2000000000000002</v>
+        <v>5.34</v>
       </c>
       <c r="D155" s="1">
-        <v>7.54833</v>
+        <v>75.740899999999996</v>
       </c>
       <c r="E155" s="1" t="s">
-        <v>385</v>
+        <v>231</v>
       </c>
     </row>
     <row r="156" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
-        <v>386</v>
+        <v>248</v>
       </c>
       <c r="B156" s="1" t="s">
-        <v>387</v>
+        <v>249</v>
       </c>
       <c r="C156" s="1">
-        <v>2.19</v>
+        <v>4.21</v>
       </c>
       <c r="D156" s="1">
-        <v>17.872699999999998</v>
+        <v>22.48</v>
       </c>
       <c r="E156" s="1" t="s">
-        <v>387</v>
+        <v>250</v>
       </c>
     </row>
     <row r="157" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
-        <v>388</v>
+        <v>307</v>
       </c>
       <c r="B157" s="1" t="s">
-        <v>389</v>
+        <v>308</v>
       </c>
       <c r="C157" s="1">
-        <v>2.17</v>
+        <v>3.02</v>
       </c>
       <c r="D157" s="1">
-        <v>9.0508400000000009</v>
+        <v>9.33</v>
       </c>
       <c r="E157" s="1" t="s">
-        <v>389</v>
+        <v>309</v>
       </c>
     </row>
     <row r="158" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
-        <v>390</v>
+        <v>207</v>
       </c>
       <c r="B158" s="1" t="s">
-        <v>391</v>
+        <v>208</v>
       </c>
       <c r="C158" s="1">
-        <v>2.15</v>
+        <v>7.27</v>
       </c>
       <c r="D158" s="1">
-        <v>10.57</v>
+        <v>27.94</v>
       </c>
       <c r="E158" s="1" t="s">
-        <v>392</v>
+        <v>209</v>
       </c>
     </row>
     <row r="159" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
-        <v>393</v>
+        <v>185</v>
       </c>
       <c r="B159" s="1" t="s">
-        <v>394</v>
+        <v>186</v>
       </c>
       <c r="C159" s="1">
-        <v>2.0499999999999998</v>
+        <v>8.3000000000000007</v>
       </c>
       <c r="D159" s="1">
-        <v>39.966799999999999</v>
+        <v>22.82</v>
       </c>
       <c r="E159" s="1" t="s">
-        <v>394</v>
+        <v>187</v>
       </c>
     </row>
     <row r="160" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
-        <v>395</v>
+        <v>114</v>
       </c>
       <c r="B160" s="1" t="s">
-        <v>396</v>
+        <v>115</v>
       </c>
       <c r="C160" s="1">
-        <v>2.04</v>
+        <v>21.6</v>
       </c>
       <c r="D160" s="1">
-        <v>48.445300000000003</v>
+        <v>37.03</v>
       </c>
       <c r="E160" s="1" t="s">
-        <v>396</v>
+        <v>116</v>
       </c>
     </row>
     <row r="161" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
-        <v>397</v>
+        <v>336</v>
       </c>
       <c r="B161" s="1" t="s">
-        <v>398</v>
+        <v>337</v>
       </c>
       <c r="C161" s="1">
-        <v>2</v>
+        <v>2.71</v>
       </c>
       <c r="D161" s="1">
-        <v>7.1333500000000001</v>
+        <v>60.637099999999997</v>
       </c>
       <c r="E161" s="1" t="s">
-        <v>398</v>
+        <v>337</v>
       </c>
     </row>
     <row r="162" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
-        <v>399</v>
+        <v>448</v>
       </c>
       <c r="B162" s="1" t="s">
-        <v>400</v>
+        <v>449</v>
       </c>
       <c r="C162" s="1">
-        <v>1.97</v>
+        <v>1.52</v>
       </c>
       <c r="D162" s="1">
-        <v>9.7591699999999992</v>
+        <v>21.6219</v>
       </c>
       <c r="E162" s="1" t="s">
-        <v>400</v>
+        <v>449</v>
       </c>
     </row>
     <row r="163" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
-        <v>401</v>
+        <v>329</v>
       </c>
       <c r="B163" s="1" t="s">
-        <v>402</v>
+        <v>330</v>
       </c>
       <c r="C163" s="1">
-        <v>1.91</v>
+        <v>2.74</v>
       </c>
       <c r="D163" s="1">
-        <v>9.5015999999999998</v>
+        <v>13.744400000000001</v>
       </c>
       <c r="E163" s="1" t="s">
-        <v>402</v>
+        <v>330</v>
       </c>
     </row>
     <row r="164" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
-        <v>403</v>
+        <v>239</v>
       </c>
       <c r="B164" s="1" t="s">
-        <v>404</v>
+        <v>240</v>
       </c>
       <c r="C164" s="1">
-        <v>1.91</v>
+        <v>4.9000000000000004</v>
       </c>
       <c r="D164" s="1">
-        <v>30.930299999999999</v>
+        <v>28.075500000000002</v>
       </c>
       <c r="E164" s="1" t="s">
-        <v>404</v>
+        <v>240</v>
       </c>
     </row>
     <row r="165" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
-        <v>405</v>
+        <v>489</v>
       </c>
       <c r="B165" s="1" t="s">
-        <v>406</v>
+        <v>490</v>
       </c>
       <c r="C165" s="1">
-        <v>1.9</v>
+        <v>1.29</v>
       </c>
       <c r="D165" s="1">
-        <v>10.3101</v>
+        <v>10.6464</v>
       </c>
       <c r="E165" s="1" t="s">
-        <v>406</v>
+        <v>490</v>
       </c>
     </row>
     <row r="166" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
-        <v>407</v>
+        <v>420</v>
       </c>
       <c r="B166" s="1" t="s">
-        <v>408</v>
+        <v>421</v>
       </c>
       <c r="C166" s="1">
-        <v>1.88</v>
+        <v>1.75</v>
       </c>
       <c r="D166" s="1">
-        <v>18.495200000000001</v>
+        <v>12.241899999999999</v>
       </c>
       <c r="E166" s="1" t="s">
-        <v>408</v>
+        <v>421</v>
       </c>
     </row>
     <row r="167" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
-        <v>409</v>
+        <v>109</v>
       </c>
       <c r="B167" s="1" t="s">
-        <v>410</v>
+        <v>110</v>
       </c>
       <c r="C167" s="1">
-        <v>1.87</v>
+        <v>22.92</v>
       </c>
       <c r="D167" s="1">
-        <v>17.95</v>
+        <v>36.060299999999998</v>
       </c>
       <c r="E167" s="1" t="s">
-        <v>411</v>
+        <v>110</v>
       </c>
     </row>
     <row r="168" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
-        <v>412</v>
+        <v>263</v>
       </c>
       <c r="B168" s="1" t="s">
-        <v>413</v>
+        <v>264</v>
       </c>
       <c r="C168" s="1">
-        <v>1.87</v>
+        <v>3.99</v>
       </c>
       <c r="D168" s="1">
-        <v>39.143999999999998</v>
+        <v>16.9283</v>
       </c>
       <c r="E168" s="1" t="s">
-        <v>413</v>
+        <v>264</v>
       </c>
     </row>
     <row r="169" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
-        <v>414</v>
+        <v>142</v>
       </c>
       <c r="B169" s="1" t="s">
-        <v>415</v>
+        <v>143</v>
       </c>
       <c r="C169" s="1">
-        <v>1.82</v>
+        <v>13.51</v>
       </c>
       <c r="D169" s="1">
-        <v>2.1321400000000001</v>
+        <v>14.703099999999999</v>
       </c>
       <c r="E169" s="1" t="s">
-        <v>415</v>
+        <v>143</v>
       </c>
     </row>
     <row r="170" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
-        <v>416</v>
+        <v>221</v>
       </c>
       <c r="B170" s="1" t="s">
-        <v>417</v>
+        <v>222</v>
       </c>
       <c r="C170" s="1">
-        <v>1.82</v>
+        <v>6.22</v>
       </c>
       <c r="D170" s="1">
-        <v>12.0916</v>
+        <v>26.880600000000001</v>
       </c>
       <c r="E170" s="1" t="s">
-        <v>417</v>
+        <v>222</v>
       </c>
     </row>
     <row r="171" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
-        <v>418</v>
+        <v>304</v>
       </c>
       <c r="B171" s="1" t="s">
-        <v>419</v>
+        <v>305</v>
       </c>
       <c r="C171" s="1">
-        <v>1.81</v>
+        <v>3.12</v>
       </c>
       <c r="D171" s="1">
-        <v>40.188600000000001</v>
+        <v>10.72</v>
       </c>
       <c r="E171" s="1" t="s">
-        <v>419</v>
+        <v>306</v>
       </c>
     </row>
     <row r="172" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
-        <v>420</v>
+        <v>84</v>
       </c>
       <c r="B172" s="1" t="s">
-        <v>421</v>
+        <v>85</v>
       </c>
       <c r="C172" s="1">
-        <v>1.78</v>
+        <v>31.4</v>
       </c>
       <c r="D172" s="1">
-        <v>4.78</v>
+        <v>68.790000000000006</v>
       </c>
       <c r="E172" s="1" t="s">
-        <v>422</v>
+        <v>86</v>
       </c>
     </row>
     <row r="173" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
-        <v>423</v>
+        <v>121</v>
       </c>
       <c r="B173" s="1" t="s">
-        <v>424</v>
+        <v>122</v>
       </c>
       <c r="C173" s="1">
-        <v>1.78</v>
+        <v>19.47</v>
       </c>
       <c r="D173" s="1">
-        <v>3.4772400000000001</v>
+        <v>104.17</v>
       </c>
       <c r="E173" s="1" t="s">
-        <v>424</v>
+        <v>123</v>
       </c>
     </row>
     <row r="174" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
-        <v>425</v>
+        <v>477</v>
       </c>
       <c r="B174" s="1" t="s">
-        <v>426</v>
+        <v>478</v>
       </c>
       <c r="C174" s="1">
-        <v>1.75</v>
+        <v>1.36</v>
       </c>
       <c r="D174" s="1">
-        <v>12.241899999999999</v>
+        <v>24.619700000000002</v>
       </c>
       <c r="E174" s="1" t="s">
-        <v>426</v>
+        <v>478</v>
       </c>
     </row>
     <row r="175" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
-        <v>427</v>
+        <v>137</v>
       </c>
       <c r="B175" s="1" t="s">
-        <v>428</v>
+        <v>138</v>
       </c>
       <c r="C175" s="1">
-        <v>1.72</v>
+        <v>14.3</v>
       </c>
       <c r="D175" s="1">
-        <v>5.55</v>
+        <v>25.77</v>
       </c>
       <c r="E175" s="1" t="s">
-        <v>429</v>
+        <v>139</v>
       </c>
     </row>
     <row r="176" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
-        <v>430</v>
+        <v>274</v>
       </c>
       <c r="B176" s="1" t="s">
-        <v>431</v>
+        <v>275</v>
       </c>
       <c r="C176" s="1">
-        <v>1.69</v>
+        <v>3.72</v>
       </c>
       <c r="D176" s="1">
-        <v>104.11</v>
+        <v>12.506600000000001</v>
       </c>
       <c r="E176" s="1" t="s">
-        <v>431</v>
+        <v>275</v>
       </c>
     </row>
     <row r="177" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
-        <v>432</v>
+        <v>427</v>
       </c>
       <c r="B177" s="1" t="s">
-        <v>433</v>
+        <v>428</v>
       </c>
       <c r="C177" s="1">
         <v>1.68</v>
@@ -5533,891 +5527,874 @@
         <v>29.477799999999998</v>
       </c>
       <c r="E177" s="1" t="s">
-        <v>433</v>
+        <v>428</v>
       </c>
     </row>
     <row r="178" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
-        <v>434</v>
+        <v>5</v>
       </c>
       <c r="B178" s="1" t="s">
-        <v>435</v>
+        <v>6</v>
       </c>
       <c r="C178" s="1">
-        <v>1.64</v>
+        <v>171.63</v>
       </c>
       <c r="D178" s="1">
-        <v>14.366899999999999</v>
+        <v>120.86</v>
       </c>
       <c r="E178" s="1" t="s">
-        <v>435</v>
+        <v>7</v>
       </c>
     </row>
     <row r="179" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
-        <v>436</v>
+        <v>511</v>
       </c>
       <c r="B179" s="1" t="s">
-        <v>437</v>
+        <v>512</v>
       </c>
       <c r="C179" s="1">
-        <v>1.64</v>
+        <v>1.17</v>
       </c>
       <c r="D179" s="1">
-        <v>27.266999999999999</v>
+        <v>11.71</v>
       </c>
       <c r="E179" s="1" t="s">
-        <v>437</v>
+        <v>513</v>
       </c>
     </row>
     <row r="180" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
-        <v>438</v>
+        <v>360</v>
       </c>
       <c r="B180" s="1" t="s">
-        <v>439</v>
+        <v>361</v>
       </c>
       <c r="C180" s="1">
-        <v>1.62</v>
+        <v>2.4</v>
       </c>
       <c r="D180" s="1">
-        <v>15.52</v>
+        <v>8.16</v>
       </c>
       <c r="E180" s="1" t="s">
-        <v>440</v>
+        <v>362</v>
       </c>
     </row>
     <row r="181" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
-        <v>441</v>
+        <v>193</v>
       </c>
       <c r="B181" s="1" t="s">
-        <v>442</v>
+        <v>194</v>
       </c>
       <c r="C181" s="1">
-        <v>1.58</v>
+        <v>7.87</v>
       </c>
       <c r="D181" s="1">
-        <v>12.7141</v>
+        <v>18.623999999999999</v>
       </c>
       <c r="E181" s="1" t="s">
-        <v>442</v>
+        <v>194</v>
       </c>
     </row>
     <row r="182" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
-        <v>443</v>
+        <v>261</v>
       </c>
       <c r="B182" s="1" t="s">
-        <v>444</v>
+        <v>262</v>
       </c>
       <c r="C182" s="1">
-        <v>1.56</v>
+        <v>4</v>
       </c>
       <c r="D182" s="1">
-        <v>45.34</v>
+        <v>18.659800000000001</v>
       </c>
       <c r="E182" s="1" t="s">
-        <v>445</v>
+        <v>262</v>
       </c>
     </row>
     <row r="183" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
-        <v>446</v>
+        <v>375</v>
       </c>
       <c r="B183" s="1" t="s">
-        <v>447</v>
+        <v>376</v>
       </c>
       <c r="C183" s="1">
-        <v>1.54</v>
+        <v>2.23</v>
       </c>
       <c r="D183" s="1">
-        <v>10.49</v>
+        <v>9.6590000000000007</v>
       </c>
       <c r="E183" s="1" t="s">
-        <v>448</v>
+        <v>376</v>
       </c>
     </row>
     <row r="184" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
-        <v>449</v>
+        <v>528</v>
       </c>
       <c r="B184" s="1" t="s">
-        <v>450</v>
+        <v>529</v>
       </c>
       <c r="C184" s="1">
-        <v>1.53</v>
+        <v>1.06</v>
       </c>
       <c r="D184" s="1">
-        <v>2.9620899999999999</v>
+        <v>17.522099999999998</v>
       </c>
       <c r="E184" s="1" t="s">
-        <v>450</v>
+        <v>529</v>
       </c>
     </row>
     <row r="185" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
-        <v>451</v>
+        <v>8</v>
       </c>
       <c r="B185" s="1" t="s">
-        <v>452</v>
+        <v>9</v>
       </c>
       <c r="C185" s="1">
-        <v>1.52</v>
+        <v>136.30000000000001</v>
       </c>
       <c r="D185" s="1">
-        <v>10.875299999999999</v>
+        <v>104.34</v>
       </c>
       <c r="E185" s="1" t="s">
-        <v>452</v>
+        <v>10</v>
       </c>
     </row>
     <row r="186" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
-        <v>453</v>
+        <v>521</v>
       </c>
       <c r="B186" s="1" t="s">
-        <v>454</v>
+        <v>522</v>
       </c>
       <c r="C186" s="1">
-        <v>1.52</v>
+        <v>1.1599999999999999</v>
       </c>
       <c r="D186" s="1">
-        <v>21.6219</v>
+        <v>12.571</v>
       </c>
       <c r="E186" s="1" t="s">
-        <v>454</v>
+        <v>522</v>
       </c>
     </row>
     <row r="187" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
-        <v>455</v>
+        <v>462</v>
       </c>
       <c r="B187" s="1" t="s">
-        <v>456</v>
+        <v>463</v>
       </c>
       <c r="C187" s="1">
-        <v>1.51</v>
+        <v>1.41</v>
       </c>
       <c r="D187" s="1">
-        <v>3.14</v>
+        <v>54.3</v>
       </c>
       <c r="E187" s="1" t="s">
-        <v>457</v>
+        <v>464</v>
       </c>
     </row>
     <row r="188" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
-        <v>458</v>
+        <v>547</v>
       </c>
       <c r="B188" s="1" t="s">
-        <v>459</v>
+        <v>548</v>
       </c>
       <c r="C188" s="1">
-        <v>1.5</v>
+        <v>1.01</v>
       </c>
       <c r="D188" s="1">
-        <v>38.306899999999999</v>
+        <v>14.152200000000001</v>
       </c>
       <c r="E188" s="1" t="s">
-        <v>459</v>
+        <v>548</v>
       </c>
     </row>
     <row r="189" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
-        <v>460</v>
+        <v>316</v>
       </c>
       <c r="B189" s="1" t="s">
-        <v>461</v>
+        <v>317</v>
       </c>
       <c r="C189" s="1">
-        <v>1.42</v>
+        <v>2.98</v>
       </c>
       <c r="D189" s="1">
-        <v>1.7743899999999999</v>
+        <v>53.603900000000003</v>
       </c>
       <c r="E189" s="1" t="s">
-        <v>461</v>
+        <v>317</v>
       </c>
     </row>
     <row r="190" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A190" t="s">
-        <v>462</v>
+        <v>484</v>
       </c>
       <c r="B190" s="1" t="s">
-        <v>463</v>
+        <v>485</v>
       </c>
       <c r="C190" s="1">
-        <v>1.41</v>
+        <v>1.32</v>
       </c>
       <c r="D190" s="1">
-        <v>13.62</v>
+        <v>11.54</v>
       </c>
       <c r="E190" s="1" t="s">
-        <v>464</v>
+        <v>486</v>
       </c>
     </row>
     <row r="191" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
-        <v>465</v>
+        <v>70</v>
       </c>
       <c r="B191" s="1" t="s">
-        <v>466</v>
+        <v>71</v>
       </c>
       <c r="C191" s="1">
-        <v>1.41</v>
+        <v>35.590000000000003</v>
       </c>
       <c r="D191" s="1">
-        <v>8.5857799999999997</v>
+        <v>62.46</v>
       </c>
       <c r="E191" s="1" t="s">
-        <v>466</v>
+        <v>72</v>
       </c>
     </row>
     <row r="192" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A192" t="s">
-        <v>467</v>
+        <v>234</v>
       </c>
       <c r="B192" s="1" t="s">
-        <v>468</v>
+        <v>235</v>
       </c>
       <c r="C192" s="1">
-        <v>1.41</v>
+        <v>5.27</v>
       </c>
       <c r="D192" s="1">
-        <v>54.3</v>
+        <v>25.15</v>
       </c>
       <c r="E192" s="1" t="s">
-        <v>469</v>
+        <v>236</v>
       </c>
     </row>
     <row r="193" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
-        <v>470</v>
+        <v>509</v>
       </c>
       <c r="B193" s="1" t="s">
-        <v>471</v>
+        <v>510</v>
       </c>
       <c r="C193" s="1">
-        <v>1.4</v>
+        <v>1.18</v>
       </c>
       <c r="D193" s="1">
-        <v>1.54</v>
+        <v>5.0727599999999997</v>
       </c>
       <c r="E193" s="1" t="s">
-        <v>472</v>
+        <v>510</v>
       </c>
     </row>
     <row r="194" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
-        <v>473</v>
+        <v>297</v>
       </c>
       <c r="B194" s="1" t="s">
-        <v>474</v>
+        <v>298</v>
       </c>
       <c r="C194" s="1">
-        <v>1.39</v>
+        <v>3.27</v>
       </c>
       <c r="D194" s="1">
-        <v>25.93</v>
+        <v>18.366399999999999</v>
       </c>
       <c r="E194" s="1" t="s">
-        <v>475</v>
+        <v>298</v>
       </c>
     </row>
     <row r="195" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
-        <v>476</v>
+        <v>385</v>
       </c>
       <c r="B195" s="1" t="s">
-        <v>477</v>
+        <v>386</v>
       </c>
       <c r="C195" s="1">
-        <v>1.39</v>
+        <v>2.15</v>
       </c>
       <c r="D195" s="1">
-        <v>4.2571199999999996</v>
+        <v>10.57</v>
       </c>
       <c r="E195" s="1" t="s">
-        <v>478</v>
+        <v>387</v>
       </c>
     </row>
     <row r="196" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
-        <v>479</v>
+        <v>155</v>
       </c>
       <c r="B196" s="1" t="s">
-        <v>480</v>
+        <v>156</v>
       </c>
       <c r="C196" s="1">
-        <v>1.38</v>
+        <v>10.7</v>
       </c>
       <c r="D196" s="1">
-        <v>6.64</v>
+        <v>93.48</v>
       </c>
       <c r="E196" s="1" t="s">
-        <v>481</v>
+        <v>157</v>
       </c>
     </row>
     <row r="197" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
-        <v>482</v>
+        <v>59</v>
       </c>
       <c r="B197" s="1" t="s">
-        <v>483</v>
+        <v>60</v>
       </c>
       <c r="C197" s="1">
-        <v>1.36</v>
+        <v>44.38</v>
       </c>
       <c r="D197" s="1">
-        <v>24.619700000000002</v>
+        <v>35.869999999999997</v>
       </c>
       <c r="E197" s="1" t="s">
-        <v>483</v>
+        <v>61</v>
       </c>
     </row>
     <row r="198" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
-        <v>484</v>
+        <v>543</v>
       </c>
       <c r="B198" s="1" t="s">
-        <v>485</v>
+        <v>544</v>
       </c>
       <c r="C198" s="1">
-        <v>1.36</v>
+        <v>1.02</v>
       </c>
       <c r="D198" s="1">
-        <v>1.75</v>
+        <v>2.7975300000000001</v>
       </c>
       <c r="E198" s="1" t="s">
-        <v>486</v>
+        <v>544</v>
       </c>
     </row>
     <row r="199" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
-        <v>487</v>
+        <v>338</v>
       </c>
       <c r="B199" s="1" t="s">
-        <v>488</v>
+        <v>339</v>
       </c>
       <c r="C199" s="1">
-        <v>1.35</v>
+        <v>2.66</v>
       </c>
       <c r="D199" s="1">
-        <v>3.9136799999999998</v>
+        <v>8.9</v>
       </c>
       <c r="E199" s="1" t="s">
-        <v>488</v>
+        <v>340</v>
       </c>
     </row>
     <row r="200" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
-        <v>489</v>
+        <v>507</v>
       </c>
       <c r="B200" s="1" t="s">
-        <v>490</v>
+        <v>508</v>
       </c>
       <c r="C200" s="1">
-        <v>1.32</v>
+        <v>1.2</v>
       </c>
       <c r="D200" s="1">
-        <v>11.54</v>
+        <v>14.316800000000001</v>
       </c>
       <c r="E200" s="1" t="s">
-        <v>491</v>
+        <v>508</v>
       </c>
     </row>
     <row r="201" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
-        <v>492</v>
+        <v>11</v>
       </c>
       <c r="B201" s="1" t="s">
-        <v>493</v>
+        <v>12</v>
       </c>
       <c r="C201" s="1">
-        <v>1.29</v>
+        <v>111.37</v>
       </c>
       <c r="D201" s="1">
-        <v>20.2195</v>
+        <v>63.28</v>
       </c>
       <c r="E201" s="1" t="s">
-        <v>493</v>
+        <v>13</v>
       </c>
     </row>
     <row r="202" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
-        <v>494</v>
+        <v>124</v>
       </c>
       <c r="B202" s="1" t="s">
-        <v>495</v>
+        <v>125</v>
       </c>
       <c r="C202" s="1">
-        <v>1.29</v>
+        <v>18.850000000000001</v>
       </c>
       <c r="D202" s="1">
-        <v>10.6464</v>
+        <v>37.67</v>
       </c>
       <c r="E202" s="1" t="s">
-        <v>495</v>
+        <v>126</v>
       </c>
     </row>
     <row r="203" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A203" t="s">
-        <v>496</v>
+        <v>199</v>
       </c>
       <c r="B203" s="1" t="s">
-        <v>497</v>
+        <v>200</v>
       </c>
       <c r="C203" s="1">
-        <v>1.29</v>
+        <v>7.56</v>
       </c>
       <c r="D203" s="1">
-        <v>7.7057399999999996</v>
+        <v>89.62</v>
       </c>
       <c r="E203" s="1" t="s">
-        <v>497</v>
+        <v>201</v>
       </c>
     </row>
     <row r="204" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A204" t="s">
-        <v>498</v>
+        <v>256</v>
       </c>
       <c r="B204" s="1" t="s">
-        <v>499</v>
+        <v>257</v>
       </c>
       <c r="C204" s="1">
-        <v>1.29</v>
+        <v>4.05</v>
       </c>
       <c r="D204" s="1">
-        <v>137.959</v>
+        <v>20.09</v>
       </c>
       <c r="E204" s="1" t="s">
-        <v>499</v>
+        <v>258</v>
       </c>
     </row>
     <row r="205" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A205" t="s">
-        <v>500</v>
+        <v>212</v>
       </c>
       <c r="B205" s="1" t="s">
-        <v>501</v>
+        <v>213</v>
       </c>
       <c r="C205" s="1">
-        <v>1.27</v>
+        <v>6.79</v>
       </c>
       <c r="D205" s="1">
-        <v>26.694600000000001</v>
+        <v>83.539599999999993</v>
       </c>
       <c r="E205" s="1" t="s">
-        <v>501</v>
+        <v>213</v>
       </c>
     </row>
     <row r="206" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
-        <v>502</v>
+        <v>450</v>
       </c>
       <c r="B206" s="1" t="s">
-        <v>503</v>
+        <v>451</v>
       </c>
       <c r="C206" s="1">
-        <v>1.26</v>
+        <v>1.51</v>
       </c>
       <c r="D206" s="1">
-        <v>6.3892499999999997</v>
+        <v>3.14</v>
       </c>
       <c r="E206" s="1" t="s">
-        <v>503</v>
+        <v>452</v>
       </c>
     </row>
     <row r="207" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A207" t="s">
-        <v>504</v>
+        <v>438</v>
       </c>
       <c r="B207" s="1" t="s">
-        <v>505</v>
+        <v>439</v>
       </c>
       <c r="C207" s="1">
-        <v>1.25</v>
+        <v>1.56</v>
       </c>
       <c r="D207" s="1">
-        <v>4.5790800000000003</v>
+        <v>45.34</v>
       </c>
       <c r="E207" s="1" t="s">
-        <v>505</v>
+        <v>440</v>
       </c>
     </row>
     <row r="208" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A208" t="s">
-        <v>506</v>
+        <v>158</v>
       </c>
       <c r="B208" s="1" t="s">
-        <v>507</v>
+        <v>159</v>
       </c>
       <c r="C208" s="1">
-        <v>1.22</v>
+        <v>10.58</v>
       </c>
       <c r="D208" s="1">
-        <v>17.93</v>
+        <v>127.413</v>
       </c>
       <c r="E208" s="1" t="s">
-        <v>507</v>
+        <v>160</v>
       </c>
     </row>
     <row r="209" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A209" t="s">
-        <v>508</v>
+        <v>130</v>
       </c>
       <c r="B209" s="1" t="s">
-        <v>509</v>
+        <v>131</v>
       </c>
       <c r="C209" s="1">
-        <v>1.21</v>
+        <v>17.07</v>
       </c>
       <c r="D209" s="1">
-        <v>8.1064100000000003</v>
+        <v>45.569000000000003</v>
       </c>
       <c r="E209" s="1" t="s">
-        <v>509</v>
+        <v>131</v>
       </c>
     </row>
     <row r="210" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A210" t="s">
-        <v>510</v>
+        <v>402</v>
       </c>
       <c r="B210" s="1" t="s">
-        <v>511</v>
+        <v>403</v>
       </c>
       <c r="C210" s="1">
-        <v>1.21</v>
+        <v>1.88</v>
       </c>
       <c r="D210" s="1">
-        <v>10.167</v>
+        <v>18.495200000000001</v>
       </c>
       <c r="E210" s="1" t="s">
-        <v>511</v>
+        <v>403</v>
       </c>
     </row>
     <row r="211" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A211" t="s">
-        <v>512</v>
+        <v>334</v>
       </c>
       <c r="B211" s="1" t="s">
-        <v>513</v>
+        <v>335</v>
       </c>
       <c r="C211" s="1">
-        <v>1.2</v>
+        <v>2.72</v>
       </c>
       <c r="D211" s="1">
-        <v>14.316800000000001</v>
+        <v>17.715299999999999</v>
       </c>
       <c r="E211" s="1" t="s">
-        <v>513</v>
+        <v>335</v>
       </c>
     </row>
     <row r="212" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A212" t="s">
-        <v>514</v>
+        <v>23</v>
       </c>
       <c r="B212" s="1" t="s">
-        <v>515</v>
+        <v>24</v>
       </c>
       <c r="C212" s="1">
-        <v>1.18</v>
+        <v>83.63</v>
       </c>
       <c r="D212" s="1">
-        <v>5.0727599999999997</v>
+        <v>184.75</v>
       </c>
       <c r="E212" s="1" t="s">
-        <v>515</v>
+        <v>25</v>
       </c>
     </row>
     <row r="213" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A213" t="s">
-        <v>516</v>
+        <v>52</v>
       </c>
       <c r="B213" s="1" t="s">
-        <v>517</v>
+        <v>53</v>
       </c>
       <c r="C213" s="1">
-        <v>1.17</v>
+        <v>50.27</v>
       </c>
       <c r="D213" s="1">
-        <v>11.71</v>
+        <v>48.12</v>
       </c>
       <c r="E213" s="1" t="s">
-        <v>518</v>
+        <v>54</v>
       </c>
     </row>
     <row r="214" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A214" t="s">
-        <v>519</v>
+        <v>495</v>
       </c>
       <c r="B214" s="1" t="s">
-        <v>520</v>
+        <v>496</v>
       </c>
       <c r="C214" s="1">
-        <v>1.17</v>
+        <v>1.27</v>
       </c>
       <c r="D214" s="1">
-        <v>53.589599999999997</v>
+        <v>26.694600000000001</v>
       </c>
       <c r="E214" s="1" t="s">
-        <v>520</v>
+        <v>496</v>
       </c>
     </row>
     <row r="215" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A215" t="s">
-        <v>521</v>
+        <v>101</v>
       </c>
       <c r="B215" s="1" t="s">
-        <v>522</v>
+        <v>102</v>
       </c>
       <c r="C215" s="1">
-        <v>1.1599999999999999</v>
+        <v>24.2</v>
       </c>
       <c r="D215" s="1">
-        <v>3.46</v>
+        <v>15.93</v>
       </c>
       <c r="E215" s="1" t="s">
-        <v>523</v>
+        <v>103</v>
       </c>
     </row>
     <row r="216" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A216" t="s">
-        <v>524</v>
+        <v>444</v>
       </c>
       <c r="B216" s="1" t="s">
-        <v>525</v>
+        <v>445</v>
       </c>
       <c r="C216" s="1">
-        <v>1.1599999999999999</v>
+        <v>1.53</v>
       </c>
       <c r="D216" s="1">
-        <v>9.8020999999999994</v>
+        <v>2.9620899999999999</v>
       </c>
       <c r="E216" s="1" t="s">
-        <v>525</v>
+        <v>445</v>
       </c>
     </row>
     <row r="217" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A217" t="s">
-        <v>526</v>
+        <v>358</v>
       </c>
       <c r="B217" s="1" t="s">
-        <v>527</v>
+        <v>359</v>
       </c>
       <c r="C217" s="1">
-        <v>1.1599999999999999</v>
+        <v>2.52</v>
       </c>
       <c r="D217" s="1">
-        <v>12.571</v>
+        <v>29.256</v>
       </c>
       <c r="E217" s="1" t="s">
-        <v>527</v>
+        <v>359</v>
       </c>
     </row>
     <row r="218" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A218" t="s">
-        <v>528</v>
+        <v>538</v>
       </c>
       <c r="B218" s="1" t="s">
-        <v>529</v>
+        <v>539</v>
       </c>
       <c r="C218" s="1">
-        <v>1.1100000000000001</v>
+        <v>1.04</v>
       </c>
       <c r="D218" s="1">
-        <v>8.1199999999999992</v>
+        <v>6.66</v>
       </c>
       <c r="E218" s="1" t="s">
-        <v>530</v>
+        <v>540</v>
       </c>
     </row>
     <row r="219" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A219" t="s">
-        <v>531</v>
+        <v>276</v>
       </c>
       <c r="B219" s="1" t="s">
-        <v>532</v>
+        <v>277</v>
       </c>
       <c r="C219" s="1">
-        <v>1.1000000000000001</v>
+        <v>3.7</v>
       </c>
       <c r="D219" s="1">
-        <v>2.61151</v>
+        <v>6.01</v>
       </c>
       <c r="E219" s="1" t="s">
-        <v>532</v>
+        <v>278</v>
       </c>
     </row>
     <row r="220" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A220" t="s">
-        <v>533</v>
+        <v>288</v>
       </c>
       <c r="B220" s="1" t="s">
-        <v>534</v>
+        <v>289</v>
       </c>
       <c r="C220" s="1">
-        <v>1.06</v>
+        <v>3.55</v>
       </c>
       <c r="D220" s="1">
-        <v>17.522099999999998</v>
+        <v>6.0386600000000001</v>
       </c>
       <c r="E220" s="1" t="s">
-        <v>534</v>
+        <v>289</v>
       </c>
     </row>
     <row r="221" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A221" t="s">
-        <v>535</v>
+        <v>411</v>
       </c>
       <c r="B221" s="1" t="s">
-        <v>536</v>
+        <v>412</v>
       </c>
       <c r="C221" s="1">
-        <v>1.06</v>
+        <v>1.82</v>
       </c>
       <c r="D221" s="1">
-        <v>31.266500000000001</v>
+        <v>12.0916</v>
       </c>
       <c r="E221" s="1" t="s">
-        <v>536</v>
+        <v>412</v>
       </c>
     </row>
     <row r="222" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A222" t="s">
-        <v>537</v>
+        <v>223</v>
       </c>
       <c r="B222" s="1" t="s">
-        <v>538</v>
+        <v>224</v>
       </c>
       <c r="C222" s="1">
-        <v>1.06</v>
+        <v>6.05</v>
       </c>
       <c r="D222" s="1">
-        <v>67.985100000000003</v>
+        <v>75.88</v>
       </c>
       <c r="E222" s="1" t="s">
-        <v>538</v>
+        <v>225</v>
       </c>
     </row>
     <row r="223" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A223" t="s">
-        <v>539</v>
+        <v>104</v>
       </c>
       <c r="B223" s="1" t="s">
-        <v>540</v>
+        <v>105</v>
       </c>
       <c r="C223" s="1">
-        <v>1.05</v>
+        <v>23.86</v>
       </c>
       <c r="D223" s="1">
-        <v>4.4216800000000003</v>
+        <v>184.53700000000001</v>
       </c>
       <c r="E223" s="1" t="s">
-        <v>540</v>
+        <v>105</v>
       </c>
     </row>
     <row r="224" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A224" t="s">
-        <v>541</v>
+        <v>398</v>
       </c>
       <c r="B224" s="1" t="s">
-        <v>542</v>
+        <v>399</v>
       </c>
       <c r="C224" s="1">
-        <v>1.05</v>
+        <v>1.91</v>
       </c>
       <c r="D224" s="1">
-        <v>153.82900000000001</v>
+        <v>30.930299999999999</v>
       </c>
       <c r="E224" s="1" t="s">
-        <v>542</v>
+        <v>399</v>
       </c>
     </row>
     <row r="225" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A225" t="s">
-        <v>543</v>
+        <v>67</v>
       </c>
       <c r="B225" s="1" t="s">
-        <v>544</v>
+        <v>68</v>
       </c>
       <c r="C225" s="1">
-        <v>1.04</v>
+        <v>35.979999999999997</v>
       </c>
       <c r="D225" s="1">
-        <v>6.66</v>
+        <v>78.98</v>
       </c>
       <c r="E225" s="1" t="s">
-        <v>545</v>
+        <v>69</v>
       </c>
     </row>
     <row r="226" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A226" t="s">
-        <v>546</v>
+        <v>99</v>
       </c>
       <c r="B226" s="1" t="s">
-        <v>547</v>
+        <v>100</v>
       </c>
       <c r="C226" s="1">
-        <v>1.02</v>
+        <v>24.29</v>
       </c>
       <c r="D226" s="1">
-        <v>18.566700000000001</v>
+        <v>186.14699999999999</v>
       </c>
       <c r="E226" s="1" t="s">
-        <v>547</v>
+        <v>100</v>
       </c>
     </row>
     <row r="227" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A227" t="s">
-        <v>548</v>
+        <v>153</v>
       </c>
       <c r="B227" s="1" t="s">
-        <v>549</v>
+        <v>154</v>
       </c>
       <c r="C227" s="1">
-        <v>1.02</v>
+        <v>10.93</v>
       </c>
       <c r="D227" s="1">
-        <v>2.7975300000000001</v>
+        <v>39.308599999999998</v>
       </c>
       <c r="E227" s="1" t="s">
-        <v>549</v>
+        <v>154</v>
       </c>
     </row>
     <row r="228" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A228" t="s">
-        <v>550</v>
+        <v>326</v>
       </c>
       <c r="B228" s="1" t="s">
-        <v>551</v>
+        <v>327</v>
       </c>
       <c r="C228" s="1">
-        <v>1.02</v>
+        <v>2.75</v>
       </c>
       <c r="D228" s="1">
-        <v>24.254799999999999</v>
+        <v>35.85</v>
       </c>
       <c r="E228" s="1" t="s">
-        <v>551</v>
-      </c>
-    </row>
-    <row r="229" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A229" t="s">
-        <v>552</v>
-      </c>
-      <c r="B229" s="1" t="s">
-        <v>553</v>
-      </c>
-      <c r="C229" s="1">
-        <v>1.01</v>
-      </c>
-      <c r="D229" s="1">
-        <v>14.152200000000001</v>
-      </c>
-      <c r="E229" s="1" t="s">
-        <v>553</v>
+        <v>328</v>
       </c>
     </row>
   </sheetData>

--- a/Tickers_Info.xlsx
+++ b/Tickers_Info.xlsx
@@ -12,14 +12,15 @@
     <workbookView xWindow="0" yWindow="0" windowWidth="16392" windowHeight="5784"/>
   </bookViews>
   <sheets>
-    <sheet name="TSX" sheetId="1" r:id="rId1"/>
+    <sheet name="TSX" sheetId="2" r:id="rId1"/>
+    <sheet name="TSX_notAccurate" sheetId="1" r:id="rId2"/>
   </sheets>
   <calcPr calcId="152511"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="686" uniqueCount="551">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1756" uniqueCount="1001">
   <si>
     <t>Name</t>
   </si>
@@ -1672,6 +1673,1356 @@
   </si>
   <si>
     <t>DSG.TO</t>
+  </si>
+  <si>
+    <t>Sector</t>
+  </si>
+  <si>
+    <t>Market Value</t>
+  </si>
+  <si>
+    <t>Weight (%)</t>
+  </si>
+  <si>
+    <t>Shares</t>
+  </si>
+  <si>
+    <t>Price</t>
+  </si>
+  <si>
+    <t>Location</t>
+  </si>
+  <si>
+    <t>ROYAL BANK OF CANADA</t>
+  </si>
+  <si>
+    <t>Financials</t>
+  </si>
+  <si>
+    <t>Canada</t>
+  </si>
+  <si>
+    <t>SHOPIFY SUBORDINATE VOTING INC CLA</t>
+  </si>
+  <si>
+    <t>Information Technology</t>
+  </si>
+  <si>
+    <t>TORONTO DOMINION</t>
+  </si>
+  <si>
+    <t>ENBRIDGE INC</t>
+  </si>
+  <si>
+    <t>Energy</t>
+  </si>
+  <si>
+    <t>BROOKFIELD CORP CLASS A</t>
+  </si>
+  <si>
+    <t>BANK OF MONTREAL</t>
+  </si>
+  <si>
+    <t>BANK OF NOVA SCOTIA</t>
+  </si>
+  <si>
+    <t>CANADIAN IMPERIAL BANK OF COMMERCE</t>
+  </si>
+  <si>
+    <t>AGNICO EAGLE MINES LTD</t>
+  </si>
+  <si>
+    <t>Materials</t>
+  </si>
+  <si>
+    <t>ABX</t>
+  </si>
+  <si>
+    <t>ABX.TO</t>
+  </si>
+  <si>
+    <t>BARRICK MINING CORP</t>
+  </si>
+  <si>
+    <t>CANADIAN PACIFIC KANSAS CITY LTD</t>
+  </si>
+  <si>
+    <t>Industrials</t>
+  </si>
+  <si>
+    <t>CANADIAN NATURAL RESOURCES LTD</t>
+  </si>
+  <si>
+    <t>MANULIFE FINANCIAL CORP</t>
+  </si>
+  <si>
+    <t>TC ENERGY CORP</t>
+  </si>
+  <si>
+    <t>CNR</t>
+  </si>
+  <si>
+    <t>CNR.TO</t>
+  </si>
+  <si>
+    <t>CANADIAN NATIONAL RAILWAY</t>
+  </si>
+  <si>
+    <t>WHEATON PRECIOUS METALS CORP</t>
+  </si>
+  <si>
+    <t>SUNCOR ENERGY INC</t>
+  </si>
+  <si>
+    <t>NA</t>
+  </si>
+  <si>
+    <t>NATIONAL BANK OF CANADA</t>
+  </si>
+  <si>
+    <t>CSU</t>
+  </si>
+  <si>
+    <t>CONSTELLATION SOFTWARE INC</t>
+  </si>
+  <si>
+    <t>WCN</t>
+  </si>
+  <si>
+    <t>WCN.TO</t>
+  </si>
+  <si>
+    <t>WASTE CONNECTIONS INC</t>
+  </si>
+  <si>
+    <t>United States</t>
+  </si>
+  <si>
+    <t>ATD</t>
+  </si>
+  <si>
+    <t>ALIMENTATION COUCHE TARD INC</t>
+  </si>
+  <si>
+    <t>Consumer Staples</t>
+  </si>
+  <si>
+    <t>DOL</t>
+  </si>
+  <si>
+    <t>DOLLARAMA INC</t>
+  </si>
+  <si>
+    <t>Consumer Discretionary</t>
+  </si>
+  <si>
+    <t>FRANCO NEVADA CORP</t>
+  </si>
+  <si>
+    <t>CCO</t>
+  </si>
+  <si>
+    <t>CCO.TO</t>
+  </si>
+  <si>
+    <t>CAMECO CORP</t>
+  </si>
+  <si>
+    <t>FFH</t>
+  </si>
+  <si>
+    <t>FAIRFAX FINANCIAL HOLDINGS SUB VOT</t>
+  </si>
+  <si>
+    <t>IFC</t>
+  </si>
+  <si>
+    <t>INTACT FINANCIAL CORP</t>
+  </si>
+  <si>
+    <t>SUN LIFE FINANCIAL INC</t>
+  </si>
+  <si>
+    <t>K</t>
+  </si>
+  <si>
+    <t>K.TO</t>
+  </si>
+  <si>
+    <t>KINROSS GOLD CORP</t>
+  </si>
+  <si>
+    <t>CELESTICA INC</t>
+  </si>
+  <si>
+    <t>NUTRIEN LTD</t>
+  </si>
+  <si>
+    <t>POW</t>
+  </si>
+  <si>
+    <t>POWER CORPORATION OF CANADA</t>
+  </si>
+  <si>
+    <t>FORTIS INC</t>
+  </si>
+  <si>
+    <t>Utilities</t>
+  </si>
+  <si>
+    <t>L</t>
+  </si>
+  <si>
+    <t>LOBLAW COMPANIES LTD</t>
+  </si>
+  <si>
+    <t>WSP</t>
+  </si>
+  <si>
+    <t>WSP GLOBAL INC</t>
+  </si>
+  <si>
+    <t>CENOVUS ENERGY INC</t>
+  </si>
+  <si>
+    <t>RESTAURANTS BRANDS INTERNATIONAL I</t>
+  </si>
+  <si>
+    <t>PPL</t>
+  </si>
+  <si>
+    <t>PPL.TO</t>
+  </si>
+  <si>
+    <t>PEMBINA PIPELINE CORP</t>
+  </si>
+  <si>
+    <t>BCE INC</t>
+  </si>
+  <si>
+    <t>Communication</t>
+  </si>
+  <si>
+    <t>PAN AMERICAN SILVER CORP</t>
+  </si>
+  <si>
+    <t>TECK.B</t>
+  </si>
+  <si>
+    <t>TECK.B.TO</t>
+  </si>
+  <si>
+    <t>TECK RESOURCES SUBORDINATE VOTING</t>
+  </si>
+  <si>
+    <t>BROOKFIELD ASSET MANAGEMENT VOTING</t>
+  </si>
+  <si>
+    <t>T</t>
+  </si>
+  <si>
+    <t>T.TO</t>
+  </si>
+  <si>
+    <t>TELUS CORP</t>
+  </si>
+  <si>
+    <t>RB GLOBAL INC</t>
+  </si>
+  <si>
+    <t>GIB.A</t>
+  </si>
+  <si>
+    <t>GIB.A.TO</t>
+  </si>
+  <si>
+    <t>CGI INC CLASS A</t>
+  </si>
+  <si>
+    <t>THOMSON REUTERS CORP</t>
+  </si>
+  <si>
+    <t>FM</t>
+  </si>
+  <si>
+    <t>FIRST QUANTUM MINERALS LTD</t>
+  </si>
+  <si>
+    <t>BIP.UN</t>
+  </si>
+  <si>
+    <t>BIP.UN.TO</t>
+  </si>
+  <si>
+    <t>BROOKFIELD INFRASTRUCTURE PARTNERS</t>
+  </si>
+  <si>
+    <t>Bermuda</t>
+  </si>
+  <si>
+    <t>TOU</t>
+  </si>
+  <si>
+    <t>TOURMALINE OIL CORP</t>
+  </si>
+  <si>
+    <t>ALAMOS GOLD INC CLASS A</t>
+  </si>
+  <si>
+    <t>EMA</t>
+  </si>
+  <si>
+    <t>EMERA INC</t>
+  </si>
+  <si>
+    <t>MG</t>
+  </si>
+  <si>
+    <t>MG.TO</t>
+  </si>
+  <si>
+    <t>MAGNA INTERNATIONAL INC</t>
+  </si>
+  <si>
+    <t>MRU</t>
+  </si>
+  <si>
+    <t>METRO INC</t>
+  </si>
+  <si>
+    <t>BBD.B</t>
+  </si>
+  <si>
+    <t>BBD.B.TO</t>
+  </si>
+  <si>
+    <t>BOMBARDIER INC CLASS B</t>
+  </si>
+  <si>
+    <t>RCI.B</t>
+  </si>
+  <si>
+    <t>RCI.B.TO</t>
+  </si>
+  <si>
+    <t>ROGERS COMMUNICATIONS NON-VOTING I</t>
+  </si>
+  <si>
+    <t>LUN</t>
+  </si>
+  <si>
+    <t>LUNDIN MINING CORP</t>
+  </si>
+  <si>
+    <t>IMPERIAL OIL LTD</t>
+  </si>
+  <si>
+    <t>GWO</t>
+  </si>
+  <si>
+    <t>GREAT WEST LIFECO INC</t>
+  </si>
+  <si>
+    <t>H</t>
+  </si>
+  <si>
+    <t>HYDRO ONE LTD</t>
+  </si>
+  <si>
+    <t>GILDAN ACTIVEWEAR INC</t>
+  </si>
+  <si>
+    <t>IA FINANCIAL INC</t>
+  </si>
+  <si>
+    <t>GFL ENVIRONMENTAL SUBORDINATE VOTI</t>
+  </si>
+  <si>
+    <t>WN</t>
+  </si>
+  <si>
+    <t>GEORGE WESTON LTD</t>
+  </si>
+  <si>
+    <t>STANTEC INC</t>
+  </si>
+  <si>
+    <t>ARX</t>
+  </si>
+  <si>
+    <t>ARC RESOURCES LTD</t>
+  </si>
+  <si>
+    <t>EQUINOX GOLD CORP</t>
+  </si>
+  <si>
+    <t>EFN</t>
+  </si>
+  <si>
+    <t>ELEMENT FLEET MANAGEMENT CORP</t>
+  </si>
+  <si>
+    <t>X</t>
+  </si>
+  <si>
+    <t>TMX GROUP LTD</t>
+  </si>
+  <si>
+    <t>ATRL</t>
+  </si>
+  <si>
+    <t>ATKINSREALIS GROUP INC</t>
+  </si>
+  <si>
+    <t>WCP</t>
+  </si>
+  <si>
+    <t>WHITECAP RESOURCES INC</t>
+  </si>
+  <si>
+    <t>TIH</t>
+  </si>
+  <si>
+    <t>TOROMONT INDUSTRIES LTD</t>
+  </si>
+  <si>
+    <t>CAE INC</t>
+  </si>
+  <si>
+    <t>IMG</t>
+  </si>
+  <si>
+    <t>IMG.TO</t>
+  </si>
+  <si>
+    <t>IAMGOLD CORP</t>
+  </si>
+  <si>
+    <t>CCL.B</t>
+  </si>
+  <si>
+    <t>CCL.B.TO</t>
+  </si>
+  <si>
+    <t>CCL INDUSTRIES INC CLASS B</t>
+  </si>
+  <si>
+    <t>ALA</t>
+  </si>
+  <si>
+    <t>ALTAGAS LTD</t>
+  </si>
+  <si>
+    <t>OPEN TEXT CORP</t>
+  </si>
+  <si>
+    <t>TFI INTERNATIONAL INC</t>
+  </si>
+  <si>
+    <t>LUG</t>
+  </si>
+  <si>
+    <t>LUNDIN GOLD INC</t>
+  </si>
+  <si>
+    <t>ATZ</t>
+  </si>
+  <si>
+    <t>ARITZIA SUBORDINATE VOTING INC</t>
+  </si>
+  <si>
+    <t>DESCARTES SYSTEMS GROUP INC</t>
+  </si>
+  <si>
+    <t>HUDBAY MINERALS INC</t>
+  </si>
+  <si>
+    <t>SAP</t>
+  </si>
+  <si>
+    <t>SAPUTO INC</t>
+  </si>
+  <si>
+    <t>FIRST MAJESTIC SILVER CORP</t>
+  </si>
+  <si>
+    <t>IVN</t>
+  </si>
+  <si>
+    <t>IVANHOE MINES LTD CLASS A</t>
+  </si>
+  <si>
+    <t>KEY</t>
+  </si>
+  <si>
+    <t>KEYERA CORP</t>
+  </si>
+  <si>
+    <t>ELD</t>
+  </si>
+  <si>
+    <t>ELD.TO</t>
+  </si>
+  <si>
+    <t>ELDORADO GOLD CORP</t>
+  </si>
+  <si>
+    <t>FTT</t>
+  </si>
+  <si>
+    <t>FINNING INTERNATIONAL INC</t>
+  </si>
+  <si>
+    <t>DPM</t>
+  </si>
+  <si>
+    <t>DPM METALS INC</t>
+  </si>
+  <si>
+    <t>CPX</t>
+  </si>
+  <si>
+    <t>CAPITAL POWER CORP</t>
+  </si>
+  <si>
+    <t>OR ROYALTIES INC</t>
+  </si>
+  <si>
+    <t>NEW GOLD INC</t>
+  </si>
+  <si>
+    <t>FIRSTSERVICE SUBORDINATE VOTING CO</t>
+  </si>
+  <si>
+    <t>Real Estate</t>
+  </si>
+  <si>
+    <t>COLLIERS INTERNATIONAL GROUP SUBOR</t>
+  </si>
+  <si>
+    <t>OGC</t>
+  </si>
+  <si>
+    <t>OCEANAGOLD CORPORATION CORP</t>
+  </si>
+  <si>
+    <t>CTC.A</t>
+  </si>
+  <si>
+    <t>CTC.A.TO</t>
+  </si>
+  <si>
+    <t>CANADIAN TIRE LTD CLASS A</t>
+  </si>
+  <si>
+    <t>BEP.UN</t>
+  </si>
+  <si>
+    <t>BEP.UN.TO</t>
+  </si>
+  <si>
+    <t>BROOKFIELD RENEWABLE PARTNERS NON</t>
+  </si>
+  <si>
+    <t>BTO</t>
+  </si>
+  <si>
+    <t>BTO.TO</t>
+  </si>
+  <si>
+    <t>B2GOLD CORP</t>
+  </si>
+  <si>
+    <t>CS</t>
+  </si>
+  <si>
+    <t>CAPSTONE COPPER CORP</t>
+  </si>
+  <si>
+    <t>SOUTH BOW CORP</t>
+  </si>
+  <si>
+    <t>QBR.B</t>
+  </si>
+  <si>
+    <t>QBR.B.TO</t>
+  </si>
+  <si>
+    <t>QUEBECOR INC CLASS B</t>
+  </si>
+  <si>
+    <t>NEXGEN ENERGY LTD</t>
+  </si>
+  <si>
+    <t>DFY</t>
+  </si>
+  <si>
+    <t>DEFINITY FINANCIAL CORP</t>
+  </si>
+  <si>
+    <t>ONEX</t>
+  </si>
+  <si>
+    <t>ONEX CORP</t>
+  </si>
+  <si>
+    <t>GMIN</t>
+  </si>
+  <si>
+    <t>GMIN.TO</t>
+  </si>
+  <si>
+    <t>G MINING VENTURES CORP</t>
+  </si>
+  <si>
+    <t>EMP.A</t>
+  </si>
+  <si>
+    <t>EMP.A.TO</t>
+  </si>
+  <si>
+    <t>EMPIRE LTD CLASS A</t>
+  </si>
+  <si>
+    <t>PSK</t>
+  </si>
+  <si>
+    <t>PRAIRIESKY ROYALTY LTD</t>
+  </si>
+  <si>
+    <t>SSR MINING INC</t>
+  </si>
+  <si>
+    <t>TXG</t>
+  </si>
+  <si>
+    <t>TOREX GOLD RESOURCES INC</t>
+  </si>
+  <si>
+    <t>ALGONQUIN POWER UTILITIES CORP</t>
+  </si>
+  <si>
+    <t>BYD</t>
+  </si>
+  <si>
+    <t>BOYD GROUP SERVICES INC</t>
+  </si>
+  <si>
+    <t>CSH.UN</t>
+  </si>
+  <si>
+    <t>CSH.UN.TO</t>
+  </si>
+  <si>
+    <t>CHARTWELL RETIREMENT RESIDENCES RE</t>
+  </si>
+  <si>
+    <t>Health Care</t>
+  </si>
+  <si>
+    <t>CAR.UN</t>
+  </si>
+  <si>
+    <t>CAR.UN.TO</t>
+  </si>
+  <si>
+    <t>CANADIAN APARTMENT PROPERTIES REAL</t>
+  </si>
+  <si>
+    <t>AC</t>
+  </si>
+  <si>
+    <t>AIR CANADA VOTING AND VARIABLE VOT</t>
+  </si>
+  <si>
+    <t>KNT</t>
+  </si>
+  <si>
+    <t>K92 MINING INC</t>
+  </si>
+  <si>
+    <t>REI.UN</t>
+  </si>
+  <si>
+    <t>REI.UN.TO</t>
+  </si>
+  <si>
+    <t>RIOCAN REAL ESTATE INVESTMENT TRUS</t>
+  </si>
+  <si>
+    <t>CU</t>
+  </si>
+  <si>
+    <t>CANADIAN UTILITIES LTD CLASS A</t>
+  </si>
+  <si>
+    <t>DSV</t>
+  </si>
+  <si>
+    <t>DISCOVERY SILVER CORP</t>
+  </si>
+  <si>
+    <t>KXS</t>
+  </si>
+  <si>
+    <t>KINAXIS INC</t>
+  </si>
+  <si>
+    <t>IGM</t>
+  </si>
+  <si>
+    <t>IGM FINANCIAL INC</t>
+  </si>
+  <si>
+    <t>GRT.UN</t>
+  </si>
+  <si>
+    <t>GRT.UN.TO</t>
+  </si>
+  <si>
+    <t>GRANITE REAL ESTATE INVESTMENT STA</t>
+  </si>
+  <si>
+    <t>OLA</t>
+  </si>
+  <si>
+    <t>OLA.TO</t>
+  </si>
+  <si>
+    <t>ORLA MINING LTD</t>
+  </si>
+  <si>
+    <t>WEST FRASER TIMBER LTD</t>
+  </si>
+  <si>
+    <t>SJ</t>
+  </si>
+  <si>
+    <t>STELLA JONES INC</t>
+  </si>
+  <si>
+    <t>TA</t>
+  </si>
+  <si>
+    <t>TA.TO</t>
+  </si>
+  <si>
+    <t>TRANSALTA CORP</t>
+  </si>
+  <si>
+    <t>NPI</t>
+  </si>
+  <si>
+    <t>NORTHLAND POWER INC</t>
+  </si>
+  <si>
+    <t>EFR</t>
+  </si>
+  <si>
+    <t>EFR.TO</t>
+  </si>
+  <si>
+    <t>ENERGY FUELS INC</t>
+  </si>
+  <si>
+    <t>ARIS</t>
+  </si>
+  <si>
+    <t>ARIS.TO</t>
+  </si>
+  <si>
+    <t>ARIS MINING CORP</t>
+  </si>
+  <si>
+    <t>PEY</t>
+  </si>
+  <si>
+    <t>PEYTO EXPLORATION &amp; DEVELOPMENT CO</t>
+  </si>
+  <si>
+    <t>PBH</t>
+  </si>
+  <si>
+    <t>PREMIUM BRANDS HOLDINGS CORP</t>
+  </si>
+  <si>
+    <t>GEI</t>
+  </si>
+  <si>
+    <t>GIBSON ENERGY INC</t>
+  </si>
+  <si>
+    <t>FVI</t>
+  </si>
+  <si>
+    <t>FVI.TO</t>
+  </si>
+  <si>
+    <t>FORTUNA MINING CORP</t>
+  </si>
+  <si>
+    <t>FCR.UN</t>
+  </si>
+  <si>
+    <t>FCR.UN.TO</t>
+  </si>
+  <si>
+    <t>FIRST CAPITAL REALTY REAL ESTATE I</t>
+  </si>
+  <si>
+    <t>EIF</t>
+  </si>
+  <si>
+    <t>EXCHANGE INCOME CORP</t>
+  </si>
+  <si>
+    <t>CHP.UN</t>
+  </si>
+  <si>
+    <t>CHP.UN.TO</t>
+  </si>
+  <si>
+    <t>CHOICE PROPERTIES REAL ESTATE INVE</t>
+  </si>
+  <si>
+    <t>ACO.X</t>
+  </si>
+  <si>
+    <t>ACO.X.TO</t>
+  </si>
+  <si>
+    <t>ATCO LTD CLASS I</t>
+  </si>
+  <si>
+    <t>CG</t>
+  </si>
+  <si>
+    <t>CG.TO</t>
+  </si>
+  <si>
+    <t>CENTERRA GOLD INC</t>
+  </si>
+  <si>
+    <t>NOVAGOLD RESOURCES INC</t>
+  </si>
+  <si>
+    <t>TVE</t>
+  </si>
+  <si>
+    <t>TAMARACK VALLEY ENERGY LTD</t>
+  </si>
+  <si>
+    <t>EDR</t>
+  </si>
+  <si>
+    <t>EDR.TO</t>
+  </si>
+  <si>
+    <t>ENDEAVOUR SILVER CORP</t>
+  </si>
+  <si>
+    <t>SKEENA RESOURCES LTD</t>
+  </si>
+  <si>
+    <t>ERO COPPER CORP</t>
+  </si>
+  <si>
+    <t>DIR.UN</t>
+  </si>
+  <si>
+    <t>DIR.UN.TO</t>
+  </si>
+  <si>
+    <t>DREAM INDUSTRIAL REAL ESTATE INVES</t>
+  </si>
+  <si>
+    <t>MX</t>
+  </si>
+  <si>
+    <t>MX.TO</t>
+  </si>
+  <si>
+    <t>METHANEX CORP</t>
+  </si>
+  <si>
+    <t>WDO</t>
+  </si>
+  <si>
+    <t>WESDOME GOLD MINES LTD</t>
+  </si>
+  <si>
+    <t>DOO</t>
+  </si>
+  <si>
+    <t>DOO.TO</t>
+  </si>
+  <si>
+    <t>BRP SUBORDINATE VOTING INC</t>
+  </si>
+  <si>
+    <t>ATH</t>
+  </si>
+  <si>
+    <t>ATHABASCA OIL CORP</t>
+  </si>
+  <si>
+    <t>NGEX</t>
+  </si>
+  <si>
+    <t>NGEX.TO</t>
+  </si>
+  <si>
+    <t>NGEX MINERALS LTD</t>
+  </si>
+  <si>
+    <t>SRU.UN</t>
+  </si>
+  <si>
+    <t>SRU.UN.TO</t>
+  </si>
+  <si>
+    <t>SMARTCENTRES RL ESTATE INVESTMENT</t>
+  </si>
+  <si>
+    <t>LNR</t>
+  </si>
+  <si>
+    <t>LINAMAR CORP</t>
+  </si>
+  <si>
+    <t>BLACKBERRY LTD</t>
+  </si>
+  <si>
+    <t>SEA</t>
+  </si>
+  <si>
+    <t>SEA.TO</t>
+  </si>
+  <si>
+    <t>SEABRIDGE GOLD INC</t>
+  </si>
+  <si>
+    <t>TRIPLE FLAG PRECIOUS METALS CORP</t>
+  </si>
+  <si>
+    <t>SES</t>
+  </si>
+  <si>
+    <t>SECURE WASTE INFRASTRUCTURE CORP</t>
+  </si>
+  <si>
+    <t>ATS CORP</t>
+  </si>
+  <si>
+    <t>TPZ</t>
+  </si>
+  <si>
+    <t>TOPAZ ENERGY CORP</t>
+  </si>
+  <si>
+    <t>MDA</t>
+  </si>
+  <si>
+    <t>MDA SPACE LTD</t>
+  </si>
+  <si>
+    <t>DML</t>
+  </si>
+  <si>
+    <t>DML.TO</t>
+  </si>
+  <si>
+    <t>DENISON MINES CORP</t>
+  </si>
+  <si>
+    <t>NVA</t>
+  </si>
+  <si>
+    <t>NUVISTA ENERGY LTD</t>
+  </si>
+  <si>
+    <t>BAYTEX ENERGY CORP</t>
+  </si>
+  <si>
+    <t>SPROTT INC</t>
+  </si>
+  <si>
+    <t>EQB</t>
+  </si>
+  <si>
+    <t>EQB INC</t>
+  </si>
+  <si>
+    <t>PPTA</t>
+  </si>
+  <si>
+    <t>PPTA.TO</t>
+  </si>
+  <si>
+    <t>PERPETUA RESOURCES CORP</t>
+  </si>
+  <si>
+    <t>HR.UN</t>
+  </si>
+  <si>
+    <t>HR.UN.TO</t>
+  </si>
+  <si>
+    <t>HANDR REAL ESTATE INVESTMENT TRUST</t>
+  </si>
+  <si>
+    <t>CEU</t>
+  </si>
+  <si>
+    <t>CEU.TO</t>
+  </si>
+  <si>
+    <t>CES ENERGY SOLUTIONS CORP</t>
+  </si>
+  <si>
+    <t>BEI.UN</t>
+  </si>
+  <si>
+    <t>BEI.UN.TO</t>
+  </si>
+  <si>
+    <t>BOARDWALK REAL ESTATE INVESTMENT T</t>
+  </si>
+  <si>
+    <t>AYA</t>
+  </si>
+  <si>
+    <t>AYA.TO</t>
+  </si>
+  <si>
+    <t>AYA GOLD &amp; SILVER INC</t>
+  </si>
+  <si>
+    <t>EFX</t>
+  </si>
+  <si>
+    <t>EFX.TO</t>
+  </si>
+  <si>
+    <t>ENERFLEX LTD</t>
+  </si>
+  <si>
+    <t>BDGI</t>
+  </si>
+  <si>
+    <t>BADGER INFRASTRUCTURE SOLUTIONS LT</t>
+  </si>
+  <si>
+    <t>RUS</t>
+  </si>
+  <si>
+    <t>RUSSEL METALS INC</t>
+  </si>
+  <si>
+    <t>BAUSCH HEALTH COMPANIES INC</t>
+  </si>
+  <si>
+    <t>TVK</t>
+  </si>
+  <si>
+    <t>TVK.TO</t>
+  </si>
+  <si>
+    <t>TERRAVEST INDUSTRIES INC</t>
+  </si>
+  <si>
+    <t>NWC</t>
+  </si>
+  <si>
+    <t>NORTH WEST COMPANY INC</t>
+  </si>
+  <si>
+    <t>AIF</t>
+  </si>
+  <si>
+    <t>ALTUS GROUP LTD</t>
+  </si>
+  <si>
+    <t>BLX</t>
+  </si>
+  <si>
+    <t>BORALEX INC CLASS A</t>
+  </si>
+  <si>
+    <t>CURA</t>
+  </si>
+  <si>
+    <t>CURA.TO</t>
+  </si>
+  <si>
+    <t>CURALEAF HLDGS SUBORDINATE VOTING</t>
+  </si>
+  <si>
+    <t>TSU</t>
+  </si>
+  <si>
+    <t>TRISURA GROUP LTD</t>
+  </si>
+  <si>
+    <t>BBU.UN</t>
+  </si>
+  <si>
+    <t>BBU.UN.TO</t>
+  </si>
+  <si>
+    <t>BROOKFIELD BUSINESS PARTNERS UNITS</t>
+  </si>
+  <si>
+    <t>RCH</t>
+  </si>
+  <si>
+    <t>RICHELIEU HARDWARE LTD</t>
+  </si>
+  <si>
+    <t>LIGHTSPEED COMMERCE INC</t>
+  </si>
+  <si>
+    <t>FRU</t>
+  </si>
+  <si>
+    <t>FREEHOLD ROYALTIES LTD</t>
+  </si>
+  <si>
+    <t>KMP.UN</t>
+  </si>
+  <si>
+    <t>KMP.UN.TO</t>
+  </si>
+  <si>
+    <t>KILLAM APARTMENT REIT UNITS CLASS</t>
+  </si>
+  <si>
+    <t>HWX</t>
+  </si>
+  <si>
+    <t>HEADWATER EXPLORATION INC</t>
+  </si>
+  <si>
+    <t>CCA</t>
+  </si>
+  <si>
+    <t>COGECO COMMUNICATIONS SUBORDINATE</t>
+  </si>
+  <si>
+    <t>BIR</t>
+  </si>
+  <si>
+    <t>BIRCHCLIFF ENERGY LTD</t>
+  </si>
+  <si>
+    <t>LIF</t>
+  </si>
+  <si>
+    <t>LABRADOR IRON ORE ROYALTY CORP</t>
+  </si>
+  <si>
+    <t>SIA</t>
+  </si>
+  <si>
+    <t>SIENNA SENIOR LIVING INC</t>
+  </si>
+  <si>
+    <t>ARE</t>
+  </si>
+  <si>
+    <t>ARE.TO</t>
+  </si>
+  <si>
+    <t>AECON GROUP INC</t>
+  </si>
+  <si>
+    <t>PET</t>
+  </si>
+  <si>
+    <t>PET VALU HOLDINGS LTD</t>
+  </si>
+  <si>
+    <t>AAV</t>
+  </si>
+  <si>
+    <t>ADVANTAGE ENERGY LTD</t>
+  </si>
+  <si>
+    <t>MFI</t>
+  </si>
+  <si>
+    <t>MAPLE LEAF FOODS INC</t>
+  </si>
+  <si>
+    <t>IIP.UN</t>
+  </si>
+  <si>
+    <t>IIP.UN.TO</t>
+  </si>
+  <si>
+    <t>INTERRENT REAL ESTATE INVESTMENT T</t>
+  </si>
+  <si>
+    <t>LB</t>
+  </si>
+  <si>
+    <t>LB.TO</t>
+  </si>
+  <si>
+    <t>LAURENTIAN BANK OF CANADA</t>
+  </si>
+  <si>
+    <t>POU</t>
+  </si>
+  <si>
+    <t>PARAMOUNT RESOURCE LTD CLASS A</t>
+  </si>
+  <si>
+    <t>VERMILION ENERGY INC</t>
+  </si>
+  <si>
+    <t>CRR.UN</t>
+  </si>
+  <si>
+    <t>CRR.UN.TO</t>
+  </si>
+  <si>
+    <t>CROMBIE REAL ESTATE INVESTMENT TRU</t>
+  </si>
+  <si>
+    <t>PXT</t>
+  </si>
+  <si>
+    <t>PXT.TO</t>
+  </si>
+  <si>
+    <t>PAREX RESOURCES INC</t>
+  </si>
+  <si>
+    <t>TCL.A</t>
+  </si>
+  <si>
+    <t>TCL.A.TO</t>
+  </si>
+  <si>
+    <t>TRANSCONTINENTAL SUB VOTING INC CL</t>
+  </si>
+  <si>
+    <t>PMZ.UN</t>
+  </si>
+  <si>
+    <t>PMZ.UN.TO</t>
+  </si>
+  <si>
+    <t>PRIMARIS REAL ESTATE INVESTMENT UN</t>
+  </si>
+  <si>
+    <t>AP.UN</t>
+  </si>
+  <si>
+    <t>AP.UN.TO</t>
+  </si>
+  <si>
+    <t>ALLIED PROPERTIES REAL ESTATE INVT</t>
+  </si>
+  <si>
+    <t>SPB</t>
+  </si>
+  <si>
+    <t>SUPERIOR PLUS CORP</t>
+  </si>
+  <si>
+    <t>BDT</t>
+  </si>
+  <si>
+    <t>BDT.TO</t>
+  </si>
+  <si>
+    <t>BIRD CONSTRUCTION INC</t>
+  </si>
+  <si>
+    <t>GSY</t>
+  </si>
+  <si>
+    <t>GOEASY LTD</t>
+  </si>
+  <si>
+    <t>IPCO</t>
+  </si>
+  <si>
+    <t>INTERNATIONAL PETROLEUM CORP</t>
+  </si>
+  <si>
+    <t>NFI</t>
+  </si>
+  <si>
+    <t>NFI GROUP INC</t>
+  </si>
+  <si>
+    <t>JWEL</t>
+  </si>
+  <si>
+    <t>JAMIESON WELLNESS INC</t>
+  </si>
+  <si>
+    <t>MTL</t>
+  </si>
+  <si>
+    <t>MTL.TO</t>
+  </si>
+  <si>
+    <t>MULLEN GROUP LTD</t>
+  </si>
+  <si>
+    <t>CRT.UN</t>
+  </si>
+  <si>
+    <t>CRT.UN.TO</t>
+  </si>
+  <si>
+    <t>CT REIT UNITS TRUST</t>
+  </si>
+  <si>
+    <t>WPK</t>
+  </si>
+  <si>
+    <t>WINPAK LTD</t>
+  </si>
+  <si>
+    <t>CJT</t>
+  </si>
+  <si>
+    <t>CARGOJET INC</t>
+  </si>
+  <si>
+    <t>KEL</t>
+  </si>
+  <si>
+    <t>KEL.TO</t>
+  </si>
+  <si>
+    <t>KELT EXPLORATION LTD</t>
+  </si>
+  <si>
+    <t>NWH.UN</t>
+  </si>
+  <si>
+    <t>NWH.UN.TO</t>
+  </si>
+  <si>
+    <t>NORTHWEST HEALTHCARE PROPERTIES RE</t>
+  </si>
+  <si>
+    <t>CPKR</t>
+  </si>
+  <si>
+    <t>CPKR.TO</t>
+  </si>
+  <si>
+    <t>CANADA PACKERS INC</t>
+  </si>
+  <si>
+    <t>LUNR ROYALTIES</t>
   </si>
 </sst>
 </file>
@@ -2155,11 +3506,12 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="17" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -2511,6 +3863,6836 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:J213"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="5" max="5" width="15" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.44140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" t="s">
+        <v>551</v>
+      </c>
+      <c r="E1" t="s">
+        <v>552</v>
+      </c>
+      <c r="F1" t="s">
+        <v>553</v>
+      </c>
+      <c r="G1" t="s">
+        <v>554</v>
+      </c>
+      <c r="H1" t="s">
+        <v>555</v>
+      </c>
+      <c r="I1" t="s">
+        <v>556</v>
+      </c>
+      <c r="J1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" t="s">
+        <v>557</v>
+      </c>
+      <c r="D2" t="s">
+        <v>558</v>
+      </c>
+      <c r="E2" s="2">
+        <v>1538808025.04</v>
+      </c>
+      <c r="F2">
+        <v>7.18</v>
+      </c>
+      <c r="G2" s="2">
+        <v>6680014</v>
+      </c>
+      <c r="H2">
+        <v>230.36</v>
+      </c>
+      <c r="I2" t="s">
+        <v>559</v>
+      </c>
+      <c r="J2">
+        <v>153.88</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" t="s">
+        <v>560</v>
+      </c>
+      <c r="D3" t="s">
+        <v>561</v>
+      </c>
+      <c r="E3" s="2">
+        <v>1333294704.5</v>
+      </c>
+      <c r="F3">
+        <v>6.22</v>
+      </c>
+      <c r="G3" s="2">
+        <v>5799455</v>
+      </c>
+      <c r="H3">
+        <v>229.9</v>
+      </c>
+      <c r="I3" t="s">
+        <v>559</v>
+      </c>
+      <c r="J3">
+        <v>133.33000000000001</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4" t="s">
+        <v>562</v>
+      </c>
+      <c r="D4" t="s">
+        <v>558</v>
+      </c>
+      <c r="E4" s="2">
+        <v>1039062750.99</v>
+      </c>
+      <c r="F4">
+        <v>4.8499999999999996</v>
+      </c>
+      <c r="G4" s="2">
+        <v>8150151</v>
+      </c>
+      <c r="H4">
+        <v>127.49</v>
+      </c>
+      <c r="I4" t="s">
+        <v>559</v>
+      </c>
+      <c r="J4">
+        <v>103.91</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" t="s">
+        <v>563</v>
+      </c>
+      <c r="D5" t="s">
+        <v>564</v>
+      </c>
+      <c r="E5" s="2">
+        <v>667580298.61000001</v>
+      </c>
+      <c r="F5">
+        <v>3.11</v>
+      </c>
+      <c r="G5" s="2">
+        <v>10361327</v>
+      </c>
+      <c r="H5">
+        <v>64.430000000000007</v>
+      </c>
+      <c r="I5" t="s">
+        <v>559</v>
+      </c>
+      <c r="J5">
+        <v>66.760000000000005</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>21</v>
+      </c>
+      <c r="B6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6" t="s">
+        <v>565</v>
+      </c>
+      <c r="D6" t="s">
+        <v>558</v>
+      </c>
+      <c r="E6" s="2">
+        <v>632702397.55999994</v>
+      </c>
+      <c r="F6">
+        <v>2.95</v>
+      </c>
+      <c r="G6" s="2">
+        <v>10251173</v>
+      </c>
+      <c r="H6">
+        <v>61.72</v>
+      </c>
+      <c r="I6" t="s">
+        <v>559</v>
+      </c>
+      <c r="J6">
+        <v>63.27</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>29</v>
+      </c>
+      <c r="B7" t="s">
+        <v>30</v>
+      </c>
+      <c r="C7" t="s">
+        <v>566</v>
+      </c>
+      <c r="D7" t="s">
+        <v>558</v>
+      </c>
+      <c r="E7" s="2">
+        <v>604815079.75999999</v>
+      </c>
+      <c r="F7">
+        <v>2.82</v>
+      </c>
+      <c r="G7" s="2">
+        <v>3403957</v>
+      </c>
+      <c r="H7">
+        <v>177.68</v>
+      </c>
+      <c r="I7" t="s">
+        <v>559</v>
+      </c>
+      <c r="J7">
+        <v>60.48</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>41</v>
+      </c>
+      <c r="B8" t="s">
+        <v>42</v>
+      </c>
+      <c r="C8" t="s">
+        <v>567</v>
+      </c>
+      <c r="D8" t="s">
+        <v>558</v>
+      </c>
+      <c r="E8" s="2">
+        <v>586494022.03999996</v>
+      </c>
+      <c r="F8">
+        <v>2.73</v>
+      </c>
+      <c r="G8" s="2">
+        <v>5903906</v>
+      </c>
+      <c r="H8">
+        <v>99.34</v>
+      </c>
+      <c r="I8" t="s">
+        <v>559</v>
+      </c>
+      <c r="J8">
+        <v>58.65</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>44</v>
+      </c>
+      <c r="B9" t="s">
+        <v>45</v>
+      </c>
+      <c r="C9" t="s">
+        <v>568</v>
+      </c>
+      <c r="D9" t="s">
+        <v>558</v>
+      </c>
+      <c r="E9" s="2">
+        <v>562113536.26999998</v>
+      </c>
+      <c r="F9">
+        <v>2.62</v>
+      </c>
+      <c r="G9" s="2">
+        <v>4416701</v>
+      </c>
+      <c r="H9">
+        <v>127.27</v>
+      </c>
+      <c r="I9" t="s">
+        <v>559</v>
+      </c>
+      <c r="J9">
+        <v>56.21</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>50</v>
+      </c>
+      <c r="B10" t="s">
+        <v>51</v>
+      </c>
+      <c r="C10" t="s">
+        <v>569</v>
+      </c>
+      <c r="D10" t="s">
+        <v>570</v>
+      </c>
+      <c r="E10" s="2">
+        <v>555479754.87</v>
+      </c>
+      <c r="F10">
+        <v>2.59</v>
+      </c>
+      <c r="G10" s="2">
+        <v>2389263</v>
+      </c>
+      <c r="H10">
+        <v>232.49</v>
+      </c>
+      <c r="I10" t="s">
+        <v>559</v>
+      </c>
+      <c r="J10">
+        <v>55.55</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>571</v>
+      </c>
+      <c r="B11" t="s">
+        <v>572</v>
+      </c>
+      <c r="C11" t="s">
+        <v>573</v>
+      </c>
+      <c r="D11" t="s">
+        <v>570</v>
+      </c>
+      <c r="E11" s="2">
+        <v>490524072.95999998</v>
+      </c>
+      <c r="F11">
+        <v>2.29</v>
+      </c>
+      <c r="G11" s="2">
+        <v>8106496</v>
+      </c>
+      <c r="H11">
+        <v>60.51</v>
+      </c>
+      <c r="I11" t="s">
+        <v>559</v>
+      </c>
+      <c r="J11">
+        <v>49.05</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>32</v>
+      </c>
+      <c r="B12" t="s">
+        <v>33</v>
+      </c>
+      <c r="C12" t="s">
+        <v>574</v>
+      </c>
+      <c r="D12" t="s">
+        <v>575</v>
+      </c>
+      <c r="E12" s="2">
+        <v>444293963.68000001</v>
+      </c>
+      <c r="F12">
+        <v>2.0699999999999998</v>
+      </c>
+      <c r="G12" s="2">
+        <v>4341352</v>
+      </c>
+      <c r="H12">
+        <v>102.34</v>
+      </c>
+      <c r="I12" t="s">
+        <v>559</v>
+      </c>
+      <c r="J12">
+        <v>44.43</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>35</v>
+      </c>
+      <c r="B13" t="s">
+        <v>36</v>
+      </c>
+      <c r="C13" t="s">
+        <v>576</v>
+      </c>
+      <c r="D13" t="s">
+        <v>564</v>
+      </c>
+      <c r="E13" s="2">
+        <v>430929984.75</v>
+      </c>
+      <c r="F13">
+        <v>2.0099999999999998</v>
+      </c>
+      <c r="G13" s="2">
+        <v>9926975</v>
+      </c>
+      <c r="H13">
+        <v>43.41</v>
+      </c>
+      <c r="I13" t="s">
+        <v>559</v>
+      </c>
+      <c r="J13">
+        <v>43.09</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>47</v>
+      </c>
+      <c r="B14" t="s">
+        <v>48</v>
+      </c>
+      <c r="C14" t="s">
+        <v>577</v>
+      </c>
+      <c r="D14" t="s">
+        <v>558</v>
+      </c>
+      <c r="E14" s="2">
+        <v>402505158.56</v>
+      </c>
+      <c r="F14">
+        <v>1.88</v>
+      </c>
+      <c r="G14" s="2">
+        <v>8071088</v>
+      </c>
+      <c r="H14">
+        <v>49.87</v>
+      </c>
+      <c r="I14" t="s">
+        <v>559</v>
+      </c>
+      <c r="J14">
+        <v>40.25</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>53</v>
+      </c>
+      <c r="B15" t="s">
+        <v>54</v>
+      </c>
+      <c r="C15" t="s">
+        <v>578</v>
+      </c>
+      <c r="D15" t="s">
+        <v>564</v>
+      </c>
+      <c r="E15" s="2">
+        <v>368250267.60000002</v>
+      </c>
+      <c r="F15">
+        <v>1.72</v>
+      </c>
+      <c r="G15" s="2">
+        <v>4941630</v>
+      </c>
+      <c r="H15">
+        <v>74.52</v>
+      </c>
+      <c r="I15" t="s">
+        <v>559</v>
+      </c>
+      <c r="J15">
+        <v>36.83</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>579</v>
+      </c>
+      <c r="B16" t="s">
+        <v>580</v>
+      </c>
+      <c r="C16" t="s">
+        <v>581</v>
+      </c>
+      <c r="D16" t="s">
+        <v>575</v>
+      </c>
+      <c r="E16" s="2">
+        <v>362179206.5</v>
+      </c>
+      <c r="F16">
+        <v>1.69</v>
+      </c>
+      <c r="G16" s="2">
+        <v>2640175</v>
+      </c>
+      <c r="H16">
+        <v>137.18</v>
+      </c>
+      <c r="I16" t="s">
+        <v>559</v>
+      </c>
+      <c r="J16">
+        <v>36.22</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>68</v>
+      </c>
+      <c r="B17" t="s">
+        <v>69</v>
+      </c>
+      <c r="C17" t="s">
+        <v>582</v>
+      </c>
+      <c r="D17" t="s">
+        <v>570</v>
+      </c>
+      <c r="E17" s="2">
+        <v>343063275.51999998</v>
+      </c>
+      <c r="F17">
+        <v>1.6</v>
+      </c>
+      <c r="G17" s="2">
+        <v>2157088</v>
+      </c>
+      <c r="H17">
+        <v>159.04</v>
+      </c>
+      <c r="I17" t="s">
+        <v>559</v>
+      </c>
+      <c r="J17">
+        <v>34.31</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>60</v>
+      </c>
+      <c r="B18" t="s">
+        <v>61</v>
+      </c>
+      <c r="C18" t="s">
+        <v>583</v>
+      </c>
+      <c r="D18" t="s">
+        <v>564</v>
+      </c>
+      <c r="E18" s="2">
+        <v>337025173.75999999</v>
+      </c>
+      <c r="F18">
+        <v>1.57</v>
+      </c>
+      <c r="G18" s="2">
+        <v>5765056</v>
+      </c>
+      <c r="H18">
+        <v>58.46</v>
+      </c>
+      <c r="I18" t="s">
+        <v>559</v>
+      </c>
+      <c r="J18">
+        <v>33.700000000000003</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>584</v>
+      </c>
+      <c r="B19" t="s">
+        <v>74</v>
+      </c>
+      <c r="C19" t="s">
+        <v>585</v>
+      </c>
+      <c r="D19" t="s">
+        <v>558</v>
+      </c>
+      <c r="E19" s="2">
+        <v>323207300.55000001</v>
+      </c>
+      <c r="F19">
+        <v>1.51</v>
+      </c>
+      <c r="G19" s="2">
+        <v>1862115</v>
+      </c>
+      <c r="H19">
+        <v>173.57</v>
+      </c>
+      <c r="I19" t="s">
+        <v>559</v>
+      </c>
+      <c r="J19">
+        <v>32.32</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>586</v>
+      </c>
+      <c r="B20" t="s">
+        <v>27</v>
+      </c>
+      <c r="C20" t="s">
+        <v>587</v>
+      </c>
+      <c r="D20" t="s">
+        <v>561</v>
+      </c>
+      <c r="E20" s="2">
+        <v>314719588.88</v>
+      </c>
+      <c r="F20">
+        <v>1.47</v>
+      </c>
+      <c r="G20" s="2">
+        <v>94636</v>
+      </c>
+      <c r="H20" s="2">
+        <v>3325.58</v>
+      </c>
+      <c r="I20" t="s">
+        <v>559</v>
+      </c>
+      <c r="J20">
+        <v>31.47</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>588</v>
+      </c>
+      <c r="B21" t="s">
+        <v>589</v>
+      </c>
+      <c r="C21" t="s">
+        <v>590</v>
+      </c>
+      <c r="D21" t="s">
+        <v>575</v>
+      </c>
+      <c r="E21" s="2">
+        <v>297150945.89999998</v>
+      </c>
+      <c r="F21">
+        <v>1.39</v>
+      </c>
+      <c r="G21" s="2">
+        <v>1227795</v>
+      </c>
+      <c r="H21">
+        <v>242.02</v>
+      </c>
+      <c r="I21" t="s">
+        <v>591</v>
+      </c>
+      <c r="J21">
+        <v>29.72</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>592</v>
+      </c>
+      <c r="B22" t="s">
+        <v>56</v>
+      </c>
+      <c r="C22" t="s">
+        <v>593</v>
+      </c>
+      <c r="D22" t="s">
+        <v>594</v>
+      </c>
+      <c r="E22" s="2">
+        <v>270474336</v>
+      </c>
+      <c r="F22">
+        <v>1.26</v>
+      </c>
+      <c r="G22" s="2">
+        <v>3642752</v>
+      </c>
+      <c r="H22">
+        <v>74.25</v>
+      </c>
+      <c r="I22" t="s">
+        <v>559</v>
+      </c>
+      <c r="J22">
+        <v>27.05</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>595</v>
+      </c>
+      <c r="B23" t="s">
+        <v>80</v>
+      </c>
+      <c r="C23" t="s">
+        <v>596</v>
+      </c>
+      <c r="D23" t="s">
+        <v>597</v>
+      </c>
+      <c r="E23" s="2">
+        <v>263867834.16</v>
+      </c>
+      <c r="F23">
+        <v>1.23</v>
+      </c>
+      <c r="G23" s="2">
+        <v>1313298</v>
+      </c>
+      <c r="H23">
+        <v>200.92</v>
+      </c>
+      <c r="I23" t="s">
+        <v>559</v>
+      </c>
+      <c r="J23">
+        <v>26.39</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>88</v>
+      </c>
+      <c r="B24" t="s">
+        <v>89</v>
+      </c>
+      <c r="C24" t="s">
+        <v>598</v>
+      </c>
+      <c r="D24" t="s">
+        <v>570</v>
+      </c>
+      <c r="E24" s="2">
+        <v>263355561.09</v>
+      </c>
+      <c r="F24">
+        <v>1.23</v>
+      </c>
+      <c r="G24" s="2">
+        <v>915669</v>
+      </c>
+      <c r="H24">
+        <v>287.61</v>
+      </c>
+      <c r="I24" t="s">
+        <v>559</v>
+      </c>
+      <c r="J24">
+        <v>26.34</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>599</v>
+      </c>
+      <c r="B25" t="s">
+        <v>600</v>
+      </c>
+      <c r="C25" t="s">
+        <v>601</v>
+      </c>
+      <c r="D25" t="s">
+        <v>564</v>
+      </c>
+      <c r="E25" s="2">
+        <v>249790896.41999999</v>
+      </c>
+      <c r="F25">
+        <v>1.1599999999999999</v>
+      </c>
+      <c r="G25" s="2">
+        <v>2068833</v>
+      </c>
+      <c r="H25">
+        <v>120.74</v>
+      </c>
+      <c r="I25" t="s">
+        <v>559</v>
+      </c>
+      <c r="J25">
+        <v>24.98</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>602</v>
+      </c>
+      <c r="B26" t="s">
+        <v>76</v>
+      </c>
+      <c r="C26" t="s">
+        <v>603</v>
+      </c>
+      <c r="D26" t="s">
+        <v>558</v>
+      </c>
+      <c r="E26" s="2">
+        <v>246241416.62</v>
+      </c>
+      <c r="F26">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="G26" s="2">
+        <v>99017</v>
+      </c>
+      <c r="H26" s="2">
+        <v>2486.86</v>
+      </c>
+      <c r="I26" t="s">
+        <v>559</v>
+      </c>
+      <c r="J26">
+        <v>24.62</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>604</v>
+      </c>
+      <c r="B27" t="s">
+        <v>66</v>
+      </c>
+      <c r="C27" t="s">
+        <v>605</v>
+      </c>
+      <c r="D27" t="s">
+        <v>558</v>
+      </c>
+      <c r="E27" s="2">
+        <v>240716752.25</v>
+      </c>
+      <c r="F27">
+        <v>1.1200000000000001</v>
+      </c>
+      <c r="G27" s="2">
+        <v>847445</v>
+      </c>
+      <c r="H27">
+        <v>284.05</v>
+      </c>
+      <c r="I27" t="s">
+        <v>559</v>
+      </c>
+      <c r="J27">
+        <v>24.07</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>71</v>
+      </c>
+      <c r="B28" t="s">
+        <v>72</v>
+      </c>
+      <c r="C28" t="s">
+        <v>606</v>
+      </c>
+      <c r="D28" t="s">
+        <v>558</v>
+      </c>
+      <c r="E28" s="2">
+        <v>226279769.52000001</v>
+      </c>
+      <c r="F28">
+        <v>1.06</v>
+      </c>
+      <c r="G28" s="2">
+        <v>2675967</v>
+      </c>
+      <c r="H28">
+        <v>84.56</v>
+      </c>
+      <c r="I28" t="s">
+        <v>559</v>
+      </c>
+      <c r="J28">
+        <v>22.63</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>607</v>
+      </c>
+      <c r="B29" t="s">
+        <v>608</v>
+      </c>
+      <c r="C29" t="s">
+        <v>609</v>
+      </c>
+      <c r="D29" t="s">
+        <v>570</v>
+      </c>
+      <c r="E29" s="2">
+        <v>222902030.40000001</v>
+      </c>
+      <c r="F29">
+        <v>1.04</v>
+      </c>
+      <c r="G29" s="2">
+        <v>5774664</v>
+      </c>
+      <c r="H29">
+        <v>38.6</v>
+      </c>
+      <c r="I29" t="s">
+        <v>559</v>
+      </c>
+      <c r="J29">
+        <v>22.29</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>149</v>
+      </c>
+      <c r="B30" t="s">
+        <v>150</v>
+      </c>
+      <c r="C30" t="s">
+        <v>610</v>
+      </c>
+      <c r="D30" t="s">
+        <v>561</v>
+      </c>
+      <c r="E30" s="2">
+        <v>203884525.56</v>
+      </c>
+      <c r="F30">
+        <v>0.95</v>
+      </c>
+      <c r="G30" s="2">
+        <v>546578</v>
+      </c>
+      <c r="H30">
+        <v>373.02</v>
+      </c>
+      <c r="I30" t="s">
+        <v>559</v>
+      </c>
+      <c r="J30">
+        <v>20.39</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>91</v>
+      </c>
+      <c r="B31" t="s">
+        <v>92</v>
+      </c>
+      <c r="C31" t="s">
+        <v>611</v>
+      </c>
+      <c r="D31" t="s">
+        <v>570</v>
+      </c>
+      <c r="E31" s="2">
+        <v>196520326.78</v>
+      </c>
+      <c r="F31">
+        <v>0.92</v>
+      </c>
+      <c r="G31" s="2">
+        <v>2313637</v>
+      </c>
+      <c r="H31">
+        <v>84.94</v>
+      </c>
+      <c r="I31" t="s">
+        <v>559</v>
+      </c>
+      <c r="J31">
+        <v>19.649999999999999</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>612</v>
+      </c>
+      <c r="B32" t="s">
+        <v>110</v>
+      </c>
+      <c r="C32" t="s">
+        <v>613</v>
+      </c>
+      <c r="D32" t="s">
+        <v>558</v>
+      </c>
+      <c r="E32" s="2">
+        <v>186900874.19999999</v>
+      </c>
+      <c r="F32">
+        <v>0.87</v>
+      </c>
+      <c r="G32" s="2">
+        <v>2563798</v>
+      </c>
+      <c r="H32">
+        <v>72.900000000000006</v>
+      </c>
+      <c r="I32" t="s">
+        <v>559</v>
+      </c>
+      <c r="J32">
+        <v>18.690000000000001</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>107</v>
+      </c>
+      <c r="B33" t="s">
+        <v>108</v>
+      </c>
+      <c r="C33" t="s">
+        <v>614</v>
+      </c>
+      <c r="D33" t="s">
+        <v>615</v>
+      </c>
+      <c r="E33" s="2">
+        <v>169618179.03999999</v>
+      </c>
+      <c r="F33">
+        <v>0.79</v>
+      </c>
+      <c r="G33" s="2">
+        <v>2393033</v>
+      </c>
+      <c r="H33">
+        <v>70.88</v>
+      </c>
+      <c r="I33" t="s">
+        <v>559</v>
+      </c>
+      <c r="J33">
+        <v>16.96</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>616</v>
+      </c>
+      <c r="B34" t="s">
+        <v>58</v>
+      </c>
+      <c r="C34" t="s">
+        <v>617</v>
+      </c>
+      <c r="D34" t="s">
+        <v>594</v>
+      </c>
+      <c r="E34" s="2">
+        <v>169234952.47999999</v>
+      </c>
+      <c r="F34">
+        <v>0.79</v>
+      </c>
+      <c r="G34" s="2">
+        <v>2708626</v>
+      </c>
+      <c r="H34">
+        <v>62.48</v>
+      </c>
+      <c r="I34" t="s">
+        <v>559</v>
+      </c>
+      <c r="J34">
+        <v>16.920000000000002</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>618</v>
+      </c>
+      <c r="B35" t="s">
+        <v>100</v>
+      </c>
+      <c r="C35" t="s">
+        <v>619</v>
+      </c>
+      <c r="D35" t="s">
+        <v>575</v>
+      </c>
+      <c r="E35" s="2">
+        <v>152474468.13999999</v>
+      </c>
+      <c r="F35">
+        <v>0.71</v>
+      </c>
+      <c r="G35" s="2">
+        <v>620294</v>
+      </c>
+      <c r="H35">
+        <v>245.81</v>
+      </c>
+      <c r="I35" t="s">
+        <v>559</v>
+      </c>
+      <c r="J35">
+        <v>15.25</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>94</v>
+      </c>
+      <c r="B36" t="s">
+        <v>95</v>
+      </c>
+      <c r="C36" t="s">
+        <v>620</v>
+      </c>
+      <c r="D36" t="s">
+        <v>564</v>
+      </c>
+      <c r="E36" s="2">
+        <v>151881541.56999999</v>
+      </c>
+      <c r="F36">
+        <v>0.71</v>
+      </c>
+      <c r="G36" s="2">
+        <v>6699671</v>
+      </c>
+      <c r="H36">
+        <v>22.67</v>
+      </c>
+      <c r="I36" t="s">
+        <v>559</v>
+      </c>
+      <c r="J36">
+        <v>15.19</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
+        <v>85</v>
+      </c>
+      <c r="B37" t="s">
+        <v>86</v>
+      </c>
+      <c r="C37" t="s">
+        <v>621</v>
+      </c>
+      <c r="D37" t="s">
+        <v>597</v>
+      </c>
+      <c r="E37" s="2">
+        <v>150121558.72</v>
+      </c>
+      <c r="F37">
+        <v>0.7</v>
+      </c>
+      <c r="G37" s="2">
+        <v>1558571</v>
+      </c>
+      <c r="H37">
+        <v>96.32</v>
+      </c>
+      <c r="I37" t="s">
+        <v>559</v>
+      </c>
+      <c r="J37">
+        <v>15.01</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
+        <v>622</v>
+      </c>
+      <c r="B38" t="s">
+        <v>623</v>
+      </c>
+      <c r="C38" t="s">
+        <v>624</v>
+      </c>
+      <c r="D38" t="s">
+        <v>564</v>
+      </c>
+      <c r="E38" s="2">
+        <v>139759970.13</v>
+      </c>
+      <c r="F38">
+        <v>0.65</v>
+      </c>
+      <c r="G38" s="2">
+        <v>2758239</v>
+      </c>
+      <c r="H38">
+        <v>50.67</v>
+      </c>
+      <c r="I38" t="s">
+        <v>559</v>
+      </c>
+      <c r="J38">
+        <v>13.98</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
+        <v>119</v>
+      </c>
+      <c r="B39" t="s">
+        <v>120</v>
+      </c>
+      <c r="C39" t="s">
+        <v>625</v>
+      </c>
+      <c r="D39" t="s">
+        <v>626</v>
+      </c>
+      <c r="E39" s="2">
+        <v>139620708.38999999</v>
+      </c>
+      <c r="F39">
+        <v>0.65</v>
+      </c>
+      <c r="G39" s="2">
+        <v>4433811</v>
+      </c>
+      <c r="H39">
+        <v>31.49</v>
+      </c>
+      <c r="I39" t="s">
+        <v>559</v>
+      </c>
+      <c r="J39">
+        <v>13.96</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
+        <v>186</v>
+      </c>
+      <c r="B40" t="s">
+        <v>187</v>
+      </c>
+      <c r="C40" t="s">
+        <v>627</v>
+      </c>
+      <c r="D40" t="s">
+        <v>570</v>
+      </c>
+      <c r="E40" s="2">
+        <v>137849923.34999999</v>
+      </c>
+      <c r="F40">
+        <v>0.64</v>
+      </c>
+      <c r="G40" s="2">
+        <v>2001015</v>
+      </c>
+      <c r="H40">
+        <v>68.89</v>
+      </c>
+      <c r="I40" t="s">
+        <v>559</v>
+      </c>
+      <c r="J40">
+        <v>13.78</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
+        <v>628</v>
+      </c>
+      <c r="B41" t="s">
+        <v>629</v>
+      </c>
+      <c r="C41" t="s">
+        <v>630</v>
+      </c>
+      <c r="D41" t="s">
+        <v>570</v>
+      </c>
+      <c r="E41" s="2">
+        <v>133142031.59999999</v>
+      </c>
+      <c r="F41">
+        <v>0.62</v>
+      </c>
+      <c r="G41" s="2">
+        <v>2135740</v>
+      </c>
+      <c r="H41">
+        <v>62.34</v>
+      </c>
+      <c r="I41" t="s">
+        <v>559</v>
+      </c>
+      <c r="J41">
+        <v>13.31</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
+        <v>18</v>
+      </c>
+      <c r="B42" t="s">
+        <v>19</v>
+      </c>
+      <c r="C42" t="s">
+        <v>631</v>
+      </c>
+      <c r="D42" t="s">
+        <v>558</v>
+      </c>
+      <c r="E42" s="2">
+        <v>129063054.88</v>
+      </c>
+      <c r="F42">
+        <v>0.6</v>
+      </c>
+      <c r="G42" s="2">
+        <v>1789808</v>
+      </c>
+      <c r="H42">
+        <v>72.11</v>
+      </c>
+      <c r="I42" t="s">
+        <v>559</v>
+      </c>
+      <c r="J42">
+        <v>12.91</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
+        <v>632</v>
+      </c>
+      <c r="B43" t="s">
+        <v>633</v>
+      </c>
+      <c r="C43" t="s">
+        <v>634</v>
+      </c>
+      <c r="D43" t="s">
+        <v>626</v>
+      </c>
+      <c r="E43" s="2">
+        <v>127842228.31999999</v>
+      </c>
+      <c r="F43">
+        <v>0.6</v>
+      </c>
+      <c r="G43" s="2">
+        <v>7330403</v>
+      </c>
+      <c r="H43">
+        <v>17.440000000000001</v>
+      </c>
+      <c r="I43" t="s">
+        <v>559</v>
+      </c>
+      <c r="J43">
+        <v>12.78</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
+        <v>122</v>
+      </c>
+      <c r="B44" t="s">
+        <v>123</v>
+      </c>
+      <c r="C44" t="s">
+        <v>635</v>
+      </c>
+      <c r="D44" t="s">
+        <v>575</v>
+      </c>
+      <c r="E44" s="2">
+        <v>126871576.40000001</v>
+      </c>
+      <c r="F44">
+        <v>0.59</v>
+      </c>
+      <c r="G44" s="2">
+        <v>882278</v>
+      </c>
+      <c r="H44">
+        <v>143.80000000000001</v>
+      </c>
+      <c r="I44" t="s">
+        <v>559</v>
+      </c>
+      <c r="J44">
+        <v>12.69</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
+        <v>636</v>
+      </c>
+      <c r="B45" t="s">
+        <v>637</v>
+      </c>
+      <c r="C45" t="s">
+        <v>638</v>
+      </c>
+      <c r="D45" t="s">
+        <v>561</v>
+      </c>
+      <c r="E45" s="2">
+        <v>120205194.44</v>
+      </c>
+      <c r="F45">
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="G45" s="2">
+        <v>945158</v>
+      </c>
+      <c r="H45">
+        <v>127.18</v>
+      </c>
+      <c r="I45" t="s">
+        <v>559</v>
+      </c>
+      <c r="J45">
+        <v>12.02</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A46" t="s">
+        <v>24</v>
+      </c>
+      <c r="B46" t="s">
+        <v>25</v>
+      </c>
+      <c r="C46" t="s">
+        <v>639</v>
+      </c>
+      <c r="D46" t="s">
+        <v>575</v>
+      </c>
+      <c r="E46" s="2">
+        <v>116352740.91</v>
+      </c>
+      <c r="F46">
+        <v>0.54</v>
+      </c>
+      <c r="G46" s="2">
+        <v>642017</v>
+      </c>
+      <c r="H46">
+        <v>181.23</v>
+      </c>
+      <c r="I46" t="s">
+        <v>559</v>
+      </c>
+      <c r="J46">
+        <v>11.64</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
+        <v>640</v>
+      </c>
+      <c r="B47" t="s">
+        <v>147</v>
+      </c>
+      <c r="C47" t="s">
+        <v>641</v>
+      </c>
+      <c r="D47" t="s">
+        <v>570</v>
+      </c>
+      <c r="E47" s="2">
+        <v>109768490.16</v>
+      </c>
+      <c r="F47">
+        <v>0.51</v>
+      </c>
+      <c r="G47" s="2">
+        <v>3206792</v>
+      </c>
+      <c r="H47">
+        <v>34.229999999999997</v>
+      </c>
+      <c r="I47" t="s">
+        <v>559</v>
+      </c>
+      <c r="J47">
+        <v>10.98</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A48" t="s">
+        <v>642</v>
+      </c>
+      <c r="B48" t="s">
+        <v>643</v>
+      </c>
+      <c r="C48" t="s">
+        <v>644</v>
+      </c>
+      <c r="D48" t="s">
+        <v>615</v>
+      </c>
+      <c r="E48" s="2">
+        <v>104300052.42</v>
+      </c>
+      <c r="F48">
+        <v>0.49</v>
+      </c>
+      <c r="G48" s="2">
+        <v>2191638</v>
+      </c>
+      <c r="H48">
+        <v>47.59</v>
+      </c>
+      <c r="I48" t="s">
+        <v>645</v>
+      </c>
+      <c r="J48">
+        <v>10.43</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A49" t="s">
+        <v>646</v>
+      </c>
+      <c r="B49" t="s">
+        <v>131</v>
+      </c>
+      <c r="C49" t="s">
+        <v>647</v>
+      </c>
+      <c r="D49" t="s">
+        <v>564</v>
+      </c>
+      <c r="E49" s="2">
+        <v>104174987.23</v>
+      </c>
+      <c r="F49">
+        <v>0.49</v>
+      </c>
+      <c r="G49" s="2">
+        <v>1745267</v>
+      </c>
+      <c r="H49">
+        <v>59.69</v>
+      </c>
+      <c r="I49" t="s">
+        <v>559</v>
+      </c>
+      <c r="J49">
+        <v>10.42</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A50" t="s">
+        <v>162</v>
+      </c>
+      <c r="B50" t="s">
+        <v>163</v>
+      </c>
+      <c r="C50" t="s">
+        <v>648</v>
+      </c>
+      <c r="D50" t="s">
+        <v>570</v>
+      </c>
+      <c r="E50" s="2">
+        <v>103737146.48</v>
+      </c>
+      <c r="F50">
+        <v>0.48</v>
+      </c>
+      <c r="G50" s="2">
+        <v>1998019</v>
+      </c>
+      <c r="H50">
+        <v>51.92</v>
+      </c>
+      <c r="I50" t="s">
+        <v>559</v>
+      </c>
+      <c r="J50">
+        <v>10.37</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A51" t="s">
+        <v>649</v>
+      </c>
+      <c r="B51" t="s">
+        <v>145</v>
+      </c>
+      <c r="C51" t="s">
+        <v>650</v>
+      </c>
+      <c r="D51" t="s">
+        <v>615</v>
+      </c>
+      <c r="E51" s="2">
+        <v>95141187.400000006</v>
+      </c>
+      <c r="F51">
+        <v>0.44</v>
+      </c>
+      <c r="G51" s="2">
+        <v>1423204</v>
+      </c>
+      <c r="H51">
+        <v>66.849999999999994</v>
+      </c>
+      <c r="I51" t="s">
+        <v>559</v>
+      </c>
+      <c r="J51">
+        <v>9.51</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A52" t="s">
+        <v>651</v>
+      </c>
+      <c r="B52" t="s">
+        <v>652</v>
+      </c>
+      <c r="C52" t="s">
+        <v>653</v>
+      </c>
+      <c r="D52" t="s">
+        <v>597</v>
+      </c>
+      <c r="E52" s="2">
+        <v>94455765.030000001</v>
+      </c>
+      <c r="F52">
+        <v>0.44</v>
+      </c>
+      <c r="G52" s="2">
+        <v>1257231</v>
+      </c>
+      <c r="H52">
+        <v>75.13</v>
+      </c>
+      <c r="I52" t="s">
+        <v>559</v>
+      </c>
+      <c r="J52">
+        <v>9.4499999999999993</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A53" t="s">
+        <v>654</v>
+      </c>
+      <c r="B53" t="s">
+        <v>136</v>
+      </c>
+      <c r="C53" t="s">
+        <v>655</v>
+      </c>
+      <c r="D53" t="s">
+        <v>594</v>
+      </c>
+      <c r="E53" s="2">
+        <v>94098520.239999995</v>
+      </c>
+      <c r="F53">
+        <v>0.44</v>
+      </c>
+      <c r="G53" s="2">
+        <v>943249</v>
+      </c>
+      <c r="H53">
+        <v>99.76</v>
+      </c>
+      <c r="I53" t="s">
+        <v>559</v>
+      </c>
+      <c r="J53">
+        <v>9.41</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A54" t="s">
+        <v>656</v>
+      </c>
+      <c r="B54" t="s">
+        <v>657</v>
+      </c>
+      <c r="C54" t="s">
+        <v>658</v>
+      </c>
+      <c r="D54" t="s">
+        <v>575</v>
+      </c>
+      <c r="E54" s="2">
+        <v>92716520.079999998</v>
+      </c>
+      <c r="F54">
+        <v>0.43</v>
+      </c>
+      <c r="G54" s="2">
+        <v>412936</v>
+      </c>
+      <c r="H54">
+        <v>224.53</v>
+      </c>
+      <c r="I54" t="s">
+        <v>559</v>
+      </c>
+      <c r="J54">
+        <v>9.27</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A55" t="s">
+        <v>659</v>
+      </c>
+      <c r="B55" t="s">
+        <v>660</v>
+      </c>
+      <c r="C55" t="s">
+        <v>661</v>
+      </c>
+      <c r="D55" t="s">
+        <v>626</v>
+      </c>
+      <c r="E55" s="2">
+        <v>92682465.829999998</v>
+      </c>
+      <c r="F55">
+        <v>0.43</v>
+      </c>
+      <c r="G55" s="2">
+        <v>1834933</v>
+      </c>
+      <c r="H55">
+        <v>50.51</v>
+      </c>
+      <c r="I55" t="s">
+        <v>559</v>
+      </c>
+      <c r="J55">
+        <v>9.27</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A56" t="s">
+        <v>662</v>
+      </c>
+      <c r="B56" t="s">
+        <v>198</v>
+      </c>
+      <c r="C56" t="s">
+        <v>663</v>
+      </c>
+      <c r="D56" t="s">
+        <v>570</v>
+      </c>
+      <c r="E56" s="2">
+        <v>89338115.620000005</v>
+      </c>
+      <c r="F56">
+        <v>0.42</v>
+      </c>
+      <c r="G56" s="2">
+        <v>3211291</v>
+      </c>
+      <c r="H56">
+        <v>27.82</v>
+      </c>
+      <c r="I56" t="s">
+        <v>559</v>
+      </c>
+      <c r="J56">
+        <v>8.93</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A57" t="s">
+        <v>63</v>
+      </c>
+      <c r="B57" t="s">
+        <v>64</v>
+      </c>
+      <c r="C57" t="s">
+        <v>664</v>
+      </c>
+      <c r="D57" t="s">
+        <v>564</v>
+      </c>
+      <c r="E57" s="2">
+        <v>86028161.120000005</v>
+      </c>
+      <c r="F57">
+        <v>0.4</v>
+      </c>
+      <c r="G57" s="2">
+        <v>746254</v>
+      </c>
+      <c r="H57">
+        <v>115.28</v>
+      </c>
+      <c r="I57" t="s">
+        <v>559</v>
+      </c>
+      <c r="J57">
+        <v>8.6</v>
+      </c>
+    </row>
+    <row r="58" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A58" t="s">
+        <v>665</v>
+      </c>
+      <c r="B58" t="s">
+        <v>78</v>
+      </c>
+      <c r="C58" t="s">
+        <v>666</v>
+      </c>
+      <c r="D58" t="s">
+        <v>558</v>
+      </c>
+      <c r="E58" s="2">
+        <v>85336278.299999997</v>
+      </c>
+      <c r="F58">
+        <v>0.4</v>
+      </c>
+      <c r="G58" s="2">
+        <v>1272726</v>
+      </c>
+      <c r="H58">
+        <v>67.05</v>
+      </c>
+      <c r="I58" t="s">
+        <v>559</v>
+      </c>
+      <c r="J58">
+        <v>8.5299999999999994</v>
+      </c>
+    </row>
+    <row r="59" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A59" t="s">
+        <v>667</v>
+      </c>
+      <c r="B59" t="s">
+        <v>118</v>
+      </c>
+      <c r="C59" t="s">
+        <v>668</v>
+      </c>
+      <c r="D59" t="s">
+        <v>615</v>
+      </c>
+      <c r="E59" s="2">
+        <v>80896440.379999995</v>
+      </c>
+      <c r="F59">
+        <v>0.38</v>
+      </c>
+      <c r="G59" s="2">
+        <v>1508699</v>
+      </c>
+      <c r="H59">
+        <v>53.62</v>
+      </c>
+      <c r="I59" t="s">
+        <v>559</v>
+      </c>
+      <c r="J59">
+        <v>8.09</v>
+      </c>
+    </row>
+    <row r="60" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A60" t="s">
+        <v>205</v>
+      </c>
+      <c r="B60" t="s">
+        <v>206</v>
+      </c>
+      <c r="C60" t="s">
+        <v>669</v>
+      </c>
+      <c r="D60" t="s">
+        <v>597</v>
+      </c>
+      <c r="E60" s="2">
+        <v>78368040.920000002</v>
+      </c>
+      <c r="F60">
+        <v>0.37</v>
+      </c>
+      <c r="G60" s="2">
+        <v>879749</v>
+      </c>
+      <c r="H60">
+        <v>89.08</v>
+      </c>
+      <c r="I60" t="s">
+        <v>559</v>
+      </c>
+      <c r="J60">
+        <v>7.84</v>
+      </c>
+    </row>
+    <row r="61" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A61" t="s">
+        <v>285</v>
+      </c>
+      <c r="B61" t="s">
+        <v>178</v>
+      </c>
+      <c r="C61" t="s">
+        <v>670</v>
+      </c>
+      <c r="D61" t="s">
+        <v>558</v>
+      </c>
+      <c r="E61" s="2">
+        <v>78077475.959999993</v>
+      </c>
+      <c r="F61">
+        <v>0.36</v>
+      </c>
+      <c r="G61" s="2">
+        <v>439774</v>
+      </c>
+      <c r="H61">
+        <v>177.54</v>
+      </c>
+      <c r="I61" t="s">
+        <v>559</v>
+      </c>
+      <c r="J61">
+        <v>7.81</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A62" t="s">
+        <v>128</v>
+      </c>
+      <c r="B62" t="s">
+        <v>129</v>
+      </c>
+      <c r="C62" t="s">
+        <v>671</v>
+      </c>
+      <c r="D62" t="s">
+        <v>575</v>
+      </c>
+      <c r="E62" s="2">
+        <v>77071406.719999999</v>
+      </c>
+      <c r="F62">
+        <v>0.36</v>
+      </c>
+      <c r="G62" s="2">
+        <v>1287958</v>
+      </c>
+      <c r="H62">
+        <v>59.84</v>
+      </c>
+      <c r="I62" t="s">
+        <v>559</v>
+      </c>
+      <c r="J62">
+        <v>7.71</v>
+      </c>
+    </row>
+    <row r="63" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A63" t="s">
+        <v>672</v>
+      </c>
+      <c r="B63" t="s">
+        <v>105</v>
+      </c>
+      <c r="C63" t="s">
+        <v>673</v>
+      </c>
+      <c r="D63" t="s">
+        <v>594</v>
+      </c>
+      <c r="E63" s="2">
+        <v>71614939.859999999</v>
+      </c>
+      <c r="F63">
+        <v>0.33</v>
+      </c>
+      <c r="G63" s="2">
+        <v>749267</v>
+      </c>
+      <c r="H63">
+        <v>95.58</v>
+      </c>
+      <c r="I63" t="s">
+        <v>559</v>
+      </c>
+      <c r="J63">
+        <v>7.16</v>
+      </c>
+    </row>
+    <row r="64" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A64" t="s">
+        <v>156</v>
+      </c>
+      <c r="B64" t="s">
+        <v>157</v>
+      </c>
+      <c r="C64" t="s">
+        <v>674</v>
+      </c>
+      <c r="D64" t="s">
+        <v>575</v>
+      </c>
+      <c r="E64" s="2">
+        <v>69653783.840000004</v>
+      </c>
+      <c r="F64">
+        <v>0.32</v>
+      </c>
+      <c r="G64" s="2">
+        <v>542644</v>
+      </c>
+      <c r="H64">
+        <v>128.36000000000001</v>
+      </c>
+      <c r="I64" t="s">
+        <v>559</v>
+      </c>
+      <c r="J64">
+        <v>6.97</v>
+      </c>
+    </row>
+    <row r="65" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A65" t="s">
+        <v>675</v>
+      </c>
+      <c r="B65" t="s">
+        <v>152</v>
+      </c>
+      <c r="C65" t="s">
+        <v>676</v>
+      </c>
+      <c r="D65" t="s">
+        <v>564</v>
+      </c>
+      <c r="E65" s="2">
+        <v>68633802.840000004</v>
+      </c>
+      <c r="F65">
+        <v>0.32</v>
+      </c>
+      <c r="G65" s="2">
+        <v>2765262</v>
+      </c>
+      <c r="H65">
+        <v>24.82</v>
+      </c>
+      <c r="I65" t="s">
+        <v>559</v>
+      </c>
+      <c r="J65">
+        <v>6.86</v>
+      </c>
+    </row>
+    <row r="66" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A66" t="s">
+        <v>324</v>
+      </c>
+      <c r="B66" t="s">
+        <v>325</v>
+      </c>
+      <c r="C66" t="s">
+        <v>677</v>
+      </c>
+      <c r="D66" t="s">
+        <v>570</v>
+      </c>
+      <c r="E66" s="2">
+        <v>68529314.700000003</v>
+      </c>
+      <c r="F66">
+        <v>0.32</v>
+      </c>
+      <c r="G66" s="2">
+        <v>3612510</v>
+      </c>
+      <c r="H66">
+        <v>18.97</v>
+      </c>
+      <c r="I66" t="s">
+        <v>559</v>
+      </c>
+      <c r="J66">
+        <v>6.85</v>
+      </c>
+    </row>
+    <row r="67" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A67" t="s">
+        <v>678</v>
+      </c>
+      <c r="B67" t="s">
+        <v>180</v>
+      </c>
+      <c r="C67" t="s">
+        <v>679</v>
+      </c>
+      <c r="D67" t="s">
+        <v>575</v>
+      </c>
+      <c r="E67" s="2">
+        <v>68338632.299999997</v>
+      </c>
+      <c r="F67">
+        <v>0.32</v>
+      </c>
+      <c r="G67" s="2">
+        <v>1906238</v>
+      </c>
+      <c r="H67">
+        <v>35.85</v>
+      </c>
+      <c r="I67" t="s">
+        <v>559</v>
+      </c>
+      <c r="J67">
+        <v>6.83</v>
+      </c>
+    </row>
+    <row r="68" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A68" t="s">
+        <v>680</v>
+      </c>
+      <c r="B68" t="s">
+        <v>154</v>
+      </c>
+      <c r="C68" t="s">
+        <v>681</v>
+      </c>
+      <c r="D68" t="s">
+        <v>558</v>
+      </c>
+      <c r="E68" s="2">
+        <v>68149874.099999994</v>
+      </c>
+      <c r="F68">
+        <v>0.32</v>
+      </c>
+      <c r="G68" s="2">
+        <v>1320990</v>
+      </c>
+      <c r="H68">
+        <v>51.59</v>
+      </c>
+      <c r="I68" t="s">
+        <v>559</v>
+      </c>
+      <c r="J68">
+        <v>6.81</v>
+      </c>
+    </row>
+    <row r="69" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A69" t="s">
+        <v>682</v>
+      </c>
+      <c r="B69" t="s">
+        <v>173</v>
+      </c>
+      <c r="C69" t="s">
+        <v>683</v>
+      </c>
+      <c r="D69" t="s">
+        <v>575</v>
+      </c>
+      <c r="E69" s="2">
+        <v>67676280.420000002</v>
+      </c>
+      <c r="F69">
+        <v>0.32</v>
+      </c>
+      <c r="G69" s="2">
+        <v>786842</v>
+      </c>
+      <c r="H69">
+        <v>86.01</v>
+      </c>
+      <c r="I69" t="s">
+        <v>559</v>
+      </c>
+      <c r="J69">
+        <v>6.77</v>
+      </c>
+    </row>
+    <row r="70" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A70" t="s">
+        <v>684</v>
+      </c>
+      <c r="B70" t="s">
+        <v>289</v>
+      </c>
+      <c r="C70" t="s">
+        <v>685</v>
+      </c>
+      <c r="D70" t="s">
+        <v>564</v>
+      </c>
+      <c r="E70" s="2">
+        <v>65186222.439999998</v>
+      </c>
+      <c r="F70">
+        <v>0.3</v>
+      </c>
+      <c r="G70" s="2">
+        <v>5851546</v>
+      </c>
+      <c r="H70">
+        <v>11.14</v>
+      </c>
+      <c r="I70" t="s">
+        <v>559</v>
+      </c>
+      <c r="J70">
+        <v>6.52</v>
+      </c>
+    </row>
+    <row r="71" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A71" t="s">
+        <v>686</v>
+      </c>
+      <c r="B71" t="s">
+        <v>213</v>
+      </c>
+      <c r="C71" t="s">
+        <v>687</v>
+      </c>
+      <c r="D71" t="s">
+        <v>575</v>
+      </c>
+      <c r="E71" s="2">
+        <v>61903535.399999999</v>
+      </c>
+      <c r="F71">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="G71" s="2">
+        <v>385812</v>
+      </c>
+      <c r="H71">
+        <v>160.44999999999999</v>
+      </c>
+      <c r="I71" t="s">
+        <v>559</v>
+      </c>
+      <c r="J71">
+        <v>6.19</v>
+      </c>
+    </row>
+    <row r="72" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A72" t="s">
+        <v>181</v>
+      </c>
+      <c r="B72" t="s">
+        <v>182</v>
+      </c>
+      <c r="C72" t="s">
+        <v>688</v>
+      </c>
+      <c r="D72" t="s">
+        <v>575</v>
+      </c>
+      <c r="E72" s="2">
+        <v>61878784.799999997</v>
+      </c>
+      <c r="F72">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="G72" s="2">
+        <v>1524108</v>
+      </c>
+      <c r="H72">
+        <v>40.6</v>
+      </c>
+      <c r="I72" t="s">
+        <v>559</v>
+      </c>
+      <c r="J72">
+        <v>6.19</v>
+      </c>
+    </row>
+    <row r="73" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A73" t="s">
+        <v>689</v>
+      </c>
+      <c r="B73" t="s">
+        <v>690</v>
+      </c>
+      <c r="C73" t="s">
+        <v>691</v>
+      </c>
+      <c r="D73" t="s">
+        <v>570</v>
+      </c>
+      <c r="E73" s="2">
+        <v>60727217.670000002</v>
+      </c>
+      <c r="F73">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="G73" s="2">
+        <v>2736693</v>
+      </c>
+      <c r="H73">
+        <v>22.19</v>
+      </c>
+      <c r="I73" t="s">
+        <v>559</v>
+      </c>
+      <c r="J73">
+        <v>6.07</v>
+      </c>
+    </row>
+    <row r="74" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A74" t="s">
+        <v>692</v>
+      </c>
+      <c r="B74" t="s">
+        <v>693</v>
+      </c>
+      <c r="C74" t="s">
+        <v>694</v>
+      </c>
+      <c r="D74" t="s">
+        <v>570</v>
+      </c>
+      <c r="E74" s="2">
+        <v>59610070.259999998</v>
+      </c>
+      <c r="F74">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="G74" s="2">
+        <v>688497</v>
+      </c>
+      <c r="H74">
+        <v>86.58</v>
+      </c>
+      <c r="I74" t="s">
+        <v>559</v>
+      </c>
+      <c r="J74">
+        <v>5.96</v>
+      </c>
+    </row>
+    <row r="75" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A75" t="s">
+        <v>695</v>
+      </c>
+      <c r="B75" t="s">
+        <v>192</v>
+      </c>
+      <c r="C75" t="s">
+        <v>696</v>
+      </c>
+      <c r="D75" t="s">
+        <v>615</v>
+      </c>
+      <c r="E75" s="2">
+        <v>58982610.439999998</v>
+      </c>
+      <c r="F75">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="G75" s="2">
+        <v>1421953</v>
+      </c>
+      <c r="H75">
+        <v>41.48</v>
+      </c>
+      <c r="I75" t="s">
+        <v>559</v>
+      </c>
+      <c r="J75">
+        <v>5.9</v>
+      </c>
+    </row>
+    <row r="76" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A76" t="s">
+        <v>208</v>
+      </c>
+      <c r="B76" t="s">
+        <v>209</v>
+      </c>
+      <c r="C76" t="s">
+        <v>697</v>
+      </c>
+      <c r="D76" t="s">
+        <v>561</v>
+      </c>
+      <c r="E76" s="2">
+        <v>55748839.560000002</v>
+      </c>
+      <c r="F76">
+        <v>0.26</v>
+      </c>
+      <c r="G76" s="2">
+        <v>1208254</v>
+      </c>
+      <c r="H76">
+        <v>46.14</v>
+      </c>
+      <c r="I76" t="s">
+        <v>559</v>
+      </c>
+      <c r="J76">
+        <v>5.57</v>
+      </c>
+    </row>
+    <row r="77" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A77" t="s">
+        <v>200</v>
+      </c>
+      <c r="B77" t="s">
+        <v>201</v>
+      </c>
+      <c r="C77" t="s">
+        <v>698</v>
+      </c>
+      <c r="D77" t="s">
+        <v>575</v>
+      </c>
+      <c r="E77" s="2">
+        <v>54799553.759999998</v>
+      </c>
+      <c r="F77">
+        <v>0.26</v>
+      </c>
+      <c r="G77" s="2">
+        <v>367881</v>
+      </c>
+      <c r="H77">
+        <v>148.96</v>
+      </c>
+      <c r="I77" t="s">
+        <v>559</v>
+      </c>
+      <c r="J77">
+        <v>5.48</v>
+      </c>
+    </row>
+    <row r="78" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A78" t="s">
+        <v>699</v>
+      </c>
+      <c r="B78" t="s">
+        <v>171</v>
+      </c>
+      <c r="C78" t="s">
+        <v>700</v>
+      </c>
+      <c r="D78" t="s">
+        <v>570</v>
+      </c>
+      <c r="E78" s="2">
+        <v>54088148.100000001</v>
+      </c>
+      <c r="F78">
+        <v>0.25</v>
+      </c>
+      <c r="G78" s="2">
+        <v>470946</v>
+      </c>
+      <c r="H78">
+        <v>114.85</v>
+      </c>
+      <c r="I78" t="s">
+        <v>559</v>
+      </c>
+      <c r="J78">
+        <v>5.41</v>
+      </c>
+    </row>
+    <row r="79" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A79" t="s">
+        <v>701</v>
+      </c>
+      <c r="B79" t="s">
+        <v>233</v>
+      </c>
+      <c r="C79" t="s">
+        <v>702</v>
+      </c>
+      <c r="D79" t="s">
+        <v>597</v>
+      </c>
+      <c r="E79" s="2">
+        <v>52035954.240000002</v>
+      </c>
+      <c r="F79">
+        <v>0.24</v>
+      </c>
+      <c r="G79" s="2">
+        <v>452644</v>
+      </c>
+      <c r="H79">
+        <v>114.96</v>
+      </c>
+      <c r="I79" t="s">
+        <v>559</v>
+      </c>
+      <c r="J79">
+        <v>5.2</v>
+      </c>
+    </row>
+    <row r="80" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A80" t="s">
+        <v>549</v>
+      </c>
+      <c r="B80" t="s">
+        <v>550</v>
+      </c>
+      <c r="C80" t="s">
+        <v>703</v>
+      </c>
+      <c r="D80" t="s">
+        <v>561</v>
+      </c>
+      <c r="E80" s="2">
+        <v>50088433.600000001</v>
+      </c>
+      <c r="F80">
+        <v>0.23</v>
+      </c>
+      <c r="G80" s="2">
+        <v>408685</v>
+      </c>
+      <c r="H80">
+        <v>122.56</v>
+      </c>
+      <c r="I80" t="s">
+        <v>559</v>
+      </c>
+      <c r="J80">
+        <v>5.01</v>
+      </c>
+    </row>
+    <row r="81" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A81" t="s">
+        <v>295</v>
+      </c>
+      <c r="B81" t="s">
+        <v>296</v>
+      </c>
+      <c r="C81" t="s">
+        <v>704</v>
+      </c>
+      <c r="D81" t="s">
+        <v>570</v>
+      </c>
+      <c r="E81" s="2">
+        <v>49174989.600000001</v>
+      </c>
+      <c r="F81">
+        <v>0.23</v>
+      </c>
+      <c r="G81" s="2">
+        <v>1876908</v>
+      </c>
+      <c r="H81">
+        <v>26.2</v>
+      </c>
+      <c r="I81" t="s">
+        <v>559</v>
+      </c>
+      <c r="J81">
+        <v>4.92</v>
+      </c>
+    </row>
+    <row r="82" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A82" t="s">
+        <v>705</v>
+      </c>
+      <c r="B82" t="s">
+        <v>194</v>
+      </c>
+      <c r="C82" t="s">
+        <v>706</v>
+      </c>
+      <c r="D82" t="s">
+        <v>594</v>
+      </c>
+      <c r="E82" s="2">
+        <v>48772156.159999996</v>
+      </c>
+      <c r="F82">
+        <v>0.23</v>
+      </c>
+      <c r="G82" s="2">
+        <v>1173536</v>
+      </c>
+      <c r="H82">
+        <v>41.56</v>
+      </c>
+      <c r="I82" t="s">
+        <v>559</v>
+      </c>
+      <c r="J82">
+        <v>4.88</v>
+      </c>
+    </row>
+    <row r="83" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A83" t="s">
+        <v>321</v>
+      </c>
+      <c r="B83" t="s">
+        <v>322</v>
+      </c>
+      <c r="C83" t="s">
+        <v>707</v>
+      </c>
+      <c r="D83" t="s">
+        <v>570</v>
+      </c>
+      <c r="E83" s="2">
+        <v>48493986.25</v>
+      </c>
+      <c r="F83">
+        <v>0.23</v>
+      </c>
+      <c r="G83" s="2">
+        <v>2179505</v>
+      </c>
+      <c r="H83">
+        <v>22.25</v>
+      </c>
+      <c r="I83" t="s">
+        <v>559</v>
+      </c>
+      <c r="J83">
+        <v>4.8499999999999996</v>
+      </c>
+    </row>
+    <row r="84" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A84" t="s">
+        <v>708</v>
+      </c>
+      <c r="B84" t="s">
+        <v>141</v>
+      </c>
+      <c r="C84" t="s">
+        <v>709</v>
+      </c>
+      <c r="D84" t="s">
+        <v>570</v>
+      </c>
+      <c r="E84" s="2">
+        <v>46888278.359999999</v>
+      </c>
+      <c r="F84">
+        <v>0.22</v>
+      </c>
+      <c r="G84" s="2">
+        <v>3417513</v>
+      </c>
+      <c r="H84">
+        <v>13.72</v>
+      </c>
+      <c r="I84" t="s">
+        <v>559</v>
+      </c>
+      <c r="J84">
+        <v>4.6900000000000004</v>
+      </c>
+    </row>
+    <row r="85" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A85" t="s">
+        <v>710</v>
+      </c>
+      <c r="B85" t="s">
+        <v>211</v>
+      </c>
+      <c r="C85" t="s">
+        <v>711</v>
+      </c>
+      <c r="D85" t="s">
+        <v>564</v>
+      </c>
+      <c r="E85" s="2">
+        <v>46789755.520000003</v>
+      </c>
+      <c r="F85">
+        <v>0.22</v>
+      </c>
+      <c r="G85" s="2">
+        <v>1091179</v>
+      </c>
+      <c r="H85">
+        <v>42.88</v>
+      </c>
+      <c r="I85" t="s">
+        <v>559</v>
+      </c>
+      <c r="J85">
+        <v>4.68</v>
+      </c>
+    </row>
+    <row r="86" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A86" t="s">
+        <v>712</v>
+      </c>
+      <c r="B86" t="s">
+        <v>713</v>
+      </c>
+      <c r="C86" t="s">
+        <v>714</v>
+      </c>
+      <c r="D86" t="s">
+        <v>570</v>
+      </c>
+      <c r="E86" s="2">
+        <v>46015014.399999999</v>
+      </c>
+      <c r="F86">
+        <v>0.21</v>
+      </c>
+      <c r="G86" s="2">
+        <v>965080</v>
+      </c>
+      <c r="H86">
+        <v>47.68</v>
+      </c>
+      <c r="I86" t="s">
+        <v>559</v>
+      </c>
+      <c r="J86">
+        <v>4.5999999999999996</v>
+      </c>
+    </row>
+    <row r="87" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A87" t="s">
+        <v>715</v>
+      </c>
+      <c r="B87" t="s">
+        <v>255</v>
+      </c>
+      <c r="C87" t="s">
+        <v>716</v>
+      </c>
+      <c r="D87" t="s">
+        <v>575</v>
+      </c>
+      <c r="E87" s="2">
+        <v>45419962.380000003</v>
+      </c>
+      <c r="F87">
+        <v>0.21</v>
+      </c>
+      <c r="G87" s="2">
+        <v>628563</v>
+      </c>
+      <c r="H87">
+        <v>72.260000000000005</v>
+      </c>
+      <c r="I87" t="s">
+        <v>559</v>
+      </c>
+      <c r="J87">
+        <v>4.54</v>
+      </c>
+    </row>
+    <row r="88" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A88" t="s">
+        <v>717</v>
+      </c>
+      <c r="B88" t="s">
+        <v>374</v>
+      </c>
+      <c r="C88" t="s">
+        <v>718</v>
+      </c>
+      <c r="D88" t="s">
+        <v>570</v>
+      </c>
+      <c r="E88" s="2">
+        <v>44679568.32</v>
+      </c>
+      <c r="F88">
+        <v>0.21</v>
+      </c>
+      <c r="G88" s="2">
+        <v>1058256</v>
+      </c>
+      <c r="H88">
+        <v>42.22</v>
+      </c>
+      <c r="I88" t="s">
+        <v>559</v>
+      </c>
+      <c r="J88">
+        <v>4.47</v>
+      </c>
+    </row>
+    <row r="89" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A89" t="s">
+        <v>719</v>
+      </c>
+      <c r="B89" t="s">
+        <v>227</v>
+      </c>
+      <c r="C89" t="s">
+        <v>720</v>
+      </c>
+      <c r="D89" t="s">
+        <v>615</v>
+      </c>
+      <c r="E89" s="2">
+        <v>44086089.039999999</v>
+      </c>
+      <c r="F89">
+        <v>0.21</v>
+      </c>
+      <c r="G89" s="2">
+        <v>740072</v>
+      </c>
+      <c r="H89">
+        <v>59.57</v>
+      </c>
+      <c r="I89" t="s">
+        <v>559</v>
+      </c>
+      <c r="J89">
+        <v>4.41</v>
+      </c>
+    </row>
+    <row r="90" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A90" t="s">
+        <v>249</v>
+      </c>
+      <c r="B90" t="s">
+        <v>250</v>
+      </c>
+      <c r="C90" t="s">
+        <v>721</v>
+      </c>
+      <c r="D90" t="s">
+        <v>570</v>
+      </c>
+      <c r="E90" s="2">
+        <v>43733977.32</v>
+      </c>
+      <c r="F90">
+        <v>0.2</v>
+      </c>
+      <c r="G90" s="2">
+        <v>892166</v>
+      </c>
+      <c r="H90">
+        <v>49.02</v>
+      </c>
+      <c r="I90" t="s">
+        <v>559</v>
+      </c>
+      <c r="J90">
+        <v>4.37</v>
+      </c>
+    </row>
+    <row r="91" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A91" t="s">
+        <v>311</v>
+      </c>
+      <c r="B91" t="s">
+        <v>312</v>
+      </c>
+      <c r="C91" t="s">
+        <v>722</v>
+      </c>
+      <c r="D91" t="s">
+        <v>570</v>
+      </c>
+      <c r="E91" s="2">
+        <v>43107701</v>
+      </c>
+      <c r="F91">
+        <v>0.2</v>
+      </c>
+      <c r="G91" s="2">
+        <v>3758300</v>
+      </c>
+      <c r="H91">
+        <v>11.47</v>
+      </c>
+      <c r="I91" t="s">
+        <v>559</v>
+      </c>
+      <c r="J91">
+        <v>4.3099999999999996</v>
+      </c>
+    </row>
+    <row r="92" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A92" t="s">
+        <v>189</v>
+      </c>
+      <c r="B92" t="s">
+        <v>190</v>
+      </c>
+      <c r="C92" t="s">
+        <v>723</v>
+      </c>
+      <c r="D92" t="s">
+        <v>724</v>
+      </c>
+      <c r="E92" s="2">
+        <v>42479019.509999998</v>
+      </c>
+      <c r="F92">
+        <v>0.2</v>
+      </c>
+      <c r="G92" s="2">
+        <v>195243</v>
+      </c>
+      <c r="H92">
+        <v>217.57</v>
+      </c>
+      <c r="I92" t="s">
+        <v>559</v>
+      </c>
+      <c r="J92">
+        <v>4.25</v>
+      </c>
+    </row>
+    <row r="93" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A93" t="s">
+        <v>215</v>
+      </c>
+      <c r="B93" t="s">
+        <v>216</v>
+      </c>
+      <c r="C93" t="s">
+        <v>725</v>
+      </c>
+      <c r="D93" t="s">
+        <v>724</v>
+      </c>
+      <c r="E93" s="2">
+        <v>42179351.759999998</v>
+      </c>
+      <c r="F93">
+        <v>0.2</v>
+      </c>
+      <c r="G93" s="2">
+        <v>208788</v>
+      </c>
+      <c r="H93">
+        <v>202.02</v>
+      </c>
+      <c r="I93" t="s">
+        <v>559</v>
+      </c>
+      <c r="J93">
+        <v>4.22</v>
+      </c>
+    </row>
+    <row r="94" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A94" t="s">
+        <v>726</v>
+      </c>
+      <c r="B94" t="s">
+        <v>319</v>
+      </c>
+      <c r="C94" t="s">
+        <v>727</v>
+      </c>
+      <c r="D94" t="s">
+        <v>570</v>
+      </c>
+      <c r="E94" s="2">
+        <v>41691866.579999998</v>
+      </c>
+      <c r="F94">
+        <v>0.19</v>
+      </c>
+      <c r="G94" s="2">
+        <v>1094562</v>
+      </c>
+      <c r="H94">
+        <v>38.090000000000003</v>
+      </c>
+      <c r="I94" t="s">
+        <v>559</v>
+      </c>
+      <c r="J94">
+        <v>4.17</v>
+      </c>
+    </row>
+    <row r="95" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A95" t="s">
+        <v>728</v>
+      </c>
+      <c r="B95" t="s">
+        <v>729</v>
+      </c>
+      <c r="C95" t="s">
+        <v>730</v>
+      </c>
+      <c r="D95" t="s">
+        <v>597</v>
+      </c>
+      <c r="E95" s="2">
+        <v>41402627.159999996</v>
+      </c>
+      <c r="F95">
+        <v>0.19</v>
+      </c>
+      <c r="G95" s="2">
+        <v>240252</v>
+      </c>
+      <c r="H95">
+        <v>172.33</v>
+      </c>
+      <c r="I95" t="s">
+        <v>559</v>
+      </c>
+      <c r="J95">
+        <v>4.1399999999999997</v>
+      </c>
+    </row>
+    <row r="96" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A96" t="s">
+        <v>731</v>
+      </c>
+      <c r="B96" t="s">
+        <v>732</v>
+      </c>
+      <c r="C96" t="s">
+        <v>733</v>
+      </c>
+      <c r="D96" t="s">
+        <v>615</v>
+      </c>
+      <c r="E96" s="2">
+        <v>39111189.960000001</v>
+      </c>
+      <c r="F96">
+        <v>0.18</v>
+      </c>
+      <c r="G96" s="2">
+        <v>1063382</v>
+      </c>
+      <c r="H96">
+        <v>36.78</v>
+      </c>
+      <c r="I96" t="s">
+        <v>645</v>
+      </c>
+      <c r="J96">
+        <v>3.91</v>
+      </c>
+    </row>
+    <row r="97" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A97" t="s">
+        <v>734</v>
+      </c>
+      <c r="B97" t="s">
+        <v>735</v>
+      </c>
+      <c r="C97" t="s">
+        <v>736</v>
+      </c>
+      <c r="D97" t="s">
+        <v>570</v>
+      </c>
+      <c r="E97" s="2">
+        <v>38815255.409999996</v>
+      </c>
+      <c r="F97">
+        <v>0.18</v>
+      </c>
+      <c r="G97" s="2">
+        <v>6270639</v>
+      </c>
+      <c r="H97">
+        <v>6.19</v>
+      </c>
+      <c r="I97" t="s">
+        <v>559</v>
+      </c>
+      <c r="J97">
+        <v>3.88</v>
+      </c>
+    </row>
+    <row r="98" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A98" t="s">
+        <v>737</v>
+      </c>
+      <c r="B98" t="s">
+        <v>271</v>
+      </c>
+      <c r="C98" t="s">
+        <v>738</v>
+      </c>
+      <c r="D98" t="s">
+        <v>570</v>
+      </c>
+      <c r="E98" s="2">
+        <v>38112111.719999999</v>
+      </c>
+      <c r="F98">
+        <v>0.18</v>
+      </c>
+      <c r="G98" s="2">
+        <v>2968233</v>
+      </c>
+      <c r="H98">
+        <v>12.84</v>
+      </c>
+      <c r="I98" t="s">
+        <v>559</v>
+      </c>
+      <c r="J98">
+        <v>3.81</v>
+      </c>
+    </row>
+    <row r="99" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A99" t="s">
+        <v>235</v>
+      </c>
+      <c r="B99" t="s">
+        <v>236</v>
+      </c>
+      <c r="C99" t="s">
+        <v>739</v>
+      </c>
+      <c r="D99" t="s">
+        <v>564</v>
+      </c>
+      <c r="E99" s="2">
+        <v>37437979.039999999</v>
+      </c>
+      <c r="F99">
+        <v>0.17</v>
+      </c>
+      <c r="G99" s="2">
+        <v>988592</v>
+      </c>
+      <c r="H99">
+        <v>37.869999999999997</v>
+      </c>
+      <c r="I99" t="s">
+        <v>559</v>
+      </c>
+      <c r="J99">
+        <v>3.74</v>
+      </c>
+    </row>
+    <row r="100" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A100" t="s">
+        <v>740</v>
+      </c>
+      <c r="B100" t="s">
+        <v>741</v>
+      </c>
+      <c r="C100" t="s">
+        <v>742</v>
+      </c>
+      <c r="D100" t="s">
+        <v>626</v>
+      </c>
+      <c r="E100" s="2">
+        <v>37142777.789999999</v>
+      </c>
+      <c r="F100">
+        <v>0.17</v>
+      </c>
+      <c r="G100" s="2">
+        <v>731301</v>
+      </c>
+      <c r="H100">
+        <v>50.79</v>
+      </c>
+      <c r="I100" t="s">
+        <v>559</v>
+      </c>
+      <c r="J100">
+        <v>3.71</v>
+      </c>
+    </row>
+    <row r="101" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A101" t="s">
+        <v>300</v>
+      </c>
+      <c r="B101" t="s">
+        <v>301</v>
+      </c>
+      <c r="C101" t="s">
+        <v>743</v>
+      </c>
+      <c r="D101" t="s">
+        <v>564</v>
+      </c>
+      <c r="E101" s="2">
+        <v>36249370.609999999</v>
+      </c>
+      <c r="F101">
+        <v>0.17</v>
+      </c>
+      <c r="G101" s="2">
+        <v>3095591</v>
+      </c>
+      <c r="H101">
+        <v>11.71</v>
+      </c>
+      <c r="I101" t="s">
+        <v>559</v>
+      </c>
+      <c r="J101">
+        <v>3.62</v>
+      </c>
+    </row>
+    <row r="102" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A102" t="s">
+        <v>744</v>
+      </c>
+      <c r="B102" t="s">
+        <v>238</v>
+      </c>
+      <c r="C102" t="s">
+        <v>745</v>
+      </c>
+      <c r="D102" t="s">
+        <v>558</v>
+      </c>
+      <c r="E102" s="2">
+        <v>34269768</v>
+      </c>
+      <c r="F102">
+        <v>0.16</v>
+      </c>
+      <c r="G102" s="2">
+        <v>450918</v>
+      </c>
+      <c r="H102">
+        <v>76</v>
+      </c>
+      <c r="I102" t="s">
+        <v>559</v>
+      </c>
+      <c r="J102">
+        <v>3.43</v>
+      </c>
+    </row>
+    <row r="103" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A103" t="s">
+        <v>746</v>
+      </c>
+      <c r="B103" t="s">
+        <v>231</v>
+      </c>
+      <c r="C103" t="s">
+        <v>747</v>
+      </c>
+      <c r="D103" t="s">
+        <v>558</v>
+      </c>
+      <c r="E103" s="2">
+        <v>30630345.719999999</v>
+      </c>
+      <c r="F103">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="G103" s="2">
+        <v>276547</v>
+      </c>
+      <c r="H103">
+        <v>110.76</v>
+      </c>
+      <c r="I103" t="s">
+        <v>559</v>
+      </c>
+      <c r="J103">
+        <v>3.06</v>
+      </c>
+    </row>
+    <row r="104" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A104" t="s">
+        <v>748</v>
+      </c>
+      <c r="B104" t="s">
+        <v>749</v>
+      </c>
+      <c r="C104" t="s">
+        <v>750</v>
+      </c>
+      <c r="D104" t="s">
+        <v>570</v>
+      </c>
+      <c r="E104" s="2">
+        <v>30429863.75</v>
+      </c>
+      <c r="F104">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="G104" s="2">
+        <v>768625</v>
+      </c>
+      <c r="H104">
+        <v>39.590000000000003</v>
+      </c>
+      <c r="I104" t="s">
+        <v>559</v>
+      </c>
+      <c r="J104">
+        <v>3.04</v>
+      </c>
+    </row>
+    <row r="105" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A105" t="s">
+        <v>751</v>
+      </c>
+      <c r="B105" t="s">
+        <v>752</v>
+      </c>
+      <c r="C105" t="s">
+        <v>753</v>
+      </c>
+      <c r="D105" t="s">
+        <v>594</v>
+      </c>
+      <c r="E105" s="2">
+        <v>29945493.989999998</v>
+      </c>
+      <c r="F105">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="G105" s="2">
+        <v>633231</v>
+      </c>
+      <c r="H105">
+        <v>47.29</v>
+      </c>
+      <c r="I105" t="s">
+        <v>559</v>
+      </c>
+      <c r="J105">
+        <v>2.99</v>
+      </c>
+    </row>
+    <row r="106" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A106" t="s">
+        <v>754</v>
+      </c>
+      <c r="B106" t="s">
+        <v>264</v>
+      </c>
+      <c r="C106" t="s">
+        <v>755</v>
+      </c>
+      <c r="D106" t="s">
+        <v>564</v>
+      </c>
+      <c r="E106" s="2">
+        <v>29880533.760000002</v>
+      </c>
+      <c r="F106">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="G106" s="2">
+        <v>1111627</v>
+      </c>
+      <c r="H106">
+        <v>26.88</v>
+      </c>
+      <c r="I106" t="s">
+        <v>559</v>
+      </c>
+      <c r="J106">
+        <v>2.99</v>
+      </c>
+    </row>
+    <row r="107" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A107" t="s">
+        <v>386</v>
+      </c>
+      <c r="B107" t="s">
+        <v>387</v>
+      </c>
+      <c r="C107" t="s">
+        <v>756</v>
+      </c>
+      <c r="D107" t="s">
+        <v>570</v>
+      </c>
+      <c r="E107" s="2">
+        <v>29626516.100000001</v>
+      </c>
+      <c r="F107">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="G107" s="2">
+        <v>957238</v>
+      </c>
+      <c r="H107">
+        <v>30.95</v>
+      </c>
+      <c r="I107" t="s">
+        <v>559</v>
+      </c>
+      <c r="J107">
+        <v>2.96</v>
+      </c>
+    </row>
+    <row r="108" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A108" t="s">
+        <v>757</v>
+      </c>
+      <c r="B108" t="s">
+        <v>359</v>
+      </c>
+      <c r="C108" t="s">
+        <v>758</v>
+      </c>
+      <c r="D108" t="s">
+        <v>570</v>
+      </c>
+      <c r="E108" s="2">
+        <v>28859859.280000001</v>
+      </c>
+      <c r="F108">
+        <v>0.13</v>
+      </c>
+      <c r="G108" s="2">
+        <v>442568</v>
+      </c>
+      <c r="H108">
+        <v>65.209999999999994</v>
+      </c>
+      <c r="I108" t="s">
+        <v>559</v>
+      </c>
+      <c r="J108">
+        <v>2.89</v>
+      </c>
+    </row>
+    <row r="109" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A109" t="s">
+        <v>246</v>
+      </c>
+      <c r="B109" t="s">
+        <v>247</v>
+      </c>
+      <c r="C109" t="s">
+        <v>759</v>
+      </c>
+      <c r="D109" t="s">
+        <v>615</v>
+      </c>
+      <c r="E109" s="2">
+        <v>28783684.800000001</v>
+      </c>
+      <c r="F109">
+        <v>0.13</v>
+      </c>
+      <c r="G109" s="2">
+        <v>3331445</v>
+      </c>
+      <c r="H109">
+        <v>8.64</v>
+      </c>
+      <c r="I109" t="s">
+        <v>559</v>
+      </c>
+      <c r="J109">
+        <v>2.88</v>
+      </c>
+    </row>
+    <row r="110" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A110" t="s">
+        <v>760</v>
+      </c>
+      <c r="B110" t="s">
+        <v>303</v>
+      </c>
+      <c r="C110" t="s">
+        <v>761</v>
+      </c>
+      <c r="D110" t="s">
+        <v>575</v>
+      </c>
+      <c r="E110" s="2">
+        <v>28554704</v>
+      </c>
+      <c r="F110">
+        <v>0.13</v>
+      </c>
+      <c r="G110" s="2">
+        <v>128048</v>
+      </c>
+      <c r="H110">
+        <v>223</v>
+      </c>
+      <c r="I110" t="s">
+        <v>559</v>
+      </c>
+      <c r="J110">
+        <v>2.86</v>
+      </c>
+    </row>
+    <row r="111" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A111" t="s">
+        <v>762</v>
+      </c>
+      <c r="B111" t="s">
+        <v>763</v>
+      </c>
+      <c r="C111" t="s">
+        <v>764</v>
+      </c>
+      <c r="D111" t="s">
+        <v>765</v>
+      </c>
+      <c r="E111" s="2">
+        <v>28270778.850000001</v>
+      </c>
+      <c r="F111">
+        <v>0.13</v>
+      </c>
+      <c r="G111" s="2">
+        <v>1375707</v>
+      </c>
+      <c r="H111">
+        <v>20.55</v>
+      </c>
+      <c r="I111" t="s">
+        <v>559</v>
+      </c>
+      <c r="J111">
+        <v>2.83</v>
+      </c>
+    </row>
+    <row r="112" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A112" t="s">
+        <v>766</v>
+      </c>
+      <c r="B112" t="s">
+        <v>767</v>
+      </c>
+      <c r="C112" t="s">
+        <v>768</v>
+      </c>
+      <c r="D112" t="s">
+        <v>724</v>
+      </c>
+      <c r="E112" s="2">
+        <v>28039685.309999999</v>
+      </c>
+      <c r="F112">
+        <v>0.13</v>
+      </c>
+      <c r="G112" s="2">
+        <v>743561</v>
+      </c>
+      <c r="H112">
+        <v>37.71</v>
+      </c>
+      <c r="I112" t="s">
+        <v>559</v>
+      </c>
+      <c r="J112">
+        <v>2.8</v>
+      </c>
+    </row>
+    <row r="113" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A113" t="s">
+        <v>769</v>
+      </c>
+      <c r="B113" t="s">
+        <v>244</v>
+      </c>
+      <c r="C113" t="s">
+        <v>770</v>
+      </c>
+      <c r="D113" t="s">
+        <v>575</v>
+      </c>
+      <c r="E113" s="2">
+        <v>27146161.079999998</v>
+      </c>
+      <c r="F113">
+        <v>0.13</v>
+      </c>
+      <c r="G113" s="2">
+        <v>1409458</v>
+      </c>
+      <c r="H113">
+        <v>19.260000000000002</v>
+      </c>
+      <c r="I113" t="s">
+        <v>559</v>
+      </c>
+      <c r="J113">
+        <v>2.71</v>
+      </c>
+    </row>
+    <row r="114" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A114" t="s">
+        <v>771</v>
+      </c>
+      <c r="B114" t="s">
+        <v>384</v>
+      </c>
+      <c r="C114" t="s">
+        <v>772</v>
+      </c>
+      <c r="D114" t="s">
+        <v>570</v>
+      </c>
+      <c r="E114" s="2">
+        <v>26510206.800000001</v>
+      </c>
+      <c r="F114">
+        <v>0.12</v>
+      </c>
+      <c r="G114" s="2">
+        <v>1147628</v>
+      </c>
+      <c r="H114">
+        <v>23.1</v>
+      </c>
+      <c r="I114" t="s">
+        <v>559</v>
+      </c>
+      <c r="J114">
+        <v>2.65</v>
+      </c>
+    </row>
+    <row r="115" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A115" t="s">
+        <v>773</v>
+      </c>
+      <c r="B115" t="s">
+        <v>774</v>
+      </c>
+      <c r="C115" t="s">
+        <v>775</v>
+      </c>
+      <c r="D115" t="s">
+        <v>724</v>
+      </c>
+      <c r="E115" s="2">
+        <v>26059446.960000001</v>
+      </c>
+      <c r="F115">
+        <v>0.12</v>
+      </c>
+      <c r="G115" s="2">
+        <v>1398039</v>
+      </c>
+      <c r="H115">
+        <v>18.64</v>
+      </c>
+      <c r="I115" t="s">
+        <v>559</v>
+      </c>
+      <c r="J115">
+        <v>2.61</v>
+      </c>
+    </row>
+    <row r="116" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A116" t="s">
+        <v>776</v>
+      </c>
+      <c r="B116" t="s">
+        <v>229</v>
+      </c>
+      <c r="C116" t="s">
+        <v>777</v>
+      </c>
+      <c r="D116" t="s">
+        <v>615</v>
+      </c>
+      <c r="E116" s="2">
+        <v>26000255.120000001</v>
+      </c>
+      <c r="F116">
+        <v>0.12</v>
+      </c>
+      <c r="G116" s="2">
+        <v>614954</v>
+      </c>
+      <c r="H116">
+        <v>42.28</v>
+      </c>
+      <c r="I116" t="s">
+        <v>559</v>
+      </c>
+      <c r="J116">
+        <v>2.6</v>
+      </c>
+    </row>
+    <row r="117" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A117" t="s">
+        <v>778</v>
+      </c>
+      <c r="B117" t="s">
+        <v>456</v>
+      </c>
+      <c r="C117" t="s">
+        <v>779</v>
+      </c>
+      <c r="D117" t="s">
+        <v>570</v>
+      </c>
+      <c r="E117" s="2">
+        <v>25949450.239999998</v>
+      </c>
+      <c r="F117">
+        <v>0.12</v>
+      </c>
+      <c r="G117" s="2">
+        <v>2989568</v>
+      </c>
+      <c r="H117">
+        <v>8.68</v>
+      </c>
+      <c r="I117" t="s">
+        <v>559</v>
+      </c>
+      <c r="J117">
+        <v>2.59</v>
+      </c>
+    </row>
+    <row r="118" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A118" t="s">
+        <v>780</v>
+      </c>
+      <c r="B118" t="s">
+        <v>266</v>
+      </c>
+      <c r="C118" t="s">
+        <v>781</v>
+      </c>
+      <c r="D118" t="s">
+        <v>561</v>
+      </c>
+      <c r="E118" s="2">
+        <v>23850693.899999999</v>
+      </c>
+      <c r="F118">
+        <v>0.11</v>
+      </c>
+      <c r="G118" s="2">
+        <v>134590</v>
+      </c>
+      <c r="H118">
+        <v>177.21</v>
+      </c>
+      <c r="I118" t="s">
+        <v>559</v>
+      </c>
+      <c r="J118">
+        <v>2.39</v>
+      </c>
+    </row>
+    <row r="119" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A119" t="s">
+        <v>782</v>
+      </c>
+      <c r="B119" t="s">
+        <v>203</v>
+      </c>
+      <c r="C119" t="s">
+        <v>783</v>
+      </c>
+      <c r="D119" t="s">
+        <v>558</v>
+      </c>
+      <c r="E119" s="2">
+        <v>23770221.600000001</v>
+      </c>
+      <c r="F119">
+        <v>0.11</v>
+      </c>
+      <c r="G119" s="2">
+        <v>379716</v>
+      </c>
+      <c r="H119">
+        <v>62.6</v>
+      </c>
+      <c r="I119" t="s">
+        <v>559</v>
+      </c>
+      <c r="J119">
+        <v>2.38</v>
+      </c>
+    </row>
+    <row r="120" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A120" t="s">
+        <v>784</v>
+      </c>
+      <c r="B120" t="s">
+        <v>785</v>
+      </c>
+      <c r="C120" t="s">
+        <v>786</v>
+      </c>
+      <c r="D120" t="s">
+        <v>724</v>
+      </c>
+      <c r="E120" s="2">
+        <v>23494685.760000002</v>
+      </c>
+      <c r="F120">
+        <v>0.11</v>
+      </c>
+      <c r="G120" s="2">
+        <v>287784</v>
+      </c>
+      <c r="H120">
+        <v>81.64</v>
+      </c>
+      <c r="I120" t="s">
+        <v>559</v>
+      </c>
+      <c r="J120">
+        <v>2.35</v>
+      </c>
+    </row>
+    <row r="121" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A121" t="s">
+        <v>787</v>
+      </c>
+      <c r="B121" t="s">
+        <v>788</v>
+      </c>
+      <c r="C121" t="s">
+        <v>789</v>
+      </c>
+      <c r="D121" t="s">
+        <v>570</v>
+      </c>
+      <c r="E121" s="2">
+        <v>23473689.120000001</v>
+      </c>
+      <c r="F121">
+        <v>0.11</v>
+      </c>
+      <c r="G121" s="2">
+        <v>1210608</v>
+      </c>
+      <c r="H121">
+        <v>19.39</v>
+      </c>
+      <c r="I121" t="s">
+        <v>559</v>
+      </c>
+      <c r="J121">
+        <v>2.35</v>
+      </c>
+    </row>
+    <row r="122" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A122" t="s">
+        <v>224</v>
+      </c>
+      <c r="B122" t="s">
+        <v>225</v>
+      </c>
+      <c r="C122" t="s">
+        <v>790</v>
+      </c>
+      <c r="D122" t="s">
+        <v>570</v>
+      </c>
+      <c r="E122" s="2">
+        <v>22860686.399999999</v>
+      </c>
+      <c r="F122">
+        <v>0.11</v>
+      </c>
+      <c r="G122" s="2">
+        <v>269520</v>
+      </c>
+      <c r="H122">
+        <v>84.82</v>
+      </c>
+      <c r="I122" t="s">
+        <v>559</v>
+      </c>
+      <c r="J122">
+        <v>2.29</v>
+      </c>
+    </row>
+    <row r="123" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A123" t="s">
+        <v>791</v>
+      </c>
+      <c r="B123" t="s">
+        <v>317</v>
+      </c>
+      <c r="C123" t="s">
+        <v>792</v>
+      </c>
+      <c r="D123" t="s">
+        <v>570</v>
+      </c>
+      <c r="E123" s="2">
+        <v>22786238</v>
+      </c>
+      <c r="F123">
+        <v>0.11</v>
+      </c>
+      <c r="G123" s="2">
+        <v>261400</v>
+      </c>
+      <c r="H123">
+        <v>87.17</v>
+      </c>
+      <c r="I123" t="s">
+        <v>559</v>
+      </c>
+      <c r="J123">
+        <v>2.2799999999999998</v>
+      </c>
+    </row>
+    <row r="124" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A124" t="s">
+        <v>793</v>
+      </c>
+      <c r="B124" t="s">
+        <v>794</v>
+      </c>
+      <c r="C124" t="s">
+        <v>795</v>
+      </c>
+      <c r="D124" t="s">
+        <v>615</v>
+      </c>
+      <c r="E124" s="2">
+        <v>21679184.199999999</v>
+      </c>
+      <c r="F124">
+        <v>0.1</v>
+      </c>
+      <c r="G124" s="2">
+        <v>1251685</v>
+      </c>
+      <c r="H124">
+        <v>17.32</v>
+      </c>
+      <c r="I124" t="s">
+        <v>559</v>
+      </c>
+      <c r="J124">
+        <v>2.17</v>
+      </c>
+    </row>
+    <row r="125" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A125" t="s">
+        <v>796</v>
+      </c>
+      <c r="B125" t="s">
+        <v>280</v>
+      </c>
+      <c r="C125" t="s">
+        <v>797</v>
+      </c>
+      <c r="D125" t="s">
+        <v>615</v>
+      </c>
+      <c r="E125" s="2">
+        <v>21378922.739999998</v>
+      </c>
+      <c r="F125">
+        <v>0.1</v>
+      </c>
+      <c r="G125" s="2">
+        <v>1241517</v>
+      </c>
+      <c r="H125">
+        <v>17.22</v>
+      </c>
+      <c r="I125" t="s">
+        <v>559</v>
+      </c>
+      <c r="J125">
+        <v>2.14</v>
+      </c>
+    </row>
+    <row r="126" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A126" t="s">
+        <v>798</v>
+      </c>
+      <c r="B126" t="s">
+        <v>799</v>
+      </c>
+      <c r="C126" t="s">
+        <v>800</v>
+      </c>
+      <c r="D126" t="s">
+        <v>564</v>
+      </c>
+      <c r="E126" s="2">
+        <v>20964278.879999999</v>
+      </c>
+      <c r="F126">
+        <v>0.1</v>
+      </c>
+      <c r="G126" s="2">
+        <v>1088488</v>
+      </c>
+      <c r="H126">
+        <v>19.260000000000002</v>
+      </c>
+      <c r="I126" t="s">
+        <v>559</v>
+      </c>
+      <c r="J126">
+        <v>2.1</v>
+      </c>
+    </row>
+    <row r="127" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A127" t="s">
+        <v>801</v>
+      </c>
+      <c r="B127" t="s">
+        <v>802</v>
+      </c>
+      <c r="C127" t="s">
+        <v>803</v>
+      </c>
+      <c r="D127" t="s">
+        <v>570</v>
+      </c>
+      <c r="E127" s="2">
+        <v>20890346.359999999</v>
+      </c>
+      <c r="F127">
+        <v>0.1</v>
+      </c>
+      <c r="G127" s="2">
+        <v>968042</v>
+      </c>
+      <c r="H127">
+        <v>21.58</v>
+      </c>
+      <c r="I127" t="s">
+        <v>559</v>
+      </c>
+      <c r="J127">
+        <v>2.09</v>
+      </c>
+    </row>
+    <row r="128" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A128" t="s">
+        <v>804</v>
+      </c>
+      <c r="B128" t="s">
+        <v>330</v>
+      </c>
+      <c r="C128" t="s">
+        <v>805</v>
+      </c>
+      <c r="D128" t="s">
+        <v>564</v>
+      </c>
+      <c r="E128" s="2">
+        <v>20683285.140000001</v>
+      </c>
+      <c r="F128">
+        <v>0.1</v>
+      </c>
+      <c r="G128" s="2">
+        <v>950082</v>
+      </c>
+      <c r="H128">
+        <v>21.77</v>
+      </c>
+      <c r="I128" t="s">
+        <v>559</v>
+      </c>
+      <c r="J128">
+        <v>2.0699999999999998</v>
+      </c>
+    </row>
+    <row r="129" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A129" t="s">
+        <v>806</v>
+      </c>
+      <c r="B129" t="s">
+        <v>337</v>
+      </c>
+      <c r="C129" t="s">
+        <v>807</v>
+      </c>
+      <c r="D129" t="s">
+        <v>594</v>
+      </c>
+      <c r="E129" s="2">
+        <v>19531442</v>
+      </c>
+      <c r="F129">
+        <v>0.09</v>
+      </c>
+      <c r="G129" s="2">
+        <v>192428</v>
+      </c>
+      <c r="H129">
+        <v>101.5</v>
+      </c>
+      <c r="I129" t="s">
+        <v>559</v>
+      </c>
+      <c r="J129">
+        <v>1.95</v>
+      </c>
+    </row>
+    <row r="130" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A130" t="s">
+        <v>808</v>
+      </c>
+      <c r="B130" t="s">
+        <v>355</v>
+      </c>
+      <c r="C130" t="s">
+        <v>809</v>
+      </c>
+      <c r="D130" t="s">
+        <v>564</v>
+      </c>
+      <c r="E130" s="2">
+        <v>19459193.800000001</v>
+      </c>
+      <c r="F130">
+        <v>0.09</v>
+      </c>
+      <c r="G130" s="2">
+        <v>781180</v>
+      </c>
+      <c r="H130">
+        <v>24.91</v>
+      </c>
+      <c r="I130" t="s">
+        <v>559</v>
+      </c>
+      <c r="J130">
+        <v>1.95</v>
+      </c>
+    </row>
+    <row r="131" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A131" t="s">
+        <v>810</v>
+      </c>
+      <c r="B131" t="s">
+        <v>811</v>
+      </c>
+      <c r="C131" t="s">
+        <v>812</v>
+      </c>
+      <c r="D131" t="s">
+        <v>570</v>
+      </c>
+      <c r="E131" s="2">
+        <v>19380693.149999999</v>
+      </c>
+      <c r="F131">
+        <v>0.09</v>
+      </c>
+      <c r="G131" s="2">
+        <v>1464905</v>
+      </c>
+      <c r="H131">
+        <v>13.23</v>
+      </c>
+      <c r="I131" t="s">
+        <v>559</v>
+      </c>
+      <c r="J131">
+        <v>1.94</v>
+      </c>
+    </row>
+    <row r="132" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A132" t="s">
+        <v>813</v>
+      </c>
+      <c r="B132" t="s">
+        <v>814</v>
+      </c>
+      <c r="C132" t="s">
+        <v>815</v>
+      </c>
+      <c r="D132" t="s">
+        <v>724</v>
+      </c>
+      <c r="E132" s="2">
+        <v>19315866.600000001</v>
+      </c>
+      <c r="F132">
+        <v>0.09</v>
+      </c>
+      <c r="G132" s="2">
+        <v>1008135</v>
+      </c>
+      <c r="H132">
+        <v>19.16</v>
+      </c>
+      <c r="I132" t="s">
+        <v>559</v>
+      </c>
+      <c r="J132">
+        <v>1.93</v>
+      </c>
+    </row>
+    <row r="133" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A133" t="s">
+        <v>816</v>
+      </c>
+      <c r="B133" t="s">
+        <v>389</v>
+      </c>
+      <c r="C133" t="s">
+        <v>817</v>
+      </c>
+      <c r="D133" t="s">
+        <v>575</v>
+      </c>
+      <c r="E133" s="2">
+        <v>19253086.84</v>
+      </c>
+      <c r="F133">
+        <v>0.09</v>
+      </c>
+      <c r="G133" s="2">
+        <v>229258</v>
+      </c>
+      <c r="H133">
+        <v>83.98</v>
+      </c>
+      <c r="I133" t="s">
+        <v>559</v>
+      </c>
+      <c r="J133">
+        <v>1.93</v>
+      </c>
+    </row>
+    <row r="134" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A134" t="s">
+        <v>818</v>
+      </c>
+      <c r="B134" t="s">
+        <v>819</v>
+      </c>
+      <c r="C134" t="s">
+        <v>820</v>
+      </c>
+      <c r="D134" t="s">
+        <v>724</v>
+      </c>
+      <c r="E134" s="2">
+        <v>19251103.489999998</v>
+      </c>
+      <c r="F134">
+        <v>0.09</v>
+      </c>
+      <c r="G134" s="2">
+        <v>1294627</v>
+      </c>
+      <c r="H134">
+        <v>14.87</v>
+      </c>
+      <c r="I134" t="s">
+        <v>559</v>
+      </c>
+      <c r="J134">
+        <v>1.93</v>
+      </c>
+    </row>
+    <row r="135" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A135" t="s">
+        <v>821</v>
+      </c>
+      <c r="B135" t="s">
+        <v>822</v>
+      </c>
+      <c r="C135" t="s">
+        <v>823</v>
+      </c>
+      <c r="D135" t="s">
+        <v>615</v>
+      </c>
+      <c r="E135" s="2">
+        <v>19005606.84</v>
+      </c>
+      <c r="F135">
+        <v>0.09</v>
+      </c>
+      <c r="G135" s="2">
+        <v>342012</v>
+      </c>
+      <c r="H135">
+        <v>55.57</v>
+      </c>
+      <c r="I135" t="s">
+        <v>559</v>
+      </c>
+      <c r="J135">
+        <v>1.9</v>
+      </c>
+    </row>
+    <row r="136" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A136" t="s">
+        <v>824</v>
+      </c>
+      <c r="B136" t="s">
+        <v>825</v>
+      </c>
+      <c r="C136" t="s">
+        <v>826</v>
+      </c>
+      <c r="D136" t="s">
+        <v>570</v>
+      </c>
+      <c r="E136" s="2">
+        <v>18561443.68</v>
+      </c>
+      <c r="F136">
+        <v>0.09</v>
+      </c>
+      <c r="G136" s="2">
+        <v>964732</v>
+      </c>
+      <c r="H136">
+        <v>19.239999999999998</v>
+      </c>
+      <c r="I136" t="s">
+        <v>559</v>
+      </c>
+      <c r="J136">
+        <v>1.86</v>
+      </c>
+    </row>
+    <row r="137" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A137" t="s">
+        <v>517</v>
+      </c>
+      <c r="B137" t="s">
+        <v>518</v>
+      </c>
+      <c r="C137" t="s">
+        <v>827</v>
+      </c>
+      <c r="D137" t="s">
+        <v>570</v>
+      </c>
+      <c r="E137" s="2">
+        <v>18158522.460000001</v>
+      </c>
+      <c r="F137">
+        <v>0.08</v>
+      </c>
+      <c r="G137" s="2">
+        <v>1369421</v>
+      </c>
+      <c r="H137">
+        <v>13.26</v>
+      </c>
+      <c r="I137" t="s">
+        <v>559</v>
+      </c>
+      <c r="J137">
+        <v>1.82</v>
+      </c>
+    </row>
+    <row r="138" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A138" t="s">
+        <v>828</v>
+      </c>
+      <c r="B138" t="s">
+        <v>445</v>
+      </c>
+      <c r="C138" t="s">
+        <v>829</v>
+      </c>
+      <c r="D138" t="s">
+        <v>564</v>
+      </c>
+      <c r="E138" s="2">
+        <v>17707517.780000001</v>
+      </c>
+      <c r="F138">
+        <v>0.08</v>
+      </c>
+      <c r="G138" s="2">
+        <v>2383246</v>
+      </c>
+      <c r="H138">
+        <v>7.43</v>
+      </c>
+      <c r="I138" t="s">
+        <v>559</v>
+      </c>
+      <c r="J138">
+        <v>1.77</v>
+      </c>
+    </row>
+    <row r="139" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A139" t="s">
+        <v>830</v>
+      </c>
+      <c r="B139" t="s">
+        <v>831</v>
+      </c>
+      <c r="C139" t="s">
+        <v>832</v>
+      </c>
+      <c r="D139" t="s">
+        <v>570</v>
+      </c>
+      <c r="E139" s="2">
+        <v>17494641.370000001</v>
+      </c>
+      <c r="F139">
+        <v>0.08</v>
+      </c>
+      <c r="G139" s="2">
+        <v>1376447</v>
+      </c>
+      <c r="H139">
+        <v>12.71</v>
+      </c>
+      <c r="I139" t="s">
+        <v>559</v>
+      </c>
+      <c r="J139">
+        <v>1.75</v>
+      </c>
+    </row>
+    <row r="140" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A140" t="s">
+        <v>485</v>
+      </c>
+      <c r="B140" t="s">
+        <v>486</v>
+      </c>
+      <c r="C140" t="s">
+        <v>833</v>
+      </c>
+      <c r="D140" t="s">
+        <v>570</v>
+      </c>
+      <c r="E140" s="2">
+        <v>17358599.16</v>
+      </c>
+      <c r="F140">
+        <v>0.08</v>
+      </c>
+      <c r="G140" s="2">
+        <v>541779</v>
+      </c>
+      <c r="H140">
+        <v>32.04</v>
+      </c>
+      <c r="I140" t="s">
+        <v>559</v>
+      </c>
+      <c r="J140">
+        <v>1.74</v>
+      </c>
+    </row>
+    <row r="141" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A141" t="s">
+        <v>458</v>
+      </c>
+      <c r="B141" t="s">
+        <v>459</v>
+      </c>
+      <c r="C141" t="s">
+        <v>834</v>
+      </c>
+      <c r="D141" t="s">
+        <v>570</v>
+      </c>
+      <c r="E141" s="2">
+        <v>17352227.199999999</v>
+      </c>
+      <c r="F141">
+        <v>0.08</v>
+      </c>
+      <c r="G141" s="2">
+        <v>492961</v>
+      </c>
+      <c r="H141">
+        <v>35.200000000000003</v>
+      </c>
+      <c r="I141" t="s">
+        <v>559</v>
+      </c>
+      <c r="J141">
+        <v>1.74</v>
+      </c>
+    </row>
+    <row r="142" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A142" t="s">
+        <v>835</v>
+      </c>
+      <c r="B142" t="s">
+        <v>836</v>
+      </c>
+      <c r="C142" t="s">
+        <v>837</v>
+      </c>
+      <c r="D142" t="s">
+        <v>724</v>
+      </c>
+      <c r="E142" s="2">
+        <v>17126065.289999999</v>
+      </c>
+      <c r="F142">
+        <v>0.08</v>
+      </c>
+      <c r="G142" s="2">
+        <v>1355983</v>
+      </c>
+      <c r="H142">
+        <v>12.63</v>
+      </c>
+      <c r="I142" t="s">
+        <v>559</v>
+      </c>
+      <c r="J142">
+        <v>1.71</v>
+      </c>
+    </row>
+    <row r="143" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A143" t="s">
+        <v>838</v>
+      </c>
+      <c r="B143" t="s">
+        <v>839</v>
+      </c>
+      <c r="C143" t="s">
+        <v>840</v>
+      </c>
+      <c r="D143" t="s">
+        <v>570</v>
+      </c>
+      <c r="E143" s="2">
+        <v>16923020.800000001</v>
+      </c>
+      <c r="F143">
+        <v>0.08</v>
+      </c>
+      <c r="G143" s="2">
+        <v>315728</v>
+      </c>
+      <c r="H143">
+        <v>53.6</v>
+      </c>
+      <c r="I143" t="s">
+        <v>559</v>
+      </c>
+      <c r="J143">
+        <v>1.69</v>
+      </c>
+    </row>
+    <row r="144" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A144" t="s">
+        <v>841</v>
+      </c>
+      <c r="B144" t="s">
+        <v>412</v>
+      </c>
+      <c r="C144" t="s">
+        <v>842</v>
+      </c>
+      <c r="D144" t="s">
+        <v>570</v>
+      </c>
+      <c r="E144" s="2">
+        <v>16771912.92</v>
+      </c>
+      <c r="F144">
+        <v>0.08</v>
+      </c>
+      <c r="G144" s="2">
+        <v>721683</v>
+      </c>
+      <c r="H144">
+        <v>23.24</v>
+      </c>
+      <c r="I144" t="s">
+        <v>559</v>
+      </c>
+      <c r="J144">
+        <v>1.68</v>
+      </c>
+    </row>
+    <row r="145" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A145" t="s">
+        <v>843</v>
+      </c>
+      <c r="B145" t="s">
+        <v>844</v>
+      </c>
+      <c r="C145" t="s">
+        <v>845</v>
+      </c>
+      <c r="D145" t="s">
+        <v>597</v>
+      </c>
+      <c r="E145" s="2">
+        <v>16261106.720000001</v>
+      </c>
+      <c r="F145">
+        <v>0.08</v>
+      </c>
+      <c r="G145" s="2">
+        <v>165188</v>
+      </c>
+      <c r="H145">
+        <v>98.44</v>
+      </c>
+      <c r="I145" t="s">
+        <v>559</v>
+      </c>
+      <c r="J145">
+        <v>1.63</v>
+      </c>
+    </row>
+    <row r="146" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A146" t="s">
+        <v>846</v>
+      </c>
+      <c r="B146" t="s">
+        <v>419</v>
+      </c>
+      <c r="C146" t="s">
+        <v>847</v>
+      </c>
+      <c r="D146" t="s">
+        <v>564</v>
+      </c>
+      <c r="E146" s="2">
+        <v>16001943.6</v>
+      </c>
+      <c r="F146">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="G146" s="2">
+        <v>2353227</v>
+      </c>
+      <c r="H146">
+        <v>6.8</v>
+      </c>
+      <c r="I146" t="s">
+        <v>559</v>
+      </c>
+      <c r="J146">
+        <v>1.6</v>
+      </c>
+    </row>
+    <row r="147" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A147" t="s">
+        <v>848</v>
+      </c>
+      <c r="B147" t="s">
+        <v>849</v>
+      </c>
+      <c r="C147" t="s">
+        <v>850</v>
+      </c>
+      <c r="D147" t="s">
+        <v>570</v>
+      </c>
+      <c r="E147" s="2">
+        <v>15882321.779999999</v>
+      </c>
+      <c r="F147">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="G147" s="2">
+        <v>610389</v>
+      </c>
+      <c r="H147">
+        <v>26.02</v>
+      </c>
+      <c r="I147" t="s">
+        <v>559</v>
+      </c>
+      <c r="J147">
+        <v>1.59</v>
+      </c>
+    </row>
+    <row r="148" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A148" t="s">
+        <v>851</v>
+      </c>
+      <c r="B148" t="s">
+        <v>852</v>
+      </c>
+      <c r="C148" t="s">
+        <v>853</v>
+      </c>
+      <c r="D148" t="s">
+        <v>724</v>
+      </c>
+      <c r="E148" s="2">
+        <v>15791596.199999999</v>
+      </c>
+      <c r="F148">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="G148" s="2">
+        <v>614220</v>
+      </c>
+      <c r="H148">
+        <v>25.71</v>
+      </c>
+      <c r="I148" t="s">
+        <v>559</v>
+      </c>
+      <c r="J148">
+        <v>1.58</v>
+      </c>
+    </row>
+    <row r="149" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A149" t="s">
+        <v>854</v>
+      </c>
+      <c r="B149" t="s">
+        <v>347</v>
+      </c>
+      <c r="C149" t="s">
+        <v>855</v>
+      </c>
+      <c r="D149" t="s">
+        <v>597</v>
+      </c>
+      <c r="E149" s="2">
+        <v>15653128</v>
+      </c>
+      <c r="F149">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="G149" s="2">
+        <v>184480</v>
+      </c>
+      <c r="H149">
+        <v>84.85</v>
+      </c>
+      <c r="I149" t="s">
+        <v>559</v>
+      </c>
+      <c r="J149">
+        <v>1.57</v>
+      </c>
+    </row>
+    <row r="150" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A150" t="s">
+        <v>371</v>
+      </c>
+      <c r="B150" t="s">
+        <v>372</v>
+      </c>
+      <c r="C150" t="s">
+        <v>856</v>
+      </c>
+      <c r="D150" t="s">
+        <v>561</v>
+      </c>
+      <c r="E150" s="2">
+        <v>15574199.58</v>
+      </c>
+      <c r="F150">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="G150" s="2">
+        <v>2582786</v>
+      </c>
+      <c r="H150">
+        <v>6.03</v>
+      </c>
+      <c r="I150" t="s">
+        <v>559</v>
+      </c>
+      <c r="J150">
+        <v>1.56</v>
+      </c>
+    </row>
+    <row r="151" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A151" t="s">
+        <v>857</v>
+      </c>
+      <c r="B151" t="s">
+        <v>858</v>
+      </c>
+      <c r="C151" t="s">
+        <v>859</v>
+      </c>
+      <c r="D151" t="s">
+        <v>570</v>
+      </c>
+      <c r="E151" s="2">
+        <v>15565665.48</v>
+      </c>
+      <c r="F151">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="G151" s="2">
+        <v>397286</v>
+      </c>
+      <c r="H151">
+        <v>39.18</v>
+      </c>
+      <c r="I151" t="s">
+        <v>559</v>
+      </c>
+      <c r="J151">
+        <v>1.56</v>
+      </c>
+    </row>
+    <row r="152" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A152" t="s">
+        <v>257</v>
+      </c>
+      <c r="B152" t="s">
+        <v>258</v>
+      </c>
+      <c r="C152" t="s">
+        <v>860</v>
+      </c>
+      <c r="D152" t="s">
+        <v>570</v>
+      </c>
+      <c r="E152" s="2">
+        <v>15217840.18</v>
+      </c>
+      <c r="F152">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="G152" s="2">
+        <v>333871</v>
+      </c>
+      <c r="H152">
+        <v>45.58</v>
+      </c>
+      <c r="I152" t="s">
+        <v>559</v>
+      </c>
+      <c r="J152">
+        <v>1.52</v>
+      </c>
+    </row>
+    <row r="153" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A153" t="s">
+        <v>861</v>
+      </c>
+      <c r="B153" t="s">
+        <v>376</v>
+      </c>
+      <c r="C153" t="s">
+        <v>862</v>
+      </c>
+      <c r="D153" t="s">
+        <v>564</v>
+      </c>
+      <c r="E153" s="2">
+        <v>14872363.5</v>
+      </c>
+      <c r="F153">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="G153" s="2">
+        <v>862166</v>
+      </c>
+      <c r="H153">
+        <v>17.25</v>
+      </c>
+      <c r="I153" t="s">
+        <v>559</v>
+      </c>
+      <c r="J153">
+        <v>1.49</v>
+      </c>
+    </row>
+    <row r="154" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A154" t="s">
+        <v>342</v>
+      </c>
+      <c r="B154" t="s">
+        <v>343</v>
+      </c>
+      <c r="C154" t="s">
+        <v>863</v>
+      </c>
+      <c r="D154" t="s">
+        <v>575</v>
+      </c>
+      <c r="E154" s="2">
+        <v>14814387</v>
+      </c>
+      <c r="F154">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="G154" s="2">
+        <v>389340</v>
+      </c>
+      <c r="H154">
+        <v>38.049999999999997</v>
+      </c>
+      <c r="I154" t="s">
+        <v>559</v>
+      </c>
+      <c r="J154">
+        <v>1.48</v>
+      </c>
+    </row>
+    <row r="155" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A155" t="s">
+        <v>864</v>
+      </c>
+      <c r="B155" t="s">
+        <v>335</v>
+      </c>
+      <c r="C155" t="s">
+        <v>865</v>
+      </c>
+      <c r="D155" t="s">
+        <v>564</v>
+      </c>
+      <c r="E155" s="2">
+        <v>14516977.640000001</v>
+      </c>
+      <c r="F155">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="G155" s="2">
+        <v>540871</v>
+      </c>
+      <c r="H155">
+        <v>26.84</v>
+      </c>
+      <c r="I155" t="s">
+        <v>559</v>
+      </c>
+      <c r="J155">
+        <v>1.45</v>
+      </c>
+    </row>
+    <row r="156" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A156" t="s">
+        <v>866</v>
+      </c>
+      <c r="B156" t="s">
+        <v>382</v>
+      </c>
+      <c r="C156" t="s">
+        <v>867</v>
+      </c>
+      <c r="D156" t="s">
+        <v>575</v>
+      </c>
+      <c r="E156" s="2">
+        <v>14480035.68</v>
+      </c>
+      <c r="F156">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="G156" s="2">
+        <v>589578</v>
+      </c>
+      <c r="H156">
+        <v>24.56</v>
+      </c>
+      <c r="I156" t="s">
+        <v>559</v>
+      </c>
+      <c r="J156">
+        <v>1.45</v>
+      </c>
+    </row>
+    <row r="157" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A157" t="s">
+        <v>868</v>
+      </c>
+      <c r="B157" t="s">
+        <v>869</v>
+      </c>
+      <c r="C157" t="s">
+        <v>870</v>
+      </c>
+      <c r="D157" t="s">
+        <v>564</v>
+      </c>
+      <c r="E157" s="2">
+        <v>14021055</v>
+      </c>
+      <c r="F157">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="G157" s="2">
+        <v>3960750</v>
+      </c>
+      <c r="H157">
+        <v>3.54</v>
+      </c>
+      <c r="I157" t="s">
+        <v>559</v>
+      </c>
+      <c r="J157">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="158" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A158" t="s">
+        <v>871</v>
+      </c>
+      <c r="B158" t="s">
+        <v>397</v>
+      </c>
+      <c r="C158" t="s">
+        <v>872</v>
+      </c>
+      <c r="D158" t="s">
+        <v>564</v>
+      </c>
+      <c r="E158" s="2">
+        <v>13564643.439999999</v>
+      </c>
+      <c r="F158">
+        <v>0.06</v>
+      </c>
+      <c r="G158" s="2">
+        <v>772474</v>
+      </c>
+      <c r="H158">
+        <v>17.559999999999999</v>
+      </c>
+      <c r="I158" t="s">
+        <v>559</v>
+      </c>
+      <c r="J158">
+        <v>1.36</v>
+      </c>
+    </row>
+    <row r="159" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A159" t="s">
+        <v>480</v>
+      </c>
+      <c r="B159" t="s">
+        <v>481</v>
+      </c>
+      <c r="C159" t="s">
+        <v>873</v>
+      </c>
+      <c r="D159" t="s">
+        <v>564</v>
+      </c>
+      <c r="E159" s="2">
+        <v>13338102.42</v>
+      </c>
+      <c r="F159">
+        <v>0.06</v>
+      </c>
+      <c r="G159" s="2">
+        <v>3183318</v>
+      </c>
+      <c r="H159">
+        <v>4.1900000000000004</v>
+      </c>
+      <c r="I159" t="s">
+        <v>559</v>
+      </c>
+      <c r="J159">
+        <v>1.33</v>
+      </c>
+    </row>
+    <row r="160" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A160" t="s">
+        <v>463</v>
+      </c>
+      <c r="B160" t="s">
+        <v>464</v>
+      </c>
+      <c r="C160" t="s">
+        <v>874</v>
+      </c>
+      <c r="D160" t="s">
+        <v>558</v>
+      </c>
+      <c r="E160" s="2">
+        <v>13248908.16</v>
+      </c>
+      <c r="F160">
+        <v>0.06</v>
+      </c>
+      <c r="G160" s="2">
+        <v>101852</v>
+      </c>
+      <c r="H160">
+        <v>130.08000000000001</v>
+      </c>
+      <c r="I160" t="s">
+        <v>559</v>
+      </c>
+      <c r="J160">
+        <v>1.32</v>
+      </c>
+    </row>
+    <row r="161" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A161" t="s">
+        <v>875</v>
+      </c>
+      <c r="B161" t="s">
+        <v>345</v>
+      </c>
+      <c r="C161" t="s">
+        <v>876</v>
+      </c>
+      <c r="D161" t="s">
+        <v>558</v>
+      </c>
+      <c r="E161" s="2">
+        <v>13141509.15</v>
+      </c>
+      <c r="F161">
+        <v>0.06</v>
+      </c>
+      <c r="G161" s="2">
+        <v>129921</v>
+      </c>
+      <c r="H161">
+        <v>101.15</v>
+      </c>
+      <c r="I161" t="s">
+        <v>559</v>
+      </c>
+      <c r="J161">
+        <v>1.31</v>
+      </c>
+    </row>
+    <row r="162" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A162" t="s">
+        <v>877</v>
+      </c>
+      <c r="B162" t="s">
+        <v>878</v>
+      </c>
+      <c r="C162" t="s">
+        <v>879</v>
+      </c>
+      <c r="D162" t="s">
+        <v>570</v>
+      </c>
+      <c r="E162" s="2">
+        <v>13085307.199999999</v>
+      </c>
+      <c r="F162">
+        <v>0.06</v>
+      </c>
+      <c r="G162" s="2">
+        <v>360080</v>
+      </c>
+      <c r="H162">
+        <v>36.340000000000003</v>
+      </c>
+      <c r="I162" t="s">
+        <v>591</v>
+      </c>
+      <c r="J162">
+        <v>1.31</v>
+      </c>
+    </row>
+    <row r="163" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A163" t="s">
+        <v>880</v>
+      </c>
+      <c r="B163" t="s">
+        <v>881</v>
+      </c>
+      <c r="C163" t="s">
+        <v>882</v>
+      </c>
+      <c r="D163" t="s">
+        <v>724</v>
+      </c>
+      <c r="E163" s="2">
+        <v>13028715.15</v>
+      </c>
+      <c r="F163">
+        <v>0.06</v>
+      </c>
+      <c r="G163" s="2">
+        <v>1246767</v>
+      </c>
+      <c r="H163">
+        <v>10.45</v>
+      </c>
+      <c r="I163" t="s">
+        <v>559</v>
+      </c>
+      <c r="J163">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="164" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A164" t="s">
+        <v>883</v>
+      </c>
+      <c r="B164" t="s">
+        <v>884</v>
+      </c>
+      <c r="C164" t="s">
+        <v>885</v>
+      </c>
+      <c r="D164" t="s">
+        <v>564</v>
+      </c>
+      <c r="E164" s="2">
+        <v>12634954.539999999</v>
+      </c>
+      <c r="F164">
+        <v>0.06</v>
+      </c>
+      <c r="G164" s="2">
+        <v>1033957</v>
+      </c>
+      <c r="H164">
+        <v>12.22</v>
+      </c>
+      <c r="I164" t="s">
+        <v>559</v>
+      </c>
+      <c r="J164">
+        <v>1.26</v>
+      </c>
+    </row>
+    <row r="165" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A165" t="s">
+        <v>886</v>
+      </c>
+      <c r="B165" t="s">
+        <v>887</v>
+      </c>
+      <c r="C165" t="s">
+        <v>888</v>
+      </c>
+      <c r="D165" t="s">
+        <v>724</v>
+      </c>
+      <c r="E165" s="2">
+        <v>12329302.26</v>
+      </c>
+      <c r="F165">
+        <v>0.06</v>
+      </c>
+      <c r="G165" s="2">
+        <v>190091</v>
+      </c>
+      <c r="H165">
+        <v>64.86</v>
+      </c>
+      <c r="I165" t="s">
+        <v>559</v>
+      </c>
+      <c r="J165">
+        <v>1.23</v>
+      </c>
+    </row>
+    <row r="166" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A166" t="s">
+        <v>889</v>
+      </c>
+      <c r="B166" t="s">
+        <v>890</v>
+      </c>
+      <c r="C166" t="s">
+        <v>891</v>
+      </c>
+      <c r="D166" t="s">
+        <v>570</v>
+      </c>
+      <c r="E166" s="2">
+        <v>11974943.75</v>
+      </c>
+      <c r="F166">
+        <v>0.06</v>
+      </c>
+      <c r="G166" s="2">
+        <v>622075</v>
+      </c>
+      <c r="H166">
+        <v>19.25</v>
+      </c>
+      <c r="I166" t="s">
+        <v>559</v>
+      </c>
+      <c r="J166">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="167" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A167" t="s">
+        <v>892</v>
+      </c>
+      <c r="B167" t="s">
+        <v>893</v>
+      </c>
+      <c r="C167" t="s">
+        <v>894</v>
+      </c>
+      <c r="D167" t="s">
+        <v>564</v>
+      </c>
+      <c r="E167" s="2">
+        <v>11957196.68</v>
+      </c>
+      <c r="F167">
+        <v>0.06</v>
+      </c>
+      <c r="G167" s="2">
+        <v>578201</v>
+      </c>
+      <c r="H167">
+        <v>20.68</v>
+      </c>
+      <c r="I167" t="s">
+        <v>559</v>
+      </c>
+      <c r="J167">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="168" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A168" t="s">
+        <v>895</v>
+      </c>
+      <c r="B168" t="s">
+        <v>531</v>
+      </c>
+      <c r="C168" t="s">
+        <v>896</v>
+      </c>
+      <c r="D168" t="s">
+        <v>575</v>
+      </c>
+      <c r="E168" s="2">
+        <v>11912862.880000001</v>
+      </c>
+      <c r="F168">
+        <v>0.06</v>
+      </c>
+      <c r="G168" s="2">
+        <v>160724</v>
+      </c>
+      <c r="H168">
+        <v>74.12</v>
+      </c>
+      <c r="I168" t="s">
+        <v>559</v>
+      </c>
+      <c r="J168">
+        <v>1.19</v>
+      </c>
+    </row>
+    <row r="169" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A169" t="s">
+        <v>897</v>
+      </c>
+      <c r="B169" t="s">
+        <v>428</v>
+      </c>
+      <c r="C169" t="s">
+        <v>898</v>
+      </c>
+      <c r="D169" t="s">
+        <v>575</v>
+      </c>
+      <c r="E169" s="2">
+        <v>11751606.630000001</v>
+      </c>
+      <c r="F169">
+        <v>0.05</v>
+      </c>
+      <c r="G169" s="2">
+        <v>268731</v>
+      </c>
+      <c r="H169">
+        <v>43.73</v>
+      </c>
+      <c r="I169" t="s">
+        <v>559</v>
+      </c>
+      <c r="J169">
+        <v>1.18</v>
+      </c>
+    </row>
+    <row r="170" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A170" t="s">
+        <v>416</v>
+      </c>
+      <c r="B170" t="s">
+        <v>417</v>
+      </c>
+      <c r="C170" t="s">
+        <v>899</v>
+      </c>
+      <c r="D170" t="s">
+        <v>765</v>
+      </c>
+      <c r="E170" s="2">
+        <v>11663144</v>
+      </c>
+      <c r="F170">
+        <v>0.05</v>
+      </c>
+      <c r="G170" s="2">
+        <v>1240760</v>
+      </c>
+      <c r="H170">
+        <v>9.4</v>
+      </c>
+      <c r="I170" t="s">
+        <v>559</v>
+      </c>
+      <c r="J170">
+        <v>1.17</v>
+      </c>
+    </row>
+    <row r="171" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A171" t="s">
+        <v>900</v>
+      </c>
+      <c r="B171" t="s">
+        <v>901</v>
+      </c>
+      <c r="C171" t="s">
+        <v>902</v>
+      </c>
+      <c r="D171" t="s">
+        <v>564</v>
+      </c>
+      <c r="E171" s="2">
+        <v>11409275.85</v>
+      </c>
+      <c r="F171">
+        <v>0.05</v>
+      </c>
+      <c r="G171" s="2">
+        <v>72051</v>
+      </c>
+      <c r="H171">
+        <v>158.35</v>
+      </c>
+      <c r="I171" t="s">
+        <v>559</v>
+      </c>
+      <c r="J171">
+        <v>1.1399999999999999</v>
+      </c>
+    </row>
+    <row r="172" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A172" t="s">
+        <v>903</v>
+      </c>
+      <c r="B172" t="s">
+        <v>408</v>
+      </c>
+      <c r="C172" t="s">
+        <v>904</v>
+      </c>
+      <c r="D172" t="s">
+        <v>594</v>
+      </c>
+      <c r="E172" s="2">
+        <v>11361673.6</v>
+      </c>
+      <c r="F172">
+        <v>0.05</v>
+      </c>
+      <c r="G172" s="2">
+        <v>229066</v>
+      </c>
+      <c r="H172">
+        <v>49.6</v>
+      </c>
+      <c r="I172" t="s">
+        <v>559</v>
+      </c>
+      <c r="J172">
+        <v>1.1399999999999999</v>
+      </c>
+    </row>
+    <row r="173" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A173" t="s">
+        <v>905</v>
+      </c>
+      <c r="B173" t="s">
+        <v>414</v>
+      </c>
+      <c r="C173" t="s">
+        <v>906</v>
+      </c>
+      <c r="D173" t="s">
+        <v>724</v>
+      </c>
+      <c r="E173" s="2">
+        <v>11326208.640000001</v>
+      </c>
+      <c r="F173">
+        <v>0.05</v>
+      </c>
+      <c r="G173" s="2">
+        <v>204888</v>
+      </c>
+      <c r="H173">
+        <v>55.28</v>
+      </c>
+      <c r="I173" t="s">
+        <v>559</v>
+      </c>
+      <c r="J173">
+        <v>1.1299999999999999</v>
+      </c>
+    </row>
+    <row r="174" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A174" t="s">
+        <v>907</v>
+      </c>
+      <c r="B174" t="s">
+        <v>366</v>
+      </c>
+      <c r="C174" t="s">
+        <v>908</v>
+      </c>
+      <c r="D174" t="s">
+        <v>615</v>
+      </c>
+      <c r="E174" s="2">
+        <v>10494658.92</v>
+      </c>
+      <c r="F174">
+        <v>0.05</v>
+      </c>
+      <c r="G174" s="2">
+        <v>414481</v>
+      </c>
+      <c r="H174">
+        <v>25.32</v>
+      </c>
+      <c r="I174" t="s">
+        <v>559</v>
+      </c>
+      <c r="J174">
+        <v>1.05</v>
+      </c>
+    </row>
+    <row r="175" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A175" t="s">
+        <v>909</v>
+      </c>
+      <c r="B175" t="s">
+        <v>910</v>
+      </c>
+      <c r="C175" t="s">
+        <v>911</v>
+      </c>
+      <c r="D175" t="s">
+        <v>765</v>
+      </c>
+      <c r="E175" s="2">
+        <v>10470354.300000001</v>
+      </c>
+      <c r="F175">
+        <v>0.05</v>
+      </c>
+      <c r="G175" s="2">
+        <v>2374230</v>
+      </c>
+      <c r="H175">
+        <v>4.41</v>
+      </c>
+      <c r="I175" t="s">
+        <v>591</v>
+      </c>
+      <c r="J175">
+        <v>1.05</v>
+      </c>
+    </row>
+    <row r="176" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A176" t="s">
+        <v>912</v>
+      </c>
+      <c r="B176" t="s">
+        <v>496</v>
+      </c>
+      <c r="C176" t="s">
+        <v>913</v>
+      </c>
+      <c r="D176" t="s">
+        <v>558</v>
+      </c>
+      <c r="E176" s="2">
+        <v>9986070.0500000007</v>
+      </c>
+      <c r="F176">
+        <v>0.05</v>
+      </c>
+      <c r="G176" s="2">
+        <v>229829</v>
+      </c>
+      <c r="H176">
+        <v>43.45</v>
+      </c>
+      <c r="I176" t="s">
+        <v>559</v>
+      </c>
+      <c r="J176">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="177" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A177" t="s">
+        <v>914</v>
+      </c>
+      <c r="B177" t="s">
+        <v>915</v>
+      </c>
+      <c r="C177" t="s">
+        <v>916</v>
+      </c>
+      <c r="D177" t="s">
+        <v>575</v>
+      </c>
+      <c r="E177" s="2">
+        <v>9920439.3599999994</v>
+      </c>
+      <c r="F177">
+        <v>0.05</v>
+      </c>
+      <c r="G177" s="2">
+        <v>207584</v>
+      </c>
+      <c r="H177">
+        <v>47.79</v>
+      </c>
+      <c r="I177" t="s">
+        <v>559</v>
+      </c>
+      <c r="J177">
+        <v>0.99</v>
+      </c>
+    </row>
+    <row r="178" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A178" t="s">
+        <v>917</v>
+      </c>
+      <c r="B178" t="s">
+        <v>478</v>
+      </c>
+      <c r="C178" t="s">
+        <v>918</v>
+      </c>
+      <c r="D178" t="s">
+        <v>575</v>
+      </c>
+      <c r="E178" s="2">
+        <v>9834467.5800000001</v>
+      </c>
+      <c r="F178">
+        <v>0.05</v>
+      </c>
+      <c r="G178" s="2">
+        <v>242109</v>
+      </c>
+      <c r="H178">
+        <v>40.619999999999997</v>
+      </c>
+      <c r="I178" t="s">
+        <v>559</v>
+      </c>
+      <c r="J178">
+        <v>0.98</v>
+      </c>
+    </row>
+    <row r="179" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A179" t="s">
+        <v>442</v>
+      </c>
+      <c r="B179" t="s">
+        <v>443</v>
+      </c>
+      <c r="C179" t="s">
+        <v>919</v>
+      </c>
+      <c r="D179" t="s">
+        <v>561</v>
+      </c>
+      <c r="E179" s="2">
+        <v>9749935.3200000003</v>
+      </c>
+      <c r="F179">
+        <v>0.05</v>
+      </c>
+      <c r="G179" s="2">
+        <v>588054</v>
+      </c>
+      <c r="H179">
+        <v>16.579999999999998</v>
+      </c>
+      <c r="I179" t="s">
+        <v>559</v>
+      </c>
+      <c r="J179">
+        <v>0.97</v>
+      </c>
+    </row>
+    <row r="180" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A180" t="s">
+        <v>920</v>
+      </c>
+      <c r="B180" t="s">
+        <v>461</v>
+      </c>
+      <c r="C180" t="s">
+        <v>921</v>
+      </c>
+      <c r="D180" t="s">
+        <v>564</v>
+      </c>
+      <c r="E180" s="2">
+        <v>9686004.3200000003</v>
+      </c>
+      <c r="F180">
+        <v>0.05</v>
+      </c>
+      <c r="G180" s="2">
+        <v>649196</v>
+      </c>
+      <c r="H180">
+        <v>14.92</v>
+      </c>
+      <c r="I180" t="s">
+        <v>559</v>
+      </c>
+      <c r="J180">
+        <v>0.97</v>
+      </c>
+    </row>
+    <row r="181" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A181" t="s">
+        <v>922</v>
+      </c>
+      <c r="B181" t="s">
+        <v>923</v>
+      </c>
+      <c r="C181" t="s">
+        <v>924</v>
+      </c>
+      <c r="D181" t="s">
+        <v>724</v>
+      </c>
+      <c r="E181" s="2">
+        <v>9537194.9000000004</v>
+      </c>
+      <c r="F181">
+        <v>0.04</v>
+      </c>
+      <c r="G181" s="2">
+        <v>575570</v>
+      </c>
+      <c r="H181">
+        <v>16.57</v>
+      </c>
+      <c r="I181" t="s">
+        <v>559</v>
+      </c>
+      <c r="J181">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="182" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A182" t="s">
+        <v>925</v>
+      </c>
+      <c r="B182" t="s">
+        <v>535</v>
+      </c>
+      <c r="C182" t="s">
+        <v>926</v>
+      </c>
+      <c r="D182" t="s">
+        <v>564</v>
+      </c>
+      <c r="E182" s="2">
+        <v>9529605</v>
+      </c>
+      <c r="F182">
+        <v>0.04</v>
+      </c>
+      <c r="G182" s="2">
+        <v>1058845</v>
+      </c>
+      <c r="H182">
+        <v>9</v>
+      </c>
+      <c r="I182" t="s">
+        <v>559</v>
+      </c>
+      <c r="J182">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="183" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A183" t="s">
+        <v>927</v>
+      </c>
+      <c r="B183" t="s">
+        <v>391</v>
+      </c>
+      <c r="C183" t="s">
+        <v>928</v>
+      </c>
+      <c r="D183" t="s">
+        <v>626</v>
+      </c>
+      <c r="E183" s="2">
+        <v>9483111.1799999997</v>
+      </c>
+      <c r="F183">
+        <v>0.04</v>
+      </c>
+      <c r="G183" s="2">
+        <v>143553</v>
+      </c>
+      <c r="H183">
+        <v>66.06</v>
+      </c>
+      <c r="I183" t="s">
+        <v>559</v>
+      </c>
+      <c r="J183">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="184" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A184" t="s">
+        <v>929</v>
+      </c>
+      <c r="B184" t="s">
+        <v>500</v>
+      </c>
+      <c r="C184" t="s">
+        <v>930</v>
+      </c>
+      <c r="D184" t="s">
+        <v>564</v>
+      </c>
+      <c r="E184" s="2">
+        <v>9316270.8000000007</v>
+      </c>
+      <c r="F184">
+        <v>0.04</v>
+      </c>
+      <c r="G184" s="2">
+        <v>1308465</v>
+      </c>
+      <c r="H184">
+        <v>7.12</v>
+      </c>
+      <c r="I184" t="s">
+        <v>559</v>
+      </c>
+      <c r="J184">
+        <v>0.93</v>
+      </c>
+    </row>
+    <row r="185" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A185" t="s">
+        <v>931</v>
+      </c>
+      <c r="B185" t="s">
+        <v>488</v>
+      </c>
+      <c r="C185" t="s">
+        <v>932</v>
+      </c>
+      <c r="D185" t="s">
+        <v>570</v>
+      </c>
+      <c r="E185" s="2">
+        <v>9304154.3800000008</v>
+      </c>
+      <c r="F185">
+        <v>0.04</v>
+      </c>
+      <c r="G185" s="2">
+        <v>303958</v>
+      </c>
+      <c r="H185">
+        <v>30.61</v>
+      </c>
+      <c r="I185" t="s">
+        <v>559</v>
+      </c>
+      <c r="J185">
+        <v>0.93</v>
+      </c>
+    </row>
+    <row r="186" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A186" t="s">
+        <v>933</v>
+      </c>
+      <c r="B186" t="s">
+        <v>522</v>
+      </c>
+      <c r="C186" t="s">
+        <v>934</v>
+      </c>
+      <c r="D186" t="s">
+        <v>765</v>
+      </c>
+      <c r="E186" s="2">
+        <v>9233897.9700000007</v>
+      </c>
+      <c r="F186">
+        <v>0.04</v>
+      </c>
+      <c r="G186" s="2">
+        <v>437833</v>
+      </c>
+      <c r="H186">
+        <v>21.09</v>
+      </c>
+      <c r="I186" t="s">
+        <v>559</v>
+      </c>
+      <c r="J186">
+        <v>0.92</v>
+      </c>
+    </row>
+    <row r="187" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A187" t="s">
+        <v>935</v>
+      </c>
+      <c r="B187" t="s">
+        <v>936</v>
+      </c>
+      <c r="C187" t="s">
+        <v>937</v>
+      </c>
+      <c r="D187" t="s">
+        <v>575</v>
+      </c>
+      <c r="E187" s="2">
+        <v>9179355.8000000007</v>
+      </c>
+      <c r="F187">
+        <v>0.04</v>
+      </c>
+      <c r="G187" s="2">
+        <v>297548</v>
+      </c>
+      <c r="H187">
+        <v>30.85</v>
+      </c>
+      <c r="I187" t="s">
+        <v>559</v>
+      </c>
+      <c r="J187">
+        <v>0.92</v>
+      </c>
+    </row>
+    <row r="188" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A188" t="s">
+        <v>938</v>
+      </c>
+      <c r="B188" t="s">
+        <v>449</v>
+      </c>
+      <c r="C188" t="s">
+        <v>939</v>
+      </c>
+      <c r="D188" t="s">
+        <v>597</v>
+      </c>
+      <c r="E188" s="2">
+        <v>9167430.9600000009</v>
+      </c>
+      <c r="F188">
+        <v>0.04</v>
+      </c>
+      <c r="G188" s="2">
+        <v>324396</v>
+      </c>
+      <c r="H188">
+        <v>28.26</v>
+      </c>
+      <c r="I188" t="s">
+        <v>559</v>
+      </c>
+      <c r="J188">
+        <v>0.92</v>
+      </c>
+    </row>
+    <row r="189" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A189" t="s">
+        <v>940</v>
+      </c>
+      <c r="B189" t="s">
+        <v>492</v>
+      </c>
+      <c r="C189" t="s">
+        <v>941</v>
+      </c>
+      <c r="D189" t="s">
+        <v>564</v>
+      </c>
+      <c r="E189" s="2">
+        <v>8960696.5999999996</v>
+      </c>
+      <c r="F189">
+        <v>0.04</v>
+      </c>
+      <c r="G189" s="2">
+        <v>792982</v>
+      </c>
+      <c r="H189">
+        <v>11.3</v>
+      </c>
+      <c r="I189" t="s">
+        <v>559</v>
+      </c>
+      <c r="J189">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="190" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A190" t="s">
+        <v>942</v>
+      </c>
+      <c r="B190" t="s">
+        <v>364</v>
+      </c>
+      <c r="C190" t="s">
+        <v>943</v>
+      </c>
+      <c r="D190" t="s">
+        <v>594</v>
+      </c>
+      <c r="E190" s="2">
+        <v>8813408.6400000006</v>
+      </c>
+      <c r="F190">
+        <v>0.04</v>
+      </c>
+      <c r="G190" s="2">
+        <v>351552</v>
+      </c>
+      <c r="H190">
+        <v>25.07</v>
+      </c>
+      <c r="I190" t="s">
+        <v>559</v>
+      </c>
+      <c r="J190">
+        <v>0.88</v>
+      </c>
+    </row>
+    <row r="191" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A191" t="s">
+        <v>944</v>
+      </c>
+      <c r="B191" t="s">
+        <v>945</v>
+      </c>
+      <c r="C191" t="s">
+        <v>946</v>
+      </c>
+      <c r="D191" t="s">
+        <v>724</v>
+      </c>
+      <c r="E191" s="2">
+        <v>8782364.6699999999</v>
+      </c>
+      <c r="F191">
+        <v>0.04</v>
+      </c>
+      <c r="G191" s="2">
+        <v>664827</v>
+      </c>
+      <c r="H191">
+        <v>13.21</v>
+      </c>
+      <c r="I191" t="s">
+        <v>559</v>
+      </c>
+      <c r="J191">
+        <v>0.88</v>
+      </c>
+    </row>
+    <row r="192" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A192" t="s">
+        <v>947</v>
+      </c>
+      <c r="B192" t="s">
+        <v>948</v>
+      </c>
+      <c r="C192" t="s">
+        <v>949</v>
+      </c>
+      <c r="D192" t="s">
+        <v>558</v>
+      </c>
+      <c r="E192" s="2">
+        <v>8431031.9800000004</v>
+      </c>
+      <c r="F192">
+        <v>0.04</v>
+      </c>
+      <c r="G192" s="2">
+        <v>210934</v>
+      </c>
+      <c r="H192">
+        <v>39.97</v>
+      </c>
+      <c r="I192" t="s">
+        <v>559</v>
+      </c>
+      <c r="J192">
+        <v>0.84</v>
+      </c>
+    </row>
+    <row r="193" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A193" t="s">
+        <v>950</v>
+      </c>
+      <c r="B193" t="s">
+        <v>421</v>
+      </c>
+      <c r="C193" t="s">
+        <v>951</v>
+      </c>
+      <c r="D193" t="s">
+        <v>564</v>
+      </c>
+      <c r="E193" s="2">
+        <v>8379088.0599999996</v>
+      </c>
+      <c r="F193">
+        <v>0.04</v>
+      </c>
+      <c r="G193" s="2">
+        <v>358387</v>
+      </c>
+      <c r="H193">
+        <v>23.38</v>
+      </c>
+      <c r="I193" t="s">
+        <v>559</v>
+      </c>
+      <c r="J193">
+        <v>0.84</v>
+      </c>
+    </row>
+    <row r="194" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A194" t="s">
+        <v>539</v>
+      </c>
+      <c r="B194" t="s">
+        <v>540</v>
+      </c>
+      <c r="C194" t="s">
+        <v>952</v>
+      </c>
+      <c r="D194" t="s">
+        <v>564</v>
+      </c>
+      <c r="E194" s="2">
+        <v>8096135.9400000004</v>
+      </c>
+      <c r="F194">
+        <v>0.04</v>
+      </c>
+      <c r="G194" s="2">
+        <v>737353</v>
+      </c>
+      <c r="H194">
+        <v>10.98</v>
+      </c>
+      <c r="I194" t="s">
+        <v>559</v>
+      </c>
+      <c r="J194">
+        <v>0.81</v>
+      </c>
+    </row>
+    <row r="195" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A195" t="s">
+        <v>953</v>
+      </c>
+      <c r="B195" t="s">
+        <v>954</v>
+      </c>
+      <c r="C195" t="s">
+        <v>955</v>
+      </c>
+      <c r="D195" t="s">
+        <v>724</v>
+      </c>
+      <c r="E195" s="2">
+        <v>8073383.7999999998</v>
+      </c>
+      <c r="F195">
+        <v>0.04</v>
+      </c>
+      <c r="G195" s="2">
+        <v>518855</v>
+      </c>
+      <c r="H195">
+        <v>15.56</v>
+      </c>
+      <c r="I195" t="s">
+        <v>559</v>
+      </c>
+      <c r="J195">
+        <v>0.81</v>
+      </c>
+    </row>
+    <row r="196" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A196" t="s">
+        <v>956</v>
+      </c>
+      <c r="B196" t="s">
+        <v>957</v>
+      </c>
+      <c r="C196" t="s">
+        <v>958</v>
+      </c>
+      <c r="D196" t="s">
+        <v>564</v>
+      </c>
+      <c r="E196" s="2">
+        <v>8064733.9500000002</v>
+      </c>
+      <c r="F196">
+        <v>0.04</v>
+      </c>
+      <c r="G196" s="2">
+        <v>459529</v>
+      </c>
+      <c r="H196">
+        <v>17.55</v>
+      </c>
+      <c r="I196" t="s">
+        <v>559</v>
+      </c>
+      <c r="J196">
+        <v>0.81</v>
+      </c>
+    </row>
+    <row r="197" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A197" t="s">
+        <v>959</v>
+      </c>
+      <c r="B197" t="s">
+        <v>960</v>
+      </c>
+      <c r="C197" t="s">
+        <v>961</v>
+      </c>
+      <c r="D197" t="s">
+        <v>570</v>
+      </c>
+      <c r="E197" s="2">
+        <v>8041114.1399999997</v>
+      </c>
+      <c r="F197">
+        <v>0.04</v>
+      </c>
+      <c r="G197" s="2">
+        <v>353611</v>
+      </c>
+      <c r="H197">
+        <v>22.74</v>
+      </c>
+      <c r="I197" t="s">
+        <v>559</v>
+      </c>
+      <c r="J197">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="198" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A198" t="s">
+        <v>962</v>
+      </c>
+      <c r="B198" t="s">
+        <v>963</v>
+      </c>
+      <c r="C198" t="s">
+        <v>964</v>
+      </c>
+      <c r="D198" t="s">
+        <v>724</v>
+      </c>
+      <c r="E198" s="2">
+        <v>7986659.8399999999</v>
+      </c>
+      <c r="F198">
+        <v>0.04</v>
+      </c>
+      <c r="G198" s="2">
+        <v>510656</v>
+      </c>
+      <c r="H198">
+        <v>15.64</v>
+      </c>
+      <c r="I198" t="s">
+        <v>559</v>
+      </c>
+      <c r="J198">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="199" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A199" t="s">
+        <v>965</v>
+      </c>
+      <c r="B199" t="s">
+        <v>966</v>
+      </c>
+      <c r="C199" t="s">
+        <v>967</v>
+      </c>
+      <c r="D199" t="s">
+        <v>724</v>
+      </c>
+      <c r="E199" s="2">
+        <v>7947426.0499999998</v>
+      </c>
+      <c r="F199">
+        <v>0.04</v>
+      </c>
+      <c r="G199" s="2">
+        <v>604367</v>
+      </c>
+      <c r="H199">
+        <v>13.15</v>
+      </c>
+      <c r="I199" t="s">
+        <v>559</v>
+      </c>
+      <c r="J199">
+        <v>0.79</v>
+      </c>
+    </row>
+    <row r="200" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A200" t="s">
+        <v>968</v>
+      </c>
+      <c r="B200" t="s">
+        <v>510</v>
+      </c>
+      <c r="C200" t="s">
+        <v>969</v>
+      </c>
+      <c r="D200" t="s">
+        <v>615</v>
+      </c>
+      <c r="E200" s="2">
+        <v>7662202.4000000004</v>
+      </c>
+      <c r="F200">
+        <v>0.04</v>
+      </c>
+      <c r="G200" s="2">
+        <v>1070140</v>
+      </c>
+      <c r="H200">
+        <v>7.16</v>
+      </c>
+      <c r="I200" t="s">
+        <v>559</v>
+      </c>
+      <c r="J200">
+        <v>0.77</v>
+      </c>
+    </row>
+    <row r="201" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A201" t="s">
+        <v>970</v>
+      </c>
+      <c r="B201" t="s">
+        <v>971</v>
+      </c>
+      <c r="C201" t="s">
+        <v>972</v>
+      </c>
+      <c r="D201" t="s">
+        <v>575</v>
+      </c>
+      <c r="E201" s="2">
+        <v>7562773.75</v>
+      </c>
+      <c r="F201">
+        <v>0.04</v>
+      </c>
+      <c r="G201" s="2">
+        <v>263053</v>
+      </c>
+      <c r="H201">
+        <v>28.75</v>
+      </c>
+      <c r="I201" t="s">
+        <v>559</v>
+      </c>
+      <c r="J201">
+        <v>0.76</v>
+      </c>
+    </row>
+    <row r="202" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A202" t="s">
+        <v>973</v>
+      </c>
+      <c r="B202" t="s">
+        <v>426</v>
+      </c>
+      <c r="C202" t="s">
+        <v>974</v>
+      </c>
+      <c r="D202" t="s">
+        <v>558</v>
+      </c>
+      <c r="E202" s="2">
+        <v>7509303.1200000001</v>
+      </c>
+      <c r="F202">
+        <v>0.04</v>
+      </c>
+      <c r="G202" s="2">
+        <v>59147</v>
+      </c>
+      <c r="H202">
+        <v>126.96</v>
+      </c>
+      <c r="I202" t="s">
+        <v>559</v>
+      </c>
+      <c r="J202">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="203" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A203" t="s">
+        <v>975</v>
+      </c>
+      <c r="B203" t="s">
+        <v>430</v>
+      </c>
+      <c r="C203" t="s">
+        <v>976</v>
+      </c>
+      <c r="D203" t="s">
+        <v>564</v>
+      </c>
+      <c r="E203" s="2">
+        <v>7437942.54</v>
+      </c>
+      <c r="F203">
+        <v>0.03</v>
+      </c>
+      <c r="G203" s="2">
+        <v>310691</v>
+      </c>
+      <c r="H203">
+        <v>23.94</v>
+      </c>
+      <c r="I203" t="s">
+        <v>559</v>
+      </c>
+      <c r="J203">
+        <v>0.74</v>
+      </c>
+    </row>
+    <row r="204" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A204" t="s">
+        <v>977</v>
+      </c>
+      <c r="B204" t="s">
+        <v>506</v>
+      </c>
+      <c r="C204" t="s">
+        <v>978</v>
+      </c>
+      <c r="D204" t="s">
+        <v>575</v>
+      </c>
+      <c r="E204" s="2">
+        <v>6943008</v>
+      </c>
+      <c r="F204">
+        <v>0.03</v>
+      </c>
+      <c r="G204" s="2">
+        <v>447936</v>
+      </c>
+      <c r="H204">
+        <v>15.5</v>
+      </c>
+      <c r="I204" t="s">
+        <v>559</v>
+      </c>
+      <c r="J204">
+        <v>0.69</v>
+      </c>
+    </row>
+    <row r="205" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A205" t="s">
+        <v>979</v>
+      </c>
+      <c r="B205" t="s">
+        <v>546</v>
+      </c>
+      <c r="C205" t="s">
+        <v>980</v>
+      </c>
+      <c r="D205" t="s">
+        <v>594</v>
+      </c>
+      <c r="E205" s="2">
+        <v>6516278.7300000004</v>
+      </c>
+      <c r="F205">
+        <v>0.03</v>
+      </c>
+      <c r="G205" s="2">
+        <v>198003</v>
+      </c>
+      <c r="H205">
+        <v>32.909999999999997</v>
+      </c>
+      <c r="I205" t="s">
+        <v>559</v>
+      </c>
+      <c r="J205">
+        <v>0.65</v>
+      </c>
+    </row>
+    <row r="206" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A206" t="s">
+        <v>981</v>
+      </c>
+      <c r="B206" t="s">
+        <v>982</v>
+      </c>
+      <c r="C206" t="s">
+        <v>983</v>
+      </c>
+      <c r="D206" t="s">
+        <v>575</v>
+      </c>
+      <c r="E206" s="2">
+        <v>6292058.8600000003</v>
+      </c>
+      <c r="F206">
+        <v>0.03</v>
+      </c>
+      <c r="G206" s="2">
+        <v>391054</v>
+      </c>
+      <c r="H206">
+        <v>16.09</v>
+      </c>
+      <c r="I206" t="s">
+        <v>559</v>
+      </c>
+      <c r="J206">
+        <v>0.63</v>
+      </c>
+    </row>
+    <row r="207" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A207" t="s">
+        <v>984</v>
+      </c>
+      <c r="B207" t="s">
+        <v>985</v>
+      </c>
+      <c r="C207" t="s">
+        <v>986</v>
+      </c>
+      <c r="D207" t="s">
+        <v>724</v>
+      </c>
+      <c r="E207" s="2">
+        <v>5837298.0300000003</v>
+      </c>
+      <c r="F207">
+        <v>0.03</v>
+      </c>
+      <c r="G207" s="2">
+        <v>359661</v>
+      </c>
+      <c r="H207">
+        <v>16.23</v>
+      </c>
+      <c r="I207" t="s">
+        <v>559</v>
+      </c>
+      <c r="J207">
+        <v>0.57999999999999996</v>
+      </c>
+    </row>
+    <row r="208" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A208" t="s">
+        <v>987</v>
+      </c>
+      <c r="B208" t="s">
+        <v>399</v>
+      </c>
+      <c r="C208" t="s">
+        <v>988</v>
+      </c>
+      <c r="D208" t="s">
+        <v>570</v>
+      </c>
+      <c r="E208" s="2">
+        <v>5799869.9199999999</v>
+      </c>
+      <c r="F208">
+        <v>0.03</v>
+      </c>
+      <c r="G208" s="2">
+        <v>128089</v>
+      </c>
+      <c r="H208">
+        <v>45.28</v>
+      </c>
+      <c r="I208" t="s">
+        <v>559</v>
+      </c>
+      <c r="J208">
+        <v>0.57999999999999996</v>
+      </c>
+    </row>
+    <row r="209" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A209" t="s">
+        <v>989</v>
+      </c>
+      <c r="B209" t="s">
+        <v>533</v>
+      </c>
+      <c r="C209" t="s">
+        <v>990</v>
+      </c>
+      <c r="D209" t="s">
+        <v>575</v>
+      </c>
+      <c r="E209" s="2">
+        <v>5781437.0800000001</v>
+      </c>
+      <c r="F209">
+        <v>0.03</v>
+      </c>
+      <c r="G209" s="2">
+        <v>70964</v>
+      </c>
+      <c r="H209">
+        <v>81.47</v>
+      </c>
+      <c r="I209" t="s">
+        <v>559</v>
+      </c>
+      <c r="J209">
+        <v>0.57999999999999996</v>
+      </c>
+    </row>
+    <row r="210" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A210" t="s">
+        <v>991</v>
+      </c>
+      <c r="B210" t="s">
+        <v>992</v>
+      </c>
+      <c r="C210" t="s">
+        <v>993</v>
+      </c>
+      <c r="D210" t="s">
+        <v>564</v>
+      </c>
+      <c r="E210" s="2">
+        <v>5731216.4000000004</v>
+      </c>
+      <c r="F210">
+        <v>0.03</v>
+      </c>
+      <c r="G210" s="2">
+        <v>787255</v>
+      </c>
+      <c r="H210">
+        <v>7.28</v>
+      </c>
+      <c r="I210" t="s">
+        <v>559</v>
+      </c>
+      <c r="J210">
+        <v>0.56999999999999995</v>
+      </c>
+    </row>
+    <row r="211" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A211" t="s">
+        <v>994</v>
+      </c>
+      <c r="B211" t="s">
+        <v>995</v>
+      </c>
+      <c r="C211" t="s">
+        <v>996</v>
+      </c>
+      <c r="D211" t="s">
+        <v>724</v>
+      </c>
+      <c r="E211" s="2">
+        <v>5383162.8799999999</v>
+      </c>
+      <c r="F211">
+        <v>0.03</v>
+      </c>
+      <c r="G211" s="2">
+        <v>1051399</v>
+      </c>
+      <c r="H211">
+        <v>5.12</v>
+      </c>
+      <c r="I211" t="s">
+        <v>559</v>
+      </c>
+      <c r="J211">
+        <v>0.54</v>
+      </c>
+    </row>
+    <row r="212" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A212" t="s">
+        <v>997</v>
+      </c>
+      <c r="B212" t="s">
+        <v>998</v>
+      </c>
+      <c r="C212" t="s">
+        <v>999</v>
+      </c>
+      <c r="D212" t="s">
+        <v>594</v>
+      </c>
+      <c r="E212" s="2">
+        <v>1090876.8</v>
+      </c>
+      <c r="F212">
+        <v>0.01</v>
+      </c>
+      <c r="G212" s="2">
+        <v>69928</v>
+      </c>
+      <c r="H212">
+        <v>15.6</v>
+      </c>
+      <c r="I212" t="s">
+        <v>559</v>
+      </c>
+      <c r="J212">
+        <v>0.11</v>
+      </c>
+    </row>
+    <row r="213" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A213" t="s">
+        <v>848</v>
+      </c>
+      <c r="B213" t="s">
+        <v>849</v>
+      </c>
+      <c r="C213" t="s">
+        <v>1000</v>
+      </c>
+      <c r="D213" t="s">
+        <v>558</v>
+      </c>
+      <c r="E213" s="2">
+        <v>43912.800000000003</v>
+      </c>
+      <c r="F213">
+        <v>0</v>
+      </c>
+      <c r="G213" s="2">
+        <v>146376</v>
+      </c>
+      <c r="H213">
+        <v>0.3</v>
+      </c>
+      <c r="I213" t="s">
+        <v>559</v>
+      </c>
+      <c r="J213">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E228"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>

--- a/Tickers_Info.xlsx
+++ b/Tickers_Info.xlsx
@@ -9,18 +9,19 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="16392" windowHeight="5784"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="16392" windowHeight="5784" activeTab="1"/>
   </bookViews>
   <sheets>
-    <sheet name="TSX" sheetId="2" r:id="rId1"/>
-    <sheet name="TSX_notAccurate" sheetId="1" r:id="rId2"/>
+    <sheet name="Info" sheetId="3" r:id="rId1"/>
+    <sheet name="TSX" sheetId="2" r:id="rId2"/>
+    <sheet name="TSX_notAccurate" sheetId="1" r:id="rId3"/>
   </sheets>
   <calcPr calcId="152511"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1756" uniqueCount="1001">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1761" uniqueCount="1006">
   <si>
     <t>Name</t>
   </si>
@@ -1909,9 +1910,6 @@
     <t>TECK.B</t>
   </si>
   <si>
-    <t>TECK.B.TO</t>
-  </si>
-  <si>
     <t>TECK RESOURCES SUBORDINATE VOTING</t>
   </si>
   <si>
@@ -1933,9 +1931,6 @@
     <t>GIB.A</t>
   </si>
   <si>
-    <t>GIB.A.TO</t>
-  </si>
-  <si>
     <t>CGI INC CLASS A</t>
   </si>
   <si>
@@ -1951,9 +1946,6 @@
     <t>BIP.UN</t>
   </si>
   <si>
-    <t>BIP.UN.TO</t>
-  </si>
-  <si>
     <t>BROOKFIELD INFRASTRUCTURE PARTNERS</t>
   </si>
   <si>
@@ -3023,6 +3015,30 @@
   </si>
   <si>
     <t>LUNR ROYALTIES</t>
+  </si>
+  <si>
+    <t>TSX</t>
+  </si>
+  <si>
+    <t>Source</t>
+  </si>
+  <si>
+    <t>XIC Holdings</t>
+  </si>
+  <si>
+    <t>Comments</t>
+  </si>
+  <si>
+    <t>Processed XIC holdings from BlackRock site. The MarketCap is not accurate; but relatively OK!</t>
+  </si>
+  <si>
+    <t>TECK-B.TO</t>
+  </si>
+  <si>
+    <t>GIB-A.TO</t>
+  </si>
+  <si>
+    <t>BIP-UN.TO</t>
   </si>
 </sst>
 </file>
@@ -3863,6 +3879,39 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:C3"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="11" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="78.6640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B1" t="s">
+        <v>999</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1001</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>998</v>
+      </c>
+      <c r="B3" t="s">
+        <v>1000</v>
+      </c>
+      <c r="C3" t="s">
+        <v>1002</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:J213"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -5155,10 +5204,10 @@
         <v>628</v>
       </c>
       <c r="B41" t="s">
+        <v>1003</v>
+      </c>
+      <c r="C41" t="s">
         <v>629</v>
-      </c>
-      <c r="C41" t="s">
-        <v>630</v>
       </c>
       <c r="D41" t="s">
         <v>570</v>
@@ -5190,7 +5239,7 @@
         <v>19</v>
       </c>
       <c r="C42" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="D42" t="s">
         <v>558</v>
@@ -5216,13 +5265,13 @@
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
+        <v>631</v>
+      </c>
+      <c r="B43" t="s">
         <v>632</v>
       </c>
-      <c r="B43" t="s">
+      <c r="C43" t="s">
         <v>633</v>
-      </c>
-      <c r="C43" t="s">
-        <v>634</v>
       </c>
       <c r="D43" t="s">
         <v>626</v>
@@ -5254,7 +5303,7 @@
         <v>123</v>
       </c>
       <c r="C44" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="D44" t="s">
         <v>575</v>
@@ -5280,13 +5329,13 @@
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
+        <v>635</v>
+      </c>
+      <c r="B45" t="s">
+        <v>1004</v>
+      </c>
+      <c r="C45" t="s">
         <v>636</v>
-      </c>
-      <c r="B45" t="s">
-        <v>637</v>
-      </c>
-      <c r="C45" t="s">
-        <v>638</v>
       </c>
       <c r="D45" t="s">
         <v>561</v>
@@ -5318,7 +5367,7 @@
         <v>25</v>
       </c>
       <c r="C46" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="D46" t="s">
         <v>575</v>
@@ -5344,13 +5393,13 @@
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="B47" t="s">
         <v>147</v>
       </c>
       <c r="C47" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="D47" t="s">
         <v>570</v>
@@ -5376,13 +5425,13 @@
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="B48" t="s">
-        <v>643</v>
+        <v>1005</v>
       </c>
       <c r="C48" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="D48" t="s">
         <v>615</v>
@@ -5400,7 +5449,7 @@
         <v>47.59</v>
       </c>
       <c r="I48" t="s">
-        <v>645</v>
+        <v>642</v>
       </c>
       <c r="J48">
         <v>10.43</v>
@@ -5408,13 +5457,13 @@
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>646</v>
+        <v>643</v>
       </c>
       <c r="B49" t="s">
         <v>131</v>
       </c>
       <c r="C49" t="s">
-        <v>647</v>
+        <v>644</v>
       </c>
       <c r="D49" t="s">
         <v>564</v>
@@ -5446,7 +5495,7 @@
         <v>163</v>
       </c>
       <c r="C50" t="s">
-        <v>648</v>
+        <v>645</v>
       </c>
       <c r="D50" t="s">
         <v>570</v>
@@ -5472,13 +5521,13 @@
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>649</v>
+        <v>646</v>
       </c>
       <c r="B51" t="s">
         <v>145</v>
       </c>
       <c r="C51" t="s">
-        <v>650</v>
+        <v>647</v>
       </c>
       <c r="D51" t="s">
         <v>615</v>
@@ -5504,13 +5553,13 @@
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>651</v>
+        <v>648</v>
       </c>
       <c r="B52" t="s">
-        <v>652</v>
+        <v>649</v>
       </c>
       <c r="C52" t="s">
-        <v>653</v>
+        <v>650</v>
       </c>
       <c r="D52" t="s">
         <v>597</v>
@@ -5536,13 +5585,13 @@
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>654</v>
+        <v>651</v>
       </c>
       <c r="B53" t="s">
         <v>136</v>
       </c>
       <c r="C53" t="s">
-        <v>655</v>
+        <v>652</v>
       </c>
       <c r="D53" t="s">
         <v>594</v>
@@ -5568,13 +5617,13 @@
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>656</v>
+        <v>653</v>
       </c>
       <c r="B54" t="s">
-        <v>657</v>
+        <v>654</v>
       </c>
       <c r="C54" t="s">
-        <v>658</v>
+        <v>655</v>
       </c>
       <c r="D54" t="s">
         <v>575</v>
@@ -5600,13 +5649,13 @@
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>659</v>
+        <v>656</v>
       </c>
       <c r="B55" t="s">
-        <v>660</v>
+        <v>657</v>
       </c>
       <c r="C55" t="s">
-        <v>661</v>
+        <v>658</v>
       </c>
       <c r="D55" t="s">
         <v>626</v>
@@ -5632,13 +5681,13 @@
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>662</v>
+        <v>659</v>
       </c>
       <c r="B56" t="s">
         <v>198</v>
       </c>
       <c r="C56" t="s">
-        <v>663</v>
+        <v>660</v>
       </c>
       <c r="D56" t="s">
         <v>570</v>
@@ -5670,7 +5719,7 @@
         <v>64</v>
       </c>
       <c r="C57" t="s">
-        <v>664</v>
+        <v>661</v>
       </c>
       <c r="D57" t="s">
         <v>564</v>
@@ -5696,13 +5745,13 @@
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>665</v>
+        <v>662</v>
       </c>
       <c r="B58" t="s">
         <v>78</v>
       </c>
       <c r="C58" t="s">
-        <v>666</v>
+        <v>663</v>
       </c>
       <c r="D58" t="s">
         <v>558</v>
@@ -5728,13 +5777,13 @@
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>667</v>
+        <v>664</v>
       </c>
       <c r="B59" t="s">
         <v>118</v>
       </c>
       <c r="C59" t="s">
-        <v>668</v>
+        <v>665</v>
       </c>
       <c r="D59" t="s">
         <v>615</v>
@@ -5766,7 +5815,7 @@
         <v>206</v>
       </c>
       <c r="C60" t="s">
-        <v>669</v>
+        <v>666</v>
       </c>
       <c r="D60" t="s">
         <v>597</v>
@@ -5798,7 +5847,7 @@
         <v>178</v>
       </c>
       <c r="C61" t="s">
-        <v>670</v>
+        <v>667</v>
       </c>
       <c r="D61" t="s">
         <v>558</v>
@@ -5830,7 +5879,7 @@
         <v>129</v>
       </c>
       <c r="C62" t="s">
-        <v>671</v>
+        <v>668</v>
       </c>
       <c r="D62" t="s">
         <v>575</v>
@@ -5856,13 +5905,13 @@
     </row>
     <row r="63" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>672</v>
+        <v>669</v>
       </c>
       <c r="B63" t="s">
         <v>105</v>
       </c>
       <c r="C63" t="s">
-        <v>673</v>
+        <v>670</v>
       </c>
       <c r="D63" t="s">
         <v>594</v>
@@ -5894,7 +5943,7 @@
         <v>157</v>
       </c>
       <c r="C64" t="s">
-        <v>674</v>
+        <v>671</v>
       </c>
       <c r="D64" t="s">
         <v>575</v>
@@ -5920,13 +5969,13 @@
     </row>
     <row r="65" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>675</v>
+        <v>672</v>
       </c>
       <c r="B65" t="s">
         <v>152</v>
       </c>
       <c r="C65" t="s">
-        <v>676</v>
+        <v>673</v>
       </c>
       <c r="D65" t="s">
         <v>564</v>
@@ -5958,7 +6007,7 @@
         <v>325</v>
       </c>
       <c r="C66" t="s">
-        <v>677</v>
+        <v>674</v>
       </c>
       <c r="D66" t="s">
         <v>570</v>
@@ -5984,13 +6033,13 @@
     </row>
     <row r="67" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>678</v>
+        <v>675</v>
       </c>
       <c r="B67" t="s">
         <v>180</v>
       </c>
       <c r="C67" t="s">
-        <v>679</v>
+        <v>676</v>
       </c>
       <c r="D67" t="s">
         <v>575</v>
@@ -6016,13 +6065,13 @@
     </row>
     <row r="68" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="B68" t="s">
         <v>154</v>
       </c>
       <c r="C68" t="s">
-        <v>681</v>
+        <v>678</v>
       </c>
       <c r="D68" t="s">
         <v>558</v>
@@ -6048,13 +6097,13 @@
     </row>
     <row r="69" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>682</v>
+        <v>679</v>
       </c>
       <c r="B69" t="s">
         <v>173</v>
       </c>
       <c r="C69" t="s">
-        <v>683</v>
+        <v>680</v>
       </c>
       <c r="D69" t="s">
         <v>575</v>
@@ -6080,13 +6129,13 @@
     </row>
     <row r="70" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>684</v>
+        <v>681</v>
       </c>
       <c r="B70" t="s">
         <v>289</v>
       </c>
       <c r="C70" t="s">
-        <v>685</v>
+        <v>682</v>
       </c>
       <c r="D70" t="s">
         <v>564</v>
@@ -6112,13 +6161,13 @@
     </row>
     <row r="71" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>686</v>
+        <v>683</v>
       </c>
       <c r="B71" t="s">
         <v>213</v>
       </c>
       <c r="C71" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
       <c r="D71" t="s">
         <v>575</v>
@@ -6150,7 +6199,7 @@
         <v>182</v>
       </c>
       <c r="C72" t="s">
-        <v>688</v>
+        <v>685</v>
       </c>
       <c r="D72" t="s">
         <v>575</v>
@@ -6176,13 +6225,13 @@
     </row>
     <row r="73" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>689</v>
+        <v>686</v>
       </c>
       <c r="B73" t="s">
-        <v>690</v>
+        <v>687</v>
       </c>
       <c r="C73" t="s">
-        <v>691</v>
+        <v>688</v>
       </c>
       <c r="D73" t="s">
         <v>570</v>
@@ -6208,13 +6257,13 @@
     </row>
     <row r="74" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>692</v>
+        <v>689</v>
       </c>
       <c r="B74" t="s">
-        <v>693</v>
+        <v>690</v>
       </c>
       <c r="C74" t="s">
-        <v>694</v>
+        <v>691</v>
       </c>
       <c r="D74" t="s">
         <v>570</v>
@@ -6240,13 +6289,13 @@
     </row>
     <row r="75" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="B75" t="s">
         <v>192</v>
       </c>
       <c r="C75" t="s">
-        <v>696</v>
+        <v>693</v>
       </c>
       <c r="D75" t="s">
         <v>615</v>
@@ -6278,7 +6327,7 @@
         <v>209</v>
       </c>
       <c r="C76" t="s">
-        <v>697</v>
+        <v>694</v>
       </c>
       <c r="D76" t="s">
         <v>561</v>
@@ -6310,7 +6359,7 @@
         <v>201</v>
       </c>
       <c r="C77" t="s">
-        <v>698</v>
+        <v>695</v>
       </c>
       <c r="D77" t="s">
         <v>575</v>
@@ -6336,13 +6385,13 @@
     </row>
     <row r="78" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>699</v>
+        <v>696</v>
       </c>
       <c r="B78" t="s">
         <v>171</v>
       </c>
       <c r="C78" t="s">
-        <v>700</v>
+        <v>697</v>
       </c>
       <c r="D78" t="s">
         <v>570</v>
@@ -6368,13 +6417,13 @@
     </row>
     <row r="79" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>701</v>
+        <v>698</v>
       </c>
       <c r="B79" t="s">
         <v>233</v>
       </c>
       <c r="C79" t="s">
-        <v>702</v>
+        <v>699</v>
       </c>
       <c r="D79" t="s">
         <v>597</v>
@@ -6406,7 +6455,7 @@
         <v>550</v>
       </c>
       <c r="C80" t="s">
-        <v>703</v>
+        <v>700</v>
       </c>
       <c r="D80" t="s">
         <v>561</v>
@@ -6438,7 +6487,7 @@
         <v>296</v>
       </c>
       <c r="C81" t="s">
-        <v>704</v>
+        <v>701</v>
       </c>
       <c r="D81" t="s">
         <v>570</v>
@@ -6464,13 +6513,13 @@
     </row>
     <row r="82" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
-        <v>705</v>
+        <v>702</v>
       </c>
       <c r="B82" t="s">
         <v>194</v>
       </c>
       <c r="C82" t="s">
-        <v>706</v>
+        <v>703</v>
       </c>
       <c r="D82" t="s">
         <v>594</v>
@@ -6502,7 +6551,7 @@
         <v>322</v>
       </c>
       <c r="C83" t="s">
-        <v>707</v>
+        <v>704</v>
       </c>
       <c r="D83" t="s">
         <v>570</v>
@@ -6528,13 +6577,13 @@
     </row>
     <row r="84" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
-        <v>708</v>
+        <v>705</v>
       </c>
       <c r="B84" t="s">
         <v>141</v>
       </c>
       <c r="C84" t="s">
-        <v>709</v>
+        <v>706</v>
       </c>
       <c r="D84" t="s">
         <v>570</v>
@@ -6560,13 +6609,13 @@
     </row>
     <row r="85" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
-        <v>710</v>
+        <v>707</v>
       </c>
       <c r="B85" t="s">
         <v>211</v>
       </c>
       <c r="C85" t="s">
-        <v>711</v>
+        <v>708</v>
       </c>
       <c r="D85" t="s">
         <v>564</v>
@@ -6592,13 +6641,13 @@
     </row>
     <row r="86" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
-        <v>712</v>
+        <v>709</v>
       </c>
       <c r="B86" t="s">
-        <v>713</v>
+        <v>710</v>
       </c>
       <c r="C86" t="s">
-        <v>714</v>
+        <v>711</v>
       </c>
       <c r="D86" t="s">
         <v>570</v>
@@ -6624,13 +6673,13 @@
     </row>
     <row r="87" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
-        <v>715</v>
+        <v>712</v>
       </c>
       <c r="B87" t="s">
         <v>255</v>
       </c>
       <c r="C87" t="s">
-        <v>716</v>
+        <v>713</v>
       </c>
       <c r="D87" t="s">
         <v>575</v>
@@ -6656,13 +6705,13 @@
     </row>
     <row r="88" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
-        <v>717</v>
+        <v>714</v>
       </c>
       <c r="B88" t="s">
         <v>374</v>
       </c>
       <c r="C88" t="s">
-        <v>718</v>
+        <v>715</v>
       </c>
       <c r="D88" t="s">
         <v>570</v>
@@ -6688,13 +6737,13 @@
     </row>
     <row r="89" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
-        <v>719</v>
+        <v>716</v>
       </c>
       <c r="B89" t="s">
         <v>227</v>
       </c>
       <c r="C89" t="s">
-        <v>720</v>
+        <v>717</v>
       </c>
       <c r="D89" t="s">
         <v>615</v>
@@ -6726,7 +6775,7 @@
         <v>250</v>
       </c>
       <c r="C90" t="s">
-        <v>721</v>
+        <v>718</v>
       </c>
       <c r="D90" t="s">
         <v>570</v>
@@ -6758,7 +6807,7 @@
         <v>312</v>
       </c>
       <c r="C91" t="s">
-        <v>722</v>
+        <v>719</v>
       </c>
       <c r="D91" t="s">
         <v>570</v>
@@ -6790,10 +6839,10 @@
         <v>190</v>
       </c>
       <c r="C92" t="s">
-        <v>723</v>
+        <v>720</v>
       </c>
       <c r="D92" t="s">
-        <v>724</v>
+        <v>721</v>
       </c>
       <c r="E92" s="2">
         <v>42479019.509999998</v>
@@ -6822,10 +6871,10 @@
         <v>216</v>
       </c>
       <c r="C93" t="s">
-        <v>725</v>
+        <v>722</v>
       </c>
       <c r="D93" t="s">
-        <v>724</v>
+        <v>721</v>
       </c>
       <c r="E93" s="2">
         <v>42179351.759999998</v>
@@ -6848,13 +6897,13 @@
     </row>
     <row r="94" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
-        <v>726</v>
+        <v>723</v>
       </c>
       <c r="B94" t="s">
         <v>319</v>
       </c>
       <c r="C94" t="s">
-        <v>727</v>
+        <v>724</v>
       </c>
       <c r="D94" t="s">
         <v>570</v>
@@ -6880,13 +6929,13 @@
     </row>
     <row r="95" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="B95" t="s">
-        <v>729</v>
+        <v>726</v>
       </c>
       <c r="C95" t="s">
-        <v>730</v>
+        <v>727</v>
       </c>
       <c r="D95" t="s">
         <v>597</v>
@@ -6912,13 +6961,13 @@
     </row>
     <row r="96" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
-        <v>731</v>
+        <v>728</v>
       </c>
       <c r="B96" t="s">
-        <v>732</v>
+        <v>729</v>
       </c>
       <c r="C96" t="s">
-        <v>733</v>
+        <v>730</v>
       </c>
       <c r="D96" t="s">
         <v>615</v>
@@ -6936,7 +6985,7 @@
         <v>36.78</v>
       </c>
       <c r="I96" t="s">
-        <v>645</v>
+        <v>642</v>
       </c>
       <c r="J96">
         <v>3.91</v>
@@ -6944,13 +6993,13 @@
     </row>
     <row r="97" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
-        <v>734</v>
+        <v>731</v>
       </c>
       <c r="B97" t="s">
-        <v>735</v>
+        <v>732</v>
       </c>
       <c r="C97" t="s">
-        <v>736</v>
+        <v>733</v>
       </c>
       <c r="D97" t="s">
         <v>570</v>
@@ -6976,13 +7025,13 @@
     </row>
     <row r="98" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
-        <v>737</v>
+        <v>734</v>
       </c>
       <c r="B98" t="s">
         <v>271</v>
       </c>
       <c r="C98" t="s">
-        <v>738</v>
+        <v>735</v>
       </c>
       <c r="D98" t="s">
         <v>570</v>
@@ -7014,7 +7063,7 @@
         <v>236</v>
       </c>
       <c r="C99" t="s">
-        <v>739</v>
+        <v>736</v>
       </c>
       <c r="D99" t="s">
         <v>564</v>
@@ -7040,13 +7089,13 @@
     </row>
     <row r="100" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
-        <v>740</v>
+        <v>737</v>
       </c>
       <c r="B100" t="s">
-        <v>741</v>
+        <v>738</v>
       </c>
       <c r="C100" t="s">
-        <v>742</v>
+        <v>739</v>
       </c>
       <c r="D100" t="s">
         <v>626</v>
@@ -7078,7 +7127,7 @@
         <v>301</v>
       </c>
       <c r="C101" t="s">
-        <v>743</v>
+        <v>740</v>
       </c>
       <c r="D101" t="s">
         <v>564</v>
@@ -7104,13 +7153,13 @@
     </row>
     <row r="102" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
-        <v>744</v>
+        <v>741</v>
       </c>
       <c r="B102" t="s">
         <v>238</v>
       </c>
       <c r="C102" t="s">
-        <v>745</v>
+        <v>742</v>
       </c>
       <c r="D102" t="s">
         <v>558</v>
@@ -7136,13 +7185,13 @@
     </row>
     <row r="103" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
-        <v>746</v>
+        <v>743</v>
       </c>
       <c r="B103" t="s">
         <v>231</v>
       </c>
       <c r="C103" t="s">
-        <v>747</v>
+        <v>744</v>
       </c>
       <c r="D103" t="s">
         <v>558</v>
@@ -7168,13 +7217,13 @@
     </row>
     <row r="104" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
-        <v>748</v>
+        <v>745</v>
       </c>
       <c r="B104" t="s">
-        <v>749</v>
+        <v>746</v>
       </c>
       <c r="C104" t="s">
-        <v>750</v>
+        <v>747</v>
       </c>
       <c r="D104" t="s">
         <v>570</v>
@@ -7200,13 +7249,13 @@
     </row>
     <row r="105" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
-        <v>751</v>
+        <v>748</v>
       </c>
       <c r="B105" t="s">
-        <v>752</v>
+        <v>749</v>
       </c>
       <c r="C105" t="s">
-        <v>753</v>
+        <v>750</v>
       </c>
       <c r="D105" t="s">
         <v>594</v>
@@ -7232,13 +7281,13 @@
     </row>
     <row r="106" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
-        <v>754</v>
+        <v>751</v>
       </c>
       <c r="B106" t="s">
         <v>264</v>
       </c>
       <c r="C106" t="s">
-        <v>755</v>
+        <v>752</v>
       </c>
       <c r="D106" t="s">
         <v>564</v>
@@ -7270,7 +7319,7 @@
         <v>387</v>
       </c>
       <c r="C107" t="s">
-        <v>756</v>
+        <v>753</v>
       </c>
       <c r="D107" t="s">
         <v>570</v>
@@ -7296,13 +7345,13 @@
     </row>
     <row r="108" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
-        <v>757</v>
+        <v>754</v>
       </c>
       <c r="B108" t="s">
         <v>359</v>
       </c>
       <c r="C108" t="s">
-        <v>758</v>
+        <v>755</v>
       </c>
       <c r="D108" t="s">
         <v>570</v>
@@ -7334,7 +7383,7 @@
         <v>247</v>
       </c>
       <c r="C109" t="s">
-        <v>759</v>
+        <v>756</v>
       </c>
       <c r="D109" t="s">
         <v>615</v>
@@ -7360,13 +7409,13 @@
     </row>
     <row r="110" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
-        <v>760</v>
+        <v>757</v>
       </c>
       <c r="B110" t="s">
         <v>303</v>
       </c>
       <c r="C110" t="s">
-        <v>761</v>
+        <v>758</v>
       </c>
       <c r="D110" t="s">
         <v>575</v>
@@ -7392,16 +7441,16 @@
     </row>
     <row r="111" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
+        <v>759</v>
+      </c>
+      <c r="B111" t="s">
+        <v>760</v>
+      </c>
+      <c r="C111" t="s">
+        <v>761</v>
+      </c>
+      <c r="D111" t="s">
         <v>762</v>
-      </c>
-      <c r="B111" t="s">
-        <v>763</v>
-      </c>
-      <c r="C111" t="s">
-        <v>764</v>
-      </c>
-      <c r="D111" t="s">
-        <v>765</v>
       </c>
       <c r="E111" s="2">
         <v>28270778.850000001</v>
@@ -7424,16 +7473,16 @@
     </row>
     <row r="112" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
-        <v>766</v>
+        <v>763</v>
       </c>
       <c r="B112" t="s">
-        <v>767</v>
+        <v>764</v>
       </c>
       <c r="C112" t="s">
-        <v>768</v>
+        <v>765</v>
       </c>
       <c r="D112" t="s">
-        <v>724</v>
+        <v>721</v>
       </c>
       <c r="E112" s="2">
         <v>28039685.309999999</v>
@@ -7456,13 +7505,13 @@
     </row>
     <row r="113" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
-        <v>769</v>
+        <v>766</v>
       </c>
       <c r="B113" t="s">
         <v>244</v>
       </c>
       <c r="C113" t="s">
-        <v>770</v>
+        <v>767</v>
       </c>
       <c r="D113" t="s">
         <v>575</v>
@@ -7488,13 +7537,13 @@
     </row>
     <row r="114" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
-        <v>771</v>
+        <v>768</v>
       </c>
       <c r="B114" t="s">
         <v>384</v>
       </c>
       <c r="C114" t="s">
-        <v>772</v>
+        <v>769</v>
       </c>
       <c r="D114" t="s">
         <v>570</v>
@@ -7520,16 +7569,16 @@
     </row>
     <row r="115" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
-        <v>773</v>
+        <v>770</v>
       </c>
       <c r="B115" t="s">
-        <v>774</v>
+        <v>771</v>
       </c>
       <c r="C115" t="s">
-        <v>775</v>
+        <v>772</v>
       </c>
       <c r="D115" t="s">
-        <v>724</v>
+        <v>721</v>
       </c>
       <c r="E115" s="2">
         <v>26059446.960000001</v>
@@ -7552,13 +7601,13 @@
     </row>
     <row r="116" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
-        <v>776</v>
+        <v>773</v>
       </c>
       <c r="B116" t="s">
         <v>229</v>
       </c>
       <c r="C116" t="s">
-        <v>777</v>
+        <v>774</v>
       </c>
       <c r="D116" t="s">
         <v>615</v>
@@ -7584,13 +7633,13 @@
     </row>
     <row r="117" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
-        <v>778</v>
+        <v>775</v>
       </c>
       <c r="B117" t="s">
         <v>456</v>
       </c>
       <c r="C117" t="s">
-        <v>779</v>
+        <v>776</v>
       </c>
       <c r="D117" t="s">
         <v>570</v>
@@ -7616,13 +7665,13 @@
     </row>
     <row r="118" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
-        <v>780</v>
+        <v>777</v>
       </c>
       <c r="B118" t="s">
         <v>266</v>
       </c>
       <c r="C118" t="s">
-        <v>781</v>
+        <v>778</v>
       </c>
       <c r="D118" t="s">
         <v>561</v>
@@ -7648,13 +7697,13 @@
     </row>
     <row r="119" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
-        <v>782</v>
+        <v>779</v>
       </c>
       <c r="B119" t="s">
         <v>203</v>
       </c>
       <c r="C119" t="s">
-        <v>783</v>
+        <v>780</v>
       </c>
       <c r="D119" t="s">
         <v>558</v>
@@ -7680,16 +7729,16 @@
     </row>
     <row r="120" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
-        <v>784</v>
+        <v>781</v>
       </c>
       <c r="B120" t="s">
-        <v>785</v>
+        <v>782</v>
       </c>
       <c r="C120" t="s">
-        <v>786</v>
+        <v>783</v>
       </c>
       <c r="D120" t="s">
-        <v>724</v>
+        <v>721</v>
       </c>
       <c r="E120" s="2">
         <v>23494685.760000002</v>
@@ -7712,13 +7761,13 @@
     </row>
     <row r="121" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
-        <v>787</v>
+        <v>784</v>
       </c>
       <c r="B121" t="s">
-        <v>788</v>
+        <v>785</v>
       </c>
       <c r="C121" t="s">
-        <v>789</v>
+        <v>786</v>
       </c>
       <c r="D121" t="s">
         <v>570</v>
@@ -7750,7 +7799,7 @@
         <v>225</v>
       </c>
       <c r="C122" t="s">
-        <v>790</v>
+        <v>787</v>
       </c>
       <c r="D122" t="s">
         <v>570</v>
@@ -7776,13 +7825,13 @@
     </row>
     <row r="123" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
-        <v>791</v>
+        <v>788</v>
       </c>
       <c r="B123" t="s">
         <v>317</v>
       </c>
       <c r="C123" t="s">
-        <v>792</v>
+        <v>789</v>
       </c>
       <c r="D123" t="s">
         <v>570</v>
@@ -7808,13 +7857,13 @@
     </row>
     <row r="124" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
-        <v>793</v>
+        <v>790</v>
       </c>
       <c r="B124" t="s">
-        <v>794</v>
+        <v>791</v>
       </c>
       <c r="C124" t="s">
-        <v>795</v>
+        <v>792</v>
       </c>
       <c r="D124" t="s">
         <v>615</v>
@@ -7840,13 +7889,13 @@
     </row>
     <row r="125" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
-        <v>796</v>
+        <v>793</v>
       </c>
       <c r="B125" t="s">
         <v>280</v>
       </c>
       <c r="C125" t="s">
-        <v>797</v>
+        <v>794</v>
       </c>
       <c r="D125" t="s">
         <v>615</v>
@@ -7872,13 +7921,13 @@
     </row>
     <row r="126" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
-        <v>798</v>
+        <v>795</v>
       </c>
       <c r="B126" t="s">
-        <v>799</v>
+        <v>796</v>
       </c>
       <c r="C126" t="s">
-        <v>800</v>
+        <v>797</v>
       </c>
       <c r="D126" t="s">
         <v>564</v>
@@ -7904,13 +7953,13 @@
     </row>
     <row r="127" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
-        <v>801</v>
+        <v>798</v>
       </c>
       <c r="B127" t="s">
-        <v>802</v>
+        <v>799</v>
       </c>
       <c r="C127" t="s">
-        <v>803</v>
+        <v>800</v>
       </c>
       <c r="D127" t="s">
         <v>570</v>
@@ -7936,13 +7985,13 @@
     </row>
     <row r="128" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
-        <v>804</v>
+        <v>801</v>
       </c>
       <c r="B128" t="s">
         <v>330</v>
       </c>
       <c r="C128" t="s">
-        <v>805</v>
+        <v>802</v>
       </c>
       <c r="D128" t="s">
         <v>564</v>
@@ -7968,13 +8017,13 @@
     </row>
     <row r="129" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
-        <v>806</v>
+        <v>803</v>
       </c>
       <c r="B129" t="s">
         <v>337</v>
       </c>
       <c r="C129" t="s">
-        <v>807</v>
+        <v>804</v>
       </c>
       <c r="D129" t="s">
         <v>594</v>
@@ -8000,13 +8049,13 @@
     </row>
     <row r="130" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
-        <v>808</v>
+        <v>805</v>
       </c>
       <c r="B130" t="s">
         <v>355</v>
       </c>
       <c r="C130" t="s">
-        <v>809</v>
+        <v>806</v>
       </c>
       <c r="D130" t="s">
         <v>564</v>
@@ -8032,13 +8081,13 @@
     </row>
     <row r="131" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
-        <v>810</v>
+        <v>807</v>
       </c>
       <c r="B131" t="s">
-        <v>811</v>
+        <v>808</v>
       </c>
       <c r="C131" t="s">
-        <v>812</v>
+        <v>809</v>
       </c>
       <c r="D131" t="s">
         <v>570</v>
@@ -8064,16 +8113,16 @@
     </row>
     <row r="132" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
-        <v>813</v>
+        <v>810</v>
       </c>
       <c r="B132" t="s">
-        <v>814</v>
+        <v>811</v>
       </c>
       <c r="C132" t="s">
-        <v>815</v>
+        <v>812</v>
       </c>
       <c r="D132" t="s">
-        <v>724</v>
+        <v>721</v>
       </c>
       <c r="E132" s="2">
         <v>19315866.600000001</v>
@@ -8096,13 +8145,13 @@
     </row>
     <row r="133" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
-        <v>816</v>
+        <v>813</v>
       </c>
       <c r="B133" t="s">
         <v>389</v>
       </c>
       <c r="C133" t="s">
-        <v>817</v>
+        <v>814</v>
       </c>
       <c r="D133" t="s">
         <v>575</v>
@@ -8128,16 +8177,16 @@
     </row>
     <row r="134" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
-        <v>818</v>
+        <v>815</v>
       </c>
       <c r="B134" t="s">
-        <v>819</v>
+        <v>816</v>
       </c>
       <c r="C134" t="s">
-        <v>820</v>
+        <v>817</v>
       </c>
       <c r="D134" t="s">
-        <v>724</v>
+        <v>721</v>
       </c>
       <c r="E134" s="2">
         <v>19251103.489999998</v>
@@ -8160,13 +8209,13 @@
     </row>
     <row r="135" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
-        <v>821</v>
+        <v>818</v>
       </c>
       <c r="B135" t="s">
-        <v>822</v>
+        <v>819</v>
       </c>
       <c r="C135" t="s">
-        <v>823</v>
+        <v>820</v>
       </c>
       <c r="D135" t="s">
         <v>615</v>
@@ -8192,13 +8241,13 @@
     </row>
     <row r="136" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="B136" t="s">
-        <v>825</v>
+        <v>822</v>
       </c>
       <c r="C136" t="s">
-        <v>826</v>
+        <v>823</v>
       </c>
       <c r="D136" t="s">
         <v>570</v>
@@ -8230,7 +8279,7 @@
         <v>518</v>
       </c>
       <c r="C137" t="s">
-        <v>827</v>
+        <v>824</v>
       </c>
       <c r="D137" t="s">
         <v>570</v>
@@ -8256,13 +8305,13 @@
     </row>
     <row r="138" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
-        <v>828</v>
+        <v>825</v>
       </c>
       <c r="B138" t="s">
         <v>445</v>
       </c>
       <c r="C138" t="s">
-        <v>829</v>
+        <v>826</v>
       </c>
       <c r="D138" t="s">
         <v>564</v>
@@ -8288,13 +8337,13 @@
     </row>
     <row r="139" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
-        <v>830</v>
+        <v>827</v>
       </c>
       <c r="B139" t="s">
-        <v>831</v>
+        <v>828</v>
       </c>
       <c r="C139" t="s">
-        <v>832</v>
+        <v>829</v>
       </c>
       <c r="D139" t="s">
         <v>570</v>
@@ -8326,7 +8375,7 @@
         <v>486</v>
       </c>
       <c r="C140" t="s">
-        <v>833</v>
+        <v>830</v>
       </c>
       <c r="D140" t="s">
         <v>570</v>
@@ -8358,7 +8407,7 @@
         <v>459</v>
       </c>
       <c r="C141" t="s">
-        <v>834</v>
+        <v>831</v>
       </c>
       <c r="D141" t="s">
         <v>570</v>
@@ -8384,16 +8433,16 @@
     </row>
     <row r="142" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
-        <v>835</v>
+        <v>832</v>
       </c>
       <c r="B142" t="s">
-        <v>836</v>
+        <v>833</v>
       </c>
       <c r="C142" t="s">
-        <v>837</v>
+        <v>834</v>
       </c>
       <c r="D142" t="s">
-        <v>724</v>
+        <v>721</v>
       </c>
       <c r="E142" s="2">
         <v>17126065.289999999</v>
@@ -8416,13 +8465,13 @@
     </row>
     <row r="143" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
-        <v>838</v>
+        <v>835</v>
       </c>
       <c r="B143" t="s">
-        <v>839</v>
+        <v>836</v>
       </c>
       <c r="C143" t="s">
-        <v>840</v>
+        <v>837</v>
       </c>
       <c r="D143" t="s">
         <v>570</v>
@@ -8448,13 +8497,13 @@
     </row>
     <row r="144" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
-        <v>841</v>
+        <v>838</v>
       </c>
       <c r="B144" t="s">
         <v>412</v>
       </c>
       <c r="C144" t="s">
-        <v>842</v>
+        <v>839</v>
       </c>
       <c r="D144" t="s">
         <v>570</v>
@@ -8480,13 +8529,13 @@
     </row>
     <row r="145" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
-        <v>843</v>
+        <v>840</v>
       </c>
       <c r="B145" t="s">
-        <v>844</v>
+        <v>841</v>
       </c>
       <c r="C145" t="s">
-        <v>845</v>
+        <v>842</v>
       </c>
       <c r="D145" t="s">
         <v>597</v>
@@ -8512,13 +8561,13 @@
     </row>
     <row r="146" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
       <c r="B146" t="s">
         <v>419</v>
       </c>
       <c r="C146" t="s">
-        <v>847</v>
+        <v>844</v>
       </c>
       <c r="D146" t="s">
         <v>564</v>
@@ -8544,13 +8593,13 @@
     </row>
     <row r="147" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
-        <v>848</v>
+        <v>845</v>
       </c>
       <c r="B147" t="s">
-        <v>849</v>
+        <v>846</v>
       </c>
       <c r="C147" t="s">
-        <v>850</v>
+        <v>847</v>
       </c>
       <c r="D147" t="s">
         <v>570</v>
@@ -8576,16 +8625,16 @@
     </row>
     <row r="148" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
-        <v>851</v>
+        <v>848</v>
       </c>
       <c r="B148" t="s">
-        <v>852</v>
+        <v>849</v>
       </c>
       <c r="C148" t="s">
-        <v>853</v>
+        <v>850</v>
       </c>
       <c r="D148" t="s">
-        <v>724</v>
+        <v>721</v>
       </c>
       <c r="E148" s="2">
         <v>15791596.199999999</v>
@@ -8608,13 +8657,13 @@
     </row>
     <row r="149" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
-        <v>854</v>
+        <v>851</v>
       </c>
       <c r="B149" t="s">
         <v>347</v>
       </c>
       <c r="C149" t="s">
-        <v>855</v>
+        <v>852</v>
       </c>
       <c r="D149" t="s">
         <v>597</v>
@@ -8646,7 +8695,7 @@
         <v>372</v>
       </c>
       <c r="C150" t="s">
-        <v>856</v>
+        <v>853</v>
       </c>
       <c r="D150" t="s">
         <v>561</v>
@@ -8672,13 +8721,13 @@
     </row>
     <row r="151" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
-        <v>857</v>
+        <v>854</v>
       </c>
       <c r="B151" t="s">
-        <v>858</v>
+        <v>855</v>
       </c>
       <c r="C151" t="s">
-        <v>859</v>
+        <v>856</v>
       </c>
       <c r="D151" t="s">
         <v>570</v>
@@ -8710,7 +8759,7 @@
         <v>258</v>
       </c>
       <c r="C152" t="s">
-        <v>860</v>
+        <v>857</v>
       </c>
       <c r="D152" t="s">
         <v>570</v>
@@ -8736,13 +8785,13 @@
     </row>
     <row r="153" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
-        <v>861</v>
+        <v>858</v>
       </c>
       <c r="B153" t="s">
         <v>376</v>
       </c>
       <c r="C153" t="s">
-        <v>862</v>
+        <v>859</v>
       </c>
       <c r="D153" t="s">
         <v>564</v>
@@ -8774,7 +8823,7 @@
         <v>343</v>
       </c>
       <c r="C154" t="s">
-        <v>863</v>
+        <v>860</v>
       </c>
       <c r="D154" t="s">
         <v>575</v>
@@ -8800,13 +8849,13 @@
     </row>
     <row r="155" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
-        <v>864</v>
+        <v>861</v>
       </c>
       <c r="B155" t="s">
         <v>335</v>
       </c>
       <c r="C155" t="s">
-        <v>865</v>
+        <v>862</v>
       </c>
       <c r="D155" t="s">
         <v>564</v>
@@ -8832,13 +8881,13 @@
     </row>
     <row r="156" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
-        <v>866</v>
+        <v>863</v>
       </c>
       <c r="B156" t="s">
         <v>382</v>
       </c>
       <c r="C156" t="s">
-        <v>867</v>
+        <v>864</v>
       </c>
       <c r="D156" t="s">
         <v>575</v>
@@ -8864,13 +8913,13 @@
     </row>
     <row r="157" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
-        <v>868</v>
+        <v>865</v>
       </c>
       <c r="B157" t="s">
-        <v>869</v>
+        <v>866</v>
       </c>
       <c r="C157" t="s">
-        <v>870</v>
+        <v>867</v>
       </c>
       <c r="D157" t="s">
         <v>564</v>
@@ -8896,13 +8945,13 @@
     </row>
     <row r="158" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
-        <v>871</v>
+        <v>868</v>
       </c>
       <c r="B158" t="s">
         <v>397</v>
       </c>
       <c r="C158" t="s">
-        <v>872</v>
+        <v>869</v>
       </c>
       <c r="D158" t="s">
         <v>564</v>
@@ -8934,7 +8983,7 @@
         <v>481</v>
       </c>
       <c r="C159" t="s">
-        <v>873</v>
+        <v>870</v>
       </c>
       <c r="D159" t="s">
         <v>564</v>
@@ -8966,7 +9015,7 @@
         <v>464</v>
       </c>
       <c r="C160" t="s">
-        <v>874</v>
+        <v>871</v>
       </c>
       <c r="D160" t="s">
         <v>558</v>
@@ -8992,13 +9041,13 @@
     </row>
     <row r="161" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
-        <v>875</v>
+        <v>872</v>
       </c>
       <c r="B161" t="s">
         <v>345</v>
       </c>
       <c r="C161" t="s">
-        <v>876</v>
+        <v>873</v>
       </c>
       <c r="D161" t="s">
         <v>558</v>
@@ -9024,13 +9073,13 @@
     </row>
     <row r="162" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
-        <v>877</v>
+        <v>874</v>
       </c>
       <c r="B162" t="s">
-        <v>878</v>
+        <v>875</v>
       </c>
       <c r="C162" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
       <c r="D162" t="s">
         <v>570</v>
@@ -9056,16 +9105,16 @@
     </row>
     <row r="163" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
-        <v>880</v>
+        <v>877</v>
       </c>
       <c r="B163" t="s">
-        <v>881</v>
+        <v>878</v>
       </c>
       <c r="C163" t="s">
-        <v>882</v>
+        <v>879</v>
       </c>
       <c r="D163" t="s">
-        <v>724</v>
+        <v>721</v>
       </c>
       <c r="E163" s="2">
         <v>13028715.15</v>
@@ -9088,13 +9137,13 @@
     </row>
     <row r="164" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
-        <v>883</v>
+        <v>880</v>
       </c>
       <c r="B164" t="s">
-        <v>884</v>
+        <v>881</v>
       </c>
       <c r="C164" t="s">
-        <v>885</v>
+        <v>882</v>
       </c>
       <c r="D164" t="s">
         <v>564</v>
@@ -9120,16 +9169,16 @@
     </row>
     <row r="165" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
-        <v>886</v>
+        <v>883</v>
       </c>
       <c r="B165" t="s">
-        <v>887</v>
+        <v>884</v>
       </c>
       <c r="C165" t="s">
-        <v>888</v>
+        <v>885</v>
       </c>
       <c r="D165" t="s">
-        <v>724</v>
+        <v>721</v>
       </c>
       <c r="E165" s="2">
         <v>12329302.26</v>
@@ -9152,13 +9201,13 @@
     </row>
     <row r="166" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
-        <v>889</v>
+        <v>886</v>
       </c>
       <c r="B166" t="s">
-        <v>890</v>
+        <v>887</v>
       </c>
       <c r="C166" t="s">
-        <v>891</v>
+        <v>888</v>
       </c>
       <c r="D166" t="s">
         <v>570</v>
@@ -9184,13 +9233,13 @@
     </row>
     <row r="167" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
-        <v>892</v>
+        <v>889</v>
       </c>
       <c r="B167" t="s">
-        <v>893</v>
+        <v>890</v>
       </c>
       <c r="C167" t="s">
-        <v>894</v>
+        <v>891</v>
       </c>
       <c r="D167" t="s">
         <v>564</v>
@@ -9216,13 +9265,13 @@
     </row>
     <row r="168" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
-        <v>895</v>
+        <v>892</v>
       </c>
       <c r="B168" t="s">
         <v>531</v>
       </c>
       <c r="C168" t="s">
-        <v>896</v>
+        <v>893</v>
       </c>
       <c r="D168" t="s">
         <v>575</v>
@@ -9248,13 +9297,13 @@
     </row>
     <row r="169" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
-        <v>897</v>
+        <v>894</v>
       </c>
       <c r="B169" t="s">
         <v>428</v>
       </c>
       <c r="C169" t="s">
-        <v>898</v>
+        <v>895</v>
       </c>
       <c r="D169" t="s">
         <v>575</v>
@@ -9286,10 +9335,10 @@
         <v>417</v>
       </c>
       <c r="C170" t="s">
-        <v>899</v>
+        <v>896</v>
       </c>
       <c r="D170" t="s">
-        <v>765</v>
+        <v>762</v>
       </c>
       <c r="E170" s="2">
         <v>11663144</v>
@@ -9312,13 +9361,13 @@
     </row>
     <row r="171" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
-        <v>900</v>
+        <v>897</v>
       </c>
       <c r="B171" t="s">
-        <v>901</v>
+        <v>898</v>
       </c>
       <c r="C171" t="s">
-        <v>902</v>
+        <v>899</v>
       </c>
       <c r="D171" t="s">
         <v>564</v>
@@ -9344,13 +9393,13 @@
     </row>
     <row r="172" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
-        <v>903</v>
+        <v>900</v>
       </c>
       <c r="B172" t="s">
         <v>408</v>
       </c>
       <c r="C172" t="s">
-        <v>904</v>
+        <v>901</v>
       </c>
       <c r="D172" t="s">
         <v>594</v>
@@ -9376,16 +9425,16 @@
     </row>
     <row r="173" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
-        <v>905</v>
+        <v>902</v>
       </c>
       <c r="B173" t="s">
         <v>414</v>
       </c>
       <c r="C173" t="s">
-        <v>906</v>
+        <v>903</v>
       </c>
       <c r="D173" t="s">
-        <v>724</v>
+        <v>721</v>
       </c>
       <c r="E173" s="2">
         <v>11326208.640000001</v>
@@ -9408,13 +9457,13 @@
     </row>
     <row r="174" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
-        <v>907</v>
+        <v>904</v>
       </c>
       <c r="B174" t="s">
         <v>366</v>
       </c>
       <c r="C174" t="s">
-        <v>908</v>
+        <v>905</v>
       </c>
       <c r="D174" t="s">
         <v>615</v>
@@ -9440,16 +9489,16 @@
     </row>
     <row r="175" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
-        <v>909</v>
+        <v>906</v>
       </c>
       <c r="B175" t="s">
-        <v>910</v>
+        <v>907</v>
       </c>
       <c r="C175" t="s">
-        <v>911</v>
+        <v>908</v>
       </c>
       <c r="D175" t="s">
-        <v>765</v>
+        <v>762</v>
       </c>
       <c r="E175" s="2">
         <v>10470354.300000001</v>
@@ -9472,13 +9521,13 @@
     </row>
     <row r="176" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
-        <v>912</v>
+        <v>909</v>
       </c>
       <c r="B176" t="s">
         <v>496</v>
       </c>
       <c r="C176" t="s">
-        <v>913</v>
+        <v>910</v>
       </c>
       <c r="D176" t="s">
         <v>558</v>
@@ -9504,13 +9553,13 @@
     </row>
     <row r="177" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
-        <v>914</v>
+        <v>911</v>
       </c>
       <c r="B177" t="s">
-        <v>915</v>
+        <v>912</v>
       </c>
       <c r="C177" t="s">
-        <v>916</v>
+        <v>913</v>
       </c>
       <c r="D177" t="s">
         <v>575</v>
@@ -9536,13 +9585,13 @@
     </row>
     <row r="178" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
-        <v>917</v>
+        <v>914</v>
       </c>
       <c r="B178" t="s">
         <v>478</v>
       </c>
       <c r="C178" t="s">
-        <v>918</v>
+        <v>915</v>
       </c>
       <c r="D178" t="s">
         <v>575</v>
@@ -9574,7 +9623,7 @@
         <v>443</v>
       </c>
       <c r="C179" t="s">
-        <v>919</v>
+        <v>916</v>
       </c>
       <c r="D179" t="s">
         <v>561</v>
@@ -9600,13 +9649,13 @@
     </row>
     <row r="180" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
-        <v>920</v>
+        <v>917</v>
       </c>
       <c r="B180" t="s">
         <v>461</v>
       </c>
       <c r="C180" t="s">
-        <v>921</v>
+        <v>918</v>
       </c>
       <c r="D180" t="s">
         <v>564</v>
@@ -9632,16 +9681,16 @@
     </row>
     <row r="181" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
-        <v>922</v>
+        <v>919</v>
       </c>
       <c r="B181" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="C181" t="s">
-        <v>924</v>
+        <v>921</v>
       </c>
       <c r="D181" t="s">
-        <v>724</v>
+        <v>721</v>
       </c>
       <c r="E181" s="2">
         <v>9537194.9000000004</v>
@@ -9664,13 +9713,13 @@
     </row>
     <row r="182" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
-        <v>925</v>
+        <v>922</v>
       </c>
       <c r="B182" t="s">
         <v>535</v>
       </c>
       <c r="C182" t="s">
-        <v>926</v>
+        <v>923</v>
       </c>
       <c r="D182" t="s">
         <v>564</v>
@@ -9696,13 +9745,13 @@
     </row>
     <row r="183" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
-        <v>927</v>
+        <v>924</v>
       </c>
       <c r="B183" t="s">
         <v>391</v>
       </c>
       <c r="C183" t="s">
-        <v>928</v>
+        <v>925</v>
       </c>
       <c r="D183" t="s">
         <v>626</v>
@@ -9728,13 +9777,13 @@
     </row>
     <row r="184" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
-        <v>929</v>
+        <v>926</v>
       </c>
       <c r="B184" t="s">
         <v>500</v>
       </c>
       <c r="C184" t="s">
-        <v>930</v>
+        <v>927</v>
       </c>
       <c r="D184" t="s">
         <v>564</v>
@@ -9760,13 +9809,13 @@
     </row>
     <row r="185" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
-        <v>931</v>
+        <v>928</v>
       </c>
       <c r="B185" t="s">
         <v>488</v>
       </c>
       <c r="C185" t="s">
-        <v>932</v>
+        <v>929</v>
       </c>
       <c r="D185" t="s">
         <v>570</v>
@@ -9792,16 +9841,16 @@
     </row>
     <row r="186" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
-        <v>933</v>
+        <v>930</v>
       </c>
       <c r="B186" t="s">
         <v>522</v>
       </c>
       <c r="C186" t="s">
-        <v>934</v>
+        <v>931</v>
       </c>
       <c r="D186" t="s">
-        <v>765</v>
+        <v>762</v>
       </c>
       <c r="E186" s="2">
         <v>9233897.9700000007</v>
@@ -9824,13 +9873,13 @@
     </row>
     <row r="187" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
-        <v>935</v>
+        <v>932</v>
       </c>
       <c r="B187" t="s">
-        <v>936</v>
+        <v>933</v>
       </c>
       <c r="C187" t="s">
-        <v>937</v>
+        <v>934</v>
       </c>
       <c r="D187" t="s">
         <v>575</v>
@@ -9856,13 +9905,13 @@
     </row>
     <row r="188" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
-        <v>938</v>
+        <v>935</v>
       </c>
       <c r="B188" t="s">
         <v>449</v>
       </c>
       <c r="C188" t="s">
-        <v>939</v>
+        <v>936</v>
       </c>
       <c r="D188" t="s">
         <v>597</v>
@@ -9888,13 +9937,13 @@
     </row>
     <row r="189" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
-        <v>940</v>
+        <v>937</v>
       </c>
       <c r="B189" t="s">
         <v>492</v>
       </c>
       <c r="C189" t="s">
-        <v>941</v>
+        <v>938</v>
       </c>
       <c r="D189" t="s">
         <v>564</v>
@@ -9920,13 +9969,13 @@
     </row>
     <row r="190" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A190" t="s">
-        <v>942</v>
+        <v>939</v>
       </c>
       <c r="B190" t="s">
         <v>364</v>
       </c>
       <c r="C190" t="s">
-        <v>943</v>
+        <v>940</v>
       </c>
       <c r="D190" t="s">
         <v>594</v>
@@ -9952,16 +10001,16 @@
     </row>
     <row r="191" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
-        <v>944</v>
+        <v>941</v>
       </c>
       <c r="B191" t="s">
-        <v>945</v>
+        <v>942</v>
       </c>
       <c r="C191" t="s">
-        <v>946</v>
+        <v>943</v>
       </c>
       <c r="D191" t="s">
-        <v>724</v>
+        <v>721</v>
       </c>
       <c r="E191" s="2">
         <v>8782364.6699999999</v>
@@ -9984,13 +10033,13 @@
     </row>
     <row r="192" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A192" t="s">
-        <v>947</v>
+        <v>944</v>
       </c>
       <c r="B192" t="s">
-        <v>948</v>
+        <v>945</v>
       </c>
       <c r="C192" t="s">
-        <v>949</v>
+        <v>946</v>
       </c>
       <c r="D192" t="s">
         <v>558</v>
@@ -10016,13 +10065,13 @@
     </row>
     <row r="193" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
-        <v>950</v>
+        <v>947</v>
       </c>
       <c r="B193" t="s">
         <v>421</v>
       </c>
       <c r="C193" t="s">
-        <v>951</v>
+        <v>948</v>
       </c>
       <c r="D193" t="s">
         <v>564</v>
@@ -10054,7 +10103,7 @@
         <v>540</v>
       </c>
       <c r="C194" t="s">
-        <v>952</v>
+        <v>949</v>
       </c>
       <c r="D194" t="s">
         <v>564</v>
@@ -10080,16 +10129,16 @@
     </row>
     <row r="195" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
-        <v>953</v>
+        <v>950</v>
       </c>
       <c r="B195" t="s">
-        <v>954</v>
+        <v>951</v>
       </c>
       <c r="C195" t="s">
-        <v>955</v>
+        <v>952</v>
       </c>
       <c r="D195" t="s">
-        <v>724</v>
+        <v>721</v>
       </c>
       <c r="E195" s="2">
         <v>8073383.7999999998</v>
@@ -10112,13 +10161,13 @@
     </row>
     <row r="196" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
-        <v>956</v>
+        <v>953</v>
       </c>
       <c r="B196" t="s">
-        <v>957</v>
+        <v>954</v>
       </c>
       <c r="C196" t="s">
-        <v>958</v>
+        <v>955</v>
       </c>
       <c r="D196" t="s">
         <v>564</v>
@@ -10144,13 +10193,13 @@
     </row>
     <row r="197" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
-        <v>959</v>
+        <v>956</v>
       </c>
       <c r="B197" t="s">
-        <v>960</v>
+        <v>957</v>
       </c>
       <c r="C197" t="s">
-        <v>961</v>
+        <v>958</v>
       </c>
       <c r="D197" t="s">
         <v>570</v>
@@ -10176,16 +10225,16 @@
     </row>
     <row r="198" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
-        <v>962</v>
+        <v>959</v>
       </c>
       <c r="B198" t="s">
-        <v>963</v>
+        <v>960</v>
       </c>
       <c r="C198" t="s">
-        <v>964</v>
+        <v>961</v>
       </c>
       <c r="D198" t="s">
-        <v>724</v>
+        <v>721</v>
       </c>
       <c r="E198" s="2">
         <v>7986659.8399999999</v>
@@ -10208,16 +10257,16 @@
     </row>
     <row r="199" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
-        <v>965</v>
+        <v>962</v>
       </c>
       <c r="B199" t="s">
-        <v>966</v>
+        <v>963</v>
       </c>
       <c r="C199" t="s">
-        <v>967</v>
+        <v>964</v>
       </c>
       <c r="D199" t="s">
-        <v>724</v>
+        <v>721</v>
       </c>
       <c r="E199" s="2">
         <v>7947426.0499999998</v>
@@ -10240,13 +10289,13 @@
     </row>
     <row r="200" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
-        <v>968</v>
+        <v>965</v>
       </c>
       <c r="B200" t="s">
         <v>510</v>
       </c>
       <c r="C200" t="s">
-        <v>969</v>
+        <v>966</v>
       </c>
       <c r="D200" t="s">
         <v>615</v>
@@ -10272,13 +10321,13 @@
     </row>
     <row r="201" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
-        <v>970</v>
+        <v>967</v>
       </c>
       <c r="B201" t="s">
-        <v>971</v>
+        <v>968</v>
       </c>
       <c r="C201" t="s">
-        <v>972</v>
+        <v>969</v>
       </c>
       <c r="D201" t="s">
         <v>575</v>
@@ -10304,13 +10353,13 @@
     </row>
     <row r="202" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
-        <v>973</v>
+        <v>970</v>
       </c>
       <c r="B202" t="s">
         <v>426</v>
       </c>
       <c r="C202" t="s">
-        <v>974</v>
+        <v>971</v>
       </c>
       <c r="D202" t="s">
         <v>558</v>
@@ -10336,13 +10385,13 @@
     </row>
     <row r="203" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A203" t="s">
-        <v>975</v>
+        <v>972</v>
       </c>
       <c r="B203" t="s">
         <v>430</v>
       </c>
       <c r="C203" t="s">
-        <v>976</v>
+        <v>973</v>
       </c>
       <c r="D203" t="s">
         <v>564</v>
@@ -10368,13 +10417,13 @@
     </row>
     <row r="204" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A204" t="s">
-        <v>977</v>
+        <v>974</v>
       </c>
       <c r="B204" t="s">
         <v>506</v>
       </c>
       <c r="C204" t="s">
-        <v>978</v>
+        <v>975</v>
       </c>
       <c r="D204" t="s">
         <v>575</v>
@@ -10400,13 +10449,13 @@
     </row>
     <row r="205" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A205" t="s">
-        <v>979</v>
+        <v>976</v>
       </c>
       <c r="B205" t="s">
         <v>546</v>
       </c>
       <c r="C205" t="s">
-        <v>980</v>
+        <v>977</v>
       </c>
       <c r="D205" t="s">
         <v>594</v>
@@ -10432,13 +10481,13 @@
     </row>
     <row r="206" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
-        <v>981</v>
+        <v>978</v>
       </c>
       <c r="B206" t="s">
-        <v>982</v>
+        <v>979</v>
       </c>
       <c r="C206" t="s">
-        <v>983</v>
+        <v>980</v>
       </c>
       <c r="D206" t="s">
         <v>575</v>
@@ -10464,16 +10513,16 @@
     </row>
     <row r="207" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A207" t="s">
-        <v>984</v>
+        <v>981</v>
       </c>
       <c r="B207" t="s">
-        <v>985</v>
+        <v>982</v>
       </c>
       <c r="C207" t="s">
-        <v>986</v>
+        <v>983</v>
       </c>
       <c r="D207" t="s">
-        <v>724</v>
+        <v>721</v>
       </c>
       <c r="E207" s="2">
         <v>5837298.0300000003</v>
@@ -10496,13 +10545,13 @@
     </row>
     <row r="208" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A208" t="s">
-        <v>987</v>
+        <v>984</v>
       </c>
       <c r="B208" t="s">
         <v>399</v>
       </c>
       <c r="C208" t="s">
-        <v>988</v>
+        <v>985</v>
       </c>
       <c r="D208" t="s">
         <v>570</v>
@@ -10528,13 +10577,13 @@
     </row>
     <row r="209" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A209" t="s">
-        <v>989</v>
+        <v>986</v>
       </c>
       <c r="B209" t="s">
         <v>533</v>
       </c>
       <c r="C209" t="s">
-        <v>990</v>
+        <v>987</v>
       </c>
       <c r="D209" t="s">
         <v>575</v>
@@ -10560,13 +10609,13 @@
     </row>
     <row r="210" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A210" t="s">
-        <v>991</v>
+        <v>988</v>
       </c>
       <c r="B210" t="s">
-        <v>992</v>
+        <v>989</v>
       </c>
       <c r="C210" t="s">
-        <v>993</v>
+        <v>990</v>
       </c>
       <c r="D210" t="s">
         <v>564</v>
@@ -10592,16 +10641,16 @@
     </row>
     <row r="211" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A211" t="s">
-        <v>994</v>
+        <v>991</v>
       </c>
       <c r="B211" t="s">
-        <v>995</v>
+        <v>992</v>
       </c>
       <c r="C211" t="s">
-        <v>996</v>
+        <v>993</v>
       </c>
       <c r="D211" t="s">
-        <v>724</v>
+        <v>721</v>
       </c>
       <c r="E211" s="2">
         <v>5383162.8799999999</v>
@@ -10624,13 +10673,13 @@
     </row>
     <row r="212" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A212" t="s">
-        <v>997</v>
+        <v>994</v>
       </c>
       <c r="B212" t="s">
-        <v>998</v>
+        <v>995</v>
       </c>
       <c r="C212" t="s">
-        <v>999</v>
+        <v>996</v>
       </c>
       <c r="D212" t="s">
         <v>594</v>
@@ -10656,13 +10705,13 @@
     </row>
     <row r="213" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A213" t="s">
-        <v>848</v>
+        <v>845</v>
       </c>
       <c r="B213" t="s">
-        <v>849</v>
+        <v>846</v>
       </c>
       <c r="C213" t="s">
-        <v>1000</v>
+        <v>997</v>
       </c>
       <c r="D213" t="s">
         <v>558</v>
@@ -10691,7 +10740,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E228"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>

--- a/Tickers_Info.xlsx
+++ b/Tickers_Info.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1761" uniqueCount="1006">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1761" uniqueCount="985">
   <si>
     <t>Name</t>
   </si>
@@ -1985,18 +1985,12 @@
     <t>BBD.B</t>
   </si>
   <si>
-    <t>BBD.B.TO</t>
-  </si>
-  <si>
     <t>BOMBARDIER INC CLASS B</t>
   </si>
   <si>
     <t>RCI.B</t>
   </si>
   <si>
-    <t>RCI.B.TO</t>
-  </si>
-  <si>
     <t>ROGERS COMMUNICATIONS NON-VOTING I</t>
   </si>
   <si>
@@ -2093,9 +2087,6 @@
     <t>CCL.B</t>
   </si>
   <si>
-    <t>CCL.B.TO</t>
-  </si>
-  <si>
     <t>CCL INDUSTRIES INC CLASS B</t>
   </si>
   <si>
@@ -2237,9 +2228,6 @@
     <t>QBR.B</t>
   </si>
   <si>
-    <t>QBR.B.TO</t>
-  </si>
-  <si>
     <t>QUEBECOR INC CLASS B</t>
   </si>
   <si>
@@ -2270,9 +2258,6 @@
     <t>EMP.A</t>
   </si>
   <si>
-    <t>EMP.A.TO</t>
-  </si>
-  <si>
     <t>EMPIRE LTD CLASS A</t>
   </si>
   <si>
@@ -2303,9 +2288,6 @@
     <t>CSH.UN</t>
   </si>
   <si>
-    <t>CSH.UN.TO</t>
-  </si>
-  <si>
     <t>CHARTWELL RETIREMENT RESIDENCES RE</t>
   </si>
   <si>
@@ -2315,9 +2297,6 @@
     <t>CAR.UN</t>
   </si>
   <si>
-    <t>CAR.UN.TO</t>
-  </si>
-  <si>
     <t>CANADIAN APARTMENT PROPERTIES REAL</t>
   </si>
   <si>
@@ -2336,9 +2315,6 @@
     <t>REI.UN</t>
   </si>
   <si>
-    <t>REI.UN.TO</t>
-  </si>
-  <si>
     <t>RIOCAN REAL ESTATE INVESTMENT TRUS</t>
   </si>
   <si>
@@ -2369,9 +2345,6 @@
     <t>GRT.UN</t>
   </si>
   <si>
-    <t>GRT.UN.TO</t>
-  </si>
-  <si>
     <t>GRANITE REAL ESTATE INVESTMENT STA</t>
   </si>
   <si>
@@ -2456,9 +2429,6 @@
     <t>FCR.UN</t>
   </si>
   <si>
-    <t>FCR.UN.TO</t>
-  </si>
-  <si>
     <t>FIRST CAPITAL REALTY REAL ESTATE I</t>
   </si>
   <si>
@@ -2471,18 +2441,12 @@
     <t>CHP.UN</t>
   </si>
   <si>
-    <t>CHP.UN.TO</t>
-  </si>
-  <si>
     <t>CHOICE PROPERTIES REAL ESTATE INVE</t>
   </si>
   <si>
     <t>ACO.X</t>
   </si>
   <si>
-    <t>ACO.X.TO</t>
-  </si>
-  <si>
     <t>ATCO LTD CLASS I</t>
   </si>
   <si>
@@ -2522,9 +2486,6 @@
     <t>DIR.UN</t>
   </si>
   <si>
-    <t>DIR.UN.TO</t>
-  </si>
-  <si>
     <t>DREAM INDUSTRIAL REAL ESTATE INVES</t>
   </si>
   <si>
@@ -2570,9 +2531,6 @@
     <t>SRU.UN</t>
   </si>
   <si>
-    <t>SRU.UN.TO</t>
-  </si>
-  <si>
     <t>SMARTCENTRES RL ESTATE INVESTMENT</t>
   </si>
   <si>
@@ -2657,9 +2615,6 @@
     <t>HR.UN</t>
   </si>
   <si>
-    <t>HR.UN.TO</t>
-  </si>
-  <si>
     <t>HANDR REAL ESTATE INVESTMENT TRUST</t>
   </si>
   <si>
@@ -2675,9 +2630,6 @@
     <t>BEI.UN</t>
   </si>
   <si>
-    <t>BEI.UN.TO</t>
-  </si>
-  <si>
     <t>BOARDWALK REAL ESTATE INVESTMENT T</t>
   </si>
   <si>
@@ -2759,9 +2711,6 @@
     <t>BBU.UN</t>
   </si>
   <si>
-    <t>BBU.UN.TO</t>
-  </si>
-  <si>
     <t>BROOKFIELD BUSINESS PARTNERS UNITS</t>
   </si>
   <si>
@@ -2783,9 +2732,6 @@
     <t>KMP.UN</t>
   </si>
   <si>
-    <t>KMP.UN.TO</t>
-  </si>
-  <si>
     <t>KILLAM APARTMENT REIT UNITS CLASS</t>
   </si>
   <si>
@@ -2849,9 +2795,6 @@
     <t>IIP.UN</t>
   </si>
   <si>
-    <t>IIP.UN.TO</t>
-  </si>
-  <si>
     <t>INTERRENT REAL ESTATE INVESTMENT T</t>
   </si>
   <si>
@@ -2876,9 +2819,6 @@
     <t>CRR.UN</t>
   </si>
   <si>
-    <t>CRR.UN.TO</t>
-  </si>
-  <si>
     <t>CROMBIE REAL ESTATE INVESTMENT TRU</t>
   </si>
   <si>
@@ -2894,27 +2834,18 @@
     <t>TCL.A</t>
   </si>
   <si>
-    <t>TCL.A.TO</t>
-  </si>
-  <si>
     <t>TRANSCONTINENTAL SUB VOTING INC CL</t>
   </si>
   <si>
     <t>PMZ.UN</t>
   </si>
   <si>
-    <t>PMZ.UN.TO</t>
-  </si>
-  <si>
     <t>PRIMARIS REAL ESTATE INVESTMENT UN</t>
   </si>
   <si>
     <t>AP.UN</t>
   </si>
   <si>
-    <t>AP.UN.TO</t>
-  </si>
-  <si>
     <t>ALLIED PROPERTIES REAL ESTATE INVT</t>
   </si>
   <si>
@@ -2969,9 +2900,6 @@
     <t>CRT.UN</t>
   </si>
   <si>
-    <t>CRT.UN.TO</t>
-  </si>
-  <si>
     <t>CT REIT UNITS TRUST</t>
   </si>
   <si>
@@ -2999,9 +2927,6 @@
     <t>NWH.UN</t>
   </si>
   <si>
-    <t>NWH.UN.TO</t>
-  </si>
-  <si>
     <t>NORTHWEST HEALTHCARE PROPERTIES RE</t>
   </si>
   <si>
@@ -3039,6 +2964,18 @@
   </si>
   <si>
     <t>BIP-UN.TO</t>
+  </si>
+  <si>
+    <t>RCI-B.TO</t>
+  </si>
+  <si>
+    <t>GRT-UN.TO</t>
+  </si>
+  <si>
+    <t>BBU-UN.TO</t>
+  </si>
+  <si>
+    <t>NWH-UN.TO</t>
   </si>
 </sst>
 </file>
@@ -3888,21 +3825,21 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B1" t="s">
-        <v>999</v>
+        <v>974</v>
       </c>
       <c r="C1" t="s">
-        <v>1001</v>
+        <v>976</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>998</v>
+        <v>973</v>
       </c>
       <c r="B3" t="s">
-        <v>1000</v>
+        <v>975</v>
       </c>
       <c r="C3" t="s">
-        <v>1002</v>
+        <v>977</v>
       </c>
     </row>
   </sheetData>
@@ -3915,6 +3852,7 @@
   <dimension ref="A1:J213"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
+    <col min="2" max="2" width="11.44140625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="15" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="12.44140625" bestFit="1" customWidth="1"/>
   </cols>
@@ -5204,7 +5142,7 @@
         <v>628</v>
       </c>
       <c r="B41" t="s">
-        <v>1003</v>
+        <v>978</v>
       </c>
       <c r="C41" t="s">
         <v>629</v>
@@ -5332,7 +5270,7 @@
         <v>635</v>
       </c>
       <c r="B45" t="s">
-        <v>1004</v>
+        <v>979</v>
       </c>
       <c r="C45" t="s">
         <v>636</v>
@@ -5428,7 +5366,7 @@
         <v>640</v>
       </c>
       <c r="B48" t="s">
-        <v>1005</v>
+        <v>980</v>
       </c>
       <c r="C48" t="s">
         <v>641</v>
@@ -5620,10 +5558,10 @@
         <v>653</v>
       </c>
       <c r="B54" t="s">
+        <v>220</v>
+      </c>
+      <c r="C54" t="s">
         <v>654</v>
-      </c>
-      <c r="C54" t="s">
-        <v>655</v>
       </c>
       <c r="D54" t="s">
         <v>575</v>
@@ -5649,13 +5587,13 @@
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
+        <v>655</v>
+      </c>
+      <c r="B55" t="s">
+        <v>981</v>
+      </c>
+      <c r="C55" t="s">
         <v>656</v>
-      </c>
-      <c r="B55" t="s">
-        <v>657</v>
-      </c>
-      <c r="C55" t="s">
-        <v>658</v>
       </c>
       <c r="D55" t="s">
         <v>626</v>
@@ -5681,13 +5619,13 @@
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="B56" t="s">
         <v>198</v>
       </c>
       <c r="C56" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="D56" t="s">
         <v>570</v>
@@ -5719,7 +5657,7 @@
         <v>64</v>
       </c>
       <c r="C57" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="D57" t="s">
         <v>564</v>
@@ -5745,13 +5683,13 @@
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="B58" t="s">
         <v>78</v>
       </c>
       <c r="C58" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="D58" t="s">
         <v>558</v>
@@ -5777,13 +5715,13 @@
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="B59" t="s">
         <v>118</v>
       </c>
       <c r="C59" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="D59" t="s">
         <v>615</v>
@@ -5815,7 +5753,7 @@
         <v>206</v>
       </c>
       <c r="C60" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="D60" t="s">
         <v>597</v>
@@ -5847,7 +5785,7 @@
         <v>178</v>
       </c>
       <c r="C61" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
       <c r="D61" t="s">
         <v>558</v>
@@ -5879,7 +5817,7 @@
         <v>129</v>
       </c>
       <c r="C62" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="D62" t="s">
         <v>575</v>
@@ -5905,13 +5843,13 @@
     </row>
     <row r="63" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="B63" t="s">
         <v>105</v>
       </c>
       <c r="C63" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="D63" t="s">
         <v>594</v>
@@ -5943,7 +5881,7 @@
         <v>157</v>
       </c>
       <c r="C64" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="D64" t="s">
         <v>575</v>
@@ -5969,13 +5907,13 @@
     </row>
     <row r="65" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="B65" t="s">
         <v>152</v>
       </c>
       <c r="C65" t="s">
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="D65" t="s">
         <v>564</v>
@@ -6007,7 +5945,7 @@
         <v>325</v>
       </c>
       <c r="C66" t="s">
-        <v>674</v>
+        <v>672</v>
       </c>
       <c r="D66" t="s">
         <v>570</v>
@@ -6033,13 +5971,13 @@
     </row>
     <row r="67" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>675</v>
+        <v>673</v>
       </c>
       <c r="B67" t="s">
         <v>180</v>
       </c>
       <c r="C67" t="s">
-        <v>676</v>
+        <v>674</v>
       </c>
       <c r="D67" t="s">
         <v>575</v>
@@ -6065,13 +6003,13 @@
     </row>
     <row r="68" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="B68" t="s">
         <v>154</v>
       </c>
       <c r="C68" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="D68" t="s">
         <v>558</v>
@@ -6097,13 +6035,13 @@
     </row>
     <row r="69" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="B69" t="s">
         <v>173</v>
       </c>
       <c r="C69" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
       <c r="D69" t="s">
         <v>575</v>
@@ -6129,13 +6067,13 @@
     </row>
     <row r="70" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="B70" t="s">
         <v>289</v>
       </c>
       <c r="C70" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="D70" t="s">
         <v>564</v>
@@ -6161,13 +6099,13 @@
     </row>
     <row r="71" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>683</v>
+        <v>681</v>
       </c>
       <c r="B71" t="s">
         <v>213</v>
       </c>
       <c r="C71" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="D71" t="s">
         <v>575</v>
@@ -6199,7 +6137,7 @@
         <v>182</v>
       </c>
       <c r="C72" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="D72" t="s">
         <v>575</v>
@@ -6225,13 +6163,13 @@
     </row>
     <row r="73" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
+        <v>684</v>
+      </c>
+      <c r="B73" t="s">
+        <v>685</v>
+      </c>
+      <c r="C73" t="s">
         <v>686</v>
-      </c>
-      <c r="B73" t="s">
-        <v>687</v>
-      </c>
-      <c r="C73" t="s">
-        <v>688</v>
       </c>
       <c r="D73" t="s">
         <v>570</v>
@@ -6257,13 +6195,13 @@
     </row>
     <row r="74" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="B74" t="s">
-        <v>690</v>
+        <v>168</v>
       </c>
       <c r="C74" t="s">
-        <v>691</v>
+        <v>688</v>
       </c>
       <c r="D74" t="s">
         <v>570</v>
@@ -6289,13 +6227,13 @@
     </row>
     <row r="75" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>692</v>
+        <v>689</v>
       </c>
       <c r="B75" t="s">
         <v>192</v>
       </c>
       <c r="C75" t="s">
-        <v>693</v>
+        <v>690</v>
       </c>
       <c r="D75" t="s">
         <v>615</v>
@@ -6327,7 +6265,7 @@
         <v>209</v>
       </c>
       <c r="C76" t="s">
-        <v>694</v>
+        <v>691</v>
       </c>
       <c r="D76" t="s">
         <v>561</v>
@@ -6359,7 +6297,7 @@
         <v>201</v>
       </c>
       <c r="C77" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="D77" t="s">
         <v>575</v>
@@ -6385,13 +6323,13 @@
     </row>
     <row r="78" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>696</v>
+        <v>693</v>
       </c>
       <c r="B78" t="s">
         <v>171</v>
       </c>
       <c r="C78" t="s">
-        <v>697</v>
+        <v>694</v>
       </c>
       <c r="D78" t="s">
         <v>570</v>
@@ -6417,13 +6355,13 @@
     </row>
     <row r="79" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>698</v>
+        <v>695</v>
       </c>
       <c r="B79" t="s">
         <v>233</v>
       </c>
       <c r="C79" t="s">
-        <v>699</v>
+        <v>696</v>
       </c>
       <c r="D79" t="s">
         <v>597</v>
@@ -6455,7 +6393,7 @@
         <v>550</v>
       </c>
       <c r="C80" t="s">
-        <v>700</v>
+        <v>697</v>
       </c>
       <c r="D80" t="s">
         <v>561</v>
@@ -6487,7 +6425,7 @@
         <v>296</v>
       </c>
       <c r="C81" t="s">
-        <v>701</v>
+        <v>698</v>
       </c>
       <c r="D81" t="s">
         <v>570</v>
@@ -6513,13 +6451,13 @@
     </row>
     <row r="82" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
-        <v>702</v>
+        <v>699</v>
       </c>
       <c r="B82" t="s">
         <v>194</v>
       </c>
       <c r="C82" t="s">
-        <v>703</v>
+        <v>700</v>
       </c>
       <c r="D82" t="s">
         <v>594</v>
@@ -6551,7 +6489,7 @@
         <v>322</v>
       </c>
       <c r="C83" t="s">
-        <v>704</v>
+        <v>701</v>
       </c>
       <c r="D83" t="s">
         <v>570</v>
@@ -6577,13 +6515,13 @@
     </row>
     <row r="84" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
-        <v>705</v>
+        <v>702</v>
       </c>
       <c r="B84" t="s">
         <v>141</v>
       </c>
       <c r="C84" t="s">
-        <v>706</v>
+        <v>703</v>
       </c>
       <c r="D84" t="s">
         <v>570</v>
@@ -6609,13 +6547,13 @@
     </row>
     <row r="85" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
-        <v>707</v>
+        <v>704</v>
       </c>
       <c r="B85" t="s">
         <v>211</v>
       </c>
       <c r="C85" t="s">
-        <v>708</v>
+        <v>705</v>
       </c>
       <c r="D85" t="s">
         <v>564</v>
@@ -6641,13 +6579,13 @@
     </row>
     <row r="86" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
-        <v>709</v>
+        <v>706</v>
       </c>
       <c r="B86" t="s">
-        <v>710</v>
+        <v>707</v>
       </c>
       <c r="C86" t="s">
-        <v>711</v>
+        <v>708</v>
       </c>
       <c r="D86" t="s">
         <v>570</v>
@@ -6673,13 +6611,13 @@
     </row>
     <row r="87" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
-        <v>712</v>
+        <v>709</v>
       </c>
       <c r="B87" t="s">
         <v>255</v>
       </c>
       <c r="C87" t="s">
-        <v>713</v>
+        <v>710</v>
       </c>
       <c r="D87" t="s">
         <v>575</v>
@@ -6705,13 +6643,13 @@
     </row>
     <row r="88" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
-        <v>714</v>
+        <v>711</v>
       </c>
       <c r="B88" t="s">
         <v>374</v>
       </c>
       <c r="C88" t="s">
-        <v>715</v>
+        <v>712</v>
       </c>
       <c r="D88" t="s">
         <v>570</v>
@@ -6737,13 +6675,13 @@
     </row>
     <row r="89" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
-        <v>716</v>
+        <v>713</v>
       </c>
       <c r="B89" t="s">
         <v>227</v>
       </c>
       <c r="C89" t="s">
-        <v>717</v>
+        <v>714</v>
       </c>
       <c r="D89" t="s">
         <v>615</v>
@@ -6775,7 +6713,7 @@
         <v>250</v>
       </c>
       <c r="C90" t="s">
-        <v>718</v>
+        <v>715</v>
       </c>
       <c r="D90" t="s">
         <v>570</v>
@@ -6807,7 +6745,7 @@
         <v>312</v>
       </c>
       <c r="C91" t="s">
-        <v>719</v>
+        <v>716</v>
       </c>
       <c r="D91" t="s">
         <v>570</v>
@@ -6839,10 +6777,10 @@
         <v>190</v>
       </c>
       <c r="C92" t="s">
-        <v>720</v>
+        <v>717</v>
       </c>
       <c r="D92" t="s">
-        <v>721</v>
+        <v>718</v>
       </c>
       <c r="E92" s="2">
         <v>42479019.509999998</v>
@@ -6871,10 +6809,10 @@
         <v>216</v>
       </c>
       <c r="C93" t="s">
-        <v>722</v>
+        <v>719</v>
       </c>
       <c r="D93" t="s">
-        <v>721</v>
+        <v>718</v>
       </c>
       <c r="E93" s="2">
         <v>42179351.759999998</v>
@@ -6897,13 +6835,13 @@
     </row>
     <row r="94" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
-        <v>723</v>
+        <v>720</v>
       </c>
       <c r="B94" t="s">
         <v>319</v>
       </c>
       <c r="C94" t="s">
-        <v>724</v>
+        <v>721</v>
       </c>
       <c r="D94" t="s">
         <v>570</v>
@@ -6929,13 +6867,13 @@
     </row>
     <row r="95" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
-        <v>725</v>
+        <v>722</v>
       </c>
       <c r="B95" t="s">
-        <v>726</v>
+        <v>723</v>
       </c>
       <c r="C95" t="s">
-        <v>727</v>
+        <v>724</v>
       </c>
       <c r="D95" t="s">
         <v>597</v>
@@ -6961,13 +6899,13 @@
     </row>
     <row r="96" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="B96" t="s">
-        <v>729</v>
+        <v>726</v>
       </c>
       <c r="C96" t="s">
-        <v>730</v>
+        <v>727</v>
       </c>
       <c r="D96" t="s">
         <v>615</v>
@@ -6993,13 +6931,13 @@
     </row>
     <row r="97" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
-        <v>731</v>
+        <v>728</v>
       </c>
       <c r="B97" t="s">
-        <v>732</v>
+        <v>729</v>
       </c>
       <c r="C97" t="s">
-        <v>733</v>
+        <v>730</v>
       </c>
       <c r="D97" t="s">
         <v>570</v>
@@ -7025,13 +6963,13 @@
     </row>
     <row r="98" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
-        <v>734</v>
+        <v>731</v>
       </c>
       <c r="B98" t="s">
         <v>271</v>
       </c>
       <c r="C98" t="s">
-        <v>735</v>
+        <v>732</v>
       </c>
       <c r="D98" t="s">
         <v>570</v>
@@ -7063,7 +7001,7 @@
         <v>236</v>
       </c>
       <c r="C99" t="s">
-        <v>736</v>
+        <v>733</v>
       </c>
       <c r="D99" t="s">
         <v>564</v>
@@ -7089,13 +7027,13 @@
     </row>
     <row r="100" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
-        <v>737</v>
+        <v>734</v>
       </c>
       <c r="B100" t="s">
-        <v>738</v>
+        <v>222</v>
       </c>
       <c r="C100" t="s">
-        <v>739</v>
+        <v>735</v>
       </c>
       <c r="D100" t="s">
         <v>626</v>
@@ -7127,7 +7065,7 @@
         <v>301</v>
       </c>
       <c r="C101" t="s">
-        <v>740</v>
+        <v>736</v>
       </c>
       <c r="D101" t="s">
         <v>564</v>
@@ -7153,13 +7091,13 @@
     </row>
     <row r="102" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
-        <v>741</v>
+        <v>737</v>
       </c>
       <c r="B102" t="s">
         <v>238</v>
       </c>
       <c r="C102" t="s">
-        <v>742</v>
+        <v>738</v>
       </c>
       <c r="D102" t="s">
         <v>558</v>
@@ -7185,13 +7123,13 @@
     </row>
     <row r="103" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
-        <v>743</v>
+        <v>739</v>
       </c>
       <c r="B103" t="s">
         <v>231</v>
       </c>
       <c r="C103" t="s">
-        <v>744</v>
+        <v>740</v>
       </c>
       <c r="D103" t="s">
         <v>558</v>
@@ -7217,13 +7155,13 @@
     </row>
     <row r="104" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
-        <v>745</v>
+        <v>741</v>
       </c>
       <c r="B104" t="s">
-        <v>746</v>
+        <v>742</v>
       </c>
       <c r="C104" t="s">
-        <v>747</v>
+        <v>743</v>
       </c>
       <c r="D104" t="s">
         <v>570</v>
@@ -7249,13 +7187,13 @@
     </row>
     <row r="105" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
-        <v>748</v>
+        <v>744</v>
       </c>
       <c r="B105" t="s">
-        <v>749</v>
+        <v>184</v>
       </c>
       <c r="C105" t="s">
-        <v>750</v>
+        <v>745</v>
       </c>
       <c r="D105" t="s">
         <v>594</v>
@@ -7281,13 +7219,13 @@
     </row>
     <row r="106" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
-        <v>751</v>
+        <v>746</v>
       </c>
       <c r="B106" t="s">
         <v>264</v>
       </c>
       <c r="C106" t="s">
-        <v>752</v>
+        <v>747</v>
       </c>
       <c r="D106" t="s">
         <v>564</v>
@@ -7319,7 +7257,7 @@
         <v>387</v>
       </c>
       <c r="C107" t="s">
-        <v>753</v>
+        <v>748</v>
       </c>
       <c r="D107" t="s">
         <v>570</v>
@@ -7345,13 +7283,13 @@
     </row>
     <row r="108" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
-        <v>754</v>
+        <v>749</v>
       </c>
       <c r="B108" t="s">
         <v>359</v>
       </c>
       <c r="C108" t="s">
-        <v>755</v>
+        <v>750</v>
       </c>
       <c r="D108" t="s">
         <v>570</v>
@@ -7383,7 +7321,7 @@
         <v>247</v>
       </c>
       <c r="C109" t="s">
-        <v>756</v>
+        <v>751</v>
       </c>
       <c r="D109" t="s">
         <v>615</v>
@@ -7409,13 +7347,13 @@
     </row>
     <row r="110" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
-        <v>757</v>
+        <v>752</v>
       </c>
       <c r="B110" t="s">
         <v>303</v>
       </c>
       <c r="C110" t="s">
-        <v>758</v>
+        <v>753</v>
       </c>
       <c r="D110" t="s">
         <v>575</v>
@@ -7441,16 +7379,16 @@
     </row>
     <row r="111" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
-        <v>759</v>
+        <v>754</v>
       </c>
       <c r="B111" t="s">
-        <v>760</v>
+        <v>287</v>
       </c>
       <c r="C111" t="s">
-        <v>761</v>
+        <v>755</v>
       </c>
       <c r="D111" t="s">
-        <v>762</v>
+        <v>756</v>
       </c>
       <c r="E111" s="2">
         <v>28270778.850000001</v>
@@ -7473,16 +7411,16 @@
     </row>
     <row r="112" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
-        <v>763</v>
+        <v>757</v>
       </c>
       <c r="B112" t="s">
-        <v>764</v>
+        <v>242</v>
       </c>
       <c r="C112" t="s">
-        <v>765</v>
+        <v>758</v>
       </c>
       <c r="D112" t="s">
-        <v>721</v>
+        <v>718</v>
       </c>
       <c r="E112" s="2">
         <v>28039685.309999999</v>
@@ -7505,13 +7443,13 @@
     </row>
     <row r="113" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
-        <v>766</v>
+        <v>759</v>
       </c>
       <c r="B113" t="s">
         <v>244</v>
       </c>
       <c r="C113" t="s">
-        <v>767</v>
+        <v>760</v>
       </c>
       <c r="D113" t="s">
         <v>575</v>
@@ -7537,13 +7475,13 @@
     </row>
     <row r="114" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
-        <v>768</v>
+        <v>761</v>
       </c>
       <c r="B114" t="s">
         <v>384</v>
       </c>
       <c r="C114" t="s">
-        <v>769</v>
+        <v>762</v>
       </c>
       <c r="D114" t="s">
         <v>570</v>
@@ -7569,16 +7507,16 @@
     </row>
     <row r="115" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
-        <v>770</v>
+        <v>763</v>
       </c>
       <c r="B115" t="s">
-        <v>771</v>
+        <v>275</v>
       </c>
       <c r="C115" t="s">
-        <v>772</v>
+        <v>764</v>
       </c>
       <c r="D115" t="s">
-        <v>721</v>
+        <v>718</v>
       </c>
       <c r="E115" s="2">
         <v>26059446.960000001</v>
@@ -7601,13 +7539,13 @@
     </row>
     <row r="116" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
-        <v>773</v>
+        <v>765</v>
       </c>
       <c r="B116" t="s">
         <v>229</v>
       </c>
       <c r="C116" t="s">
-        <v>774</v>
+        <v>766</v>
       </c>
       <c r="D116" t="s">
         <v>615</v>
@@ -7633,13 +7571,13 @@
     </row>
     <row r="117" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
-        <v>775</v>
+        <v>767</v>
       </c>
       <c r="B117" t="s">
         <v>456</v>
       </c>
       <c r="C117" t="s">
-        <v>776</v>
+        <v>768</v>
       </c>
       <c r="D117" t="s">
         <v>570</v>
@@ -7665,13 +7603,13 @@
     </row>
     <row r="118" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
-        <v>777</v>
+        <v>769</v>
       </c>
       <c r="B118" t="s">
         <v>266</v>
       </c>
       <c r="C118" t="s">
-        <v>778</v>
+        <v>770</v>
       </c>
       <c r="D118" t="s">
         <v>561</v>
@@ -7697,13 +7635,13 @@
     </row>
     <row r="119" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
-        <v>779</v>
+        <v>771</v>
       </c>
       <c r="B119" t="s">
         <v>203</v>
       </c>
       <c r="C119" t="s">
-        <v>780</v>
+        <v>772</v>
       </c>
       <c r="D119" t="s">
         <v>558</v>
@@ -7729,16 +7667,16 @@
     </row>
     <row r="120" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
-        <v>781</v>
+        <v>773</v>
       </c>
       <c r="B120" t="s">
-        <v>782</v>
+        <v>982</v>
       </c>
       <c r="C120" t="s">
-        <v>783</v>
+        <v>774</v>
       </c>
       <c r="D120" t="s">
-        <v>721</v>
+        <v>718</v>
       </c>
       <c r="E120" s="2">
         <v>23494685.760000002</v>
@@ -7761,13 +7699,13 @@
     </row>
     <row r="121" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
-        <v>784</v>
+        <v>775</v>
       </c>
       <c r="B121" t="s">
-        <v>785</v>
+        <v>776</v>
       </c>
       <c r="C121" t="s">
-        <v>786</v>
+        <v>777</v>
       </c>
       <c r="D121" t="s">
         <v>570</v>
@@ -7799,7 +7737,7 @@
         <v>225</v>
       </c>
       <c r="C122" t="s">
-        <v>787</v>
+        <v>778</v>
       </c>
       <c r="D122" t="s">
         <v>570</v>
@@ -7825,13 +7763,13 @@
     </row>
     <row r="123" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
-        <v>788</v>
+        <v>779</v>
       </c>
       <c r="B123" t="s">
         <v>317</v>
       </c>
       <c r="C123" t="s">
-        <v>789</v>
+        <v>780</v>
       </c>
       <c r="D123" t="s">
         <v>570</v>
@@ -7857,13 +7795,13 @@
     </row>
     <row r="124" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
-        <v>790</v>
+        <v>781</v>
       </c>
       <c r="B124" t="s">
-        <v>791</v>
+        <v>782</v>
       </c>
       <c r="C124" t="s">
-        <v>792</v>
+        <v>783</v>
       </c>
       <c r="D124" t="s">
         <v>615</v>
@@ -7889,13 +7827,13 @@
     </row>
     <row r="125" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
-        <v>793</v>
+        <v>784</v>
       </c>
       <c r="B125" t="s">
         <v>280</v>
       </c>
       <c r="C125" t="s">
-        <v>794</v>
+        <v>785</v>
       </c>
       <c r="D125" t="s">
         <v>615</v>
@@ -7921,13 +7859,13 @@
     </row>
     <row r="126" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
-        <v>795</v>
+        <v>786</v>
       </c>
       <c r="B126" t="s">
-        <v>796</v>
+        <v>787</v>
       </c>
       <c r="C126" t="s">
-        <v>797</v>
+        <v>788</v>
       </c>
       <c r="D126" t="s">
         <v>564</v>
@@ -7953,13 +7891,13 @@
     </row>
     <row r="127" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
-        <v>798</v>
+        <v>789</v>
       </c>
       <c r="B127" t="s">
-        <v>799</v>
+        <v>790</v>
       </c>
       <c r="C127" t="s">
-        <v>800</v>
+        <v>791</v>
       </c>
       <c r="D127" t="s">
         <v>570</v>
@@ -7985,13 +7923,13 @@
     </row>
     <row r="128" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
-        <v>801</v>
+        <v>792</v>
       </c>
       <c r="B128" t="s">
         <v>330</v>
       </c>
       <c r="C128" t="s">
-        <v>802</v>
+        <v>793</v>
       </c>
       <c r="D128" t="s">
         <v>564</v>
@@ -8017,13 +7955,13 @@
     </row>
     <row r="129" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
-        <v>803</v>
+        <v>794</v>
       </c>
       <c r="B129" t="s">
         <v>337</v>
       </c>
       <c r="C129" t="s">
-        <v>804</v>
+        <v>795</v>
       </c>
       <c r="D129" t="s">
         <v>594</v>
@@ -8049,13 +7987,13 @@
     </row>
     <row r="130" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
-        <v>805</v>
+        <v>796</v>
       </c>
       <c r="B130" t="s">
         <v>355</v>
       </c>
       <c r="C130" t="s">
-        <v>806</v>
+        <v>797</v>
       </c>
       <c r="D130" t="s">
         <v>564</v>
@@ -8081,13 +8019,13 @@
     </row>
     <row r="131" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
-        <v>807</v>
+        <v>798</v>
       </c>
       <c r="B131" t="s">
-        <v>808</v>
+        <v>799</v>
       </c>
       <c r="C131" t="s">
-        <v>809</v>
+        <v>800</v>
       </c>
       <c r="D131" t="s">
         <v>570</v>
@@ -8113,16 +8051,16 @@
     </row>
     <row r="132" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
-        <v>810</v>
+        <v>801</v>
       </c>
       <c r="B132" t="s">
-        <v>811</v>
+        <v>349</v>
       </c>
       <c r="C132" t="s">
-        <v>812</v>
+        <v>802</v>
       </c>
       <c r="D132" t="s">
-        <v>721</v>
+        <v>718</v>
       </c>
       <c r="E132" s="2">
         <v>19315866.600000001</v>
@@ -8145,13 +8083,13 @@
     </row>
     <row r="133" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
-        <v>813</v>
+        <v>803</v>
       </c>
       <c r="B133" t="s">
         <v>389</v>
       </c>
       <c r="C133" t="s">
-        <v>814</v>
+        <v>804</v>
       </c>
       <c r="D133" t="s">
         <v>575</v>
@@ -8177,16 +8115,16 @@
     </row>
     <row r="134" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
-        <v>815</v>
+        <v>805</v>
       </c>
       <c r="B134" t="s">
-        <v>816</v>
+        <v>196</v>
       </c>
       <c r="C134" t="s">
-        <v>817</v>
+        <v>806</v>
       </c>
       <c r="D134" t="s">
-        <v>721</v>
+        <v>718</v>
       </c>
       <c r="E134" s="2">
         <v>19251103.489999998</v>
@@ -8209,13 +8147,13 @@
     </row>
     <row r="135" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
-        <v>818</v>
+        <v>807</v>
       </c>
       <c r="B135" t="s">
-        <v>819</v>
+        <v>260</v>
       </c>
       <c r="C135" t="s">
-        <v>820</v>
+        <v>808</v>
       </c>
       <c r="D135" t="s">
         <v>615</v>
@@ -8241,13 +8179,13 @@
     </row>
     <row r="136" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
-        <v>821</v>
+        <v>809</v>
       </c>
       <c r="B136" t="s">
-        <v>822</v>
+        <v>810</v>
       </c>
       <c r="C136" t="s">
-        <v>823</v>
+        <v>811</v>
       </c>
       <c r="D136" t="s">
         <v>570</v>
@@ -8279,7 +8217,7 @@
         <v>518</v>
       </c>
       <c r="C137" t="s">
-        <v>824</v>
+        <v>812</v>
       </c>
       <c r="D137" t="s">
         <v>570</v>
@@ -8305,13 +8243,13 @@
     </row>
     <row r="138" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
-        <v>825</v>
+        <v>813</v>
       </c>
       <c r="B138" t="s">
         <v>445</v>
       </c>
       <c r="C138" t="s">
-        <v>826</v>
+        <v>814</v>
       </c>
       <c r="D138" t="s">
         <v>564</v>
@@ -8337,13 +8275,13 @@
     </row>
     <row r="139" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
-        <v>827</v>
+        <v>815</v>
       </c>
       <c r="B139" t="s">
-        <v>828</v>
+        <v>816</v>
       </c>
       <c r="C139" t="s">
-        <v>829</v>
+        <v>817</v>
       </c>
       <c r="D139" t="s">
         <v>570</v>
@@ -8375,7 +8313,7 @@
         <v>486</v>
       </c>
       <c r="C140" t="s">
-        <v>830</v>
+        <v>818</v>
       </c>
       <c r="D140" t="s">
         <v>570</v>
@@ -8407,7 +8345,7 @@
         <v>459</v>
       </c>
       <c r="C141" t="s">
-        <v>831</v>
+        <v>819</v>
       </c>
       <c r="D141" t="s">
         <v>570</v>
@@ -8433,16 +8371,16 @@
     </row>
     <row r="142" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
-        <v>832</v>
+        <v>820</v>
       </c>
       <c r="B142" t="s">
-        <v>833</v>
+        <v>380</v>
       </c>
       <c r="C142" t="s">
-        <v>834</v>
+        <v>821</v>
       </c>
       <c r="D142" t="s">
-        <v>721</v>
+        <v>718</v>
       </c>
       <c r="E142" s="2">
         <v>17126065.289999999</v>
@@ -8465,13 +8403,13 @@
     </row>
     <row r="143" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
-        <v>835</v>
+        <v>822</v>
       </c>
       <c r="B143" t="s">
-        <v>836</v>
+        <v>823</v>
       </c>
       <c r="C143" t="s">
-        <v>837</v>
+        <v>824</v>
       </c>
       <c r="D143" t="s">
         <v>570</v>
@@ -8497,13 +8435,13 @@
     </row>
     <row r="144" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
-        <v>838</v>
+        <v>825</v>
       </c>
       <c r="B144" t="s">
         <v>412</v>
       </c>
       <c r="C144" t="s">
-        <v>839</v>
+        <v>826</v>
       </c>
       <c r="D144" t="s">
         <v>570</v>
@@ -8529,13 +8467,13 @@
     </row>
     <row r="145" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
-        <v>840</v>
+        <v>827</v>
       </c>
       <c r="B145" t="s">
-        <v>841</v>
+        <v>828</v>
       </c>
       <c r="C145" t="s">
-        <v>842</v>
+        <v>829</v>
       </c>
       <c r="D145" t="s">
         <v>597</v>
@@ -8561,13 +8499,13 @@
     </row>
     <row r="146" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
-        <v>843</v>
+        <v>830</v>
       </c>
       <c r="B146" t="s">
         <v>419</v>
       </c>
       <c r="C146" t="s">
-        <v>844</v>
+        <v>831</v>
       </c>
       <c r="D146" t="s">
         <v>564</v>
@@ -8593,13 +8531,13 @@
     </row>
     <row r="147" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
-        <v>845</v>
+        <v>832</v>
       </c>
       <c r="B147" t="s">
-        <v>846</v>
+        <v>833</v>
       </c>
       <c r="C147" t="s">
-        <v>847</v>
+        <v>834</v>
       </c>
       <c r="D147" t="s">
         <v>570</v>
@@ -8625,16 +8563,16 @@
     </row>
     <row r="148" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
-        <v>848</v>
+        <v>835</v>
       </c>
       <c r="B148" t="s">
-        <v>849</v>
+        <v>298</v>
       </c>
       <c r="C148" t="s">
-        <v>850</v>
+        <v>836</v>
       </c>
       <c r="D148" t="s">
-        <v>721</v>
+        <v>718</v>
       </c>
       <c r="E148" s="2">
         <v>15791596.199999999</v>
@@ -8657,13 +8595,13 @@
     </row>
     <row r="149" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
-        <v>851</v>
+        <v>837</v>
       </c>
       <c r="B149" t="s">
         <v>347</v>
       </c>
       <c r="C149" t="s">
-        <v>852</v>
+        <v>838</v>
       </c>
       <c r="D149" t="s">
         <v>597</v>
@@ -8695,7 +8633,7 @@
         <v>372</v>
       </c>
       <c r="C150" t="s">
-        <v>853</v>
+        <v>839</v>
       </c>
       <c r="D150" t="s">
         <v>561</v>
@@ -8721,13 +8659,13 @@
     </row>
     <row r="151" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
-        <v>854</v>
+        <v>840</v>
       </c>
       <c r="B151" t="s">
-        <v>855</v>
+        <v>841</v>
       </c>
       <c r="C151" t="s">
-        <v>856</v>
+        <v>842</v>
       </c>
       <c r="D151" t="s">
         <v>570</v>
@@ -8759,7 +8697,7 @@
         <v>258</v>
       </c>
       <c r="C152" t="s">
-        <v>857</v>
+        <v>843</v>
       </c>
       <c r="D152" t="s">
         <v>570</v>
@@ -8785,13 +8723,13 @@
     </row>
     <row r="153" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
-        <v>858</v>
+        <v>844</v>
       </c>
       <c r="B153" t="s">
         <v>376</v>
       </c>
       <c r="C153" t="s">
-        <v>859</v>
+        <v>845</v>
       </c>
       <c r="D153" t="s">
         <v>564</v>
@@ -8823,7 +8761,7 @@
         <v>343</v>
       </c>
       <c r="C154" t="s">
-        <v>860</v>
+        <v>846</v>
       </c>
       <c r="D154" t="s">
         <v>575</v>
@@ -8849,13 +8787,13 @@
     </row>
     <row r="155" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
-        <v>861</v>
+        <v>847</v>
       </c>
       <c r="B155" t="s">
         <v>335</v>
       </c>
       <c r="C155" t="s">
-        <v>862</v>
+        <v>848</v>
       </c>
       <c r="D155" t="s">
         <v>564</v>
@@ -8881,13 +8819,13 @@
     </row>
     <row r="156" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
-        <v>863</v>
+        <v>849</v>
       </c>
       <c r="B156" t="s">
         <v>382</v>
       </c>
       <c r="C156" t="s">
-        <v>864</v>
+        <v>850</v>
       </c>
       <c r="D156" t="s">
         <v>575</v>
@@ -8913,13 +8851,13 @@
     </row>
     <row r="157" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
-        <v>865</v>
+        <v>851</v>
       </c>
       <c r="B157" t="s">
-        <v>866</v>
+        <v>852</v>
       </c>
       <c r="C157" t="s">
-        <v>867</v>
+        <v>853</v>
       </c>
       <c r="D157" t="s">
         <v>564</v>
@@ -8945,13 +8883,13 @@
     </row>
     <row r="158" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
-        <v>868</v>
+        <v>854</v>
       </c>
       <c r="B158" t="s">
         <v>397</v>
       </c>
       <c r="C158" t="s">
-        <v>869</v>
+        <v>855</v>
       </c>
       <c r="D158" t="s">
         <v>564</v>
@@ -8983,7 +8921,7 @@
         <v>481</v>
       </c>
       <c r="C159" t="s">
-        <v>870</v>
+        <v>856</v>
       </c>
       <c r="D159" t="s">
         <v>564</v>
@@ -9015,7 +8953,7 @@
         <v>464</v>
       </c>
       <c r="C160" t="s">
-        <v>871</v>
+        <v>857</v>
       </c>
       <c r="D160" t="s">
         <v>558</v>
@@ -9041,13 +8979,13 @@
     </row>
     <row r="161" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
-        <v>872</v>
+        <v>858</v>
       </c>
       <c r="B161" t="s">
         <v>345</v>
       </c>
       <c r="C161" t="s">
-        <v>873</v>
+        <v>859</v>
       </c>
       <c r="D161" t="s">
         <v>558</v>
@@ -9073,13 +9011,13 @@
     </row>
     <row r="162" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
-        <v>874</v>
+        <v>860</v>
       </c>
       <c r="B162" t="s">
-        <v>875</v>
+        <v>861</v>
       </c>
       <c r="C162" t="s">
-        <v>876</v>
+        <v>862</v>
       </c>
       <c r="D162" t="s">
         <v>570</v>
@@ -9105,16 +9043,16 @@
     </row>
     <row r="163" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
-        <v>877</v>
+        <v>863</v>
       </c>
       <c r="B163" t="s">
-        <v>878</v>
+        <v>393</v>
       </c>
       <c r="C163" t="s">
-        <v>879</v>
+        <v>864</v>
       </c>
       <c r="D163" t="s">
-        <v>721</v>
+        <v>718</v>
       </c>
       <c r="E163" s="2">
         <v>13028715.15</v>
@@ -9137,13 +9075,13 @@
     </row>
     <row r="164" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
-        <v>880</v>
+        <v>865</v>
       </c>
       <c r="B164" t="s">
-        <v>881</v>
+        <v>866</v>
       </c>
       <c r="C164" t="s">
-        <v>882</v>
+        <v>867</v>
       </c>
       <c r="D164" t="s">
         <v>564</v>
@@ -9169,16 +9107,16 @@
     </row>
     <row r="165" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
-        <v>883</v>
+        <v>868</v>
       </c>
       <c r="B165" t="s">
-        <v>884</v>
+        <v>357</v>
       </c>
       <c r="C165" t="s">
-        <v>885</v>
+        <v>869</v>
       </c>
       <c r="D165" t="s">
-        <v>721</v>
+        <v>718</v>
       </c>
       <c r="E165" s="2">
         <v>12329302.26</v>
@@ -9201,13 +9139,13 @@
     </row>
     <row r="166" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
-        <v>886</v>
+        <v>870</v>
       </c>
       <c r="B166" t="s">
-        <v>887</v>
+        <v>871</v>
       </c>
       <c r="C166" t="s">
-        <v>888</v>
+        <v>872</v>
       </c>
       <c r="D166" t="s">
         <v>570</v>
@@ -9233,13 +9171,13 @@
     </row>
     <row r="167" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
-        <v>889</v>
+        <v>873</v>
       </c>
       <c r="B167" t="s">
-        <v>890</v>
+        <v>874</v>
       </c>
       <c r="C167" t="s">
-        <v>891</v>
+        <v>875</v>
       </c>
       <c r="D167" t="s">
         <v>564</v>
@@ -9265,13 +9203,13 @@
     </row>
     <row r="168" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
-        <v>892</v>
+        <v>876</v>
       </c>
       <c r="B168" t="s">
         <v>531</v>
       </c>
       <c r="C168" t="s">
-        <v>893</v>
+        <v>877</v>
       </c>
       <c r="D168" t="s">
         <v>575</v>
@@ -9297,13 +9235,13 @@
     </row>
     <row r="169" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
-        <v>894</v>
+        <v>878</v>
       </c>
       <c r="B169" t="s">
         <v>428</v>
       </c>
       <c r="C169" t="s">
-        <v>895</v>
+        <v>879</v>
       </c>
       <c r="D169" t="s">
         <v>575</v>
@@ -9335,10 +9273,10 @@
         <v>417</v>
       </c>
       <c r="C170" t="s">
-        <v>896</v>
+        <v>880</v>
       </c>
       <c r="D170" t="s">
-        <v>762</v>
+        <v>756</v>
       </c>
       <c r="E170" s="2">
         <v>11663144</v>
@@ -9361,13 +9299,13 @@
     </row>
     <row r="171" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
-        <v>897</v>
+        <v>881</v>
       </c>
       <c r="B171" t="s">
-        <v>898</v>
+        <v>882</v>
       </c>
       <c r="C171" t="s">
-        <v>899</v>
+        <v>883</v>
       </c>
       <c r="D171" t="s">
         <v>564</v>
@@ -9393,13 +9331,13 @@
     </row>
     <row r="172" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
-        <v>900</v>
+        <v>884</v>
       </c>
       <c r="B172" t="s">
         <v>408</v>
       </c>
       <c r="C172" t="s">
-        <v>901</v>
+        <v>885</v>
       </c>
       <c r="D172" t="s">
         <v>594</v>
@@ -9425,16 +9363,16 @@
     </row>
     <row r="173" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
-        <v>902</v>
+        <v>886</v>
       </c>
       <c r="B173" t="s">
         <v>414</v>
       </c>
       <c r="C173" t="s">
-        <v>903</v>
+        <v>887</v>
       </c>
       <c r="D173" t="s">
-        <v>721</v>
+        <v>718</v>
       </c>
       <c r="E173" s="2">
         <v>11326208.640000001</v>
@@ -9457,13 +9395,13 @@
     </row>
     <row r="174" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
-        <v>904</v>
+        <v>888</v>
       </c>
       <c r="B174" t="s">
         <v>366</v>
       </c>
       <c r="C174" t="s">
-        <v>905</v>
+        <v>889</v>
       </c>
       <c r="D174" t="s">
         <v>615</v>
@@ -9489,16 +9427,16 @@
     </row>
     <row r="175" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
-        <v>906</v>
+        <v>890</v>
       </c>
       <c r="B175" t="s">
-        <v>907</v>
+        <v>891</v>
       </c>
       <c r="C175" t="s">
-        <v>908</v>
+        <v>892</v>
       </c>
       <c r="D175" t="s">
-        <v>762</v>
+        <v>756</v>
       </c>
       <c r="E175" s="2">
         <v>10470354.300000001</v>
@@ -9521,13 +9459,13 @@
     </row>
     <row r="176" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
-        <v>909</v>
+        <v>893</v>
       </c>
       <c r="B176" t="s">
         <v>496</v>
       </c>
       <c r="C176" t="s">
-        <v>910</v>
+        <v>894</v>
       </c>
       <c r="D176" t="s">
         <v>558</v>
@@ -9553,13 +9491,13 @@
     </row>
     <row r="177" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
-        <v>911</v>
+        <v>895</v>
       </c>
       <c r="B177" t="s">
-        <v>912</v>
+        <v>983</v>
       </c>
       <c r="C177" t="s">
-        <v>913</v>
+        <v>896</v>
       </c>
       <c r="D177" t="s">
         <v>575</v>
@@ -9585,13 +9523,13 @@
     </row>
     <row r="178" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
-        <v>914</v>
+        <v>897</v>
       </c>
       <c r="B178" t="s">
         <v>478</v>
       </c>
       <c r="C178" t="s">
-        <v>915</v>
+        <v>898</v>
       </c>
       <c r="D178" t="s">
         <v>575</v>
@@ -9623,7 +9561,7 @@
         <v>443</v>
       </c>
       <c r="C179" t="s">
-        <v>916</v>
+        <v>899</v>
       </c>
       <c r="D179" t="s">
         <v>561</v>
@@ -9649,13 +9587,13 @@
     </row>
     <row r="180" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
-        <v>917</v>
+        <v>900</v>
       </c>
       <c r="B180" t="s">
         <v>461</v>
       </c>
       <c r="C180" t="s">
-        <v>918</v>
+        <v>901</v>
       </c>
       <c r="D180" t="s">
         <v>564</v>
@@ -9681,16 +9619,16 @@
     </row>
     <row r="181" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
-        <v>919</v>
+        <v>902</v>
       </c>
       <c r="B181" t="s">
-        <v>920</v>
+        <v>437</v>
       </c>
       <c r="C181" t="s">
-        <v>921</v>
+        <v>903</v>
       </c>
       <c r="D181" t="s">
-        <v>721</v>
+        <v>718</v>
       </c>
       <c r="E181" s="2">
         <v>9537194.9000000004</v>
@@ -9713,13 +9651,13 @@
     </row>
     <row r="182" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
-        <v>922</v>
+        <v>904</v>
       </c>
       <c r="B182" t="s">
         <v>535</v>
       </c>
       <c r="C182" t="s">
-        <v>923</v>
+        <v>905</v>
       </c>
       <c r="D182" t="s">
         <v>564</v>
@@ -9745,13 +9683,13 @@
     </row>
     <row r="183" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
-        <v>924</v>
+        <v>906</v>
       </c>
       <c r="B183" t="s">
         <v>391</v>
       </c>
       <c r="C183" t="s">
-        <v>925</v>
+        <v>907</v>
       </c>
       <c r="D183" t="s">
         <v>626</v>
@@ -9777,13 +9715,13 @@
     </row>
     <row r="184" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
-        <v>926</v>
+        <v>908</v>
       </c>
       <c r="B184" t="s">
         <v>500</v>
       </c>
       <c r="C184" t="s">
-        <v>927</v>
+        <v>909</v>
       </c>
       <c r="D184" t="s">
         <v>564</v>
@@ -9809,13 +9747,13 @@
     </row>
     <row r="185" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
-        <v>928</v>
+        <v>910</v>
       </c>
       <c r="B185" t="s">
         <v>488</v>
       </c>
       <c r="C185" t="s">
-        <v>929</v>
+        <v>911</v>
       </c>
       <c r="D185" t="s">
         <v>570</v>
@@ -9841,16 +9779,16 @@
     </row>
     <row r="186" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
-        <v>930</v>
+        <v>912</v>
       </c>
       <c r="B186" t="s">
         <v>522</v>
       </c>
       <c r="C186" t="s">
-        <v>931</v>
+        <v>913</v>
       </c>
       <c r="D186" t="s">
-        <v>762</v>
+        <v>756</v>
       </c>
       <c r="E186" s="2">
         <v>9233897.9700000007</v>
@@ -9873,13 +9811,13 @@
     </row>
     <row r="187" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
-        <v>932</v>
+        <v>914</v>
       </c>
       <c r="B187" t="s">
-        <v>933</v>
+        <v>915</v>
       </c>
       <c r="C187" t="s">
-        <v>934</v>
+        <v>916</v>
       </c>
       <c r="D187" t="s">
         <v>575</v>
@@ -9905,13 +9843,13 @@
     </row>
     <row r="188" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
-        <v>935</v>
+        <v>917</v>
       </c>
       <c r="B188" t="s">
         <v>449</v>
       </c>
       <c r="C188" t="s">
-        <v>936</v>
+        <v>918</v>
       </c>
       <c r="D188" t="s">
         <v>597</v>
@@ -9937,13 +9875,13 @@
     </row>
     <row r="189" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
-        <v>937</v>
+        <v>919</v>
       </c>
       <c r="B189" t="s">
         <v>492</v>
       </c>
       <c r="C189" t="s">
-        <v>938</v>
+        <v>920</v>
       </c>
       <c r="D189" t="s">
         <v>564</v>
@@ -9969,13 +9907,13 @@
     </row>
     <row r="190" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A190" t="s">
-        <v>939</v>
+        <v>921</v>
       </c>
       <c r="B190" t="s">
         <v>364</v>
       </c>
       <c r="C190" t="s">
-        <v>940</v>
+        <v>922</v>
       </c>
       <c r="D190" t="s">
         <v>594</v>
@@ -10001,16 +9939,16 @@
     </row>
     <row r="191" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
-        <v>941</v>
+        <v>923</v>
       </c>
       <c r="B191" t="s">
-        <v>942</v>
+        <v>504</v>
       </c>
       <c r="C191" t="s">
-        <v>943</v>
+        <v>924</v>
       </c>
       <c r="D191" t="s">
-        <v>721</v>
+        <v>718</v>
       </c>
       <c r="E191" s="2">
         <v>8782364.6699999999</v>
@@ -10033,13 +9971,13 @@
     </row>
     <row r="192" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A192" t="s">
-        <v>944</v>
+        <v>925</v>
       </c>
       <c r="B192" t="s">
-        <v>945</v>
+        <v>926</v>
       </c>
       <c r="C192" t="s">
-        <v>946</v>
+        <v>927</v>
       </c>
       <c r="D192" t="s">
         <v>558</v>
@@ -10065,13 +10003,13 @@
     </row>
     <row r="193" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
-        <v>947</v>
+        <v>928</v>
       </c>
       <c r="B193" t="s">
         <v>421</v>
       </c>
       <c r="C193" t="s">
-        <v>948</v>
+        <v>929</v>
       </c>
       <c r="D193" t="s">
         <v>564</v>
@@ -10103,7 +10041,7 @@
         <v>540</v>
       </c>
       <c r="C194" t="s">
-        <v>949</v>
+        <v>930</v>
       </c>
       <c r="D194" t="s">
         <v>564</v>
@@ -10129,16 +10067,16 @@
     </row>
     <row r="195" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
-        <v>950</v>
+        <v>931</v>
       </c>
       <c r="B195" t="s">
-        <v>951</v>
+        <v>401</v>
       </c>
       <c r="C195" t="s">
-        <v>952</v>
+        <v>932</v>
       </c>
       <c r="D195" t="s">
-        <v>721</v>
+        <v>718</v>
       </c>
       <c r="E195" s="2">
         <v>8073383.7999999998</v>
@@ -10161,13 +10099,13 @@
     </row>
     <row r="196" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
-        <v>953</v>
+        <v>933</v>
       </c>
       <c r="B196" t="s">
-        <v>954</v>
+        <v>934</v>
       </c>
       <c r="C196" t="s">
-        <v>955</v>
+        <v>935</v>
       </c>
       <c r="D196" t="s">
         <v>564</v>
@@ -10193,13 +10131,13 @@
     </row>
     <row r="197" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
-        <v>956</v>
+        <v>936</v>
       </c>
       <c r="B197" t="s">
-        <v>957</v>
+        <v>508</v>
       </c>
       <c r="C197" t="s">
-        <v>958</v>
+        <v>937</v>
       </c>
       <c r="D197" t="s">
         <v>570</v>
@@ -10225,16 +10163,16 @@
     </row>
     <row r="198" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
-        <v>959</v>
+        <v>938</v>
       </c>
       <c r="B198" t="s">
-        <v>960</v>
+        <v>490</v>
       </c>
       <c r="C198" t="s">
-        <v>961</v>
+        <v>939</v>
       </c>
       <c r="D198" t="s">
-        <v>721</v>
+        <v>718</v>
       </c>
       <c r="E198" s="2">
         <v>7986659.8399999999</v>
@@ -10257,16 +10195,16 @@
     </row>
     <row r="199" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
-        <v>962</v>
+        <v>940</v>
       </c>
       <c r="B199" t="s">
-        <v>963</v>
+        <v>447</v>
       </c>
       <c r="C199" t="s">
-        <v>964</v>
+        <v>941</v>
       </c>
       <c r="D199" t="s">
-        <v>721</v>
+        <v>718</v>
       </c>
       <c r="E199" s="2">
         <v>7947426.0499999998</v>
@@ -10289,13 +10227,13 @@
     </row>
     <row r="200" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
-        <v>965</v>
+        <v>942</v>
       </c>
       <c r="B200" t="s">
         <v>510</v>
       </c>
       <c r="C200" t="s">
-        <v>966</v>
+        <v>943</v>
       </c>
       <c r="D200" t="s">
         <v>615</v>
@@ -10321,13 +10259,13 @@
     </row>
     <row r="201" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
-        <v>967</v>
+        <v>944</v>
       </c>
       <c r="B201" t="s">
-        <v>968</v>
+        <v>945</v>
       </c>
       <c r="C201" t="s">
-        <v>969</v>
+        <v>946</v>
       </c>
       <c r="D201" t="s">
         <v>575</v>
@@ -10353,13 +10291,13 @@
     </row>
     <row r="202" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
-        <v>970</v>
+        <v>947</v>
       </c>
       <c r="B202" t="s">
         <v>426</v>
       </c>
       <c r="C202" t="s">
-        <v>971</v>
+        <v>948</v>
       </c>
       <c r="D202" t="s">
         <v>558</v>
@@ -10385,13 +10323,13 @@
     </row>
     <row r="203" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A203" t="s">
-        <v>972</v>
+        <v>949</v>
       </c>
       <c r="B203" t="s">
         <v>430</v>
       </c>
       <c r="C203" t="s">
-        <v>973</v>
+        <v>950</v>
       </c>
       <c r="D203" t="s">
         <v>564</v>
@@ -10417,13 +10355,13 @@
     </row>
     <row r="204" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A204" t="s">
-        <v>974</v>
+        <v>951</v>
       </c>
       <c r="B204" t="s">
         <v>506</v>
       </c>
       <c r="C204" t="s">
-        <v>975</v>
+        <v>952</v>
       </c>
       <c r="D204" t="s">
         <v>575</v>
@@ -10449,13 +10387,13 @@
     </row>
     <row r="205" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A205" t="s">
-        <v>976</v>
+        <v>953</v>
       </c>
       <c r="B205" t="s">
         <v>546</v>
       </c>
       <c r="C205" t="s">
-        <v>977</v>
+        <v>954</v>
       </c>
       <c r="D205" t="s">
         <v>594</v>
@@ -10481,13 +10419,13 @@
     </row>
     <row r="206" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
-        <v>978</v>
+        <v>955</v>
       </c>
       <c r="B206" t="s">
-        <v>979</v>
+        <v>956</v>
       </c>
       <c r="C206" t="s">
-        <v>980</v>
+        <v>957</v>
       </c>
       <c r="D206" t="s">
         <v>575</v>
@@ -10513,16 +10451,16 @@
     </row>
     <row r="207" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A207" t="s">
-        <v>981</v>
+        <v>958</v>
       </c>
       <c r="B207" t="s">
-        <v>982</v>
+        <v>353</v>
       </c>
       <c r="C207" t="s">
-        <v>983</v>
+        <v>959</v>
       </c>
       <c r="D207" t="s">
-        <v>721</v>
+        <v>718</v>
       </c>
       <c r="E207" s="2">
         <v>5837298.0300000003</v>
@@ -10545,13 +10483,13 @@
     </row>
     <row r="208" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A208" t="s">
-        <v>984</v>
+        <v>960</v>
       </c>
       <c r="B208" t="s">
         <v>399</v>
       </c>
       <c r="C208" t="s">
-        <v>985</v>
+        <v>961</v>
       </c>
       <c r="D208" t="s">
         <v>570</v>
@@ -10577,13 +10515,13 @@
     </row>
     <row r="209" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A209" t="s">
-        <v>986</v>
+        <v>962</v>
       </c>
       <c r="B209" t="s">
         <v>533</v>
       </c>
       <c r="C209" t="s">
-        <v>987</v>
+        <v>963</v>
       </c>
       <c r="D209" t="s">
         <v>575</v>
@@ -10609,13 +10547,13 @@
     </row>
     <row r="210" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A210" t="s">
-        <v>988</v>
+        <v>964</v>
       </c>
       <c r="B210" t="s">
-        <v>989</v>
+        <v>965</v>
       </c>
       <c r="C210" t="s">
-        <v>990</v>
+        <v>966</v>
       </c>
       <c r="D210" t="s">
         <v>564</v>
@@ -10641,16 +10579,16 @@
     </row>
     <row r="211" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A211" t="s">
-        <v>991</v>
+        <v>967</v>
       </c>
       <c r="B211" t="s">
-        <v>992</v>
+        <v>984</v>
       </c>
       <c r="C211" t="s">
-        <v>993</v>
+        <v>968</v>
       </c>
       <c r="D211" t="s">
-        <v>721</v>
+        <v>718</v>
       </c>
       <c r="E211" s="2">
         <v>5383162.8799999999</v>
@@ -10673,13 +10611,13 @@
     </row>
     <row r="212" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A212" t="s">
-        <v>994</v>
+        <v>969</v>
       </c>
       <c r="B212" t="s">
-        <v>995</v>
+        <v>970</v>
       </c>
       <c r="C212" t="s">
-        <v>996</v>
+        <v>971</v>
       </c>
       <c r="D212" t="s">
         <v>594</v>
@@ -10705,13 +10643,13 @@
     </row>
     <row r="213" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A213" t="s">
-        <v>845</v>
+        <v>832</v>
       </c>
       <c r="B213" t="s">
-        <v>846</v>
+        <v>833</v>
       </c>
       <c r="C213" t="s">
-        <v>997</v>
+        <v>972</v>
       </c>
       <c r="D213" t="s">
         <v>558</v>

--- a/Tickers_Info.xlsx
+++ b/Tickers_Info.xlsx
@@ -2192,18 +2192,12 @@
     <t>CTC.A</t>
   </si>
   <si>
-    <t>CTC.A.TO</t>
-  </si>
-  <si>
     <t>CANADIAN TIRE LTD CLASS A</t>
   </si>
   <si>
     <t>BEP.UN</t>
   </si>
   <si>
-    <t>BEP.UN.TO</t>
-  </si>
-  <si>
     <t>BROOKFIELD RENEWABLE PARTNERS NON</t>
   </si>
   <si>
@@ -2976,6 +2970,12 @@
   </si>
   <si>
     <t>NWH-UN.TO</t>
+  </si>
+  <si>
+    <t>CTC-A.TO</t>
+  </si>
+  <si>
+    <t>BEP-UN.TO</t>
   </si>
 </sst>
 </file>
@@ -3825,21 +3825,21 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B1" t="s">
+        <v>972</v>
+      </c>
+      <c r="C1" t="s">
         <v>974</v>
-      </c>
-      <c r="C1" t="s">
-        <v>976</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
+        <v>971</v>
+      </c>
+      <c r="B3" t="s">
         <v>973</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C3" t="s">
         <v>975</v>
-      </c>
-      <c r="C3" t="s">
-        <v>977</v>
       </c>
     </row>
   </sheetData>
@@ -5142,7 +5142,7 @@
         <v>628</v>
       </c>
       <c r="B41" t="s">
-        <v>978</v>
+        <v>976</v>
       </c>
       <c r="C41" t="s">
         <v>629</v>
@@ -5270,7 +5270,7 @@
         <v>635</v>
       </c>
       <c r="B45" t="s">
-        <v>979</v>
+        <v>977</v>
       </c>
       <c r="C45" t="s">
         <v>636</v>
@@ -5366,7 +5366,7 @@
         <v>640</v>
       </c>
       <c r="B48" t="s">
-        <v>980</v>
+        <v>978</v>
       </c>
       <c r="C48" t="s">
         <v>641</v>
@@ -5590,7 +5590,7 @@
         <v>655</v>
       </c>
       <c r="B55" t="s">
-        <v>981</v>
+        <v>979</v>
       </c>
       <c r="C55" t="s">
         <v>656</v>
@@ -6870,10 +6870,10 @@
         <v>722</v>
       </c>
       <c r="B95" t="s">
+        <v>983</v>
+      </c>
+      <c r="C95" t="s">
         <v>723</v>
-      </c>
-      <c r="C95" t="s">
-        <v>724</v>
       </c>
       <c r="D95" t="s">
         <v>597</v>
@@ -6899,13 +6899,13 @@
     </row>
     <row r="96" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
+        <v>724</v>
+      </c>
+      <c r="B96" t="s">
+        <v>984</v>
+      </c>
+      <c r="C96" t="s">
         <v>725</v>
-      </c>
-      <c r="B96" t="s">
-        <v>726</v>
-      </c>
-      <c r="C96" t="s">
-        <v>727</v>
       </c>
       <c r="D96" t="s">
         <v>615</v>
@@ -6931,13 +6931,13 @@
     </row>
     <row r="97" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
+        <v>726</v>
+      </c>
+      <c r="B97" t="s">
+        <v>727</v>
+      </c>
+      <c r="C97" t="s">
         <v>728</v>
-      </c>
-      <c r="B97" t="s">
-        <v>729</v>
-      </c>
-      <c r="C97" t="s">
-        <v>730</v>
       </c>
       <c r="D97" t="s">
         <v>570</v>
@@ -6963,13 +6963,13 @@
     </row>
     <row r="98" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
-        <v>731</v>
+        <v>729</v>
       </c>
       <c r="B98" t="s">
         <v>271</v>
       </c>
       <c r="C98" t="s">
-        <v>732</v>
+        <v>730</v>
       </c>
       <c r="D98" t="s">
         <v>570</v>
@@ -7001,7 +7001,7 @@
         <v>236</v>
       </c>
       <c r="C99" t="s">
-        <v>733</v>
+        <v>731</v>
       </c>
       <c r="D99" t="s">
         <v>564</v>
@@ -7027,13 +7027,13 @@
     </row>
     <row r="100" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
-        <v>734</v>
+        <v>732</v>
       </c>
       <c r="B100" t="s">
         <v>222</v>
       </c>
       <c r="C100" t="s">
-        <v>735</v>
+        <v>733</v>
       </c>
       <c r="D100" t="s">
         <v>626</v>
@@ -7065,7 +7065,7 @@
         <v>301</v>
       </c>
       <c r="C101" t="s">
-        <v>736</v>
+        <v>734</v>
       </c>
       <c r="D101" t="s">
         <v>564</v>
@@ -7091,13 +7091,13 @@
     </row>
     <row r="102" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
-        <v>737</v>
+        <v>735</v>
       </c>
       <c r="B102" t="s">
         <v>238</v>
       </c>
       <c r="C102" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
       <c r="D102" t="s">
         <v>558</v>
@@ -7123,13 +7123,13 @@
     </row>
     <row r="103" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
       <c r="B103" t="s">
         <v>231</v>
       </c>
       <c r="C103" t="s">
-        <v>740</v>
+        <v>738</v>
       </c>
       <c r="D103" t="s">
         <v>558</v>
@@ -7155,13 +7155,13 @@
     </row>
     <row r="104" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
+        <v>739</v>
+      </c>
+      <c r="B104" t="s">
+        <v>740</v>
+      </c>
+      <c r="C104" t="s">
         <v>741</v>
-      </c>
-      <c r="B104" t="s">
-        <v>742</v>
-      </c>
-      <c r="C104" t="s">
-        <v>743</v>
       </c>
       <c r="D104" t="s">
         <v>570</v>
@@ -7187,13 +7187,13 @@
     </row>
     <row r="105" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
-        <v>744</v>
+        <v>742</v>
       </c>
       <c r="B105" t="s">
         <v>184</v>
       </c>
       <c r="C105" t="s">
-        <v>745</v>
+        <v>743</v>
       </c>
       <c r="D105" t="s">
         <v>594</v>
@@ -7219,13 +7219,13 @@
     </row>
     <row r="106" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
-        <v>746</v>
+        <v>744</v>
       </c>
       <c r="B106" t="s">
         <v>264</v>
       </c>
       <c r="C106" t="s">
-        <v>747</v>
+        <v>745</v>
       </c>
       <c r="D106" t="s">
         <v>564</v>
@@ -7257,7 +7257,7 @@
         <v>387</v>
       </c>
       <c r="C107" t="s">
-        <v>748</v>
+        <v>746</v>
       </c>
       <c r="D107" t="s">
         <v>570</v>
@@ -7283,13 +7283,13 @@
     </row>
     <row r="108" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
-        <v>749</v>
+        <v>747</v>
       </c>
       <c r="B108" t="s">
         <v>359</v>
       </c>
       <c r="C108" t="s">
-        <v>750</v>
+        <v>748</v>
       </c>
       <c r="D108" t="s">
         <v>570</v>
@@ -7321,7 +7321,7 @@
         <v>247</v>
       </c>
       <c r="C109" t="s">
-        <v>751</v>
+        <v>749</v>
       </c>
       <c r="D109" t="s">
         <v>615</v>
@@ -7347,13 +7347,13 @@
     </row>
     <row r="110" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
-        <v>752</v>
+        <v>750</v>
       </c>
       <c r="B110" t="s">
         <v>303</v>
       </c>
       <c r="C110" t="s">
-        <v>753</v>
+        <v>751</v>
       </c>
       <c r="D110" t="s">
         <v>575</v>
@@ -7379,16 +7379,16 @@
     </row>
     <row r="111" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
-        <v>754</v>
+        <v>752</v>
       </c>
       <c r="B111" t="s">
         <v>287</v>
       </c>
       <c r="C111" t="s">
-        <v>755</v>
+        <v>753</v>
       </c>
       <c r="D111" t="s">
-        <v>756</v>
+        <v>754</v>
       </c>
       <c r="E111" s="2">
         <v>28270778.850000001</v>
@@ -7411,13 +7411,13 @@
     </row>
     <row r="112" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
-        <v>757</v>
+        <v>755</v>
       </c>
       <c r="B112" t="s">
         <v>242</v>
       </c>
       <c r="C112" t="s">
-        <v>758</v>
+        <v>756</v>
       </c>
       <c r="D112" t="s">
         <v>718</v>
@@ -7443,13 +7443,13 @@
     </row>
     <row r="113" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
-        <v>759</v>
+        <v>757</v>
       </c>
       <c r="B113" t="s">
         <v>244</v>
       </c>
       <c r="C113" t="s">
-        <v>760</v>
+        <v>758</v>
       </c>
       <c r="D113" t="s">
         <v>575</v>
@@ -7475,13 +7475,13 @@
     </row>
     <row r="114" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
-        <v>761</v>
+        <v>759</v>
       </c>
       <c r="B114" t="s">
         <v>384</v>
       </c>
       <c r="C114" t="s">
-        <v>762</v>
+        <v>760</v>
       </c>
       <c r="D114" t="s">
         <v>570</v>
@@ -7507,13 +7507,13 @@
     </row>
     <row r="115" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
-        <v>763</v>
+        <v>761</v>
       </c>
       <c r="B115" t="s">
         <v>275</v>
       </c>
       <c r="C115" t="s">
-        <v>764</v>
+        <v>762</v>
       </c>
       <c r="D115" t="s">
         <v>718</v>
@@ -7539,13 +7539,13 @@
     </row>
     <row r="116" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
-        <v>765</v>
+        <v>763</v>
       </c>
       <c r="B116" t="s">
         <v>229</v>
       </c>
       <c r="C116" t="s">
-        <v>766</v>
+        <v>764</v>
       </c>
       <c r="D116" t="s">
         <v>615</v>
@@ -7571,13 +7571,13 @@
     </row>
     <row r="117" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
-        <v>767</v>
+        <v>765</v>
       </c>
       <c r="B117" t="s">
         <v>456</v>
       </c>
       <c r="C117" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
       <c r="D117" t="s">
         <v>570</v>
@@ -7603,13 +7603,13 @@
     </row>
     <row r="118" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="B118" t="s">
         <v>266</v>
       </c>
       <c r="C118" t="s">
-        <v>770</v>
+        <v>768</v>
       </c>
       <c r="D118" t="s">
         <v>561</v>
@@ -7635,13 +7635,13 @@
     </row>
     <row r="119" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
-        <v>771</v>
+        <v>769</v>
       </c>
       <c r="B119" t="s">
         <v>203</v>
       </c>
       <c r="C119" t="s">
-        <v>772</v>
+        <v>770</v>
       </c>
       <c r="D119" t="s">
         <v>558</v>
@@ -7667,13 +7667,13 @@
     </row>
     <row r="120" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="B120" t="s">
-        <v>982</v>
+        <v>980</v>
       </c>
       <c r="C120" t="s">
-        <v>774</v>
+        <v>772</v>
       </c>
       <c r="D120" t="s">
         <v>718</v>
@@ -7699,13 +7699,13 @@
     </row>
     <row r="121" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
+        <v>773</v>
+      </c>
+      <c r="B121" t="s">
+        <v>774</v>
+      </c>
+      <c r="C121" t="s">
         <v>775</v>
-      </c>
-      <c r="B121" t="s">
-        <v>776</v>
-      </c>
-      <c r="C121" t="s">
-        <v>777</v>
       </c>
       <c r="D121" t="s">
         <v>570</v>
@@ -7737,7 +7737,7 @@
         <v>225</v>
       </c>
       <c r="C122" t="s">
-        <v>778</v>
+        <v>776</v>
       </c>
       <c r="D122" t="s">
         <v>570</v>
@@ -7763,13 +7763,13 @@
     </row>
     <row r="123" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
-        <v>779</v>
+        <v>777</v>
       </c>
       <c r="B123" t="s">
         <v>317</v>
       </c>
       <c r="C123" t="s">
-        <v>780</v>
+        <v>778</v>
       </c>
       <c r="D123" t="s">
         <v>570</v>
@@ -7795,13 +7795,13 @@
     </row>
     <row r="124" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
+        <v>779</v>
+      </c>
+      <c r="B124" t="s">
+        <v>780</v>
+      </c>
+      <c r="C124" t="s">
         <v>781</v>
-      </c>
-      <c r="B124" t="s">
-        <v>782</v>
-      </c>
-      <c r="C124" t="s">
-        <v>783</v>
       </c>
       <c r="D124" t="s">
         <v>615</v>
@@ -7827,13 +7827,13 @@
     </row>
     <row r="125" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
       <c r="B125" t="s">
         <v>280</v>
       </c>
       <c r="C125" t="s">
-        <v>785</v>
+        <v>783</v>
       </c>
       <c r="D125" t="s">
         <v>615</v>
@@ -7859,13 +7859,13 @@
     </row>
     <row r="126" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
+        <v>784</v>
+      </c>
+      <c r="B126" t="s">
+        <v>785</v>
+      </c>
+      <c r="C126" t="s">
         <v>786</v>
-      </c>
-      <c r="B126" t="s">
-        <v>787</v>
-      </c>
-      <c r="C126" t="s">
-        <v>788</v>
       </c>
       <c r="D126" t="s">
         <v>564</v>
@@ -7891,13 +7891,13 @@
     </row>
     <row r="127" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
+        <v>787</v>
+      </c>
+      <c r="B127" t="s">
+        <v>788</v>
+      </c>
+      <c r="C127" t="s">
         <v>789</v>
-      </c>
-      <c r="B127" t="s">
-        <v>790</v>
-      </c>
-      <c r="C127" t="s">
-        <v>791</v>
       </c>
       <c r="D127" t="s">
         <v>570</v>
@@ -7923,13 +7923,13 @@
     </row>
     <row r="128" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
-        <v>792</v>
+        <v>790</v>
       </c>
       <c r="B128" t="s">
         <v>330</v>
       </c>
       <c r="C128" t="s">
-        <v>793</v>
+        <v>791</v>
       </c>
       <c r="D128" t="s">
         <v>564</v>
@@ -7955,13 +7955,13 @@
     </row>
     <row r="129" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
-        <v>794</v>
+        <v>792</v>
       </c>
       <c r="B129" t="s">
         <v>337</v>
       </c>
       <c r="C129" t="s">
-        <v>795</v>
+        <v>793</v>
       </c>
       <c r="D129" t="s">
         <v>594</v>
@@ -7987,13 +7987,13 @@
     </row>
     <row r="130" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
-        <v>796</v>
+        <v>794</v>
       </c>
       <c r="B130" t="s">
         <v>355</v>
       </c>
       <c r="C130" t="s">
-        <v>797</v>
+        <v>795</v>
       </c>
       <c r="D130" t="s">
         <v>564</v>
@@ -8019,13 +8019,13 @@
     </row>
     <row r="131" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
+        <v>796</v>
+      </c>
+      <c r="B131" t="s">
+        <v>797</v>
+      </c>
+      <c r="C131" t="s">
         <v>798</v>
-      </c>
-      <c r="B131" t="s">
-        <v>799</v>
-      </c>
-      <c r="C131" t="s">
-        <v>800</v>
       </c>
       <c r="D131" t="s">
         <v>570</v>
@@ -8051,13 +8051,13 @@
     </row>
     <row r="132" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
-        <v>801</v>
+        <v>799</v>
       </c>
       <c r="B132" t="s">
         <v>349</v>
       </c>
       <c r="C132" t="s">
-        <v>802</v>
+        <v>800</v>
       </c>
       <c r="D132" t="s">
         <v>718</v>
@@ -8083,13 +8083,13 @@
     </row>
     <row r="133" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
-        <v>803</v>
+        <v>801</v>
       </c>
       <c r="B133" t="s">
         <v>389</v>
       </c>
       <c r="C133" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="D133" t="s">
         <v>575</v>
@@ -8115,13 +8115,13 @@
     </row>
     <row r="134" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
-        <v>805</v>
+        <v>803</v>
       </c>
       <c r="B134" t="s">
         <v>196</v>
       </c>
       <c r="C134" t="s">
-        <v>806</v>
+        <v>804</v>
       </c>
       <c r="D134" t="s">
         <v>718</v>
@@ -8147,13 +8147,13 @@
     </row>
     <row r="135" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
-        <v>807</v>
+        <v>805</v>
       </c>
       <c r="B135" t="s">
         <v>260</v>
       </c>
       <c r="C135" t="s">
-        <v>808</v>
+        <v>806</v>
       </c>
       <c r="D135" t="s">
         <v>615</v>
@@ -8179,13 +8179,13 @@
     </row>
     <row r="136" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
+        <v>807</v>
+      </c>
+      <c r="B136" t="s">
+        <v>808</v>
+      </c>
+      <c r="C136" t="s">
         <v>809</v>
-      </c>
-      <c r="B136" t="s">
-        <v>810</v>
-      </c>
-      <c r="C136" t="s">
-        <v>811</v>
       </c>
       <c r="D136" t="s">
         <v>570</v>
@@ -8217,7 +8217,7 @@
         <v>518</v>
       </c>
       <c r="C137" t="s">
-        <v>812</v>
+        <v>810</v>
       </c>
       <c r="D137" t="s">
         <v>570</v>
@@ -8243,13 +8243,13 @@
     </row>
     <row r="138" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
-        <v>813</v>
+        <v>811</v>
       </c>
       <c r="B138" t="s">
         <v>445</v>
       </c>
       <c r="C138" t="s">
-        <v>814</v>
+        <v>812</v>
       </c>
       <c r="D138" t="s">
         <v>564</v>
@@ -8275,13 +8275,13 @@
     </row>
     <row r="139" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
+        <v>813</v>
+      </c>
+      <c r="B139" t="s">
+        <v>814</v>
+      </c>
+      <c r="C139" t="s">
         <v>815</v>
-      </c>
-      <c r="B139" t="s">
-        <v>816</v>
-      </c>
-      <c r="C139" t="s">
-        <v>817</v>
       </c>
       <c r="D139" t="s">
         <v>570</v>
@@ -8313,7 +8313,7 @@
         <v>486</v>
       </c>
       <c r="C140" t="s">
-        <v>818</v>
+        <v>816</v>
       </c>
       <c r="D140" t="s">
         <v>570</v>
@@ -8345,7 +8345,7 @@
         <v>459</v>
       </c>
       <c r="C141" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="D141" t="s">
         <v>570</v>
@@ -8371,13 +8371,13 @@
     </row>
     <row r="142" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
-        <v>820</v>
+        <v>818</v>
       </c>
       <c r="B142" t="s">
         <v>380</v>
       </c>
       <c r="C142" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="D142" t="s">
         <v>718</v>
@@ -8403,13 +8403,13 @@
     </row>
     <row r="143" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
+        <v>820</v>
+      </c>
+      <c r="B143" t="s">
+        <v>821</v>
+      </c>
+      <c r="C143" t="s">
         <v>822</v>
-      </c>
-      <c r="B143" t="s">
-        <v>823</v>
-      </c>
-      <c r="C143" t="s">
-        <v>824</v>
       </c>
       <c r="D143" t="s">
         <v>570</v>
@@ -8435,13 +8435,13 @@
     </row>
     <row r="144" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
-        <v>825</v>
+        <v>823</v>
       </c>
       <c r="B144" t="s">
         <v>412</v>
       </c>
       <c r="C144" t="s">
-        <v>826</v>
+        <v>824</v>
       </c>
       <c r="D144" t="s">
         <v>570</v>
@@ -8467,13 +8467,13 @@
     </row>
     <row r="145" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
+        <v>825</v>
+      </c>
+      <c r="B145" t="s">
+        <v>826</v>
+      </c>
+      <c r="C145" t="s">
         <v>827</v>
-      </c>
-      <c r="B145" t="s">
-        <v>828</v>
-      </c>
-      <c r="C145" t="s">
-        <v>829</v>
       </c>
       <c r="D145" t="s">
         <v>597</v>
@@ -8499,13 +8499,13 @@
     </row>
     <row r="146" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
-        <v>830</v>
+        <v>828</v>
       </c>
       <c r="B146" t="s">
         <v>419</v>
       </c>
       <c r="C146" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
       <c r="D146" t="s">
         <v>564</v>
@@ -8531,13 +8531,13 @@
     </row>
     <row r="147" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
+        <v>830</v>
+      </c>
+      <c r="B147" t="s">
+        <v>831</v>
+      </c>
+      <c r="C147" t="s">
         <v>832</v>
-      </c>
-      <c r="B147" t="s">
-        <v>833</v>
-      </c>
-      <c r="C147" t="s">
-        <v>834</v>
       </c>
       <c r="D147" t="s">
         <v>570</v>
@@ -8563,13 +8563,13 @@
     </row>
     <row r="148" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
-        <v>835</v>
+        <v>833</v>
       </c>
       <c r="B148" t="s">
         <v>298</v>
       </c>
       <c r="C148" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
       <c r="D148" t="s">
         <v>718</v>
@@ -8595,13 +8595,13 @@
     </row>
     <row r="149" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
-        <v>837</v>
+        <v>835</v>
       </c>
       <c r="B149" t="s">
         <v>347</v>
       </c>
       <c r="C149" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
       <c r="D149" t="s">
         <v>597</v>
@@ -8633,7 +8633,7 @@
         <v>372</v>
       </c>
       <c r="C150" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="D150" t="s">
         <v>561</v>
@@ -8659,13 +8659,13 @@
     </row>
     <row r="151" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
+        <v>838</v>
+      </c>
+      <c r="B151" t="s">
+        <v>839</v>
+      </c>
+      <c r="C151" t="s">
         <v>840</v>
-      </c>
-      <c r="B151" t="s">
-        <v>841</v>
-      </c>
-      <c r="C151" t="s">
-        <v>842</v>
       </c>
       <c r="D151" t="s">
         <v>570</v>
@@ -8697,7 +8697,7 @@
         <v>258</v>
       </c>
       <c r="C152" t="s">
-        <v>843</v>
+        <v>841</v>
       </c>
       <c r="D152" t="s">
         <v>570</v>
@@ -8723,13 +8723,13 @@
     </row>
     <row r="153" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
-        <v>844</v>
+        <v>842</v>
       </c>
       <c r="B153" t="s">
         <v>376</v>
       </c>
       <c r="C153" t="s">
-        <v>845</v>
+        <v>843</v>
       </c>
       <c r="D153" t="s">
         <v>564</v>
@@ -8761,7 +8761,7 @@
         <v>343</v>
       </c>
       <c r="C154" t="s">
-        <v>846</v>
+        <v>844</v>
       </c>
       <c r="D154" t="s">
         <v>575</v>
@@ -8787,13 +8787,13 @@
     </row>
     <row r="155" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
-        <v>847</v>
+        <v>845</v>
       </c>
       <c r="B155" t="s">
         <v>335</v>
       </c>
       <c r="C155" t="s">
-        <v>848</v>
+        <v>846</v>
       </c>
       <c r="D155" t="s">
         <v>564</v>
@@ -8819,13 +8819,13 @@
     </row>
     <row r="156" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
-        <v>849</v>
+        <v>847</v>
       </c>
       <c r="B156" t="s">
         <v>382</v>
       </c>
       <c r="C156" t="s">
-        <v>850</v>
+        <v>848</v>
       </c>
       <c r="D156" t="s">
         <v>575</v>
@@ -8851,13 +8851,13 @@
     </row>
     <row r="157" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
+        <v>849</v>
+      </c>
+      <c r="B157" t="s">
+        <v>850</v>
+      </c>
+      <c r="C157" t="s">
         <v>851</v>
-      </c>
-      <c r="B157" t="s">
-        <v>852</v>
-      </c>
-      <c r="C157" t="s">
-        <v>853</v>
       </c>
       <c r="D157" t="s">
         <v>564</v>
@@ -8883,13 +8883,13 @@
     </row>
     <row r="158" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
-        <v>854</v>
+        <v>852</v>
       </c>
       <c r="B158" t="s">
         <v>397</v>
       </c>
       <c r="C158" t="s">
-        <v>855</v>
+        <v>853</v>
       </c>
       <c r="D158" t="s">
         <v>564</v>
@@ -8921,7 +8921,7 @@
         <v>481</v>
       </c>
       <c r="C159" t="s">
-        <v>856</v>
+        <v>854</v>
       </c>
       <c r="D159" t="s">
         <v>564</v>
@@ -8953,7 +8953,7 @@
         <v>464</v>
       </c>
       <c r="C160" t="s">
-        <v>857</v>
+        <v>855</v>
       </c>
       <c r="D160" t="s">
         <v>558</v>
@@ -8979,13 +8979,13 @@
     </row>
     <row r="161" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
-        <v>858</v>
+        <v>856</v>
       </c>
       <c r="B161" t="s">
         <v>345</v>
       </c>
       <c r="C161" t="s">
-        <v>859</v>
+        <v>857</v>
       </c>
       <c r="D161" t="s">
         <v>558</v>
@@ -9011,13 +9011,13 @@
     </row>
     <row r="162" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
+        <v>858</v>
+      </c>
+      <c r="B162" t="s">
+        <v>859</v>
+      </c>
+      <c r="C162" t="s">
         <v>860</v>
-      </c>
-      <c r="B162" t="s">
-        <v>861</v>
-      </c>
-      <c r="C162" t="s">
-        <v>862</v>
       </c>
       <c r="D162" t="s">
         <v>570</v>
@@ -9043,13 +9043,13 @@
     </row>
     <row r="163" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
-        <v>863</v>
+        <v>861</v>
       </c>
       <c r="B163" t="s">
         <v>393</v>
       </c>
       <c r="C163" t="s">
-        <v>864</v>
+        <v>862</v>
       </c>
       <c r="D163" t="s">
         <v>718</v>
@@ -9075,13 +9075,13 @@
     </row>
     <row r="164" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
+        <v>863</v>
+      </c>
+      <c r="B164" t="s">
+        <v>864</v>
+      </c>
+      <c r="C164" t="s">
         <v>865</v>
-      </c>
-      <c r="B164" t="s">
-        <v>866</v>
-      </c>
-      <c r="C164" t="s">
-        <v>867</v>
       </c>
       <c r="D164" t="s">
         <v>564</v>
@@ -9107,13 +9107,13 @@
     </row>
     <row r="165" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
-        <v>868</v>
+        <v>866</v>
       </c>
       <c r="B165" t="s">
         <v>357</v>
       </c>
       <c r="C165" t="s">
-        <v>869</v>
+        <v>867</v>
       </c>
       <c r="D165" t="s">
         <v>718</v>
@@ -9139,13 +9139,13 @@
     </row>
     <row r="166" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
+        <v>868</v>
+      </c>
+      <c r="B166" t="s">
+        <v>869</v>
+      </c>
+      <c r="C166" t="s">
         <v>870</v>
-      </c>
-      <c r="B166" t="s">
-        <v>871</v>
-      </c>
-      <c r="C166" t="s">
-        <v>872</v>
       </c>
       <c r="D166" t="s">
         <v>570</v>
@@ -9171,13 +9171,13 @@
     </row>
     <row r="167" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
+        <v>871</v>
+      </c>
+      <c r="B167" t="s">
+        <v>872</v>
+      </c>
+      <c r="C167" t="s">
         <v>873</v>
-      </c>
-      <c r="B167" t="s">
-        <v>874</v>
-      </c>
-      <c r="C167" t="s">
-        <v>875</v>
       </c>
       <c r="D167" t="s">
         <v>564</v>
@@ -9203,13 +9203,13 @@
     </row>
     <row r="168" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
-        <v>876</v>
+        <v>874</v>
       </c>
       <c r="B168" t="s">
         <v>531</v>
       </c>
       <c r="C168" t="s">
-        <v>877</v>
+        <v>875</v>
       </c>
       <c r="D168" t="s">
         <v>575</v>
@@ -9235,13 +9235,13 @@
     </row>
     <row r="169" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
-        <v>878</v>
+        <v>876</v>
       </c>
       <c r="B169" t="s">
         <v>428</v>
       </c>
       <c r="C169" t="s">
-        <v>879</v>
+        <v>877</v>
       </c>
       <c r="D169" t="s">
         <v>575</v>
@@ -9273,10 +9273,10 @@
         <v>417</v>
       </c>
       <c r="C170" t="s">
-        <v>880</v>
+        <v>878</v>
       </c>
       <c r="D170" t="s">
-        <v>756</v>
+        <v>754</v>
       </c>
       <c r="E170" s="2">
         <v>11663144</v>
@@ -9299,13 +9299,13 @@
     </row>
     <row r="171" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
+        <v>879</v>
+      </c>
+      <c r="B171" t="s">
+        <v>880</v>
+      </c>
+      <c r="C171" t="s">
         <v>881</v>
-      </c>
-      <c r="B171" t="s">
-        <v>882</v>
-      </c>
-      <c r="C171" t="s">
-        <v>883</v>
       </c>
       <c r="D171" t="s">
         <v>564</v>
@@ -9331,13 +9331,13 @@
     </row>
     <row r="172" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
-        <v>884</v>
+        <v>882</v>
       </c>
       <c r="B172" t="s">
         <v>408</v>
       </c>
       <c r="C172" t="s">
-        <v>885</v>
+        <v>883</v>
       </c>
       <c r="D172" t="s">
         <v>594</v>
@@ -9363,13 +9363,13 @@
     </row>
     <row r="173" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
-        <v>886</v>
+        <v>884</v>
       </c>
       <c r="B173" t="s">
         <v>414</v>
       </c>
       <c r="C173" t="s">
-        <v>887</v>
+        <v>885</v>
       </c>
       <c r="D173" t="s">
         <v>718</v>
@@ -9395,13 +9395,13 @@
     </row>
     <row r="174" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
-        <v>888</v>
+        <v>886</v>
       </c>
       <c r="B174" t="s">
         <v>366</v>
       </c>
       <c r="C174" t="s">
-        <v>889</v>
+        <v>887</v>
       </c>
       <c r="D174" t="s">
         <v>615</v>
@@ -9427,16 +9427,16 @@
     </row>
     <row r="175" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
+        <v>888</v>
+      </c>
+      <c r="B175" t="s">
+        <v>889</v>
+      </c>
+      <c r="C175" t="s">
         <v>890</v>
       </c>
-      <c r="B175" t="s">
-        <v>891</v>
-      </c>
-      <c r="C175" t="s">
-        <v>892</v>
-      </c>
       <c r="D175" t="s">
-        <v>756</v>
+        <v>754</v>
       </c>
       <c r="E175" s="2">
         <v>10470354.300000001</v>
@@ -9459,13 +9459,13 @@
     </row>
     <row r="176" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
-        <v>893</v>
+        <v>891</v>
       </c>
       <c r="B176" t="s">
         <v>496</v>
       </c>
       <c r="C176" t="s">
-        <v>894</v>
+        <v>892</v>
       </c>
       <c r="D176" t="s">
         <v>558</v>
@@ -9491,13 +9491,13 @@
     </row>
     <row r="177" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
-        <v>895</v>
+        <v>893</v>
       </c>
       <c r="B177" t="s">
-        <v>983</v>
+        <v>981</v>
       </c>
       <c r="C177" t="s">
-        <v>896</v>
+        <v>894</v>
       </c>
       <c r="D177" t="s">
         <v>575</v>
@@ -9523,13 +9523,13 @@
     </row>
     <row r="178" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
-        <v>897</v>
+        <v>895</v>
       </c>
       <c r="B178" t="s">
         <v>478</v>
       </c>
       <c r="C178" t="s">
-        <v>898</v>
+        <v>896</v>
       </c>
       <c r="D178" t="s">
         <v>575</v>
@@ -9561,7 +9561,7 @@
         <v>443</v>
       </c>
       <c r="C179" t="s">
-        <v>899</v>
+        <v>897</v>
       </c>
       <c r="D179" t="s">
         <v>561</v>
@@ -9587,13 +9587,13 @@
     </row>
     <row r="180" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
-        <v>900</v>
+        <v>898</v>
       </c>
       <c r="B180" t="s">
         <v>461</v>
       </c>
       <c r="C180" t="s">
-        <v>901</v>
+        <v>899</v>
       </c>
       <c r="D180" t="s">
         <v>564</v>
@@ -9619,13 +9619,13 @@
     </row>
     <row r="181" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
-        <v>902</v>
+        <v>900</v>
       </c>
       <c r="B181" t="s">
         <v>437</v>
       </c>
       <c r="C181" t="s">
-        <v>903</v>
+        <v>901</v>
       </c>
       <c r="D181" t="s">
         <v>718</v>
@@ -9651,13 +9651,13 @@
     </row>
     <row r="182" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
-        <v>904</v>
+        <v>902</v>
       </c>
       <c r="B182" t="s">
         <v>535</v>
       </c>
       <c r="C182" t="s">
-        <v>905</v>
+        <v>903</v>
       </c>
       <c r="D182" t="s">
         <v>564</v>
@@ -9683,13 +9683,13 @@
     </row>
     <row r="183" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
-        <v>906</v>
+        <v>904</v>
       </c>
       <c r="B183" t="s">
         <v>391</v>
       </c>
       <c r="C183" t="s">
-        <v>907</v>
+        <v>905</v>
       </c>
       <c r="D183" t="s">
         <v>626</v>
@@ -9715,13 +9715,13 @@
     </row>
     <row r="184" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
-        <v>908</v>
+        <v>906</v>
       </c>
       <c r="B184" t="s">
         <v>500</v>
       </c>
       <c r="C184" t="s">
-        <v>909</v>
+        <v>907</v>
       </c>
       <c r="D184" t="s">
         <v>564</v>
@@ -9747,13 +9747,13 @@
     </row>
     <row r="185" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
-        <v>910</v>
+        <v>908</v>
       </c>
       <c r="B185" t="s">
         <v>488</v>
       </c>
       <c r="C185" t="s">
-        <v>911</v>
+        <v>909</v>
       </c>
       <c r="D185" t="s">
         <v>570</v>
@@ -9779,16 +9779,16 @@
     </row>
     <row r="186" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
-        <v>912</v>
+        <v>910</v>
       </c>
       <c r="B186" t="s">
         <v>522</v>
       </c>
       <c r="C186" t="s">
-        <v>913</v>
+        <v>911</v>
       </c>
       <c r="D186" t="s">
-        <v>756</v>
+        <v>754</v>
       </c>
       <c r="E186" s="2">
         <v>9233897.9700000007</v>
@@ -9811,13 +9811,13 @@
     </row>
     <row r="187" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
+        <v>912</v>
+      </c>
+      <c r="B187" t="s">
+        <v>913</v>
+      </c>
+      <c r="C187" t="s">
         <v>914</v>
-      </c>
-      <c r="B187" t="s">
-        <v>915</v>
-      </c>
-      <c r="C187" t="s">
-        <v>916</v>
       </c>
       <c r="D187" t="s">
         <v>575</v>
@@ -9843,13 +9843,13 @@
     </row>
     <row r="188" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
-        <v>917</v>
+        <v>915</v>
       </c>
       <c r="B188" t="s">
         <v>449</v>
       </c>
       <c r="C188" t="s">
-        <v>918</v>
+        <v>916</v>
       </c>
       <c r="D188" t="s">
         <v>597</v>
@@ -9875,13 +9875,13 @@
     </row>
     <row r="189" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
-        <v>919</v>
+        <v>917</v>
       </c>
       <c r="B189" t="s">
         <v>492</v>
       </c>
       <c r="C189" t="s">
-        <v>920</v>
+        <v>918</v>
       </c>
       <c r="D189" t="s">
         <v>564</v>
@@ -9907,13 +9907,13 @@
     </row>
     <row r="190" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A190" t="s">
-        <v>921</v>
+        <v>919</v>
       </c>
       <c r="B190" t="s">
         <v>364</v>
       </c>
       <c r="C190" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="D190" t="s">
         <v>594</v>
@@ -9939,13 +9939,13 @@
     </row>
     <row r="191" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
-        <v>923</v>
+        <v>921</v>
       </c>
       <c r="B191" t="s">
         <v>504</v>
       </c>
       <c r="C191" t="s">
-        <v>924</v>
+        <v>922</v>
       </c>
       <c r="D191" t="s">
         <v>718</v>
@@ -9971,13 +9971,13 @@
     </row>
     <row r="192" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A192" t="s">
+        <v>923</v>
+      </c>
+      <c r="B192" t="s">
+        <v>924</v>
+      </c>
+      <c r="C192" t="s">
         <v>925</v>
-      </c>
-      <c r="B192" t="s">
-        <v>926</v>
-      </c>
-      <c r="C192" t="s">
-        <v>927</v>
       </c>
       <c r="D192" t="s">
         <v>558</v>
@@ -10003,13 +10003,13 @@
     </row>
     <row r="193" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
-        <v>928</v>
+        <v>926</v>
       </c>
       <c r="B193" t="s">
         <v>421</v>
       </c>
       <c r="C193" t="s">
-        <v>929</v>
+        <v>927</v>
       </c>
       <c r="D193" t="s">
         <v>564</v>
@@ -10041,7 +10041,7 @@
         <v>540</v>
       </c>
       <c r="C194" t="s">
-        <v>930</v>
+        <v>928</v>
       </c>
       <c r="D194" t="s">
         <v>564</v>
@@ -10067,13 +10067,13 @@
     </row>
     <row r="195" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
-        <v>931</v>
+        <v>929</v>
       </c>
       <c r="B195" t="s">
         <v>401</v>
       </c>
       <c r="C195" t="s">
-        <v>932</v>
+        <v>930</v>
       </c>
       <c r="D195" t="s">
         <v>718</v>
@@ -10099,13 +10099,13 @@
     </row>
     <row r="196" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
+        <v>931</v>
+      </c>
+      <c r="B196" t="s">
+        <v>932</v>
+      </c>
+      <c r="C196" t="s">
         <v>933</v>
-      </c>
-      <c r="B196" t="s">
-        <v>934</v>
-      </c>
-      <c r="C196" t="s">
-        <v>935</v>
       </c>
       <c r="D196" t="s">
         <v>564</v>
@@ -10131,13 +10131,13 @@
     </row>
     <row r="197" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
-        <v>936</v>
+        <v>934</v>
       </c>
       <c r="B197" t="s">
         <v>508</v>
       </c>
       <c r="C197" t="s">
-        <v>937</v>
+        <v>935</v>
       </c>
       <c r="D197" t="s">
         <v>570</v>
@@ -10163,13 +10163,13 @@
     </row>
     <row r="198" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
-        <v>938</v>
+        <v>936</v>
       </c>
       <c r="B198" t="s">
         <v>490</v>
       </c>
       <c r="C198" t="s">
-        <v>939</v>
+        <v>937</v>
       </c>
       <c r="D198" t="s">
         <v>718</v>
@@ -10195,13 +10195,13 @@
     </row>
     <row r="199" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
-        <v>940</v>
+        <v>938</v>
       </c>
       <c r="B199" t="s">
         <v>447</v>
       </c>
       <c r="C199" t="s">
-        <v>941</v>
+        <v>939</v>
       </c>
       <c r="D199" t="s">
         <v>718</v>
@@ -10227,13 +10227,13 @@
     </row>
     <row r="200" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
-        <v>942</v>
+        <v>940</v>
       </c>
       <c r="B200" t="s">
         <v>510</v>
       </c>
       <c r="C200" t="s">
-        <v>943</v>
+        <v>941</v>
       </c>
       <c r="D200" t="s">
         <v>615</v>
@@ -10259,13 +10259,13 @@
     </row>
     <row r="201" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
+        <v>942</v>
+      </c>
+      <c r="B201" t="s">
+        <v>943</v>
+      </c>
+      <c r="C201" t="s">
         <v>944</v>
-      </c>
-      <c r="B201" t="s">
-        <v>945</v>
-      </c>
-      <c r="C201" t="s">
-        <v>946</v>
       </c>
       <c r="D201" t="s">
         <v>575</v>
@@ -10291,13 +10291,13 @@
     </row>
     <row r="202" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
-        <v>947</v>
+        <v>945</v>
       </c>
       <c r="B202" t="s">
         <v>426</v>
       </c>
       <c r="C202" t="s">
-        <v>948</v>
+        <v>946</v>
       </c>
       <c r="D202" t="s">
         <v>558</v>
@@ -10323,13 +10323,13 @@
     </row>
     <row r="203" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A203" t="s">
-        <v>949</v>
+        <v>947</v>
       </c>
       <c r="B203" t="s">
         <v>430</v>
       </c>
       <c r="C203" t="s">
-        <v>950</v>
+        <v>948</v>
       </c>
       <c r="D203" t="s">
         <v>564</v>
@@ -10355,13 +10355,13 @@
     </row>
     <row r="204" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A204" t="s">
-        <v>951</v>
+        <v>949</v>
       </c>
       <c r="B204" t="s">
         <v>506</v>
       </c>
       <c r="C204" t="s">
-        <v>952</v>
+        <v>950</v>
       </c>
       <c r="D204" t="s">
         <v>575</v>
@@ -10387,13 +10387,13 @@
     </row>
     <row r="205" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A205" t="s">
-        <v>953</v>
+        <v>951</v>
       </c>
       <c r="B205" t="s">
         <v>546</v>
       </c>
       <c r="C205" t="s">
-        <v>954</v>
+        <v>952</v>
       </c>
       <c r="D205" t="s">
         <v>594</v>
@@ -10419,13 +10419,13 @@
     </row>
     <row r="206" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
+        <v>953</v>
+      </c>
+      <c r="B206" t="s">
+        <v>954</v>
+      </c>
+      <c r="C206" t="s">
         <v>955</v>
-      </c>
-      <c r="B206" t="s">
-        <v>956</v>
-      </c>
-      <c r="C206" t="s">
-        <v>957</v>
       </c>
       <c r="D206" t="s">
         <v>575</v>
@@ -10451,13 +10451,13 @@
     </row>
     <row r="207" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A207" t="s">
-        <v>958</v>
+        <v>956</v>
       </c>
       <c r="B207" t="s">
         <v>353</v>
       </c>
       <c r="C207" t="s">
-        <v>959</v>
+        <v>957</v>
       </c>
       <c r="D207" t="s">
         <v>718</v>
@@ -10483,13 +10483,13 @@
     </row>
     <row r="208" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A208" t="s">
-        <v>960</v>
+        <v>958</v>
       </c>
       <c r="B208" t="s">
         <v>399</v>
       </c>
       <c r="C208" t="s">
-        <v>961</v>
+        <v>959</v>
       </c>
       <c r="D208" t="s">
         <v>570</v>
@@ -10515,13 +10515,13 @@
     </row>
     <row r="209" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A209" t="s">
-        <v>962</v>
+        <v>960</v>
       </c>
       <c r="B209" t="s">
         <v>533</v>
       </c>
       <c r="C209" t="s">
-        <v>963</v>
+        <v>961</v>
       </c>
       <c r="D209" t="s">
         <v>575</v>
@@ -10547,13 +10547,13 @@
     </row>
     <row r="210" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A210" t="s">
+        <v>962</v>
+      </c>
+      <c r="B210" t="s">
+        <v>963</v>
+      </c>
+      <c r="C210" t="s">
         <v>964</v>
-      </c>
-      <c r="B210" t="s">
-        <v>965</v>
-      </c>
-      <c r="C210" t="s">
-        <v>966</v>
       </c>
       <c r="D210" t="s">
         <v>564</v>
@@ -10579,13 +10579,13 @@
     </row>
     <row r="211" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A211" t="s">
-        <v>967</v>
+        <v>965</v>
       </c>
       <c r="B211" t="s">
-        <v>984</v>
+        <v>982</v>
       </c>
       <c r="C211" t="s">
-        <v>968</v>
+        <v>966</v>
       </c>
       <c r="D211" t="s">
         <v>718</v>
@@ -10611,13 +10611,13 @@
     </row>
     <row r="212" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A212" t="s">
+        <v>967</v>
+      </c>
+      <c r="B212" t="s">
+        <v>968</v>
+      </c>
+      <c r="C212" t="s">
         <v>969</v>
-      </c>
-      <c r="B212" t="s">
-        <v>970</v>
-      </c>
-      <c r="C212" t="s">
-        <v>971</v>
       </c>
       <c r="D212" t="s">
         <v>594</v>
@@ -10643,13 +10643,13 @@
     </row>
     <row r="213" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A213" t="s">
-        <v>832</v>
+        <v>830</v>
       </c>
       <c r="B213" t="s">
-        <v>833</v>
+        <v>831</v>
       </c>
       <c r="C213" t="s">
-        <v>972</v>
+        <v>970</v>
       </c>
       <c r="D213" t="s">
         <v>558</v>

--- a/Tickers_Info.xlsx
+++ b/Tickers_Info.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1761" uniqueCount="985">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1766" uniqueCount="989">
   <si>
     <t>Name</t>
   </si>
@@ -2976,6 +2976,18 @@
   </si>
   <si>
     <t>BEP-UN.TO</t>
+  </si>
+  <si>
+    <t>Domain</t>
+  </si>
+  <si>
+    <t>RBC.com</t>
+  </si>
+  <si>
+    <t>TD.com</t>
+  </si>
+  <si>
+    <t>Shopify.com</t>
   </si>
 </sst>
 </file>
@@ -3849,15 +3861,17 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J213"/>
+  <dimension ref="A1:K213"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="11.44140625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="15" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.88671875" customWidth="1"/>
+    <col min="11" max="11" width="12.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -3888,8 +3902,11 @@
       <c r="J1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K1" t="s">
+        <v>985</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -3920,8 +3937,11 @@
       <c r="J2">
         <v>153.88</v>
       </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K2" t="s">
+        <v>986</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -3952,8 +3972,11 @@
       <c r="J3">
         <v>133.33000000000001</v>
       </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K3" t="s">
+        <v>988</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -3984,8 +4007,11 @@
       <c r="J4">
         <v>103.91</v>
       </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K4" t="s">
+        <v>987</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>15</v>
       </c>
@@ -4016,8 +4042,11 @@
       <c r="J5">
         <v>66.760000000000005</v>
       </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K5" t="s">
+        <v>987</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>21</v>
       </c>
@@ -4049,7 +4078,7 @@
         <v>63.27</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>29</v>
       </c>
@@ -4081,7 +4110,7 @@
         <v>60.48</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>41</v>
       </c>
@@ -4113,7 +4142,7 @@
         <v>58.65</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>44</v>
       </c>
@@ -4145,7 +4174,7 @@
         <v>56.21</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>50</v>
       </c>
@@ -4177,7 +4206,7 @@
         <v>55.55</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>571</v>
       </c>
@@ -4209,7 +4238,7 @@
         <v>49.05</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>32</v>
       </c>
@@ -4241,7 +4270,7 @@
         <v>44.43</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>35</v>
       </c>
@@ -4273,7 +4302,7 @@
         <v>43.09</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>47</v>
       </c>
@@ -4305,7 +4334,7 @@
         <v>40.25</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>53</v>
       </c>
@@ -4337,7 +4366,7 @@
         <v>36.83</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>579</v>
       </c>

--- a/Tickers_Info.xlsx
+++ b/Tickers_Info.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1766" uniqueCount="989">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1765" uniqueCount="989">
   <si>
     <t>Name</t>
   </si>
@@ -2933,9 +2933,6 @@
     <t>CANADA PACKERS INC</t>
   </si>
   <si>
-    <t>LUNR ROYALTIES</t>
-  </si>
-  <si>
     <t>TSX</t>
   </si>
   <si>
@@ -2988,6 +2985,9 @@
   </si>
   <si>
     <t>Shopify.com</t>
+  </si>
+  <si>
+    <t>NGEx Minerals Ltd</t>
   </si>
 </sst>
 </file>
@@ -3471,12 +3471,15 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="17" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -3837,21 +3840,21 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B1" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="C1" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="B3" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
       <c r="C3" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
     </row>
   </sheetData>
@@ -3865,9 +3868,10 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="11.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="38.109375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="15" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.88671875" customWidth="1"/>
+    <col min="10" max="10" width="12.6640625" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="12.33203125" customWidth="1"/>
   </cols>
   <sheetData>
@@ -3903,7 +3907,7 @@
         <v>2</v>
       </c>
       <c r="K1" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
@@ -3935,10 +3939,10 @@
         <v>559</v>
       </c>
       <c r="J2">
-        <v>153.88</v>
+        <v>329.22</v>
       </c>
       <c r="K2" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
@@ -3970,10 +3974,10 @@
         <v>559</v>
       </c>
       <c r="J3">
-        <v>133.33000000000001</v>
+        <v>300.39</v>
       </c>
       <c r="K3" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.3">
@@ -4005,77 +4009,74 @@
         <v>559</v>
       </c>
       <c r="J4">
-        <v>103.91</v>
+        <v>220.23</v>
       </c>
       <c r="K4" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="B5" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="C5" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="D5" t="s">
-        <v>564</v>
+        <v>558</v>
       </c>
       <c r="E5" s="2">
-        <v>667580298.61000001</v>
+        <v>632702397.55999994</v>
       </c>
       <c r="F5">
-        <v>3.11</v>
+        <v>2.95</v>
       </c>
       <c r="G5" s="2">
-        <v>10361327</v>
+        <v>10251173</v>
       </c>
       <c r="H5">
-        <v>64.430000000000007</v>
+        <v>61.72</v>
       </c>
       <c r="I5" t="s">
         <v>559</v>
       </c>
       <c r="J5">
-        <v>66.760000000000005</v>
-      </c>
-      <c r="K5" t="s">
-        <v>987</v>
+        <v>142.11000000000001</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="B6" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="C6" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="D6" t="s">
-        <v>558</v>
+        <v>564</v>
       </c>
       <c r="E6" s="2">
-        <v>632702397.55999994</v>
+        <v>667580298.61000001</v>
       </c>
       <c r="F6">
-        <v>2.95</v>
+        <v>3.11</v>
       </c>
       <c r="G6" s="2">
-        <v>10251173</v>
+        <v>10361327</v>
       </c>
       <c r="H6">
-        <v>61.72</v>
+        <v>64.430000000000007</v>
       </c>
       <c r="I6" t="s">
         <v>559</v>
       </c>
       <c r="J6">
-        <v>63.27</v>
+        <v>141.74</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.3">
@@ -4107,7 +4108,7 @@
         <v>559</v>
       </c>
       <c r="J7">
-        <v>60.48</v>
+        <v>128.4</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.3">
@@ -4139,231 +4140,231 @@
         <v>559</v>
       </c>
       <c r="J8">
-        <v>58.65</v>
+        <v>125.45</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="B9" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="C9" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="D9" t="s">
-        <v>558</v>
+        <v>570</v>
       </c>
       <c r="E9" s="2">
-        <v>562113536.26999998</v>
+        <v>555479754.87</v>
       </c>
       <c r="F9">
-        <v>2.62</v>
+        <v>2.59</v>
       </c>
       <c r="G9" s="2">
-        <v>4416701</v>
+        <v>2389263</v>
       </c>
       <c r="H9">
-        <v>127.27</v>
+        <v>232.49</v>
       </c>
       <c r="I9" t="s">
         <v>559</v>
       </c>
       <c r="J9">
-        <v>56.21</v>
+        <v>124.4</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="B10" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="C10" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="D10" t="s">
-        <v>570</v>
+        <v>558</v>
       </c>
       <c r="E10" s="2">
-        <v>555479754.87</v>
+        <v>562113536.26999998</v>
       </c>
       <c r="F10">
-        <v>2.59</v>
+        <v>2.62</v>
       </c>
       <c r="G10" s="2">
-        <v>2389263</v>
+        <v>4416701</v>
       </c>
       <c r="H10">
-        <v>232.49</v>
+        <v>127.27</v>
       </c>
       <c r="I10" t="s">
         <v>559</v>
       </c>
       <c r="J10">
-        <v>55.55</v>
+        <v>118.06</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>571</v>
+        <v>18</v>
       </c>
       <c r="B11" t="s">
-        <v>572</v>
+        <v>19</v>
       </c>
       <c r="C11" t="s">
-        <v>573</v>
+        <v>630</v>
       </c>
       <c r="D11" t="s">
-        <v>570</v>
+        <v>558</v>
       </c>
       <c r="E11" s="2">
-        <v>490524072.95999998</v>
+        <v>129063054.88</v>
       </c>
       <c r="F11">
-        <v>2.29</v>
+        <v>0.6</v>
       </c>
       <c r="G11" s="2">
-        <v>8106496</v>
+        <v>1789808</v>
       </c>
       <c r="H11">
-        <v>60.51</v>
+        <v>72.11</v>
       </c>
       <c r="I11" t="s">
         <v>559</v>
       </c>
       <c r="J11">
-        <v>49.05</v>
+        <v>117.11</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>32</v>
+        <v>571</v>
       </c>
       <c r="B12" t="s">
-        <v>33</v>
+        <v>572</v>
       </c>
       <c r="C12" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="D12" t="s">
-        <v>575</v>
+        <v>570</v>
       </c>
       <c r="E12" s="2">
-        <v>444293963.68000001</v>
+        <v>490524072.95999998</v>
       </c>
       <c r="F12">
-        <v>2.0699999999999998</v>
+        <v>2.29</v>
       </c>
       <c r="G12" s="2">
-        <v>4341352</v>
+        <v>8106496</v>
       </c>
       <c r="H12">
-        <v>102.34</v>
+        <v>60.51</v>
       </c>
       <c r="I12" t="s">
         <v>559</v>
       </c>
       <c r="J12">
-        <v>44.43</v>
+        <v>106.93</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="B13" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C13" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="D13" t="s">
-        <v>564</v>
+        <v>575</v>
       </c>
       <c r="E13" s="2">
-        <v>430929984.75</v>
+        <v>444293963.68000001</v>
       </c>
       <c r="F13">
-        <v>2.0099999999999998</v>
+        <v>2.0699999999999998</v>
       </c>
       <c r="G13" s="2">
-        <v>9926975</v>
+        <v>4341352</v>
       </c>
       <c r="H13">
-        <v>43.41</v>
+        <v>102.34</v>
       </c>
       <c r="I13" t="s">
         <v>559</v>
       </c>
       <c r="J13">
-        <v>43.09</v>
+        <v>93.27</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="B14" t="s">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="C14" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="D14" t="s">
-        <v>558</v>
+        <v>564</v>
       </c>
       <c r="E14" s="2">
-        <v>402505158.56</v>
+        <v>430929984.75</v>
       </c>
       <c r="F14">
-        <v>1.88</v>
+        <v>2.0099999999999998</v>
       </c>
       <c r="G14" s="2">
-        <v>8071088</v>
+        <v>9926975</v>
       </c>
       <c r="H14">
-        <v>49.87</v>
+        <v>43.41</v>
       </c>
       <c r="I14" t="s">
         <v>559</v>
       </c>
       <c r="J14">
-        <v>40.25</v>
+        <v>93.09</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="B15" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="C15" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="D15" t="s">
-        <v>564</v>
+        <v>558</v>
       </c>
       <c r="E15" s="2">
-        <v>368250267.60000002</v>
+        <v>402505158.56</v>
       </c>
       <c r="F15">
-        <v>1.72</v>
+        <v>1.88</v>
       </c>
       <c r="G15" s="2">
-        <v>4941630</v>
+        <v>8071088</v>
       </c>
       <c r="H15">
-        <v>74.52</v>
+        <v>49.87</v>
       </c>
       <c r="I15" t="s">
         <v>559</v>
       </c>
       <c r="J15">
-        <v>36.83</v>
+        <v>84.84</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.3">
@@ -4395,1447 +4396,1447 @@
         <v>559</v>
       </c>
       <c r="J16">
-        <v>36.22</v>
+        <v>84.15</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>68</v>
+        <v>24</v>
       </c>
       <c r="B17" t="s">
-        <v>69</v>
+        <v>25</v>
       </c>
       <c r="C17" t="s">
-        <v>582</v>
+        <v>637</v>
       </c>
       <c r="D17" t="s">
-        <v>570</v>
+        <v>575</v>
       </c>
       <c r="E17" s="2">
-        <v>343063275.51999998</v>
+        <v>116352740.91</v>
       </c>
       <c r="F17">
-        <v>1.6</v>
+        <v>0.54</v>
       </c>
       <c r="G17" s="2">
-        <v>2157088</v>
+        <v>642017</v>
       </c>
       <c r="H17">
-        <v>159.04</v>
+        <v>181.23</v>
       </c>
       <c r="I17" t="s">
         <v>559</v>
       </c>
       <c r="J17">
-        <v>34.31</v>
+        <v>81.81</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="B18" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="C18" t="s">
-        <v>583</v>
+        <v>578</v>
       </c>
       <c r="D18" t="s">
         <v>564</v>
       </c>
       <c r="E18" s="2">
-        <v>337025173.75999999</v>
+        <v>368250267.60000002</v>
       </c>
       <c r="F18">
-        <v>1.57</v>
+        <v>1.72</v>
       </c>
       <c r="G18" s="2">
-        <v>5765056</v>
+        <v>4941630</v>
       </c>
       <c r="H18">
-        <v>58.46</v>
+        <v>74.52</v>
       </c>
       <c r="I18" t="s">
         <v>559</v>
       </c>
       <c r="J18">
-        <v>33.700000000000003</v>
+        <v>79.44</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>584</v>
+        <v>68</v>
       </c>
       <c r="B19" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="C19" t="s">
-        <v>585</v>
+        <v>582</v>
       </c>
       <c r="D19" t="s">
-        <v>558</v>
+        <v>570</v>
       </c>
       <c r="E19" s="2">
-        <v>323207300.55000001</v>
+        <v>343063275.51999998</v>
       </c>
       <c r="F19">
-        <v>1.51</v>
+        <v>1.6</v>
       </c>
       <c r="G19" s="2">
-        <v>1862115</v>
+        <v>2157088</v>
       </c>
       <c r="H19">
-        <v>173.57</v>
+        <v>159.04</v>
       </c>
       <c r="I19" t="s">
         <v>559</v>
       </c>
       <c r="J19">
-        <v>32.32</v>
+        <v>76.16</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>586</v>
+        <v>616</v>
       </c>
       <c r="B20" t="s">
-        <v>27</v>
+        <v>58</v>
       </c>
       <c r="C20" t="s">
-        <v>587</v>
+        <v>617</v>
       </c>
       <c r="D20" t="s">
-        <v>561</v>
+        <v>594</v>
       </c>
       <c r="E20" s="2">
-        <v>314719588.88</v>
+        <v>169234952.47999999</v>
       </c>
       <c r="F20">
-        <v>1.47</v>
+        <v>0.79</v>
       </c>
       <c r="G20" s="2">
-        <v>94636</v>
-      </c>
-      <c r="H20" s="2">
-        <v>3325.58</v>
+        <v>2708626</v>
+      </c>
+      <c r="H20">
+        <v>62.48</v>
       </c>
       <c r="I20" t="s">
         <v>559</v>
       </c>
       <c r="J20">
-        <v>31.47</v>
+        <v>73.11</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>588</v>
+        <v>60</v>
       </c>
       <c r="B21" t="s">
-        <v>589</v>
+        <v>61</v>
       </c>
       <c r="C21" t="s">
-        <v>590</v>
+        <v>583</v>
       </c>
       <c r="D21" t="s">
-        <v>575</v>
+        <v>564</v>
       </c>
       <c r="E21" s="2">
-        <v>297150945.89999998</v>
+        <v>337025173.75999999</v>
       </c>
       <c r="F21">
-        <v>1.39</v>
+        <v>1.57</v>
       </c>
       <c r="G21" s="2">
-        <v>1227795</v>
+        <v>5765056</v>
       </c>
       <c r="H21">
-        <v>242.02</v>
+        <v>58.46</v>
       </c>
       <c r="I21" t="s">
-        <v>591</v>
+        <v>559</v>
       </c>
       <c r="J21">
-        <v>29.72</v>
+        <v>71.09</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>592</v>
+        <v>586</v>
       </c>
       <c r="B22" t="s">
-        <v>56</v>
+        <v>27</v>
       </c>
       <c r="C22" t="s">
-        <v>593</v>
+        <v>587</v>
       </c>
       <c r="D22" t="s">
-        <v>594</v>
+        <v>561</v>
       </c>
       <c r="E22" s="2">
-        <v>270474336</v>
+        <v>314719588.88</v>
       </c>
       <c r="F22">
-        <v>1.26</v>
+        <v>1.47</v>
       </c>
       <c r="G22" s="2">
-        <v>3642752</v>
-      </c>
-      <c r="H22">
-        <v>74.25</v>
+        <v>94636</v>
+      </c>
+      <c r="H22" s="2">
+        <v>3325.58</v>
       </c>
       <c r="I22" t="s">
         <v>559</v>
       </c>
       <c r="J22">
-        <v>27.05</v>
+        <v>70.569999999999993</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>595</v>
+        <v>592</v>
       </c>
       <c r="B23" t="s">
-        <v>80</v>
+        <v>56</v>
       </c>
       <c r="C23" t="s">
-        <v>596</v>
+        <v>593</v>
       </c>
       <c r="D23" t="s">
-        <v>597</v>
+        <v>594</v>
       </c>
       <c r="E23" s="2">
-        <v>263867834.16</v>
+        <v>270474336</v>
       </c>
       <c r="F23">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="G23" s="2">
-        <v>1313298</v>
+        <v>3642752</v>
       </c>
       <c r="H23">
-        <v>200.92</v>
+        <v>74.25</v>
       </c>
       <c r="I23" t="s">
         <v>559</v>
       </c>
       <c r="J23">
-        <v>26.39</v>
+        <v>69.78</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>88</v>
+        <v>584</v>
       </c>
       <c r="B24" t="s">
-        <v>89</v>
+        <v>74</v>
       </c>
       <c r="C24" t="s">
-        <v>598</v>
+        <v>585</v>
       </c>
       <c r="D24" t="s">
-        <v>570</v>
+        <v>558</v>
       </c>
       <c r="E24" s="2">
-        <v>263355561.09</v>
+        <v>323207300.55000001</v>
       </c>
       <c r="F24">
-        <v>1.23</v>
+        <v>1.51</v>
       </c>
       <c r="G24" s="2">
-        <v>915669</v>
+        <v>1862115</v>
       </c>
       <c r="H24">
-        <v>287.61</v>
+        <v>173.57</v>
       </c>
       <c r="I24" t="s">
         <v>559</v>
       </c>
       <c r="J24">
-        <v>26.34</v>
+        <v>69.09</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>599</v>
+        <v>588</v>
       </c>
       <c r="B25" t="s">
-        <v>600</v>
+        <v>589</v>
       </c>
       <c r="C25" t="s">
-        <v>601</v>
+        <v>590</v>
       </c>
       <c r="D25" t="s">
-        <v>564</v>
+        <v>575</v>
       </c>
       <c r="E25" s="2">
-        <v>249790896.41999999</v>
+        <v>297150945.89999998</v>
       </c>
       <c r="F25">
-        <v>1.1599999999999999</v>
+        <v>1.39</v>
       </c>
       <c r="G25" s="2">
-        <v>2068833</v>
+        <v>1227795</v>
       </c>
       <c r="H25">
-        <v>120.74</v>
+        <v>242.02</v>
       </c>
       <c r="I25" t="s">
-        <v>559</v>
+        <v>591</v>
       </c>
       <c r="J25">
-        <v>24.98</v>
+        <v>62.69</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>602</v>
+        <v>660</v>
       </c>
       <c r="B26" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C26" t="s">
-        <v>603</v>
+        <v>661</v>
       </c>
       <c r="D26" t="s">
         <v>558</v>
       </c>
       <c r="E26" s="2">
-        <v>246241416.62</v>
+        <v>85336278.299999997</v>
       </c>
       <c r="F26">
-        <v>1.1499999999999999</v>
+        <v>0.4</v>
       </c>
       <c r="G26" s="2">
-        <v>99017</v>
-      </c>
-      <c r="H26" s="2">
-        <v>2486.86</v>
+        <v>1272726</v>
+      </c>
+      <c r="H26">
+        <v>67.05</v>
       </c>
       <c r="I26" t="s">
         <v>559</v>
       </c>
       <c r="J26">
-        <v>24.62</v>
+        <v>62.33</v>
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>604</v>
+        <v>63</v>
       </c>
       <c r="B27" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C27" t="s">
-        <v>605</v>
+        <v>659</v>
       </c>
       <c r="D27" t="s">
-        <v>558</v>
+        <v>564</v>
       </c>
       <c r="E27" s="2">
-        <v>240716752.25</v>
+        <v>86028161.120000005</v>
       </c>
       <c r="F27">
-        <v>1.1200000000000001</v>
+        <v>0.4</v>
       </c>
       <c r="G27" s="2">
-        <v>847445</v>
+        <v>746254</v>
       </c>
       <c r="H27">
-        <v>284.05</v>
+        <v>115.28</v>
       </c>
       <c r="I27" t="s">
         <v>559</v>
       </c>
       <c r="J27">
-        <v>24.07</v>
+        <v>59.97</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>71</v>
+        <v>602</v>
       </c>
       <c r="B28" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="C28" t="s">
-        <v>606</v>
+        <v>603</v>
       </c>
       <c r="D28" t="s">
         <v>558</v>
       </c>
       <c r="E28" s="2">
-        <v>226279769.52000001</v>
+        <v>246241416.62</v>
       </c>
       <c r="F28">
-        <v>1.06</v>
+        <v>1.1499999999999999</v>
       </c>
       <c r="G28" s="2">
-        <v>2675967</v>
-      </c>
-      <c r="H28">
-        <v>84.56</v>
+        <v>99017</v>
+      </c>
+      <c r="H28" s="2">
+        <v>2486.86</v>
       </c>
       <c r="I28" t="s">
         <v>559</v>
       </c>
       <c r="J28">
-        <v>22.63</v>
+        <v>57.26</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>607</v>
+        <v>88</v>
       </c>
       <c r="B29" t="s">
-        <v>608</v>
+        <v>89</v>
       </c>
       <c r="C29" t="s">
-        <v>609</v>
+        <v>598</v>
       </c>
       <c r="D29" t="s">
         <v>570</v>
       </c>
       <c r="E29" s="2">
-        <v>222902030.40000001</v>
+        <v>263355561.09</v>
       </c>
       <c r="F29">
-        <v>1.04</v>
+        <v>1.23</v>
       </c>
       <c r="G29" s="2">
-        <v>5774664</v>
+        <v>915669</v>
       </c>
       <c r="H29">
-        <v>38.6</v>
+        <v>287.61</v>
       </c>
       <c r="I29" t="s">
         <v>559</v>
       </c>
       <c r="J29">
-        <v>22.29</v>
+        <v>56.76</v>
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>149</v>
+        <v>595</v>
       </c>
       <c r="B30" t="s">
-        <v>150</v>
+        <v>80</v>
       </c>
       <c r="C30" t="s">
-        <v>610</v>
+        <v>596</v>
       </c>
       <c r="D30" t="s">
-        <v>561</v>
+        <v>597</v>
       </c>
       <c r="E30" s="2">
-        <v>203884525.56</v>
+        <v>263867834.16</v>
       </c>
       <c r="F30">
-        <v>0.95</v>
+        <v>1.23</v>
       </c>
       <c r="G30" s="2">
-        <v>546578</v>
+        <v>1313298</v>
       </c>
       <c r="H30">
-        <v>373.02</v>
+        <v>200.92</v>
       </c>
       <c r="I30" t="s">
         <v>559</v>
       </c>
       <c r="J30">
-        <v>20.39</v>
+        <v>56.17</v>
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>91</v>
+        <v>599</v>
       </c>
       <c r="B31" t="s">
-        <v>92</v>
+        <v>600</v>
       </c>
       <c r="C31" t="s">
-        <v>611</v>
+        <v>601</v>
       </c>
       <c r="D31" t="s">
-        <v>570</v>
+        <v>564</v>
       </c>
       <c r="E31" s="2">
-        <v>196520326.78</v>
+        <v>249790896.41999999</v>
       </c>
       <c r="F31">
-        <v>0.92</v>
+        <v>1.1599999999999999</v>
       </c>
       <c r="G31" s="2">
-        <v>2313637</v>
+        <v>2068833</v>
       </c>
       <c r="H31">
-        <v>84.94</v>
+        <v>120.74</v>
       </c>
       <c r="I31" t="s">
         <v>559</v>
       </c>
       <c r="J31">
-        <v>19.649999999999999</v>
+        <v>55.85</v>
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>612</v>
+        <v>604</v>
       </c>
       <c r="B32" t="s">
-        <v>110</v>
+        <v>66</v>
       </c>
       <c r="C32" t="s">
-        <v>613</v>
+        <v>605</v>
       </c>
       <c r="D32" t="s">
         <v>558</v>
       </c>
       <c r="E32" s="2">
-        <v>186900874.19999999</v>
+        <v>240716752.25</v>
       </c>
       <c r="F32">
-        <v>0.87</v>
+        <v>1.1200000000000001</v>
       </c>
       <c r="G32" s="2">
-        <v>2563798</v>
+        <v>847445</v>
       </c>
       <c r="H32">
-        <v>72.900000000000006</v>
+        <v>284.05</v>
       </c>
       <c r="I32" t="s">
         <v>559</v>
       </c>
       <c r="J32">
-        <v>18.690000000000001</v>
+        <v>50.8</v>
       </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>107</v>
+        <v>607</v>
       </c>
       <c r="B33" t="s">
-        <v>108</v>
+        <v>608</v>
       </c>
       <c r="C33" t="s">
-        <v>614</v>
+        <v>609</v>
       </c>
       <c r="D33" t="s">
-        <v>615</v>
+        <v>570</v>
       </c>
       <c r="E33" s="2">
-        <v>169618179.03999999</v>
+        <v>222902030.40000001</v>
       </c>
       <c r="F33">
-        <v>0.79</v>
+        <v>1.04</v>
       </c>
       <c r="G33" s="2">
-        <v>2393033</v>
+        <v>5774664</v>
       </c>
       <c r="H33">
-        <v>70.88</v>
+        <v>38.6</v>
       </c>
       <c r="I33" t="s">
         <v>559</v>
       </c>
       <c r="J33">
-        <v>16.96</v>
+        <v>49.06</v>
       </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>616</v>
+        <v>149</v>
       </c>
       <c r="B34" t="s">
-        <v>58</v>
+        <v>150</v>
       </c>
       <c r="C34" t="s">
-        <v>617</v>
+        <v>610</v>
       </c>
       <c r="D34" t="s">
-        <v>594</v>
+        <v>561</v>
       </c>
       <c r="E34" s="2">
-        <v>169234952.47999999</v>
+        <v>203884525.56</v>
       </c>
       <c r="F34">
-        <v>0.79</v>
+        <v>0.95</v>
       </c>
       <c r="G34" s="2">
-        <v>2708626</v>
+        <v>546578</v>
       </c>
       <c r="H34">
-        <v>62.48</v>
+        <v>373.02</v>
       </c>
       <c r="I34" t="s">
         <v>559</v>
       </c>
       <c r="J34">
-        <v>16.920000000000002</v>
+        <v>47.89</v>
       </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>618</v>
+        <v>71</v>
       </c>
       <c r="B35" t="s">
-        <v>100</v>
+        <v>72</v>
       </c>
       <c r="C35" t="s">
-        <v>619</v>
+        <v>606</v>
       </c>
       <c r="D35" t="s">
-        <v>575</v>
+        <v>558</v>
       </c>
       <c r="E35" s="2">
-        <v>152474468.13999999</v>
+        <v>226279769.52000001</v>
       </c>
       <c r="F35">
-        <v>0.71</v>
+        <v>1.06</v>
       </c>
       <c r="G35" s="2">
-        <v>620294</v>
+        <v>2675967</v>
       </c>
       <c r="H35">
-        <v>245.81</v>
+        <v>84.56</v>
       </c>
       <c r="I35" t="s">
         <v>559</v>
       </c>
       <c r="J35">
-        <v>15.25</v>
+        <v>47.87</v>
       </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>94</v>
+        <v>612</v>
       </c>
       <c r="B36" t="s">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="C36" t="s">
-        <v>620</v>
+        <v>613</v>
       </c>
       <c r="D36" t="s">
-        <v>564</v>
+        <v>558</v>
       </c>
       <c r="E36" s="2">
-        <v>151881541.56999999</v>
+        <v>186900874.19999999</v>
       </c>
       <c r="F36">
-        <v>0.71</v>
+        <v>0.87</v>
       </c>
       <c r="G36" s="2">
-        <v>6699671</v>
+        <v>2563798</v>
       </c>
       <c r="H36">
-        <v>22.67</v>
+        <v>72.900000000000006</v>
       </c>
       <c r="I36" t="s">
         <v>559</v>
       </c>
       <c r="J36">
-        <v>15.19</v>
+        <v>46.86</v>
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="B37" t="s">
-        <v>86</v>
+        <v>95</v>
       </c>
       <c r="C37" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="D37" t="s">
-        <v>597</v>
+        <v>564</v>
       </c>
       <c r="E37" s="2">
-        <v>150121558.72</v>
+        <v>151881541.56999999</v>
       </c>
       <c r="F37">
-        <v>0.7</v>
+        <v>0.71</v>
       </c>
       <c r="G37" s="2">
-        <v>1558571</v>
+        <v>6699671</v>
       </c>
       <c r="H37">
-        <v>96.32</v>
+        <v>22.67</v>
       </c>
       <c r="I37" t="s">
         <v>559</v>
       </c>
       <c r="J37">
-        <v>15.01</v>
+        <v>43.01</v>
       </c>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>622</v>
+        <v>85</v>
       </c>
       <c r="B38" t="s">
-        <v>623</v>
+        <v>86</v>
       </c>
       <c r="C38" t="s">
-        <v>624</v>
+        <v>621</v>
       </c>
       <c r="D38" t="s">
-        <v>564</v>
+        <v>597</v>
       </c>
       <c r="E38" s="2">
-        <v>139759970.13</v>
+        <v>150121558.72</v>
       </c>
       <c r="F38">
-        <v>0.65</v>
+        <v>0.7</v>
       </c>
       <c r="G38" s="2">
-        <v>2758239</v>
+        <v>1558571</v>
       </c>
       <c r="H38">
-        <v>50.67</v>
+        <v>96.32</v>
       </c>
       <c r="I38" t="s">
         <v>559</v>
       </c>
       <c r="J38">
-        <v>13.98</v>
+        <v>42.97</v>
       </c>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>119</v>
+        <v>91</v>
       </c>
       <c r="B39" t="s">
-        <v>120</v>
+        <v>92</v>
       </c>
       <c r="C39" t="s">
-        <v>625</v>
+        <v>611</v>
       </c>
       <c r="D39" t="s">
-        <v>626</v>
+        <v>570</v>
       </c>
       <c r="E39" s="2">
-        <v>139620708.38999999</v>
+        <v>196520326.78</v>
       </c>
       <c r="F39">
-        <v>0.65</v>
+        <v>0.92</v>
       </c>
       <c r="G39" s="2">
-        <v>4433811</v>
+        <v>2313637</v>
       </c>
       <c r="H39">
-        <v>31.49</v>
+        <v>84.94</v>
       </c>
       <c r="I39" t="s">
         <v>559</v>
       </c>
       <c r="J39">
-        <v>13.96</v>
+        <v>42.2</v>
       </c>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>186</v>
+        <v>667</v>
       </c>
       <c r="B40" t="s">
-        <v>187</v>
+        <v>105</v>
       </c>
       <c r="C40" t="s">
-        <v>627</v>
+        <v>668</v>
       </c>
       <c r="D40" t="s">
-        <v>570</v>
+        <v>594</v>
       </c>
       <c r="E40" s="2">
-        <v>137849923.34999999</v>
+        <v>71614939.859999999</v>
       </c>
       <c r="F40">
-        <v>0.64</v>
+        <v>0.33</v>
       </c>
       <c r="G40" s="2">
-        <v>2001015</v>
+        <v>749267</v>
       </c>
       <c r="H40">
-        <v>68.89</v>
+        <v>95.58</v>
       </c>
       <c r="I40" t="s">
         <v>559</v>
       </c>
       <c r="J40">
-        <v>13.78</v>
+        <v>36.24</v>
       </c>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>628</v>
+        <v>107</v>
       </c>
       <c r="B41" t="s">
-        <v>976</v>
+        <v>108</v>
       </c>
       <c r="C41" t="s">
-        <v>629</v>
+        <v>614</v>
       </c>
       <c r="D41" t="s">
-        <v>570</v>
+        <v>615</v>
       </c>
       <c r="E41" s="2">
-        <v>133142031.59999999</v>
+        <v>169618179.03999999</v>
       </c>
       <c r="F41">
-        <v>0.62</v>
+        <v>0.79</v>
       </c>
       <c r="G41" s="2">
-        <v>2135740</v>
+        <v>2393033</v>
       </c>
       <c r="H41">
-        <v>62.34</v>
+        <v>70.88</v>
       </c>
       <c r="I41" t="s">
         <v>559</v>
       </c>
       <c r="J41">
-        <v>13.31</v>
+        <v>35.82</v>
       </c>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>18</v>
+        <v>618</v>
       </c>
       <c r="B42" t="s">
-        <v>19</v>
+        <v>100</v>
       </c>
       <c r="C42" t="s">
-        <v>630</v>
+        <v>619</v>
       </c>
       <c r="D42" t="s">
-        <v>558</v>
+        <v>575</v>
       </c>
       <c r="E42" s="2">
-        <v>129063054.88</v>
+        <v>152474468.13999999</v>
       </c>
       <c r="F42">
-        <v>0.6</v>
+        <v>0.71</v>
       </c>
       <c r="G42" s="2">
-        <v>1789808</v>
+        <v>620294</v>
       </c>
       <c r="H42">
-        <v>72.11</v>
+        <v>245.81</v>
       </c>
       <c r="I42" t="s">
         <v>559</v>
       </c>
       <c r="J42">
-        <v>12.91</v>
+        <v>32.909999999999997</v>
       </c>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>631</v>
+        <v>662</v>
       </c>
       <c r="B43" t="s">
-        <v>632</v>
+        <v>118</v>
       </c>
       <c r="C43" t="s">
-        <v>633</v>
+        <v>663</v>
       </c>
       <c r="D43" t="s">
-        <v>626</v>
+        <v>615</v>
       </c>
       <c r="E43" s="2">
-        <v>127842228.31999999</v>
+        <v>80896440.379999995</v>
       </c>
       <c r="F43">
-        <v>0.6</v>
+        <v>0.38</v>
       </c>
       <c r="G43" s="2">
-        <v>7330403</v>
+        <v>1508699</v>
       </c>
       <c r="H43">
-        <v>17.440000000000001</v>
+        <v>53.62</v>
       </c>
       <c r="I43" t="s">
         <v>559</v>
       </c>
       <c r="J43">
-        <v>12.78</v>
+        <v>32.409999999999997</v>
       </c>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>122</v>
+        <v>628</v>
       </c>
       <c r="B44" t="s">
-        <v>123</v>
+        <v>975</v>
       </c>
       <c r="C44" t="s">
-        <v>634</v>
+        <v>629</v>
       </c>
       <c r="D44" t="s">
-        <v>575</v>
+        <v>570</v>
       </c>
       <c r="E44" s="2">
-        <v>126871576.40000001</v>
+        <v>133142031.59999999</v>
       </c>
       <c r="F44">
-        <v>0.59</v>
+        <v>0.62</v>
       </c>
       <c r="G44" s="2">
-        <v>882278</v>
+        <v>2135740</v>
       </c>
       <c r="H44">
-        <v>143.80000000000001</v>
+        <v>62.34</v>
       </c>
       <c r="I44" t="s">
         <v>559</v>
       </c>
       <c r="J44">
-        <v>12.69</v>
+        <v>31.3</v>
       </c>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>635</v>
+        <v>186</v>
       </c>
       <c r="B45" t="s">
-        <v>977</v>
+        <v>187</v>
       </c>
       <c r="C45" t="s">
-        <v>636</v>
+        <v>627</v>
       </c>
       <c r="D45" t="s">
-        <v>561</v>
+        <v>570</v>
       </c>
       <c r="E45" s="2">
-        <v>120205194.44</v>
+        <v>137849923.34999999</v>
       </c>
       <c r="F45">
-        <v>0.56000000000000005</v>
+        <v>0.64</v>
       </c>
       <c r="G45" s="2">
-        <v>945158</v>
+        <v>2001015</v>
       </c>
       <c r="H45">
-        <v>127.18</v>
+        <v>68.89</v>
       </c>
       <c r="I45" t="s">
         <v>559</v>
       </c>
       <c r="J45">
-        <v>12.02</v>
+        <v>31.18</v>
       </c>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>24</v>
+        <v>638</v>
       </c>
       <c r="B46" t="s">
-        <v>25</v>
+        <v>147</v>
       </c>
       <c r="C46" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="D46" t="s">
-        <v>575</v>
+        <v>570</v>
       </c>
       <c r="E46" s="2">
-        <v>116352740.91</v>
+        <v>109768490.16</v>
       </c>
       <c r="F46">
-        <v>0.54</v>
+        <v>0.51</v>
       </c>
       <c r="G46" s="2">
-        <v>642017</v>
+        <v>3206792</v>
       </c>
       <c r="H46">
-        <v>181.23</v>
+        <v>34.229999999999997</v>
       </c>
       <c r="I46" t="s">
         <v>559</v>
       </c>
       <c r="J46">
-        <v>11.64</v>
+        <v>30.58</v>
       </c>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>638</v>
+        <v>622</v>
       </c>
       <c r="B47" t="s">
-        <v>147</v>
+        <v>623</v>
       </c>
       <c r="C47" t="s">
-        <v>639</v>
+        <v>624</v>
       </c>
       <c r="D47" t="s">
-        <v>570</v>
+        <v>564</v>
       </c>
       <c r="E47" s="2">
-        <v>109768490.16</v>
+        <v>139759970.13</v>
       </c>
       <c r="F47">
-        <v>0.51</v>
+        <v>0.65</v>
       </c>
       <c r="G47" s="2">
-        <v>3206792</v>
+        <v>2758239</v>
       </c>
       <c r="H47">
-        <v>34.229999999999997</v>
+        <v>50.67</v>
       </c>
       <c r="I47" t="s">
         <v>559</v>
       </c>
       <c r="J47">
-        <v>10.98</v>
+        <v>29.98</v>
       </c>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>640</v>
+        <v>119</v>
       </c>
       <c r="B48" t="s">
-        <v>978</v>
+        <v>120</v>
       </c>
       <c r="C48" t="s">
-        <v>641</v>
+        <v>625</v>
       </c>
       <c r="D48" t="s">
-        <v>615</v>
+        <v>626</v>
       </c>
       <c r="E48" s="2">
-        <v>104300052.42</v>
+        <v>139620708.38999999</v>
       </c>
       <c r="F48">
-        <v>0.49</v>
+        <v>0.65</v>
       </c>
       <c r="G48" s="2">
-        <v>2191638</v>
+        <v>4433811</v>
       </c>
       <c r="H48">
-        <v>47.59</v>
+        <v>31.49</v>
       </c>
       <c r="I48" t="s">
-        <v>642</v>
+        <v>559</v>
       </c>
       <c r="J48">
-        <v>10.43</v>
+        <v>29.01</v>
       </c>
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>643</v>
+        <v>693</v>
       </c>
       <c r="B49" t="s">
-        <v>131</v>
+        <v>171</v>
       </c>
       <c r="C49" t="s">
-        <v>644</v>
+        <v>694</v>
       </c>
       <c r="D49" t="s">
-        <v>564</v>
+        <v>570</v>
       </c>
       <c r="E49" s="2">
-        <v>104174987.23</v>
+        <v>54088148.100000001</v>
       </c>
       <c r="F49">
-        <v>0.49</v>
+        <v>0.25</v>
       </c>
       <c r="G49" s="2">
-        <v>1745267</v>
+        <v>470946</v>
       </c>
       <c r="H49">
-        <v>59.69</v>
+        <v>114.85</v>
       </c>
       <c r="I49" t="s">
         <v>559</v>
       </c>
       <c r="J49">
-        <v>10.42</v>
+        <v>28.86</v>
       </c>
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>162</v>
+        <v>635</v>
       </c>
       <c r="B50" t="s">
-        <v>163</v>
+        <v>976</v>
       </c>
       <c r="C50" t="s">
-        <v>645</v>
+        <v>636</v>
       </c>
       <c r="D50" t="s">
-        <v>570</v>
+        <v>561</v>
       </c>
       <c r="E50" s="2">
-        <v>103737146.48</v>
+        <v>120205194.44</v>
       </c>
       <c r="F50">
-        <v>0.48</v>
+        <v>0.56000000000000005</v>
       </c>
       <c r="G50" s="2">
-        <v>1998019</v>
+        <v>945158</v>
       </c>
       <c r="H50">
-        <v>51.92</v>
+        <v>127.18</v>
       </c>
       <c r="I50" t="s">
         <v>559</v>
       </c>
       <c r="J50">
-        <v>10.37</v>
+        <v>27.84</v>
       </c>
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>646</v>
+        <v>655</v>
       </c>
       <c r="B51" t="s">
-        <v>145</v>
+        <v>978</v>
       </c>
       <c r="C51" t="s">
-        <v>647</v>
+        <v>656</v>
       </c>
       <c r="D51" t="s">
-        <v>615</v>
+        <v>626</v>
       </c>
       <c r="E51" s="2">
-        <v>95141187.400000006</v>
+        <v>92682465.829999998</v>
       </c>
       <c r="F51">
-        <v>0.44</v>
+        <v>0.43</v>
       </c>
       <c r="G51" s="2">
-        <v>1423204</v>
+        <v>1834933</v>
       </c>
       <c r="H51">
-        <v>66.849999999999994</v>
+        <v>50.51</v>
       </c>
       <c r="I51" t="s">
         <v>559</v>
       </c>
       <c r="J51">
-        <v>9.51</v>
+        <v>27.6</v>
       </c>
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>648</v>
+        <v>631</v>
       </c>
       <c r="B52" t="s">
-        <v>649</v>
+        <v>632</v>
       </c>
       <c r="C52" t="s">
-        <v>650</v>
+        <v>633</v>
       </c>
       <c r="D52" t="s">
-        <v>597</v>
+        <v>626</v>
       </c>
       <c r="E52" s="2">
-        <v>94455765.030000001</v>
+        <v>127842228.31999999</v>
       </c>
       <c r="F52">
-        <v>0.44</v>
+        <v>0.6</v>
       </c>
       <c r="G52" s="2">
-        <v>1257231</v>
+        <v>7330403</v>
       </c>
       <c r="H52">
-        <v>75.13</v>
+        <v>17.440000000000001</v>
       </c>
       <c r="I52" t="s">
         <v>559</v>
       </c>
       <c r="J52">
-        <v>9.4499999999999993</v>
+        <v>26.96</v>
       </c>
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>651</v>
+        <v>122</v>
       </c>
       <c r="B53" t="s">
-        <v>136</v>
+        <v>123</v>
       </c>
       <c r="C53" t="s">
-        <v>652</v>
+        <v>634</v>
       </c>
       <c r="D53" t="s">
-        <v>594</v>
+        <v>575</v>
       </c>
       <c r="E53" s="2">
-        <v>94098520.239999995</v>
+        <v>126871576.40000001</v>
       </c>
       <c r="F53">
-        <v>0.44</v>
+        <v>0.59</v>
       </c>
       <c r="G53" s="2">
-        <v>943249</v>
+        <v>882278</v>
       </c>
       <c r="H53">
-        <v>99.76</v>
+        <v>143.80000000000001</v>
       </c>
       <c r="I53" t="s">
         <v>559</v>
       </c>
       <c r="J53">
-        <v>9.41</v>
+        <v>26.8</v>
       </c>
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>653</v>
+        <v>724</v>
       </c>
       <c r="B54" t="s">
-        <v>220</v>
+        <v>983</v>
       </c>
       <c r="C54" t="s">
-        <v>654</v>
+        <v>725</v>
       </c>
       <c r="D54" t="s">
-        <v>575</v>
+        <v>615</v>
       </c>
       <c r="E54" s="2">
-        <v>92716520.079999998</v>
+        <v>39111189.960000001</v>
       </c>
       <c r="F54">
-        <v>0.43</v>
+        <v>0.18</v>
       </c>
       <c r="G54" s="2">
-        <v>412936</v>
+        <v>1063382</v>
       </c>
       <c r="H54">
-        <v>224.53</v>
+        <v>36.78</v>
       </c>
       <c r="I54" t="s">
-        <v>559</v>
+        <v>642</v>
       </c>
       <c r="J54">
-        <v>9.27</v>
+        <v>25.39</v>
       </c>
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="B55" t="s">
-        <v>979</v>
+        <v>198</v>
       </c>
       <c r="C55" t="s">
-        <v>656</v>
+        <v>658</v>
       </c>
       <c r="D55" t="s">
-        <v>626</v>
+        <v>570</v>
       </c>
       <c r="E55" s="2">
-        <v>92682465.829999998</v>
+        <v>89338115.620000005</v>
       </c>
       <c r="F55">
-        <v>0.43</v>
+        <v>0.42</v>
       </c>
       <c r="G55" s="2">
-        <v>1834933</v>
+        <v>3211291</v>
       </c>
       <c r="H55">
-        <v>50.51</v>
+        <v>27.82</v>
       </c>
       <c r="I55" t="s">
         <v>559</v>
       </c>
       <c r="J55">
-        <v>9.27</v>
+        <v>25.25</v>
       </c>
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>657</v>
+        <v>653</v>
       </c>
       <c r="B56" t="s">
-        <v>198</v>
+        <v>220</v>
       </c>
       <c r="C56" t="s">
-        <v>658</v>
+        <v>654</v>
       </c>
       <c r="D56" t="s">
-        <v>570</v>
+        <v>575</v>
       </c>
       <c r="E56" s="2">
-        <v>89338115.620000005</v>
+        <v>92716520.079999998</v>
       </c>
       <c r="F56">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="G56" s="2">
-        <v>3211291</v>
+        <v>412936</v>
       </c>
       <c r="H56">
-        <v>27.82</v>
+        <v>224.53</v>
       </c>
       <c r="I56" t="s">
         <v>559</v>
       </c>
       <c r="J56">
-        <v>8.93</v>
+        <v>23.88</v>
       </c>
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>63</v>
+        <v>643</v>
       </c>
       <c r="B57" t="s">
-        <v>64</v>
+        <v>131</v>
       </c>
       <c r="C57" t="s">
-        <v>659</v>
+        <v>644</v>
       </c>
       <c r="D57" t="s">
         <v>564</v>
       </c>
       <c r="E57" s="2">
-        <v>86028161.120000005</v>
+        <v>104174987.23</v>
       </c>
       <c r="F57">
-        <v>0.4</v>
+        <v>0.49</v>
       </c>
       <c r="G57" s="2">
-        <v>746254</v>
+        <v>1745267</v>
       </c>
       <c r="H57">
-        <v>115.28</v>
+        <v>59.69</v>
       </c>
       <c r="I57" t="s">
         <v>559</v>
       </c>
       <c r="J57">
-        <v>8.6</v>
+        <v>23.63</v>
       </c>
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>660</v>
+        <v>162</v>
       </c>
       <c r="B58" t="s">
-        <v>78</v>
+        <v>163</v>
       </c>
       <c r="C58" t="s">
-        <v>661</v>
+        <v>645</v>
       </c>
       <c r="D58" t="s">
-        <v>558</v>
+        <v>570</v>
       </c>
       <c r="E58" s="2">
-        <v>85336278.299999997</v>
+        <v>103737146.48</v>
       </c>
       <c r="F58">
-        <v>0.4</v>
+        <v>0.48</v>
       </c>
       <c r="G58" s="2">
-        <v>1272726</v>
+        <v>1998019</v>
       </c>
       <c r="H58">
-        <v>67.05</v>
+        <v>51.92</v>
       </c>
       <c r="I58" t="s">
         <v>559</v>
       </c>
       <c r="J58">
-        <v>8.5299999999999994</v>
+        <v>23.27</v>
       </c>
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>662</v>
+        <v>702</v>
       </c>
       <c r="B59" t="s">
-        <v>118</v>
+        <v>141</v>
       </c>
       <c r="C59" t="s">
-        <v>663</v>
+        <v>703</v>
       </c>
       <c r="D59" t="s">
-        <v>615</v>
+        <v>570</v>
       </c>
       <c r="E59" s="2">
-        <v>80896440.379999995</v>
+        <v>46888278.359999999</v>
       </c>
       <c r="F59">
-        <v>0.38</v>
+        <v>0.22</v>
       </c>
       <c r="G59" s="2">
-        <v>1508699</v>
+        <v>3417513</v>
       </c>
       <c r="H59">
-        <v>53.62</v>
+        <v>13.72</v>
       </c>
       <c r="I59" t="s">
         <v>559</v>
       </c>
       <c r="J59">
-        <v>8.09</v>
+        <v>22.5</v>
       </c>
     </row>
     <row r="60" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>205</v>
+        <v>640</v>
       </c>
       <c r="B60" t="s">
-        <v>206</v>
+        <v>977</v>
       </c>
       <c r="C60" t="s">
-        <v>664</v>
+        <v>641</v>
       </c>
       <c r="D60" t="s">
-        <v>597</v>
+        <v>615</v>
       </c>
       <c r="E60" s="2">
-        <v>78368040.920000002</v>
+        <v>104300052.42</v>
       </c>
       <c r="F60">
-        <v>0.37</v>
+        <v>0.49</v>
       </c>
       <c r="G60" s="2">
-        <v>879749</v>
+        <v>2191638</v>
       </c>
       <c r="H60">
-        <v>89.08</v>
+        <v>47.59</v>
       </c>
       <c r="I60" t="s">
-        <v>559</v>
+        <v>642</v>
       </c>
       <c r="J60">
-        <v>7.84</v>
+        <v>22.16</v>
       </c>
     </row>
     <row r="61" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>285</v>
+        <v>651</v>
       </c>
       <c r="B61" t="s">
-        <v>178</v>
+        <v>136</v>
       </c>
       <c r="C61" t="s">
-        <v>665</v>
+        <v>652</v>
       </c>
       <c r="D61" t="s">
-        <v>558</v>
+        <v>594</v>
       </c>
       <c r="E61" s="2">
-        <v>78077475.959999993</v>
+        <v>94098520.239999995</v>
       </c>
       <c r="F61">
-        <v>0.36</v>
+        <v>0.44</v>
       </c>
       <c r="G61" s="2">
-        <v>439774</v>
+        <v>943249</v>
       </c>
       <c r="H61">
-        <v>177.54</v>
+        <v>99.76</v>
       </c>
       <c r="I61" t="s">
         <v>559</v>
       </c>
       <c r="J61">
-        <v>7.81</v>
+        <v>21.44</v>
       </c>
     </row>
     <row r="62" spans="1:10" x14ac:dyDescent="0.3">
@@ -5867,519 +5868,519 @@
         <v>559</v>
       </c>
       <c r="J62">
-        <v>7.71</v>
+        <v>21.39</v>
       </c>
     </row>
     <row r="63" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>667</v>
+        <v>648</v>
       </c>
       <c r="B63" t="s">
-        <v>105</v>
+        <v>649</v>
       </c>
       <c r="C63" t="s">
-        <v>668</v>
+        <v>650</v>
       </c>
       <c r="D63" t="s">
-        <v>594</v>
+        <v>597</v>
       </c>
       <c r="E63" s="2">
-        <v>71614939.859999999</v>
+        <v>94455765.030000001</v>
       </c>
       <c r="F63">
-        <v>0.33</v>
+        <v>0.44</v>
       </c>
       <c r="G63" s="2">
-        <v>749267</v>
+        <v>1257231</v>
       </c>
       <c r="H63">
-        <v>95.58</v>
+        <v>75.13</v>
       </c>
       <c r="I63" t="s">
         <v>559</v>
       </c>
       <c r="J63">
-        <v>7.16</v>
+        <v>20.81</v>
       </c>
     </row>
     <row r="64" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>156</v>
+        <v>646</v>
       </c>
       <c r="B64" t="s">
-        <v>157</v>
+        <v>145</v>
       </c>
       <c r="C64" t="s">
-        <v>669</v>
+        <v>647</v>
       </c>
       <c r="D64" t="s">
-        <v>575</v>
+        <v>615</v>
       </c>
       <c r="E64" s="2">
-        <v>69653783.840000004</v>
+        <v>95141187.400000006</v>
       </c>
       <c r="F64">
-        <v>0.32</v>
+        <v>0.44</v>
       </c>
       <c r="G64" s="2">
-        <v>542644</v>
+        <v>1423204</v>
       </c>
       <c r="H64">
-        <v>128.36000000000001</v>
+        <v>66.849999999999994</v>
       </c>
       <c r="I64" t="s">
         <v>559</v>
       </c>
       <c r="J64">
-        <v>6.97</v>
+        <v>20.260000000000002</v>
       </c>
     </row>
     <row r="65" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>670</v>
+        <v>699</v>
       </c>
       <c r="B65" t="s">
-        <v>152</v>
+        <v>194</v>
       </c>
       <c r="C65" t="s">
-        <v>671</v>
+        <v>700</v>
       </c>
       <c r="D65" t="s">
-        <v>564</v>
+        <v>594</v>
       </c>
       <c r="E65" s="2">
-        <v>68633802.840000004</v>
+        <v>48772156.159999996</v>
       </c>
       <c r="F65">
-        <v>0.32</v>
+        <v>0.23</v>
       </c>
       <c r="G65" s="2">
-        <v>2765262</v>
+        <v>1173536</v>
       </c>
       <c r="H65">
-        <v>24.82</v>
+        <v>41.56</v>
       </c>
       <c r="I65" t="s">
         <v>559</v>
       </c>
       <c r="J65">
-        <v>6.86</v>
+        <v>17.05</v>
       </c>
     </row>
     <row r="66" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>324</v>
+        <v>285</v>
       </c>
       <c r="B66" t="s">
-        <v>325</v>
+        <v>178</v>
       </c>
       <c r="C66" t="s">
-        <v>672</v>
+        <v>665</v>
       </c>
       <c r="D66" t="s">
-        <v>570</v>
+        <v>558</v>
       </c>
       <c r="E66" s="2">
-        <v>68529314.700000003</v>
+        <v>78077475.959999993</v>
       </c>
       <c r="F66">
-        <v>0.32</v>
+        <v>0.36</v>
       </c>
       <c r="G66" s="2">
-        <v>3612510</v>
+        <v>439774</v>
       </c>
       <c r="H66">
-        <v>18.97</v>
+        <v>177.54</v>
       </c>
       <c r="I66" t="s">
         <v>559</v>
       </c>
       <c r="J66">
-        <v>6.85</v>
+        <v>16.62</v>
       </c>
     </row>
     <row r="67" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>673</v>
+        <v>205</v>
       </c>
       <c r="B67" t="s">
-        <v>180</v>
+        <v>206</v>
       </c>
       <c r="C67" t="s">
-        <v>674</v>
+        <v>664</v>
       </c>
       <c r="D67" t="s">
-        <v>575</v>
+        <v>597</v>
       </c>
       <c r="E67" s="2">
-        <v>68338632.299999997</v>
+        <v>78368040.920000002</v>
       </c>
       <c r="F67">
-        <v>0.32</v>
+        <v>0.37</v>
       </c>
       <c r="G67" s="2">
-        <v>1906238</v>
+        <v>879749</v>
       </c>
       <c r="H67">
-        <v>35.85</v>
+        <v>89.08</v>
       </c>
       <c r="I67" t="s">
         <v>559</v>
       </c>
       <c r="J67">
-        <v>6.83</v>
+        <v>16.02</v>
       </c>
     </row>
     <row r="68" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>675</v>
+        <v>324</v>
       </c>
       <c r="B68" t="s">
-        <v>154</v>
+        <v>325</v>
       </c>
       <c r="C68" t="s">
-        <v>676</v>
+        <v>672</v>
       </c>
       <c r="D68" t="s">
-        <v>558</v>
+        <v>570</v>
       </c>
       <c r="E68" s="2">
-        <v>68149874.099999994</v>
+        <v>68529314.700000003</v>
       </c>
       <c r="F68">
         <v>0.32</v>
       </c>
       <c r="G68" s="2">
-        <v>1320990</v>
+        <v>3612510</v>
       </c>
       <c r="H68">
-        <v>51.59</v>
+        <v>18.97</v>
       </c>
       <c r="I68" t="s">
         <v>559</v>
       </c>
       <c r="J68">
-        <v>6.81</v>
+        <v>16.010000000000002</v>
       </c>
     </row>
     <row r="69" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>677</v>
+        <v>687</v>
       </c>
       <c r="B69" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="C69" t="s">
-        <v>678</v>
+        <v>688</v>
       </c>
       <c r="D69" t="s">
-        <v>575</v>
+        <v>570</v>
       </c>
       <c r="E69" s="2">
-        <v>67676280.420000002</v>
+        <v>59610070.259999998</v>
       </c>
       <c r="F69">
-        <v>0.32</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="G69" s="2">
-        <v>786842</v>
+        <v>688497</v>
       </c>
       <c r="H69">
-        <v>86.01</v>
+        <v>86.58</v>
       </c>
       <c r="I69" t="s">
         <v>559</v>
       </c>
       <c r="J69">
-        <v>6.77</v>
+        <v>15.22</v>
       </c>
     </row>
     <row r="70" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="B70" t="s">
-        <v>289</v>
+        <v>173</v>
       </c>
       <c r="C70" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
       <c r="D70" t="s">
-        <v>564</v>
+        <v>575</v>
       </c>
       <c r="E70" s="2">
-        <v>65186222.439999998</v>
+        <v>67676280.420000002</v>
       </c>
       <c r="F70">
-        <v>0.3</v>
+        <v>0.32</v>
       </c>
       <c r="G70" s="2">
-        <v>5851546</v>
+        <v>786842</v>
       </c>
       <c r="H70">
-        <v>11.14</v>
+        <v>86.01</v>
       </c>
       <c r="I70" t="s">
         <v>559</v>
       </c>
       <c r="J70">
-        <v>6.52</v>
+        <v>14.94</v>
       </c>
     </row>
     <row r="71" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>681</v>
+        <v>156</v>
       </c>
       <c r="B71" t="s">
-        <v>213</v>
+        <v>157</v>
       </c>
       <c r="C71" t="s">
-        <v>682</v>
+        <v>669</v>
       </c>
       <c r="D71" t="s">
         <v>575</v>
       </c>
       <c r="E71" s="2">
-        <v>61903535.399999999</v>
+        <v>69653783.840000004</v>
       </c>
       <c r="F71">
-        <v>0.28999999999999998</v>
+        <v>0.32</v>
       </c>
       <c r="G71" s="2">
-        <v>385812</v>
+        <v>542644</v>
       </c>
       <c r="H71">
-        <v>160.44999999999999</v>
+        <v>128.36000000000001</v>
       </c>
       <c r="I71" t="s">
         <v>559</v>
       </c>
       <c r="J71">
-        <v>6.19</v>
+        <v>14.92</v>
       </c>
     </row>
     <row r="72" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>181</v>
+        <v>769</v>
       </c>
       <c r="B72" t="s">
-        <v>182</v>
+        <v>203</v>
       </c>
       <c r="C72" t="s">
-        <v>683</v>
+        <v>770</v>
       </c>
       <c r="D72" t="s">
-        <v>575</v>
+        <v>558</v>
       </c>
       <c r="E72" s="2">
-        <v>61878784.799999997</v>
+        <v>23770221.600000001</v>
       </c>
       <c r="F72">
-        <v>0.28999999999999998</v>
+        <v>0.11</v>
       </c>
       <c r="G72" s="2">
-        <v>1524108</v>
+        <v>379716</v>
       </c>
       <c r="H72">
-        <v>40.6</v>
+        <v>62.6</v>
       </c>
       <c r="I72" t="s">
         <v>559</v>
       </c>
       <c r="J72">
-        <v>6.19</v>
+        <v>14.9</v>
       </c>
     </row>
     <row r="73" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>684</v>
+        <v>670</v>
       </c>
       <c r="B73" t="s">
-        <v>685</v>
+        <v>152</v>
       </c>
       <c r="C73" t="s">
-        <v>686</v>
+        <v>671</v>
       </c>
       <c r="D73" t="s">
-        <v>570</v>
+        <v>564</v>
       </c>
       <c r="E73" s="2">
-        <v>60727217.670000002</v>
+        <v>68633802.840000004</v>
       </c>
       <c r="F73">
-        <v>0.28000000000000003</v>
+        <v>0.32</v>
       </c>
       <c r="G73" s="2">
-        <v>2736693</v>
+        <v>2765262</v>
       </c>
       <c r="H73">
-        <v>22.19</v>
+        <v>24.82</v>
       </c>
       <c r="I73" t="s">
         <v>559</v>
       </c>
       <c r="J73">
-        <v>6.07</v>
+        <v>14.85</v>
       </c>
     </row>
     <row r="74" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>687</v>
+        <v>673</v>
       </c>
       <c r="B74" t="s">
-        <v>168</v>
+        <v>180</v>
       </c>
       <c r="C74" t="s">
-        <v>688</v>
+        <v>674</v>
       </c>
       <c r="D74" t="s">
-        <v>570</v>
+        <v>575</v>
       </c>
       <c r="E74" s="2">
-        <v>59610070.259999998</v>
+        <v>68338632.299999997</v>
       </c>
       <c r="F74">
-        <v>0.28000000000000003</v>
+        <v>0.32</v>
       </c>
       <c r="G74" s="2">
-        <v>688497</v>
+        <v>1906238</v>
       </c>
       <c r="H74">
-        <v>86.58</v>
+        <v>35.85</v>
       </c>
       <c r="I74" t="s">
         <v>559</v>
       </c>
       <c r="J74">
-        <v>5.96</v>
+        <v>14.66</v>
       </c>
     </row>
     <row r="75" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>689</v>
+        <v>675</v>
       </c>
       <c r="B75" t="s">
-        <v>192</v>
+        <v>154</v>
       </c>
       <c r="C75" t="s">
-        <v>690</v>
+        <v>676</v>
       </c>
       <c r="D75" t="s">
-        <v>615</v>
+        <v>558</v>
       </c>
       <c r="E75" s="2">
-        <v>58982610.439999998</v>
+        <v>68149874.099999994</v>
       </c>
       <c r="F75">
-        <v>0.28000000000000003</v>
+        <v>0.32</v>
       </c>
       <c r="G75" s="2">
-        <v>1421953</v>
+        <v>1320990</v>
       </c>
       <c r="H75">
-        <v>41.48</v>
+        <v>51.59</v>
       </c>
       <c r="I75" t="s">
         <v>559</v>
       </c>
       <c r="J75">
-        <v>5.9</v>
+        <v>14.54</v>
       </c>
     </row>
     <row r="76" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>208</v>
+        <v>684</v>
       </c>
       <c r="B76" t="s">
-        <v>209</v>
+        <v>685</v>
       </c>
       <c r="C76" t="s">
-        <v>691</v>
+        <v>686</v>
       </c>
       <c r="D76" t="s">
-        <v>561</v>
+        <v>570</v>
       </c>
       <c r="E76" s="2">
-        <v>55748839.560000002</v>
+        <v>60727217.670000002</v>
       </c>
       <c r="F76">
-        <v>0.26</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="G76" s="2">
-        <v>1208254</v>
+        <v>2736693</v>
       </c>
       <c r="H76">
-        <v>46.14</v>
+        <v>22.19</v>
       </c>
       <c r="I76" t="s">
         <v>559</v>
       </c>
       <c r="J76">
-        <v>5.57</v>
+        <v>14.37</v>
       </c>
     </row>
     <row r="77" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>200</v>
+        <v>679</v>
       </c>
       <c r="B77" t="s">
-        <v>201</v>
+        <v>289</v>
       </c>
       <c r="C77" t="s">
-        <v>692</v>
+        <v>680</v>
       </c>
       <c r="D77" t="s">
-        <v>575</v>
+        <v>564</v>
       </c>
       <c r="E77" s="2">
-        <v>54799553.759999998</v>
+        <v>65186222.439999998</v>
       </c>
       <c r="F77">
-        <v>0.26</v>
+        <v>0.3</v>
       </c>
       <c r="G77" s="2">
-        <v>367881</v>
+        <v>5851546</v>
       </c>
       <c r="H77">
-        <v>148.96</v>
+        <v>11.14</v>
       </c>
       <c r="I77" t="s">
         <v>559</v>
       </c>
       <c r="J77">
-        <v>5.48</v>
+        <v>14.05</v>
       </c>
     </row>
     <row r="78" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>693</v>
+        <v>181</v>
       </c>
       <c r="B78" t="s">
-        <v>171</v>
+        <v>182</v>
       </c>
       <c r="C78" t="s">
-        <v>694</v>
+        <v>683</v>
       </c>
       <c r="D78" t="s">
-        <v>570</v>
+        <v>575</v>
       </c>
       <c r="E78" s="2">
-        <v>54088148.100000001</v>
+        <v>61878784.799999997</v>
       </c>
       <c r="F78">
-        <v>0.25</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="G78" s="2">
-        <v>470946</v>
+        <v>1524108</v>
       </c>
       <c r="H78">
-        <v>114.85</v>
+        <v>40.6</v>
       </c>
       <c r="I78" t="s">
         <v>559</v>
       </c>
       <c r="J78">
-        <v>5.41</v>
+        <v>13.89</v>
       </c>
     </row>
     <row r="79" spans="1:10" x14ac:dyDescent="0.3">
@@ -6411,2567 +6412,2567 @@
         <v>559</v>
       </c>
       <c r="J79">
-        <v>5.2</v>
+        <v>13.53</v>
       </c>
     </row>
     <row r="80" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
-        <v>549</v>
+        <v>681</v>
       </c>
       <c r="B80" t="s">
-        <v>550</v>
+        <v>213</v>
       </c>
       <c r="C80" t="s">
-        <v>697</v>
+        <v>682</v>
       </c>
       <c r="D80" t="s">
-        <v>561</v>
+        <v>575</v>
       </c>
       <c r="E80" s="2">
-        <v>50088433.600000001</v>
+        <v>61903535.399999999</v>
       </c>
       <c r="F80">
-        <v>0.23</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="G80" s="2">
-        <v>408685</v>
+        <v>385812</v>
       </c>
       <c r="H80">
-        <v>122.56</v>
+        <v>160.44999999999999</v>
       </c>
       <c r="I80" t="s">
         <v>559</v>
       </c>
       <c r="J80">
-        <v>5.01</v>
+        <v>13.52</v>
       </c>
     </row>
     <row r="81" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
-        <v>295</v>
+        <v>689</v>
       </c>
       <c r="B81" t="s">
-        <v>296</v>
+        <v>192</v>
       </c>
       <c r="C81" t="s">
-        <v>698</v>
+        <v>690</v>
       </c>
       <c r="D81" t="s">
-        <v>570</v>
+        <v>615</v>
       </c>
       <c r="E81" s="2">
-        <v>49174989.600000001</v>
+        <v>58982610.439999998</v>
       </c>
       <c r="F81">
-        <v>0.23</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="G81" s="2">
-        <v>1876908</v>
+        <v>1421953</v>
       </c>
       <c r="H81">
-        <v>26.2</v>
+        <v>41.48</v>
       </c>
       <c r="I81" t="s">
         <v>559</v>
       </c>
       <c r="J81">
-        <v>4.92</v>
+        <v>13.01</v>
       </c>
     </row>
     <row r="82" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
-        <v>699</v>
+        <v>732</v>
       </c>
       <c r="B82" t="s">
-        <v>194</v>
+        <v>222</v>
       </c>
       <c r="C82" t="s">
-        <v>700</v>
+        <v>733</v>
       </c>
       <c r="D82" t="s">
-        <v>594</v>
+        <v>626</v>
       </c>
       <c r="E82" s="2">
-        <v>48772156.159999996</v>
+        <v>37142777.789999999</v>
       </c>
       <c r="F82">
-        <v>0.23</v>
+        <v>0.17</v>
       </c>
       <c r="G82" s="2">
-        <v>1173536</v>
+        <v>731301</v>
       </c>
       <c r="H82">
-        <v>41.56</v>
+        <v>50.79</v>
       </c>
       <c r="I82" t="s">
         <v>559</v>
       </c>
       <c r="J82">
-        <v>4.88</v>
+        <v>12.1</v>
       </c>
     </row>
     <row r="83" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
-        <v>321</v>
+        <v>200</v>
       </c>
       <c r="B83" t="s">
-        <v>322</v>
+        <v>201</v>
       </c>
       <c r="C83" t="s">
-        <v>701</v>
+        <v>692</v>
       </c>
       <c r="D83" t="s">
-        <v>570</v>
+        <v>575</v>
       </c>
       <c r="E83" s="2">
-        <v>48493986.25</v>
+        <v>54799553.759999998</v>
       </c>
       <c r="F83">
-        <v>0.23</v>
+        <v>0.26</v>
       </c>
       <c r="G83" s="2">
-        <v>2179505</v>
+        <v>367881</v>
       </c>
       <c r="H83">
-        <v>22.25</v>
+        <v>148.96</v>
       </c>
       <c r="I83" t="s">
         <v>559</v>
       </c>
       <c r="J83">
-        <v>4.8499999999999996</v>
+        <v>12.03</v>
       </c>
     </row>
     <row r="84" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
-        <v>702</v>
+        <v>208</v>
       </c>
       <c r="B84" t="s">
-        <v>141</v>
+        <v>209</v>
       </c>
       <c r="C84" t="s">
-        <v>703</v>
+        <v>691</v>
       </c>
       <c r="D84" t="s">
-        <v>570</v>
+        <v>561</v>
       </c>
       <c r="E84" s="2">
-        <v>46888278.359999999</v>
+        <v>55748839.560000002</v>
       </c>
       <c r="F84">
-        <v>0.22</v>
+        <v>0.26</v>
       </c>
       <c r="G84" s="2">
-        <v>3417513</v>
+        <v>1208254</v>
       </c>
       <c r="H84">
-        <v>13.72</v>
+        <v>46.14</v>
       </c>
       <c r="I84" t="s">
         <v>559</v>
       </c>
       <c r="J84">
-        <v>4.6900000000000004</v>
+        <v>11.62</v>
       </c>
     </row>
     <row r="85" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
-        <v>704</v>
+        <v>321</v>
       </c>
       <c r="B85" t="s">
-        <v>211</v>
+        <v>322</v>
       </c>
       <c r="C85" t="s">
-        <v>705</v>
+        <v>701</v>
       </c>
       <c r="D85" t="s">
-        <v>564</v>
+        <v>570</v>
       </c>
       <c r="E85" s="2">
-        <v>46789755.520000003</v>
+        <v>48493986.25</v>
       </c>
       <c r="F85">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="G85" s="2">
-        <v>1091179</v>
+        <v>2179505</v>
       </c>
       <c r="H85">
-        <v>42.88</v>
+        <v>22.25</v>
       </c>
       <c r="I85" t="s">
         <v>559</v>
       </c>
       <c r="J85">
-        <v>4.68</v>
+        <v>11.6</v>
       </c>
     </row>
     <row r="86" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
-        <v>706</v>
+        <v>763</v>
       </c>
       <c r="B86" t="s">
-        <v>707</v>
+        <v>229</v>
       </c>
       <c r="C86" t="s">
-        <v>708</v>
+        <v>764</v>
       </c>
       <c r="D86" t="s">
-        <v>570</v>
+        <v>615</v>
       </c>
       <c r="E86" s="2">
-        <v>46015014.399999999</v>
+        <v>26000255.120000001</v>
       </c>
       <c r="F86">
-        <v>0.21</v>
+        <v>0.12</v>
       </c>
       <c r="G86" s="2">
-        <v>965080</v>
+        <v>614954</v>
       </c>
       <c r="H86">
-        <v>47.68</v>
+        <v>42.28</v>
       </c>
       <c r="I86" t="s">
         <v>559</v>
       </c>
       <c r="J86">
-        <v>4.5999999999999996</v>
+        <v>11.5</v>
       </c>
     </row>
     <row r="87" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
-        <v>709</v>
+        <v>742</v>
       </c>
       <c r="B87" t="s">
-        <v>255</v>
+        <v>184</v>
       </c>
       <c r="C87" t="s">
-        <v>710</v>
+        <v>743</v>
       </c>
       <c r="D87" t="s">
-        <v>575</v>
+        <v>594</v>
       </c>
       <c r="E87" s="2">
-        <v>45419962.380000003</v>
+        <v>29945493.989999998</v>
       </c>
       <c r="F87">
-        <v>0.21</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="G87" s="2">
-        <v>628563</v>
+        <v>633231</v>
       </c>
       <c r="H87">
-        <v>72.260000000000005</v>
+        <v>47.29</v>
       </c>
       <c r="I87" t="s">
         <v>559</v>
       </c>
       <c r="J87">
-        <v>4.54</v>
+        <v>10.87</v>
       </c>
     </row>
     <row r="88" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
-        <v>711</v>
+        <v>295</v>
       </c>
       <c r="B88" t="s">
-        <v>374</v>
+        <v>296</v>
       </c>
       <c r="C88" t="s">
-        <v>712</v>
+        <v>698</v>
       </c>
       <c r="D88" t="s">
         <v>570</v>
       </c>
       <c r="E88" s="2">
-        <v>44679568.32</v>
+        <v>49174989.600000001</v>
       </c>
       <c r="F88">
-        <v>0.21</v>
+        <v>0.23</v>
       </c>
       <c r="G88" s="2">
-        <v>1058256</v>
+        <v>1876908</v>
       </c>
       <c r="H88">
-        <v>42.22</v>
+        <v>26.2</v>
       </c>
       <c r="I88" t="s">
         <v>559</v>
       </c>
       <c r="J88">
-        <v>4.47</v>
+        <v>10.86</v>
       </c>
     </row>
     <row r="89" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
-        <v>713</v>
+        <v>803</v>
       </c>
       <c r="B89" t="s">
-        <v>227</v>
+        <v>196</v>
       </c>
       <c r="C89" t="s">
-        <v>714</v>
+        <v>804</v>
       </c>
       <c r="D89" t="s">
-        <v>615</v>
+        <v>718</v>
       </c>
       <c r="E89" s="2">
-        <v>44086089.039999999</v>
+        <v>19251103.489999998</v>
       </c>
       <c r="F89">
-        <v>0.21</v>
+        <v>0.09</v>
       </c>
       <c r="G89" s="2">
-        <v>740072</v>
+        <v>1294627</v>
       </c>
       <c r="H89">
-        <v>59.57</v>
+        <v>14.87</v>
       </c>
       <c r="I89" t="s">
         <v>559</v>
       </c>
       <c r="J89">
-        <v>4.41</v>
+        <v>10.67</v>
       </c>
     </row>
     <row r="90" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
-        <v>249</v>
+        <v>549</v>
       </c>
       <c r="B90" t="s">
-        <v>250</v>
+        <v>550</v>
       </c>
       <c r="C90" t="s">
-        <v>715</v>
+        <v>697</v>
       </c>
       <c r="D90" t="s">
-        <v>570</v>
+        <v>561</v>
       </c>
       <c r="E90" s="2">
-        <v>43733977.32</v>
+        <v>50088433.600000001</v>
       </c>
       <c r="F90">
-        <v>0.2</v>
+        <v>0.23</v>
       </c>
       <c r="G90" s="2">
-        <v>892166</v>
+        <v>408685</v>
       </c>
       <c r="H90">
-        <v>49.02</v>
+        <v>122.56</v>
       </c>
       <c r="I90" t="s">
         <v>559</v>
       </c>
       <c r="J90">
-        <v>4.37</v>
+        <v>10.49</v>
       </c>
     </row>
     <row r="91" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
-        <v>311</v>
+        <v>729</v>
       </c>
       <c r="B91" t="s">
-        <v>312</v>
+        <v>271</v>
       </c>
       <c r="C91" t="s">
-        <v>716</v>
+        <v>730</v>
       </c>
       <c r="D91" t="s">
         <v>570</v>
       </c>
       <c r="E91" s="2">
-        <v>43107701</v>
+        <v>38112111.719999999</v>
       </c>
       <c r="F91">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="G91" s="2">
-        <v>3758300</v>
+        <v>2968233</v>
       </c>
       <c r="H91">
-        <v>11.47</v>
+        <v>12.84</v>
       </c>
       <c r="I91" t="s">
         <v>559</v>
       </c>
       <c r="J91">
-        <v>4.3099999999999996</v>
+        <v>10.44</v>
       </c>
     </row>
     <row r="92" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
-        <v>189</v>
+        <v>215</v>
       </c>
       <c r="B92" t="s">
-        <v>190</v>
+        <v>216</v>
       </c>
       <c r="C92" t="s">
-        <v>717</v>
+        <v>719</v>
       </c>
       <c r="D92" t="s">
         <v>718</v>
       </c>
       <c r="E92" s="2">
-        <v>42479019.509999998</v>
+        <v>42179351.759999998</v>
       </c>
       <c r="F92">
         <v>0.2</v>
       </c>
       <c r="G92" s="2">
-        <v>195243</v>
+        <v>208788</v>
       </c>
       <c r="H92">
-        <v>217.57</v>
+        <v>202.02</v>
       </c>
       <c r="I92" t="s">
         <v>559</v>
       </c>
       <c r="J92">
-        <v>4.25</v>
+        <v>10.4</v>
       </c>
     </row>
     <row r="93" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
-        <v>215</v>
+        <v>706</v>
       </c>
       <c r="B93" t="s">
-        <v>216</v>
+        <v>707</v>
       </c>
       <c r="C93" t="s">
-        <v>719</v>
+        <v>708</v>
       </c>
       <c r="D93" t="s">
-        <v>718</v>
+        <v>570</v>
       </c>
       <c r="E93" s="2">
-        <v>42179351.759999998</v>
+        <v>46015014.399999999</v>
       </c>
       <c r="F93">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="G93" s="2">
-        <v>208788</v>
+        <v>965080</v>
       </c>
       <c r="H93">
-        <v>202.02</v>
+        <v>47.68</v>
       </c>
       <c r="I93" t="s">
         <v>559</v>
       </c>
       <c r="J93">
-        <v>4.22</v>
+        <v>10.28</v>
       </c>
     </row>
     <row r="94" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
-        <v>720</v>
+        <v>704</v>
       </c>
       <c r="B94" t="s">
-        <v>319</v>
+        <v>211</v>
       </c>
       <c r="C94" t="s">
-        <v>721</v>
+        <v>705</v>
       </c>
       <c r="D94" t="s">
-        <v>570</v>
+        <v>564</v>
       </c>
       <c r="E94" s="2">
-        <v>41691866.579999998</v>
+        <v>46789755.520000003</v>
       </c>
       <c r="F94">
-        <v>0.19</v>
+        <v>0.22</v>
       </c>
       <c r="G94" s="2">
-        <v>1094562</v>
+        <v>1091179</v>
       </c>
       <c r="H94">
-        <v>38.090000000000003</v>
+        <v>42.88</v>
       </c>
       <c r="I94" t="s">
         <v>559</v>
       </c>
       <c r="J94">
-        <v>4.17</v>
+        <v>10.06</v>
       </c>
     </row>
     <row r="95" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
-        <v>722</v>
+        <v>311</v>
       </c>
       <c r="B95" t="s">
-        <v>983</v>
+        <v>312</v>
       </c>
       <c r="C95" t="s">
-        <v>723</v>
+        <v>716</v>
       </c>
       <c r="D95" t="s">
-        <v>597</v>
+        <v>570</v>
       </c>
       <c r="E95" s="2">
-        <v>41402627.159999996</v>
+        <v>43107701</v>
       </c>
       <c r="F95">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="G95" s="2">
-        <v>240252</v>
+        <v>3758300</v>
       </c>
       <c r="H95">
-        <v>172.33</v>
+        <v>11.47</v>
       </c>
       <c r="I95" t="s">
         <v>559</v>
       </c>
       <c r="J95">
-        <v>4.1399999999999997</v>
+        <v>9.9</v>
       </c>
     </row>
     <row r="96" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
-        <v>724</v>
+        <v>709</v>
       </c>
       <c r="B96" t="s">
-        <v>984</v>
+        <v>255</v>
       </c>
       <c r="C96" t="s">
-        <v>725</v>
+        <v>710</v>
       </c>
       <c r="D96" t="s">
-        <v>615</v>
+        <v>575</v>
       </c>
       <c r="E96" s="2">
-        <v>39111189.960000001</v>
+        <v>45419962.380000003</v>
       </c>
       <c r="F96">
-        <v>0.18</v>
+        <v>0.21</v>
       </c>
       <c r="G96" s="2">
-        <v>1063382</v>
+        <v>628563</v>
       </c>
       <c r="H96">
-        <v>36.78</v>
+        <v>72.260000000000005</v>
       </c>
       <c r="I96" t="s">
-        <v>642</v>
+        <v>559</v>
       </c>
       <c r="J96">
-        <v>3.91</v>
+        <v>9.89</v>
       </c>
     </row>
     <row r="97" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
-        <v>726</v>
+        <v>739</v>
       </c>
       <c r="B97" t="s">
-        <v>727</v>
+        <v>740</v>
       </c>
       <c r="C97" t="s">
-        <v>728</v>
+        <v>741</v>
       </c>
       <c r="D97" t="s">
         <v>570</v>
       </c>
       <c r="E97" s="2">
-        <v>38815255.409999996</v>
+        <v>30429863.75</v>
       </c>
       <c r="F97">
-        <v>0.18</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="G97" s="2">
-        <v>6270639</v>
+        <v>768625</v>
       </c>
       <c r="H97">
-        <v>6.19</v>
+        <v>39.590000000000003</v>
       </c>
       <c r="I97" t="s">
         <v>559</v>
       </c>
       <c r="J97">
-        <v>3.88</v>
+        <v>9.89</v>
       </c>
     </row>
     <row r="98" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
-        <v>729</v>
+        <v>257</v>
       </c>
       <c r="B98" t="s">
-        <v>271</v>
+        <v>258</v>
       </c>
       <c r="C98" t="s">
-        <v>730</v>
+        <v>841</v>
       </c>
       <c r="D98" t="s">
         <v>570</v>
       </c>
       <c r="E98" s="2">
-        <v>38112111.719999999</v>
+        <v>15217840.18</v>
       </c>
       <c r="F98">
-        <v>0.18</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="G98" s="2">
-        <v>2968233</v>
+        <v>333871</v>
       </c>
       <c r="H98">
-        <v>12.84</v>
+        <v>45.58</v>
       </c>
       <c r="I98" t="s">
         <v>559</v>
       </c>
       <c r="J98">
-        <v>3.81</v>
+        <v>9.8800000000000008</v>
       </c>
     </row>
     <row r="99" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
-        <v>235</v>
+        <v>711</v>
       </c>
       <c r="B99" t="s">
-        <v>236</v>
+        <v>374</v>
       </c>
       <c r="C99" t="s">
-        <v>731</v>
+        <v>712</v>
       </c>
       <c r="D99" t="s">
-        <v>564</v>
+        <v>570</v>
       </c>
       <c r="E99" s="2">
-        <v>37437979.039999999</v>
+        <v>44679568.32</v>
       </c>
       <c r="F99">
-        <v>0.17</v>
+        <v>0.21</v>
       </c>
       <c r="G99" s="2">
-        <v>988592</v>
+        <v>1058256</v>
       </c>
       <c r="H99">
-        <v>37.869999999999997</v>
+        <v>42.22</v>
       </c>
       <c r="I99" t="s">
         <v>559</v>
       </c>
       <c r="J99">
-        <v>3.74</v>
+        <v>9.69</v>
       </c>
     </row>
     <row r="100" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
-        <v>732</v>
+        <v>189</v>
       </c>
       <c r="B100" t="s">
-        <v>222</v>
+        <v>190</v>
       </c>
       <c r="C100" t="s">
-        <v>733</v>
+        <v>717</v>
       </c>
       <c r="D100" t="s">
-        <v>626</v>
+        <v>718</v>
       </c>
       <c r="E100" s="2">
-        <v>37142777.789999999</v>
+        <v>42479019.509999998</v>
       </c>
       <c r="F100">
-        <v>0.17</v>
+        <v>0.2</v>
       </c>
       <c r="G100" s="2">
-        <v>731301</v>
+        <v>195243</v>
       </c>
       <c r="H100">
-        <v>50.79</v>
+        <v>217.57</v>
       </c>
       <c r="I100" t="s">
         <v>559</v>
       </c>
       <c r="J100">
-        <v>3.71</v>
+        <v>9.64</v>
       </c>
     </row>
     <row r="101" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
-        <v>300</v>
+        <v>249</v>
       </c>
       <c r="B101" t="s">
-        <v>301</v>
+        <v>250</v>
       </c>
       <c r="C101" t="s">
-        <v>734</v>
+        <v>715</v>
       </c>
       <c r="D101" t="s">
-        <v>564</v>
+        <v>570</v>
       </c>
       <c r="E101" s="2">
-        <v>36249370.609999999</v>
+        <v>43733977.32</v>
       </c>
       <c r="F101">
-        <v>0.17</v>
+        <v>0.2</v>
       </c>
       <c r="G101" s="2">
-        <v>3095591</v>
+        <v>892166</v>
       </c>
       <c r="H101">
-        <v>11.71</v>
+        <v>49.02</v>
       </c>
       <c r="I101" t="s">
         <v>559</v>
       </c>
       <c r="J101">
-        <v>3.62</v>
+        <v>9.61</v>
       </c>
     </row>
     <row r="102" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
-        <v>735</v>
+        <v>722</v>
       </c>
       <c r="B102" t="s">
-        <v>238</v>
+        <v>982</v>
       </c>
       <c r="C102" t="s">
-        <v>736</v>
+        <v>723</v>
       </c>
       <c r="D102" t="s">
-        <v>558</v>
+        <v>597</v>
       </c>
       <c r="E102" s="2">
-        <v>34269768</v>
+        <v>41402627.159999996</v>
       </c>
       <c r="F102">
-        <v>0.16</v>
+        <v>0.19</v>
       </c>
       <c r="G102" s="2">
-        <v>450918</v>
+        <v>240252</v>
       </c>
       <c r="H102">
-        <v>76</v>
+        <v>172.33</v>
       </c>
       <c r="I102" t="s">
         <v>559</v>
       </c>
       <c r="J102">
-        <v>3.43</v>
+        <v>9.27</v>
       </c>
     </row>
     <row r="103" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
-        <v>737</v>
+        <v>735</v>
       </c>
       <c r="B103" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="C103" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
       <c r="D103" t="s">
         <v>558</v>
       </c>
       <c r="E103" s="2">
-        <v>30630345.719999999</v>
+        <v>34269768</v>
       </c>
       <c r="F103">
-        <v>0.14000000000000001</v>
+        <v>0.16</v>
       </c>
       <c r="G103" s="2">
-        <v>276547</v>
+        <v>450918</v>
       </c>
       <c r="H103">
-        <v>110.76</v>
+        <v>76</v>
       </c>
       <c r="I103" t="s">
         <v>559</v>
       </c>
       <c r="J103">
-        <v>3.06</v>
+        <v>9.1999999999999993</v>
       </c>
     </row>
     <row r="104" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
-        <v>739</v>
+        <v>713</v>
       </c>
       <c r="B104" t="s">
-        <v>740</v>
+        <v>227</v>
       </c>
       <c r="C104" t="s">
-        <v>741</v>
+        <v>714</v>
       </c>
       <c r="D104" t="s">
-        <v>570</v>
+        <v>615</v>
       </c>
       <c r="E104" s="2">
-        <v>30429863.75</v>
+        <v>44086089.039999999</v>
       </c>
       <c r="F104">
-        <v>0.14000000000000001</v>
+        <v>0.21</v>
       </c>
       <c r="G104" s="2">
-        <v>768625</v>
+        <v>740072</v>
       </c>
       <c r="H104">
-        <v>39.590000000000003</v>
+        <v>59.57</v>
       </c>
       <c r="I104" t="s">
         <v>559</v>
       </c>
       <c r="J104">
-        <v>3.04</v>
+        <v>9.18</v>
       </c>
     </row>
     <row r="105" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
-        <v>742</v>
+        <v>720</v>
       </c>
       <c r="B105" t="s">
-        <v>184</v>
+        <v>319</v>
       </c>
       <c r="C105" t="s">
-        <v>743</v>
+        <v>721</v>
       </c>
       <c r="D105" t="s">
-        <v>594</v>
+        <v>570</v>
       </c>
       <c r="E105" s="2">
-        <v>29945493.989999998</v>
+        <v>41691866.579999998</v>
       </c>
       <c r="F105">
-        <v>0.14000000000000001</v>
+        <v>0.19</v>
       </c>
       <c r="G105" s="2">
-        <v>633231</v>
+        <v>1094562</v>
       </c>
       <c r="H105">
-        <v>47.29</v>
+        <v>38.090000000000003</v>
       </c>
       <c r="I105" t="s">
         <v>559</v>
       </c>
       <c r="J105">
-        <v>2.99</v>
+        <v>9.11</v>
       </c>
     </row>
     <row r="106" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
-        <v>744</v>
+        <v>726</v>
       </c>
       <c r="B106" t="s">
-        <v>264</v>
+        <v>727</v>
       </c>
       <c r="C106" t="s">
-        <v>745</v>
+        <v>728</v>
       </c>
       <c r="D106" t="s">
-        <v>564</v>
+        <v>570</v>
       </c>
       <c r="E106" s="2">
-        <v>29880533.760000002</v>
+        <v>38815255.409999996</v>
       </c>
       <c r="F106">
-        <v>0.14000000000000001</v>
+        <v>0.18</v>
       </c>
       <c r="G106" s="2">
-        <v>1111627</v>
+        <v>6270639</v>
       </c>
       <c r="H106">
-        <v>26.88</v>
+        <v>6.19</v>
       </c>
       <c r="I106" t="s">
         <v>559</v>
       </c>
       <c r="J106">
-        <v>2.99</v>
+        <v>8.75</v>
       </c>
     </row>
     <row r="107" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
-        <v>386</v>
+        <v>300</v>
       </c>
       <c r="B107" t="s">
-        <v>387</v>
+        <v>301</v>
       </c>
       <c r="C107" t="s">
-        <v>746</v>
+        <v>734</v>
       </c>
       <c r="D107" t="s">
-        <v>570</v>
+        <v>564</v>
       </c>
       <c r="E107" s="2">
-        <v>29626516.100000001</v>
+        <v>36249370.609999999</v>
       </c>
       <c r="F107">
-        <v>0.14000000000000001</v>
+        <v>0.17</v>
       </c>
       <c r="G107" s="2">
-        <v>957238</v>
+        <v>3095591</v>
       </c>
       <c r="H107">
-        <v>30.95</v>
+        <v>11.71</v>
       </c>
       <c r="I107" t="s">
         <v>559</v>
       </c>
       <c r="J107">
-        <v>2.96</v>
+        <v>8.52</v>
       </c>
     </row>
     <row r="108" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
-        <v>747</v>
+        <v>235</v>
       </c>
       <c r="B108" t="s">
-        <v>359</v>
+        <v>236</v>
       </c>
       <c r="C108" t="s">
-        <v>748</v>
+        <v>731</v>
       </c>
       <c r="D108" t="s">
-        <v>570</v>
+        <v>564</v>
       </c>
       <c r="E108" s="2">
-        <v>28859859.280000001</v>
+        <v>37437979.039999999</v>
       </c>
       <c r="F108">
-        <v>0.13</v>
+        <v>0.17</v>
       </c>
       <c r="G108" s="2">
-        <v>442568</v>
+        <v>988592</v>
       </c>
       <c r="H108">
-        <v>65.209999999999994</v>
+        <v>37.869999999999997</v>
       </c>
       <c r="I108" t="s">
         <v>559</v>
       </c>
       <c r="J108">
-        <v>2.89</v>
+        <v>8.0299999999999994</v>
       </c>
     </row>
     <row r="109" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
-        <v>246</v>
+        <v>737</v>
       </c>
       <c r="B109" t="s">
-        <v>247</v>
+        <v>231</v>
       </c>
       <c r="C109" t="s">
-        <v>749</v>
+        <v>738</v>
       </c>
       <c r="D109" t="s">
-        <v>615</v>
+        <v>558</v>
       </c>
       <c r="E109" s="2">
-        <v>28783684.800000001</v>
+        <v>30630345.719999999</v>
       </c>
       <c r="F109">
-        <v>0.13</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="G109" s="2">
-        <v>3331445</v>
+        <v>276547</v>
       </c>
       <c r="H109">
-        <v>8.64</v>
+        <v>110.76</v>
       </c>
       <c r="I109" t="s">
         <v>559</v>
       </c>
       <c r="J109">
-        <v>2.88</v>
+        <v>7.68</v>
       </c>
     </row>
     <row r="110" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
-        <v>750</v>
+        <v>825</v>
       </c>
       <c r="B110" t="s">
-        <v>303</v>
+        <v>826</v>
       </c>
       <c r="C110" t="s">
-        <v>751</v>
+        <v>827</v>
       </c>
       <c r="D110" t="s">
-        <v>575</v>
+        <v>597</v>
       </c>
       <c r="E110" s="2">
-        <v>28554704</v>
+        <v>16261106.720000001</v>
       </c>
       <c r="F110">
-        <v>0.13</v>
+        <v>0.08</v>
       </c>
       <c r="G110" s="2">
-        <v>128048</v>
+        <v>165188</v>
       </c>
       <c r="H110">
-        <v>223</v>
+        <v>98.44</v>
       </c>
       <c r="I110" t="s">
         <v>559</v>
       </c>
       <c r="J110">
-        <v>2.86</v>
+        <v>7.29</v>
       </c>
     </row>
     <row r="111" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
-        <v>752</v>
+        <v>765</v>
       </c>
       <c r="B111" t="s">
-        <v>287</v>
+        <v>456</v>
       </c>
       <c r="C111" t="s">
-        <v>753</v>
+        <v>766</v>
       </c>
       <c r="D111" t="s">
-        <v>754</v>
+        <v>570</v>
       </c>
       <c r="E111" s="2">
-        <v>28270778.850000001</v>
+        <v>25949450.239999998</v>
       </c>
       <c r="F111">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="G111" s="2">
-        <v>1375707</v>
+        <v>2989568</v>
       </c>
       <c r="H111">
-        <v>20.55</v>
+        <v>8.68</v>
       </c>
       <c r="I111" t="s">
         <v>559</v>
       </c>
       <c r="J111">
-        <v>2.83</v>
+        <v>7.21</v>
       </c>
     </row>
     <row r="112" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
-        <v>755</v>
+        <v>773</v>
       </c>
       <c r="B112" t="s">
-        <v>242</v>
+        <v>774</v>
       </c>
       <c r="C112" t="s">
-        <v>756</v>
+        <v>775</v>
       </c>
       <c r="D112" t="s">
-        <v>718</v>
+        <v>570</v>
       </c>
       <c r="E112" s="2">
-        <v>28039685.309999999</v>
+        <v>23473689.120000001</v>
       </c>
       <c r="F112">
-        <v>0.13</v>
+        <v>0.11</v>
       </c>
       <c r="G112" s="2">
-        <v>743561</v>
+        <v>1210608</v>
       </c>
       <c r="H112">
-        <v>37.71</v>
+        <v>19.39</v>
       </c>
       <c r="I112" t="s">
         <v>559</v>
       </c>
       <c r="J112">
-        <v>2.8</v>
+        <v>6.75</v>
       </c>
     </row>
     <row r="113" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
-        <v>757</v>
+        <v>747</v>
       </c>
       <c r="B113" t="s">
-        <v>244</v>
+        <v>359</v>
       </c>
       <c r="C113" t="s">
-        <v>758</v>
+        <v>748</v>
       </c>
       <c r="D113" t="s">
-        <v>575</v>
+        <v>570</v>
       </c>
       <c r="E113" s="2">
-        <v>27146161.079999998</v>
+        <v>28859859.280000001</v>
       </c>
       <c r="F113">
         <v>0.13</v>
       </c>
       <c r="G113" s="2">
-        <v>1409458</v>
+        <v>442568</v>
       </c>
       <c r="H113">
-        <v>19.260000000000002</v>
+        <v>65.209999999999994</v>
       </c>
       <c r="I113" t="s">
         <v>559</v>
       </c>
       <c r="J113">
-        <v>2.71</v>
+        <v>6.66</v>
       </c>
     </row>
     <row r="114" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
-        <v>759</v>
+        <v>246</v>
       </c>
       <c r="B114" t="s">
-        <v>384</v>
+        <v>247</v>
       </c>
       <c r="C114" t="s">
-        <v>760</v>
+        <v>749</v>
       </c>
       <c r="D114" t="s">
-        <v>570</v>
+        <v>615</v>
       </c>
       <c r="E114" s="2">
-        <v>26510206.800000001</v>
+        <v>28783684.800000001</v>
       </c>
       <c r="F114">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="G114" s="2">
-        <v>1147628</v>
+        <v>3331445</v>
       </c>
       <c r="H114">
-        <v>23.1</v>
+        <v>8.64</v>
       </c>
       <c r="I114" t="s">
         <v>559</v>
       </c>
       <c r="J114">
-        <v>2.65</v>
+        <v>6.58</v>
       </c>
     </row>
     <row r="115" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
-        <v>761</v>
+        <v>386</v>
       </c>
       <c r="B115" t="s">
-        <v>275</v>
+        <v>387</v>
       </c>
       <c r="C115" t="s">
-        <v>762</v>
+        <v>746</v>
       </c>
       <c r="D115" t="s">
-        <v>718</v>
+        <v>570</v>
       </c>
       <c r="E115" s="2">
-        <v>26059446.960000001</v>
+        <v>29626516.100000001</v>
       </c>
       <c r="F115">
-        <v>0.12</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="G115" s="2">
-        <v>1398039</v>
+        <v>957238</v>
       </c>
       <c r="H115">
-        <v>18.64</v>
+        <v>30.95</v>
       </c>
       <c r="I115" t="s">
         <v>559</v>
       </c>
       <c r="J115">
-        <v>2.61</v>
+        <v>6.43</v>
       </c>
     </row>
     <row r="116" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
-        <v>763</v>
+        <v>224</v>
       </c>
       <c r="B116" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="C116" t="s">
-        <v>764</v>
+        <v>776</v>
       </c>
       <c r="D116" t="s">
-        <v>615</v>
+        <v>570</v>
       </c>
       <c r="E116" s="2">
-        <v>26000255.120000001</v>
+        <v>22860686.399999999</v>
       </c>
       <c r="F116">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="G116" s="2">
-        <v>614954</v>
+        <v>269520</v>
       </c>
       <c r="H116">
-        <v>42.28</v>
+        <v>84.82</v>
       </c>
       <c r="I116" t="s">
         <v>559</v>
       </c>
       <c r="J116">
-        <v>2.6</v>
+        <v>6.43</v>
       </c>
     </row>
     <row r="117" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
-        <v>765</v>
+        <v>805</v>
       </c>
       <c r="B117" t="s">
-        <v>456</v>
+        <v>260</v>
       </c>
       <c r="C117" t="s">
-        <v>766</v>
+        <v>806</v>
       </c>
       <c r="D117" t="s">
-        <v>570</v>
+        <v>615</v>
       </c>
       <c r="E117" s="2">
-        <v>25949450.239999998</v>
+        <v>19005606.84</v>
       </c>
       <c r="F117">
-        <v>0.12</v>
+        <v>0.09</v>
       </c>
       <c r="G117" s="2">
-        <v>2989568</v>
+        <v>342012</v>
       </c>
       <c r="H117">
-        <v>8.68</v>
+        <v>55.57</v>
       </c>
       <c r="I117" t="s">
         <v>559</v>
       </c>
       <c r="J117">
-        <v>2.59</v>
+        <v>6.38</v>
       </c>
     </row>
     <row r="118" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
-        <v>767</v>
+        <v>744</v>
       </c>
       <c r="B118" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="C118" t="s">
-        <v>768</v>
+        <v>745</v>
       </c>
       <c r="D118" t="s">
-        <v>561</v>
+        <v>564</v>
       </c>
       <c r="E118" s="2">
-        <v>23850693.899999999</v>
+        <v>29880533.760000002</v>
       </c>
       <c r="F118">
-        <v>0.11</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="G118" s="2">
-        <v>134590</v>
+        <v>1111627</v>
       </c>
       <c r="H118">
-        <v>177.21</v>
+        <v>26.88</v>
       </c>
       <c r="I118" t="s">
         <v>559</v>
       </c>
       <c r="J118">
-        <v>2.39</v>
+        <v>6.34</v>
       </c>
     </row>
     <row r="119" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
-        <v>769</v>
+        <v>752</v>
       </c>
       <c r="B119" t="s">
-        <v>203</v>
+        <v>287</v>
       </c>
       <c r="C119" t="s">
-        <v>770</v>
+        <v>753</v>
       </c>
       <c r="D119" t="s">
-        <v>558</v>
+        <v>754</v>
       </c>
       <c r="E119" s="2">
-        <v>23770221.600000001</v>
+        <v>28270778.850000001</v>
       </c>
       <c r="F119">
-        <v>0.11</v>
+        <v>0.13</v>
       </c>
       <c r="G119" s="2">
-        <v>379716</v>
+        <v>1375707</v>
       </c>
       <c r="H119">
-        <v>62.6</v>
+        <v>20.55</v>
       </c>
       <c r="I119" t="s">
         <v>559</v>
       </c>
       <c r="J119">
-        <v>2.38</v>
+        <v>6.23</v>
       </c>
     </row>
     <row r="120" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
-        <v>771</v>
+        <v>750</v>
       </c>
       <c r="B120" t="s">
-        <v>980</v>
+        <v>303</v>
       </c>
       <c r="C120" t="s">
-        <v>772</v>
+        <v>751</v>
       </c>
       <c r="D120" t="s">
-        <v>718</v>
+        <v>575</v>
       </c>
       <c r="E120" s="2">
-        <v>23494685.760000002</v>
+        <v>28554704</v>
       </c>
       <c r="F120">
-        <v>0.11</v>
+        <v>0.13</v>
       </c>
       <c r="G120" s="2">
-        <v>287784</v>
+        <v>128048</v>
       </c>
       <c r="H120">
-        <v>81.64</v>
+        <v>223</v>
       </c>
       <c r="I120" t="s">
         <v>559</v>
       </c>
       <c r="J120">
-        <v>2.35</v>
+        <v>6.19</v>
       </c>
     </row>
     <row r="121" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
-        <v>773</v>
+        <v>755</v>
       </c>
       <c r="B121" t="s">
-        <v>774</v>
+        <v>242</v>
       </c>
       <c r="C121" t="s">
-        <v>775</v>
+        <v>756</v>
       </c>
       <c r="D121" t="s">
-        <v>570</v>
+        <v>718</v>
       </c>
       <c r="E121" s="2">
-        <v>23473689.120000001</v>
+        <v>28039685.309999999</v>
       </c>
       <c r="F121">
-        <v>0.11</v>
+        <v>0.13</v>
       </c>
       <c r="G121" s="2">
-        <v>1210608</v>
+        <v>743561</v>
       </c>
       <c r="H121">
-        <v>19.39</v>
+        <v>37.71</v>
       </c>
       <c r="I121" t="s">
         <v>559</v>
       </c>
       <c r="J121">
-        <v>2.35</v>
+        <v>5.83</v>
       </c>
     </row>
     <row r="122" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
-        <v>224</v>
+        <v>757</v>
       </c>
       <c r="B122" t="s">
-        <v>225</v>
+        <v>244</v>
       </c>
       <c r="C122" t="s">
-        <v>776</v>
+        <v>758</v>
       </c>
       <c r="D122" t="s">
-        <v>570</v>
+        <v>575</v>
       </c>
       <c r="E122" s="2">
-        <v>22860686.399999999</v>
+        <v>27146161.079999998</v>
       </c>
       <c r="F122">
-        <v>0.11</v>
+        <v>0.13</v>
       </c>
       <c r="G122" s="2">
-        <v>269520</v>
+        <v>1409458</v>
       </c>
       <c r="H122">
-        <v>84.82</v>
+        <v>19.260000000000002</v>
       </c>
       <c r="I122" t="s">
         <v>559</v>
       </c>
       <c r="J122">
-        <v>2.29</v>
+        <v>5.78</v>
       </c>
     </row>
     <row r="123" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
-        <v>777</v>
+        <v>759</v>
       </c>
       <c r="B123" t="s">
-        <v>317</v>
+        <v>384</v>
       </c>
       <c r="C123" t="s">
-        <v>778</v>
+        <v>760</v>
       </c>
       <c r="D123" t="s">
         <v>570</v>
       </c>
       <c r="E123" s="2">
-        <v>22786238</v>
+        <v>26510206.800000001</v>
       </c>
       <c r="F123">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="G123" s="2">
-        <v>261400</v>
+        <v>1147628</v>
       </c>
       <c r="H123">
-        <v>87.17</v>
+        <v>23.1</v>
       </c>
       <c r="I123" t="s">
         <v>559</v>
       </c>
       <c r="J123">
-        <v>2.2799999999999998</v>
+        <v>5.76</v>
       </c>
     </row>
     <row r="124" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
-        <v>779</v>
+        <v>517</v>
       </c>
       <c r="B124" t="s">
-        <v>780</v>
+        <v>518</v>
       </c>
       <c r="C124" t="s">
-        <v>781</v>
+        <v>810</v>
       </c>
       <c r="D124" t="s">
-        <v>615</v>
+        <v>570</v>
       </c>
       <c r="E124" s="2">
-        <v>21679184.199999999</v>
+        <v>18158522.460000001</v>
       </c>
       <c r="F124">
-        <v>0.1</v>
+        <v>0.08</v>
       </c>
       <c r="G124" s="2">
-        <v>1251685</v>
+        <v>1369421</v>
       </c>
       <c r="H124">
-        <v>17.32</v>
+        <v>13.26</v>
       </c>
       <c r="I124" t="s">
         <v>559</v>
       </c>
       <c r="J124">
-        <v>2.17</v>
+        <v>5.63</v>
       </c>
     </row>
     <row r="125" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
-        <v>782</v>
+        <v>830</v>
       </c>
       <c r="B125" t="s">
-        <v>280</v>
-      </c>
-      <c r="C125" t="s">
-        <v>783</v>
+        <v>831</v>
+      </c>
+      <c r="C125" s="3" t="s">
+        <v>988</v>
       </c>
       <c r="D125" t="s">
-        <v>615</v>
+        <v>558</v>
       </c>
       <c r="E125" s="2">
-        <v>21378922.739999998</v>
+        <v>43912.800000000003</v>
       </c>
       <c r="F125">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="G125" s="2">
-        <v>1241517</v>
+        <v>146376</v>
       </c>
       <c r="H125">
-        <v>17.22</v>
+        <v>0.3</v>
       </c>
       <c r="I125" t="s">
         <v>559</v>
       </c>
       <c r="J125">
-        <v>2.14</v>
+        <v>5.62</v>
       </c>
     </row>
     <row r="126" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
-        <v>784</v>
+        <v>830</v>
       </c>
       <c r="B126" t="s">
-        <v>785</v>
+        <v>831</v>
       </c>
       <c r="C126" t="s">
-        <v>786</v>
+        <v>832</v>
       </c>
       <c r="D126" t="s">
-        <v>564</v>
+        <v>570</v>
       </c>
       <c r="E126" s="2">
-        <v>20964278.879999999</v>
+        <v>15882321.779999999</v>
       </c>
       <c r="F126">
-        <v>0.1</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="G126" s="2">
-        <v>1088488</v>
+        <v>610389</v>
       </c>
       <c r="H126">
-        <v>19.260000000000002</v>
+        <v>26.02</v>
       </c>
       <c r="I126" t="s">
         <v>559</v>
       </c>
       <c r="J126">
-        <v>2.1</v>
+        <v>5.62</v>
       </c>
     </row>
     <row r="127" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
-        <v>787</v>
+        <v>761</v>
       </c>
       <c r="B127" t="s">
-        <v>788</v>
+        <v>275</v>
       </c>
       <c r="C127" t="s">
-        <v>789</v>
+        <v>762</v>
       </c>
       <c r="D127" t="s">
-        <v>570</v>
+        <v>718</v>
       </c>
       <c r="E127" s="2">
-        <v>20890346.359999999</v>
+        <v>26059446.960000001</v>
       </c>
       <c r="F127">
-        <v>0.1</v>
+        <v>0.12</v>
       </c>
       <c r="G127" s="2">
-        <v>968042</v>
+        <v>1398039</v>
       </c>
       <c r="H127">
-        <v>21.58</v>
+        <v>18.64</v>
       </c>
       <c r="I127" t="s">
         <v>559</v>
       </c>
       <c r="J127">
-        <v>2.09</v>
+        <v>5.48</v>
       </c>
     </row>
     <row r="128" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
-        <v>790</v>
+        <v>779</v>
       </c>
       <c r="B128" t="s">
-        <v>330</v>
+        <v>780</v>
       </c>
       <c r="C128" t="s">
-        <v>791</v>
+        <v>781</v>
       </c>
       <c r="D128" t="s">
-        <v>564</v>
+        <v>615</v>
       </c>
       <c r="E128" s="2">
-        <v>20683285.140000001</v>
+        <v>21679184.199999999</v>
       </c>
       <c r="F128">
         <v>0.1</v>
       </c>
       <c r="G128" s="2">
-        <v>950082</v>
+        <v>1251685</v>
       </c>
       <c r="H128">
-        <v>21.77</v>
+        <v>17.32</v>
       </c>
       <c r="I128" t="s">
         <v>559</v>
       </c>
       <c r="J128">
-        <v>2.0699999999999998</v>
+        <v>5.1100000000000003</v>
       </c>
     </row>
     <row r="129" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
-        <v>792</v>
+        <v>835</v>
       </c>
       <c r="B129" t="s">
-        <v>337</v>
+        <v>347</v>
       </c>
       <c r="C129" t="s">
-        <v>793</v>
+        <v>836</v>
       </c>
       <c r="D129" t="s">
-        <v>594</v>
+        <v>597</v>
       </c>
       <c r="E129" s="2">
-        <v>19531442</v>
+        <v>15653128</v>
       </c>
       <c r="F129">
-        <v>0.09</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="G129" s="2">
-        <v>192428</v>
+        <v>184480</v>
       </c>
       <c r="H129">
-        <v>101.5</v>
+        <v>84.85</v>
       </c>
       <c r="I129" t="s">
         <v>559</v>
       </c>
       <c r="J129">
-        <v>1.95</v>
+        <v>5.07</v>
       </c>
     </row>
     <row r="130" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
-        <v>794</v>
+        <v>784</v>
       </c>
       <c r="B130" t="s">
-        <v>355</v>
+        <v>785</v>
       </c>
       <c r="C130" t="s">
-        <v>795</v>
+        <v>786</v>
       </c>
       <c r="D130" t="s">
         <v>564</v>
       </c>
       <c r="E130" s="2">
-        <v>19459193.800000001</v>
+        <v>20964278.879999999</v>
       </c>
       <c r="F130">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
       <c r="G130" s="2">
-        <v>781180</v>
+        <v>1088488</v>
       </c>
       <c r="H130">
-        <v>24.91</v>
+        <v>19.260000000000002</v>
       </c>
       <c r="I130" t="s">
         <v>559</v>
       </c>
       <c r="J130">
-        <v>1.95</v>
+        <v>4.96</v>
       </c>
     </row>
     <row r="131" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
-        <v>796</v>
+        <v>771</v>
       </c>
       <c r="B131" t="s">
-        <v>797</v>
+        <v>979</v>
       </c>
       <c r="C131" t="s">
-        <v>798</v>
+        <v>772</v>
       </c>
       <c r="D131" t="s">
-        <v>570</v>
+        <v>718</v>
       </c>
       <c r="E131" s="2">
-        <v>19380693.149999999</v>
+        <v>23494685.760000002</v>
       </c>
       <c r="F131">
-        <v>0.09</v>
+        <v>0.11</v>
       </c>
       <c r="G131" s="2">
-        <v>1464905</v>
+        <v>287784</v>
       </c>
       <c r="H131">
-        <v>13.23</v>
+        <v>81.64</v>
       </c>
       <c r="I131" t="s">
         <v>559</v>
       </c>
       <c r="J131">
-        <v>1.94</v>
+        <v>4.93</v>
       </c>
     </row>
     <row r="132" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
-        <v>799</v>
+        <v>767</v>
       </c>
       <c r="B132" t="s">
-        <v>349</v>
+        <v>266</v>
       </c>
       <c r="C132" t="s">
-        <v>800</v>
+        <v>768</v>
       </c>
       <c r="D132" t="s">
-        <v>718</v>
+        <v>561</v>
       </c>
       <c r="E132" s="2">
-        <v>19315866.600000001</v>
+        <v>23850693.899999999</v>
       </c>
       <c r="F132">
-        <v>0.09</v>
+        <v>0.11</v>
       </c>
       <c r="G132" s="2">
-        <v>1008135</v>
+        <v>134590</v>
       </c>
       <c r="H132">
-        <v>19.16</v>
+        <v>177.21</v>
       </c>
       <c r="I132" t="s">
         <v>559</v>
       </c>
       <c r="J132">
-        <v>1.93</v>
+        <v>4.92</v>
       </c>
     </row>
     <row r="133" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
-        <v>801</v>
+        <v>777</v>
       </c>
       <c r="B133" t="s">
-        <v>389</v>
+        <v>317</v>
       </c>
       <c r="C133" t="s">
-        <v>802</v>
+        <v>778</v>
       </c>
       <c r="D133" t="s">
-        <v>575</v>
+        <v>570</v>
       </c>
       <c r="E133" s="2">
-        <v>19253086.84</v>
+        <v>22786238</v>
       </c>
       <c r="F133">
-        <v>0.09</v>
+        <v>0.11</v>
       </c>
       <c r="G133" s="2">
-        <v>229258</v>
+        <v>261400</v>
       </c>
       <c r="H133">
-        <v>83.98</v>
+        <v>87.17</v>
       </c>
       <c r="I133" t="s">
         <v>559</v>
       </c>
       <c r="J133">
-        <v>1.93</v>
+        <v>4.7699999999999996</v>
       </c>
     </row>
     <row r="134" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
-        <v>803</v>
+        <v>858</v>
       </c>
       <c r="B134" t="s">
-        <v>196</v>
+        <v>859</v>
       </c>
       <c r="C134" t="s">
-        <v>804</v>
+        <v>860</v>
       </c>
       <c r="D134" t="s">
-        <v>718</v>
+        <v>570</v>
       </c>
       <c r="E134" s="2">
-        <v>19251103.489999998</v>
+        <v>13085307.199999999</v>
       </c>
       <c r="F134">
-        <v>0.09</v>
+        <v>0.06</v>
       </c>
       <c r="G134" s="2">
-        <v>1294627</v>
+        <v>360080</v>
       </c>
       <c r="H134">
-        <v>14.87</v>
+        <v>36.340000000000003</v>
       </c>
       <c r="I134" t="s">
-        <v>559</v>
+        <v>591</v>
       </c>
       <c r="J134">
-        <v>1.93</v>
+        <v>4.62</v>
       </c>
     </row>
     <row r="135" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
-        <v>805</v>
+        <v>782</v>
       </c>
       <c r="B135" t="s">
-        <v>260</v>
+        <v>280</v>
       </c>
       <c r="C135" t="s">
-        <v>806</v>
+        <v>783</v>
       </c>
       <c r="D135" t="s">
         <v>615</v>
       </c>
       <c r="E135" s="2">
-        <v>19005606.84</v>
+        <v>21378922.739999998</v>
       </c>
       <c r="F135">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
       <c r="G135" s="2">
-        <v>342012</v>
+        <v>1241517</v>
       </c>
       <c r="H135">
-        <v>55.57</v>
+        <v>17.22</v>
       </c>
       <c r="I135" t="s">
         <v>559</v>
       </c>
       <c r="J135">
-        <v>1.9</v>
+        <v>4.59</v>
       </c>
     </row>
     <row r="136" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
-        <v>807</v>
+        <v>790</v>
       </c>
       <c r="B136" t="s">
-        <v>808</v>
+        <v>330</v>
       </c>
       <c r="C136" t="s">
-        <v>809</v>
+        <v>791</v>
       </c>
       <c r="D136" t="s">
-        <v>570</v>
+        <v>564</v>
       </c>
       <c r="E136" s="2">
-        <v>18561443.68</v>
+        <v>20683285.140000001</v>
       </c>
       <c r="F136">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
       <c r="G136" s="2">
-        <v>964732</v>
+        <v>950082</v>
       </c>
       <c r="H136">
-        <v>19.239999999999998</v>
+        <v>21.77</v>
       </c>
       <c r="I136" t="s">
         <v>559</v>
       </c>
       <c r="J136">
-        <v>1.86</v>
+        <v>4.59</v>
       </c>
     </row>
     <row r="137" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
-        <v>517</v>
+        <v>801</v>
       </c>
       <c r="B137" t="s">
-        <v>518</v>
+        <v>389</v>
       </c>
       <c r="C137" t="s">
-        <v>810</v>
+        <v>802</v>
       </c>
       <c r="D137" t="s">
-        <v>570</v>
+        <v>575</v>
       </c>
       <c r="E137" s="2">
-        <v>18158522.460000001</v>
+        <v>19253086.84</v>
       </c>
       <c r="F137">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="G137" s="2">
-        <v>1369421</v>
+        <v>229258</v>
       </c>
       <c r="H137">
-        <v>13.26</v>
+        <v>83.98</v>
       </c>
       <c r="I137" t="s">
         <v>559</v>
       </c>
       <c r="J137">
-        <v>1.82</v>
+        <v>4.59</v>
       </c>
     </row>
     <row r="138" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
-        <v>811</v>
+        <v>792</v>
       </c>
       <c r="B138" t="s">
-        <v>445</v>
+        <v>337</v>
       </c>
       <c r="C138" t="s">
-        <v>812</v>
+        <v>793</v>
       </c>
       <c r="D138" t="s">
-        <v>564</v>
+        <v>594</v>
       </c>
       <c r="E138" s="2">
-        <v>17707517.780000001</v>
+        <v>19531442</v>
       </c>
       <c r="F138">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="G138" s="2">
-        <v>2383246</v>
+        <v>192428</v>
       </c>
       <c r="H138">
-        <v>7.43</v>
+        <v>101.5</v>
       </c>
       <c r="I138" t="s">
         <v>559</v>
       </c>
       <c r="J138">
-        <v>1.77</v>
+        <v>4.5599999999999996</v>
       </c>
     </row>
     <row r="139" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
-        <v>813</v>
+        <v>787</v>
       </c>
       <c r="B139" t="s">
-        <v>814</v>
+        <v>788</v>
       </c>
       <c r="C139" t="s">
-        <v>815</v>
+        <v>789</v>
       </c>
       <c r="D139" t="s">
         <v>570</v>
       </c>
       <c r="E139" s="2">
-        <v>17494641.370000001</v>
+        <v>20890346.359999999</v>
       </c>
       <c r="F139">
-        <v>0.08</v>
+        <v>0.1</v>
       </c>
       <c r="G139" s="2">
-        <v>1376447</v>
+        <v>968042</v>
       </c>
       <c r="H139">
-        <v>12.71</v>
+        <v>21.58</v>
       </c>
       <c r="I139" t="s">
         <v>559</v>
       </c>
       <c r="J139">
-        <v>1.75</v>
+        <v>4.5199999999999996</v>
       </c>
     </row>
     <row r="140" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
-        <v>485</v>
+        <v>838</v>
       </c>
       <c r="B140" t="s">
-        <v>486</v>
+        <v>839</v>
       </c>
       <c r="C140" t="s">
-        <v>816</v>
+        <v>840</v>
       </c>
       <c r="D140" t="s">
         <v>570</v>
       </c>
       <c r="E140" s="2">
-        <v>17358599.16</v>
+        <v>15565665.48</v>
       </c>
       <c r="F140">
-        <v>0.08</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="G140" s="2">
-        <v>541779</v>
+        <v>397286</v>
       </c>
       <c r="H140">
-        <v>32.04</v>
+        <v>39.18</v>
       </c>
       <c r="I140" t="s">
         <v>559</v>
       </c>
       <c r="J140">
-        <v>1.74</v>
+        <v>4.46</v>
       </c>
     </row>
     <row r="141" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
-        <v>458</v>
+        <v>833</v>
       </c>
       <c r="B141" t="s">
-        <v>459</v>
+        <v>298</v>
       </c>
       <c r="C141" t="s">
-        <v>817</v>
+        <v>834</v>
       </c>
       <c r="D141" t="s">
-        <v>570</v>
+        <v>718</v>
       </c>
       <c r="E141" s="2">
-        <v>17352227.199999999</v>
+        <v>15791596.199999999</v>
       </c>
       <c r="F141">
-        <v>0.08</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="G141" s="2">
-        <v>492961</v>
+        <v>614220</v>
       </c>
       <c r="H141">
-        <v>35.200000000000003</v>
+        <v>25.71</v>
       </c>
       <c r="I141" t="s">
         <v>559</v>
       </c>
       <c r="J141">
-        <v>1.74</v>
+        <v>4.37</v>
       </c>
     </row>
     <row r="142" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
-        <v>818</v>
+        <v>820</v>
       </c>
       <c r="B142" t="s">
-        <v>380</v>
+        <v>821</v>
       </c>
       <c r="C142" t="s">
-        <v>819</v>
+        <v>822</v>
       </c>
       <c r="D142" t="s">
-        <v>718</v>
+        <v>570</v>
       </c>
       <c r="E142" s="2">
-        <v>17126065.289999999</v>
+        <v>16923020.800000001</v>
       </c>
       <c r="F142">
         <v>0.08</v>
       </c>
       <c r="G142" s="2">
-        <v>1355983</v>
+        <v>315728</v>
       </c>
       <c r="H142">
-        <v>12.63</v>
+        <v>53.6</v>
       </c>
       <c r="I142" t="s">
         <v>559</v>
       </c>
       <c r="J142">
-        <v>1.71</v>
+        <v>4.2699999999999996</v>
       </c>
     </row>
     <row r="143" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
-        <v>820</v>
+        <v>893</v>
       </c>
       <c r="B143" t="s">
-        <v>821</v>
+        <v>980</v>
       </c>
       <c r="C143" t="s">
-        <v>822</v>
+        <v>894</v>
       </c>
       <c r="D143" t="s">
-        <v>570</v>
+        <v>575</v>
       </c>
       <c r="E143" s="2">
-        <v>16923020.800000001</v>
+        <v>9920439.3599999994</v>
       </c>
       <c r="F143">
-        <v>0.08</v>
+        <v>0.05</v>
       </c>
       <c r="G143" s="2">
-        <v>315728</v>
+        <v>207584</v>
       </c>
       <c r="H143">
-        <v>53.6</v>
+        <v>47.79</v>
       </c>
       <c r="I143" t="s">
         <v>559</v>
       </c>
       <c r="J143">
-        <v>1.69</v>
+        <v>4.2699999999999996</v>
       </c>
     </row>
     <row r="144" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
-        <v>823</v>
+        <v>796</v>
       </c>
       <c r="B144" t="s">
-        <v>412</v>
+        <v>797</v>
       </c>
       <c r="C144" t="s">
-        <v>824</v>
+        <v>798</v>
       </c>
       <c r="D144" t="s">
         <v>570</v>
       </c>
       <c r="E144" s="2">
-        <v>16771912.92</v>
+        <v>19380693.149999999</v>
       </c>
       <c r="F144">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="G144" s="2">
-        <v>721683</v>
+        <v>1464905</v>
       </c>
       <c r="H144">
-        <v>23.24</v>
+        <v>13.23</v>
       </c>
       <c r="I144" t="s">
         <v>559</v>
       </c>
       <c r="J144">
-        <v>1.68</v>
+        <v>4.25</v>
       </c>
     </row>
     <row r="145" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
-        <v>825</v>
+        <v>845</v>
       </c>
       <c r="B145" t="s">
-        <v>826</v>
+        <v>335</v>
       </c>
       <c r="C145" t="s">
-        <v>827</v>
+        <v>846</v>
       </c>
       <c r="D145" t="s">
-        <v>597</v>
+        <v>564</v>
       </c>
       <c r="E145" s="2">
-        <v>16261106.720000001</v>
+        <v>14516977.640000001</v>
       </c>
       <c r="F145">
-        <v>0.08</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="G145" s="2">
-        <v>165188</v>
+        <v>540871</v>
       </c>
       <c r="H145">
-        <v>98.44</v>
+        <v>26.84</v>
       </c>
       <c r="I145" t="s">
         <v>559</v>
       </c>
       <c r="J145">
-        <v>1.63</v>
+        <v>4.21</v>
       </c>
     </row>
     <row r="146" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
-        <v>828</v>
+        <v>794</v>
       </c>
       <c r="B146" t="s">
-        <v>419</v>
+        <v>355</v>
       </c>
       <c r="C146" t="s">
-        <v>829</v>
+        <v>795</v>
       </c>
       <c r="D146" t="s">
         <v>564</v>
       </c>
       <c r="E146" s="2">
-        <v>16001943.6</v>
+        <v>19459193.800000001</v>
       </c>
       <c r="F146">
-        <v>7.0000000000000007E-2</v>
+        <v>0.09</v>
       </c>
       <c r="G146" s="2">
-        <v>2353227</v>
+        <v>781180</v>
       </c>
       <c r="H146">
-        <v>6.8</v>
+        <v>24.91</v>
       </c>
       <c r="I146" t="s">
         <v>559</v>
       </c>
       <c r="J146">
-        <v>1.6</v>
+        <v>4.18</v>
       </c>
     </row>
     <row r="147" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
-        <v>830</v>
+        <v>807</v>
       </c>
       <c r="B147" t="s">
-        <v>831</v>
+        <v>808</v>
       </c>
       <c r="C147" t="s">
-        <v>832</v>
+        <v>809</v>
       </c>
       <c r="D147" t="s">
         <v>570</v>
       </c>
       <c r="E147" s="2">
-        <v>15882321.779999999</v>
+        <v>18561443.68</v>
       </c>
       <c r="F147">
-        <v>7.0000000000000007E-2</v>
+        <v>0.09</v>
       </c>
       <c r="G147" s="2">
-        <v>610389</v>
+        <v>964732</v>
       </c>
       <c r="H147">
-        <v>26.02</v>
+        <v>19.239999999999998</v>
       </c>
       <c r="I147" t="s">
         <v>559</v>
       </c>
       <c r="J147">
-        <v>1.59</v>
+        <v>4.13</v>
       </c>
     </row>
     <row r="148" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
-        <v>833</v>
+        <v>485</v>
       </c>
       <c r="B148" t="s">
-        <v>298</v>
+        <v>486</v>
       </c>
       <c r="C148" t="s">
-        <v>834</v>
+        <v>816</v>
       </c>
       <c r="D148" t="s">
-        <v>718</v>
+        <v>570</v>
       </c>
       <c r="E148" s="2">
-        <v>15791596.199999999</v>
+        <v>17358599.16</v>
       </c>
       <c r="F148">
-        <v>7.0000000000000007E-2</v>
+        <v>0.08</v>
       </c>
       <c r="G148" s="2">
-        <v>614220</v>
+        <v>541779</v>
       </c>
       <c r="H148">
-        <v>25.71</v>
+        <v>32.04</v>
       </c>
       <c r="I148" t="s">
         <v>559</v>
       </c>
       <c r="J148">
-        <v>1.58</v>
+        <v>4.07</v>
       </c>
     </row>
     <row r="149" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
-        <v>835</v>
+        <v>799</v>
       </c>
       <c r="B149" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="C149" t="s">
-        <v>836</v>
+        <v>800</v>
       </c>
       <c r="D149" t="s">
-        <v>597</v>
+        <v>718</v>
       </c>
       <c r="E149" s="2">
-        <v>15653128</v>
+        <v>19315866.600000001</v>
       </c>
       <c r="F149">
-        <v>7.0000000000000007E-2</v>
+        <v>0.09</v>
       </c>
       <c r="G149" s="2">
-        <v>184480</v>
+        <v>1008135</v>
       </c>
       <c r="H149">
-        <v>84.85</v>
+        <v>19.16</v>
       </c>
       <c r="I149" t="s">
         <v>559</v>
       </c>
       <c r="J149">
-        <v>1.57</v>
+        <v>4.01</v>
       </c>
     </row>
     <row r="150" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
-        <v>371</v>
+        <v>856</v>
       </c>
       <c r="B150" t="s">
-        <v>372</v>
+        <v>345</v>
       </c>
       <c r="C150" t="s">
-        <v>837</v>
+        <v>857</v>
       </c>
       <c r="D150" t="s">
-        <v>561</v>
+        <v>558</v>
       </c>
       <c r="E150" s="2">
-        <v>15574199.58</v>
+        <v>13141509.15</v>
       </c>
       <c r="F150">
-        <v>7.0000000000000007E-2</v>
+        <v>0.06</v>
       </c>
       <c r="G150" s="2">
-        <v>2582786</v>
+        <v>129921</v>
       </c>
       <c r="H150">
-        <v>6.03</v>
+        <v>101.15</v>
       </c>
       <c r="I150" t="s">
         <v>559</v>
       </c>
       <c r="J150">
-        <v>1.56</v>
+        <v>3.98</v>
       </c>
     </row>
     <row r="151" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
-        <v>838</v>
+        <v>813</v>
       </c>
       <c r="B151" t="s">
-        <v>839</v>
+        <v>814</v>
       </c>
       <c r="C151" t="s">
-        <v>840</v>
+        <v>815</v>
       </c>
       <c r="D151" t="s">
         <v>570</v>
       </c>
       <c r="E151" s="2">
-        <v>15565665.48</v>
+        <v>17494641.370000001</v>
       </c>
       <c r="F151">
-        <v>7.0000000000000007E-2</v>
+        <v>0.08</v>
       </c>
       <c r="G151" s="2">
-        <v>397286</v>
+        <v>1376447</v>
       </c>
       <c r="H151">
-        <v>39.18</v>
+        <v>12.71</v>
       </c>
       <c r="I151" t="s">
         <v>559</v>
       </c>
       <c r="J151">
-        <v>1.56</v>
+        <v>3.97</v>
       </c>
     </row>
     <row r="152" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
-        <v>257</v>
+        <v>811</v>
       </c>
       <c r="B152" t="s">
-        <v>258</v>
+        <v>445</v>
       </c>
       <c r="C152" t="s">
-        <v>841</v>
+        <v>812</v>
       </c>
       <c r="D152" t="s">
-        <v>570</v>
+        <v>564</v>
       </c>
       <c r="E152" s="2">
-        <v>15217840.18</v>
+        <v>17707517.780000001</v>
       </c>
       <c r="F152">
-        <v>7.0000000000000007E-2</v>
+        <v>0.08</v>
       </c>
       <c r="G152" s="2">
-        <v>333871</v>
+        <v>2383246</v>
       </c>
       <c r="H152">
-        <v>45.58</v>
+        <v>7.43</v>
       </c>
       <c r="I152" t="s">
         <v>559</v>
       </c>
       <c r="J152">
-        <v>1.52</v>
+        <v>3.95</v>
       </c>
     </row>
     <row r="153" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
-        <v>842</v>
+        <v>458</v>
       </c>
       <c r="B153" t="s">
-        <v>376</v>
+        <v>459</v>
       </c>
       <c r="C153" t="s">
-        <v>843</v>
+        <v>817</v>
       </c>
       <c r="D153" t="s">
-        <v>564</v>
+        <v>570</v>
       </c>
       <c r="E153" s="2">
-        <v>14872363.5</v>
+        <v>17352227.199999999</v>
       </c>
       <c r="F153">
-        <v>7.0000000000000007E-2</v>
+        <v>0.08</v>
       </c>
       <c r="G153" s="2">
-        <v>862166</v>
+        <v>492961</v>
       </c>
       <c r="H153">
-        <v>17.25</v>
+        <v>35.200000000000003</v>
       </c>
       <c r="I153" t="s">
         <v>559</v>
       </c>
       <c r="J153">
-        <v>1.49</v>
+        <v>3.9</v>
       </c>
     </row>
     <row r="154" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
-        <v>342</v>
+        <v>842</v>
       </c>
       <c r="B154" t="s">
-        <v>343</v>
+        <v>376</v>
       </c>
       <c r="C154" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="D154" t="s">
-        <v>575</v>
+        <v>564</v>
       </c>
       <c r="E154" s="2">
-        <v>14814387</v>
+        <v>14872363.5</v>
       </c>
       <c r="F154">
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="G154" s="2">
-        <v>389340</v>
+        <v>862166</v>
       </c>
       <c r="H154">
-        <v>38.049999999999997</v>
+        <v>17.25</v>
       </c>
       <c r="I154" t="s">
         <v>559</v>
       </c>
       <c r="J154">
-        <v>1.48</v>
+        <v>3.88</v>
       </c>
     </row>
     <row r="155" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
-        <v>845</v>
+        <v>956</v>
       </c>
       <c r="B155" t="s">
-        <v>335</v>
+        <v>353</v>
       </c>
       <c r="C155" t="s">
-        <v>846</v>
+        <v>957</v>
       </c>
       <c r="D155" t="s">
-        <v>564</v>
+        <v>718</v>
       </c>
       <c r="E155" s="2">
-        <v>14516977.640000001</v>
+        <v>5837298.0300000003</v>
       </c>
       <c r="F155">
-        <v>7.0000000000000007E-2</v>
+        <v>0.03</v>
       </c>
       <c r="G155" s="2">
-        <v>540871</v>
+        <v>359661</v>
       </c>
       <c r="H155">
-        <v>26.84</v>
+        <v>16.23</v>
       </c>
       <c r="I155" t="s">
         <v>559</v>
       </c>
       <c r="J155">
-        <v>1.45</v>
+        <v>3.87</v>
       </c>
     </row>
     <row r="156" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
-        <v>847</v>
+        <v>342</v>
       </c>
       <c r="B156" t="s">
-        <v>382</v>
+        <v>343</v>
       </c>
       <c r="C156" t="s">
-        <v>848</v>
+        <v>844</v>
       </c>
       <c r="D156" t="s">
         <v>575</v>
       </c>
       <c r="E156" s="2">
-        <v>14480035.68</v>
+        <v>14814387</v>
       </c>
       <c r="F156">
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="G156" s="2">
-        <v>589578</v>
+        <v>389340</v>
       </c>
       <c r="H156">
-        <v>24.56</v>
+        <v>38.049999999999997</v>
       </c>
       <c r="I156" t="s">
         <v>559</v>
       </c>
       <c r="J156">
-        <v>1.45</v>
+        <v>3.74</v>
       </c>
     </row>
     <row r="157" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
-        <v>849</v>
+        <v>818</v>
       </c>
       <c r="B157" t="s">
-        <v>850</v>
+        <v>380</v>
       </c>
       <c r="C157" t="s">
-        <v>851</v>
+        <v>819</v>
       </c>
       <c r="D157" t="s">
-        <v>564</v>
+        <v>718</v>
       </c>
       <c r="E157" s="2">
-        <v>14021055</v>
+        <v>17126065.289999999</v>
       </c>
       <c r="F157">
-        <v>7.0000000000000007E-2</v>
+        <v>0.08</v>
       </c>
       <c r="G157" s="2">
-        <v>3960750</v>
+        <v>1355983</v>
       </c>
       <c r="H157">
-        <v>3.54</v>
+        <v>12.63</v>
       </c>
       <c r="I157" t="s">
         <v>559</v>
       </c>
       <c r="J157">
-        <v>1.4</v>
+        <v>3.69</v>
       </c>
     </row>
     <row r="158" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
-        <v>852</v>
+        <v>823</v>
       </c>
       <c r="B158" t="s">
-        <v>397</v>
+        <v>412</v>
       </c>
       <c r="C158" t="s">
-        <v>853</v>
+        <v>824</v>
       </c>
       <c r="D158" t="s">
-        <v>564</v>
+        <v>570</v>
       </c>
       <c r="E158" s="2">
-        <v>13564643.439999999</v>
+        <v>16771912.92</v>
       </c>
       <c r="F158">
-        <v>0.06</v>
+        <v>0.08</v>
       </c>
       <c r="G158" s="2">
-        <v>772474</v>
+        <v>721683</v>
       </c>
       <c r="H158">
-        <v>17.559999999999999</v>
+        <v>23.24</v>
       </c>
       <c r="I158" t="s">
         <v>559</v>
       </c>
       <c r="J158">
-        <v>1.36</v>
+        <v>3.65</v>
       </c>
     </row>
     <row r="159" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
-        <v>480</v>
+        <v>416</v>
       </c>
       <c r="B159" t="s">
-        <v>481</v>
+        <v>417</v>
       </c>
       <c r="C159" t="s">
-        <v>854</v>
+        <v>878</v>
       </c>
       <c r="D159" t="s">
-        <v>564</v>
+        <v>754</v>
       </c>
       <c r="E159" s="2">
-        <v>13338102.42</v>
+        <v>11663144</v>
       </c>
       <c r="F159">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="G159" s="2">
-        <v>3183318</v>
+        <v>1240760</v>
       </c>
       <c r="H159">
-        <v>4.1900000000000004</v>
+        <v>9.4</v>
       </c>
       <c r="I159" t="s">
         <v>559</v>
       </c>
       <c r="J159">
-        <v>1.33</v>
+        <v>3.65</v>
       </c>
     </row>
     <row r="160" spans="1:10" x14ac:dyDescent="0.3">
@@ -9003,135 +9004,135 @@
         <v>559</v>
       </c>
       <c r="J160">
-        <v>1.32</v>
+        <v>3.57</v>
       </c>
     </row>
     <row r="161" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
-        <v>856</v>
+        <v>879</v>
       </c>
       <c r="B161" t="s">
-        <v>345</v>
+        <v>880</v>
       </c>
       <c r="C161" t="s">
-        <v>857</v>
+        <v>881</v>
       </c>
       <c r="D161" t="s">
-        <v>558</v>
+        <v>564</v>
       </c>
       <c r="E161" s="2">
-        <v>13141509.15</v>
+        <v>11409275.85</v>
       </c>
       <c r="F161">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="G161" s="2">
-        <v>129921</v>
+        <v>72051</v>
       </c>
       <c r="H161">
-        <v>101.15</v>
+        <v>158.35</v>
       </c>
       <c r="I161" t="s">
         <v>559</v>
       </c>
       <c r="J161">
-        <v>1.31</v>
+        <v>3.57</v>
       </c>
     </row>
     <row r="162" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
-        <v>858</v>
+        <v>852</v>
       </c>
       <c r="B162" t="s">
-        <v>859</v>
+        <v>397</v>
       </c>
       <c r="C162" t="s">
-        <v>860</v>
+        <v>853</v>
       </c>
       <c r="D162" t="s">
-        <v>570</v>
+        <v>564</v>
       </c>
       <c r="E162" s="2">
-        <v>13085307.199999999</v>
+        <v>13564643.439999999</v>
       </c>
       <c r="F162">
         <v>0.06</v>
       </c>
       <c r="G162" s="2">
-        <v>360080</v>
+        <v>772474</v>
       </c>
       <c r="H162">
-        <v>36.340000000000003</v>
+        <v>17.559999999999999</v>
       </c>
       <c r="I162" t="s">
-        <v>591</v>
+        <v>559</v>
       </c>
       <c r="J162">
-        <v>1.31</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="163" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
-        <v>861</v>
+        <v>926</v>
       </c>
       <c r="B163" t="s">
-        <v>393</v>
+        <v>421</v>
       </c>
       <c r="C163" t="s">
-        <v>862</v>
+        <v>927</v>
       </c>
       <c r="D163" t="s">
-        <v>718</v>
+        <v>564</v>
       </c>
       <c r="E163" s="2">
-        <v>13028715.15</v>
+        <v>8379088.0599999996</v>
       </c>
       <c r="F163">
-        <v>0.06</v>
+        <v>0.04</v>
       </c>
       <c r="G163" s="2">
-        <v>1246767</v>
+        <v>358387</v>
       </c>
       <c r="H163">
-        <v>10.45</v>
+        <v>23.38</v>
       </c>
       <c r="I163" t="s">
         <v>559</v>
       </c>
       <c r="J163">
-        <v>1.3</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="164" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
-        <v>863</v>
+        <v>849</v>
       </c>
       <c r="B164" t="s">
-        <v>864</v>
+        <v>850</v>
       </c>
       <c r="C164" t="s">
-        <v>865</v>
+        <v>851</v>
       </c>
       <c r="D164" t="s">
         <v>564</v>
       </c>
       <c r="E164" s="2">
-        <v>12634954.539999999</v>
+        <v>14021055</v>
       </c>
       <c r="F164">
-        <v>0.06</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="G164" s="2">
-        <v>1033957</v>
+        <v>3960750</v>
       </c>
       <c r="H164">
-        <v>12.22</v>
+        <v>3.54</v>
       </c>
       <c r="I164" t="s">
         <v>559</v>
       </c>
       <c r="J164">
-        <v>1.26</v>
+        <v>3.46</v>
       </c>
     </row>
     <row r="165" spans="1:10" x14ac:dyDescent="0.3">
@@ -9163,295 +9164,295 @@
         <v>559</v>
       </c>
       <c r="J165">
-        <v>1.23</v>
+        <v>3.41</v>
       </c>
     </row>
     <row r="166" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
-        <v>868</v>
+        <v>828</v>
       </c>
       <c r="B166" t="s">
-        <v>869</v>
+        <v>419</v>
       </c>
       <c r="C166" t="s">
-        <v>870</v>
+        <v>829</v>
       </c>
       <c r="D166" t="s">
-        <v>570</v>
+        <v>564</v>
       </c>
       <c r="E166" s="2">
-        <v>11974943.75</v>
+        <v>16001943.6</v>
       </c>
       <c r="F166">
-        <v>0.06</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="G166" s="2">
-        <v>622075</v>
+        <v>2353227</v>
       </c>
       <c r="H166">
-        <v>19.25</v>
+        <v>6.8</v>
       </c>
       <c r="I166" t="s">
         <v>559</v>
       </c>
       <c r="J166">
-        <v>1.2</v>
+        <v>3.37</v>
       </c>
     </row>
     <row r="167" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
-        <v>871</v>
+        <v>847</v>
       </c>
       <c r="B167" t="s">
-        <v>872</v>
+        <v>382</v>
       </c>
       <c r="C167" t="s">
-        <v>873</v>
+        <v>848</v>
       </c>
       <c r="D167" t="s">
-        <v>564</v>
+        <v>575</v>
       </c>
       <c r="E167" s="2">
-        <v>11957196.68</v>
+        <v>14480035.68</v>
       </c>
       <c r="F167">
-        <v>0.06</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="G167" s="2">
-        <v>578201</v>
+        <v>589578</v>
       </c>
       <c r="H167">
-        <v>20.68</v>
+        <v>24.56</v>
       </c>
       <c r="I167" t="s">
         <v>559</v>
       </c>
       <c r="J167">
-        <v>1.2</v>
+        <v>3.36</v>
       </c>
     </row>
     <row r="168" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
-        <v>874</v>
+        <v>480</v>
       </c>
       <c r="B168" t="s">
-        <v>531</v>
+        <v>481</v>
       </c>
       <c r="C168" t="s">
-        <v>875</v>
+        <v>854</v>
       </c>
       <c r="D168" t="s">
-        <v>575</v>
+        <v>564</v>
       </c>
       <c r="E168" s="2">
-        <v>11912862.880000001</v>
+        <v>13338102.42</v>
       </c>
       <c r="F168">
         <v>0.06</v>
       </c>
       <c r="G168" s="2">
-        <v>160724</v>
+        <v>3183318</v>
       </c>
       <c r="H168">
-        <v>74.12</v>
+        <v>4.1900000000000004</v>
       </c>
       <c r="I168" t="s">
         <v>559</v>
       </c>
       <c r="J168">
-        <v>1.19</v>
+        <v>3.32</v>
       </c>
     </row>
     <row r="169" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
-        <v>876</v>
+        <v>371</v>
       </c>
       <c r="B169" t="s">
-        <v>428</v>
+        <v>372</v>
       </c>
       <c r="C169" t="s">
-        <v>877</v>
+        <v>837</v>
       </c>
       <c r="D169" t="s">
-        <v>575</v>
+        <v>561</v>
       </c>
       <c r="E169" s="2">
-        <v>11751606.630000001</v>
+        <v>15574199.58</v>
       </c>
       <c r="F169">
-        <v>0.05</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="G169" s="2">
-        <v>268731</v>
+        <v>2582786</v>
       </c>
       <c r="H169">
-        <v>43.73</v>
+        <v>6.03</v>
       </c>
       <c r="I169" t="s">
         <v>559</v>
       </c>
       <c r="J169">
-        <v>1.18</v>
+        <v>3.23</v>
       </c>
     </row>
     <row r="170" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
-        <v>416</v>
+        <v>919</v>
       </c>
       <c r="B170" t="s">
-        <v>417</v>
+        <v>364</v>
       </c>
       <c r="C170" t="s">
-        <v>878</v>
+        <v>920</v>
       </c>
       <c r="D170" t="s">
-        <v>754</v>
+        <v>594</v>
       </c>
       <c r="E170" s="2">
-        <v>11663144</v>
+        <v>8813408.6400000006</v>
       </c>
       <c r="F170">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="G170" s="2">
-        <v>1240760</v>
+        <v>351552</v>
       </c>
       <c r="H170">
-        <v>9.4</v>
+        <v>25.07</v>
       </c>
       <c r="I170" t="s">
         <v>559</v>
       </c>
       <c r="J170">
-        <v>1.17</v>
+        <v>3.14</v>
       </c>
     </row>
     <row r="171" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
-        <v>879</v>
+        <v>861</v>
       </c>
       <c r="B171" t="s">
-        <v>880</v>
+        <v>393</v>
       </c>
       <c r="C171" t="s">
-        <v>881</v>
+        <v>862</v>
       </c>
       <c r="D171" t="s">
-        <v>564</v>
+        <v>718</v>
       </c>
       <c r="E171" s="2">
-        <v>11409275.85</v>
+        <v>13028715.15</v>
       </c>
       <c r="F171">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="G171" s="2">
-        <v>72051</v>
+        <v>1246767</v>
       </c>
       <c r="H171">
-        <v>158.35</v>
+        <v>10.45</v>
       </c>
       <c r="I171" t="s">
         <v>559</v>
       </c>
       <c r="J171">
-        <v>1.1399999999999999</v>
+        <v>2.88</v>
       </c>
     </row>
     <row r="172" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
-        <v>882</v>
+        <v>929</v>
       </c>
       <c r="B172" t="s">
-        <v>408</v>
+        <v>401</v>
       </c>
       <c r="C172" t="s">
-        <v>883</v>
+        <v>930</v>
       </c>
       <c r="D172" t="s">
-        <v>594</v>
+        <v>718</v>
       </c>
       <c r="E172" s="2">
-        <v>11361673.6</v>
+        <v>8073383.7999999998</v>
       </c>
       <c r="F172">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="G172" s="2">
-        <v>229066</v>
+        <v>518855</v>
       </c>
       <c r="H172">
-        <v>49.6</v>
+        <v>15.56</v>
       </c>
       <c r="I172" t="s">
         <v>559</v>
       </c>
       <c r="J172">
-        <v>1.1399999999999999</v>
+        <v>2.86</v>
       </c>
     </row>
     <row r="173" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
-        <v>884</v>
+        <v>868</v>
       </c>
       <c r="B173" t="s">
-        <v>414</v>
+        <v>869</v>
       </c>
       <c r="C173" t="s">
-        <v>885</v>
+        <v>870</v>
       </c>
       <c r="D173" t="s">
-        <v>718</v>
+        <v>570</v>
       </c>
       <c r="E173" s="2">
-        <v>11326208.640000001</v>
+        <v>11974943.75</v>
       </c>
       <c r="F173">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="G173" s="2">
-        <v>204888</v>
+        <v>622075</v>
       </c>
       <c r="H173">
-        <v>55.28</v>
+        <v>19.25</v>
       </c>
       <c r="I173" t="s">
         <v>559</v>
       </c>
       <c r="J173">
-        <v>1.1299999999999999</v>
+        <v>2.81</v>
       </c>
     </row>
     <row r="174" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
-        <v>886</v>
+        <v>904</v>
       </c>
       <c r="B174" t="s">
-        <v>366</v>
+        <v>391</v>
       </c>
       <c r="C174" t="s">
-        <v>887</v>
+        <v>905</v>
       </c>
       <c r="D174" t="s">
-        <v>615</v>
+        <v>626</v>
       </c>
       <c r="E174" s="2">
-        <v>10494658.92</v>
+        <v>9483111.1799999997</v>
       </c>
       <c r="F174">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="G174" s="2">
-        <v>414481</v>
+        <v>143553</v>
       </c>
       <c r="H174">
-        <v>25.32</v>
+        <v>66.06</v>
       </c>
       <c r="I174" t="s">
         <v>559</v>
       </c>
       <c r="J174">
-        <v>1.05</v>
+        <v>2.79</v>
       </c>
     </row>
     <row r="175" spans="1:10" x14ac:dyDescent="0.3">
@@ -9483,1127 +9484,1127 @@
         <v>591</v>
       </c>
       <c r="J175">
-        <v>1.05</v>
+        <v>2.78</v>
       </c>
     </row>
     <row r="176" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
-        <v>891</v>
+        <v>947</v>
       </c>
       <c r="B176" t="s">
-        <v>496</v>
+        <v>430</v>
       </c>
       <c r="C176" t="s">
-        <v>892</v>
+        <v>948</v>
       </c>
       <c r="D176" t="s">
-        <v>558</v>
+        <v>564</v>
       </c>
       <c r="E176" s="2">
-        <v>9986070.0500000007</v>
+        <v>7437942.54</v>
       </c>
       <c r="F176">
-        <v>0.05</v>
+        <v>0.03</v>
       </c>
       <c r="G176" s="2">
-        <v>229829</v>
+        <v>310691</v>
       </c>
       <c r="H176">
-        <v>43.45</v>
+        <v>23.94</v>
       </c>
       <c r="I176" t="s">
         <v>559</v>
       </c>
       <c r="J176">
-        <v>1</v>
+        <v>2.78</v>
       </c>
     </row>
     <row r="177" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
-        <v>893</v>
+        <v>958</v>
       </c>
       <c r="B177" t="s">
-        <v>981</v>
+        <v>399</v>
       </c>
       <c r="C177" t="s">
-        <v>894</v>
+        <v>959</v>
       </c>
       <c r="D177" t="s">
-        <v>575</v>
+        <v>570</v>
       </c>
       <c r="E177" s="2">
-        <v>9920439.3599999994</v>
+        <v>5799869.9199999999</v>
       </c>
       <c r="F177">
-        <v>0.05</v>
+        <v>0.03</v>
       </c>
       <c r="G177" s="2">
-        <v>207584</v>
+        <v>128089</v>
       </c>
       <c r="H177">
-        <v>47.79</v>
+        <v>45.28</v>
       </c>
       <c r="I177" t="s">
         <v>559</v>
       </c>
       <c r="J177">
-        <v>0.99</v>
+        <v>2.73</v>
       </c>
     </row>
     <row r="178" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
-        <v>895</v>
+        <v>863</v>
       </c>
       <c r="B178" t="s">
-        <v>478</v>
+        <v>864</v>
       </c>
       <c r="C178" t="s">
-        <v>896</v>
+        <v>865</v>
       </c>
       <c r="D178" t="s">
-        <v>575</v>
+        <v>564</v>
       </c>
       <c r="E178" s="2">
-        <v>9834467.5800000001</v>
+        <v>12634954.539999999</v>
       </c>
       <c r="F178">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="G178" s="2">
-        <v>242109</v>
+        <v>1033957</v>
       </c>
       <c r="H178">
-        <v>40.619999999999997</v>
+        <v>12.22</v>
       </c>
       <c r="I178" t="s">
         <v>559</v>
       </c>
       <c r="J178">
-        <v>0.98</v>
+        <v>2.59</v>
       </c>
     </row>
     <row r="179" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
-        <v>442</v>
+        <v>886</v>
       </c>
       <c r="B179" t="s">
-        <v>443</v>
+        <v>366</v>
       </c>
       <c r="C179" t="s">
-        <v>897</v>
+        <v>887</v>
       </c>
       <c r="D179" t="s">
-        <v>561</v>
+        <v>615</v>
       </c>
       <c r="E179" s="2">
-        <v>9749935.3200000003</v>
+        <v>10494658.92</v>
       </c>
       <c r="F179">
         <v>0.05</v>
       </c>
       <c r="G179" s="2">
-        <v>588054</v>
+        <v>414481</v>
       </c>
       <c r="H179">
-        <v>16.579999999999998</v>
+        <v>25.32</v>
       </c>
       <c r="I179" t="s">
         <v>559</v>
       </c>
       <c r="J179">
-        <v>0.97</v>
+        <v>2.59</v>
       </c>
     </row>
     <row r="180" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
-        <v>898</v>
+        <v>871</v>
       </c>
       <c r="B180" t="s">
-        <v>461</v>
+        <v>872</v>
       </c>
       <c r="C180" t="s">
-        <v>899</v>
+        <v>873</v>
       </c>
       <c r="D180" t="s">
         <v>564</v>
       </c>
       <c r="E180" s="2">
-        <v>9686004.3200000003</v>
+        <v>11957196.68</v>
       </c>
       <c r="F180">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="G180" s="2">
-        <v>649196</v>
+        <v>578201</v>
       </c>
       <c r="H180">
-        <v>14.92</v>
+        <v>20.68</v>
       </c>
       <c r="I180" t="s">
         <v>559</v>
       </c>
       <c r="J180">
-        <v>0.97</v>
+        <v>2.56</v>
       </c>
     </row>
     <row r="181" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
-        <v>900</v>
+        <v>874</v>
       </c>
       <c r="B181" t="s">
-        <v>437</v>
+        <v>531</v>
       </c>
       <c r="C181" t="s">
-        <v>901</v>
+        <v>875</v>
       </c>
       <c r="D181" t="s">
-        <v>718</v>
+        <v>575</v>
       </c>
       <c r="E181" s="2">
-        <v>9537194.9000000004</v>
+        <v>11912862.880000001</v>
       </c>
       <c r="F181">
-        <v>0.04</v>
+        <v>0.06</v>
       </c>
       <c r="G181" s="2">
-        <v>575570</v>
+        <v>160724</v>
       </c>
       <c r="H181">
-        <v>16.57</v>
+        <v>74.12</v>
       </c>
       <c r="I181" t="s">
         <v>559</v>
       </c>
       <c r="J181">
-        <v>0.95</v>
+        <v>2.52</v>
       </c>
     </row>
     <row r="182" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
-        <v>902</v>
+        <v>898</v>
       </c>
       <c r="B182" t="s">
-        <v>535</v>
+        <v>461</v>
       </c>
       <c r="C182" t="s">
-        <v>903</v>
+        <v>899</v>
       </c>
       <c r="D182" t="s">
         <v>564</v>
       </c>
       <c r="E182" s="2">
-        <v>9529605</v>
+        <v>9686004.3200000003</v>
       </c>
       <c r="F182">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="G182" s="2">
-        <v>1058845</v>
+        <v>649196</v>
       </c>
       <c r="H182">
-        <v>9</v>
+        <v>14.92</v>
       </c>
       <c r="I182" t="s">
         <v>559</v>
       </c>
       <c r="J182">
-        <v>0.95</v>
+        <v>2.4900000000000002</v>
       </c>
     </row>
     <row r="183" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
-        <v>904</v>
+        <v>876</v>
       </c>
       <c r="B183" t="s">
-        <v>391</v>
+        <v>428</v>
       </c>
       <c r="C183" t="s">
-        <v>905</v>
+        <v>877</v>
       </c>
       <c r="D183" t="s">
-        <v>626</v>
+        <v>575</v>
       </c>
       <c r="E183" s="2">
-        <v>9483111.1799999997</v>
+        <v>11751606.630000001</v>
       </c>
       <c r="F183">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="G183" s="2">
-        <v>143553</v>
+        <v>268731</v>
       </c>
       <c r="H183">
-        <v>66.06</v>
+        <v>43.73</v>
       </c>
       <c r="I183" t="s">
         <v>559</v>
       </c>
       <c r="J183">
-        <v>0.95</v>
+        <v>2.46</v>
       </c>
     </row>
     <row r="184" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
-        <v>906</v>
+        <v>884</v>
       </c>
       <c r="B184" t="s">
-        <v>500</v>
+        <v>414</v>
       </c>
       <c r="C184" t="s">
-        <v>907</v>
+        <v>885</v>
       </c>
       <c r="D184" t="s">
-        <v>564</v>
+        <v>718</v>
       </c>
       <c r="E184" s="2">
-        <v>9316270.8000000007</v>
+        <v>11326208.640000001</v>
       </c>
       <c r="F184">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="G184" s="2">
-        <v>1308465</v>
+        <v>204888</v>
       </c>
       <c r="H184">
-        <v>7.12</v>
+        <v>55.28</v>
       </c>
       <c r="I184" t="s">
         <v>559</v>
       </c>
       <c r="J184">
-        <v>0.93</v>
+        <v>2.44</v>
       </c>
     </row>
     <row r="185" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
-        <v>908</v>
+        <v>882</v>
       </c>
       <c r="B185" t="s">
-        <v>488</v>
+        <v>408</v>
       </c>
       <c r="C185" t="s">
-        <v>909</v>
+        <v>883</v>
       </c>
       <c r="D185" t="s">
-        <v>570</v>
+        <v>594</v>
       </c>
       <c r="E185" s="2">
-        <v>9304154.3800000008</v>
+        <v>11361673.6</v>
       </c>
       <c r="F185">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="G185" s="2">
-        <v>303958</v>
+        <v>229066</v>
       </c>
       <c r="H185">
-        <v>30.61</v>
+        <v>49.6</v>
       </c>
       <c r="I185" t="s">
         <v>559</v>
       </c>
       <c r="J185">
-        <v>0.93</v>
+        <v>2.35</v>
       </c>
     </row>
     <row r="186" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
-        <v>910</v>
+        <v>442</v>
       </c>
       <c r="B186" t="s">
-        <v>522</v>
+        <v>443</v>
       </c>
       <c r="C186" t="s">
-        <v>911</v>
+        <v>897</v>
       </c>
       <c r="D186" t="s">
-        <v>754</v>
+        <v>561</v>
       </c>
       <c r="E186" s="2">
-        <v>9233897.9700000007</v>
+        <v>9749935.3200000003</v>
       </c>
       <c r="F186">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="G186" s="2">
-        <v>437833</v>
+        <v>588054</v>
       </c>
       <c r="H186">
-        <v>21.09</v>
+        <v>16.579999999999998</v>
       </c>
       <c r="I186" t="s">
         <v>559</v>
       </c>
       <c r="J186">
-        <v>0.92</v>
+        <v>2.27</v>
       </c>
     </row>
     <row r="187" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
-        <v>912</v>
+        <v>902</v>
       </c>
       <c r="B187" t="s">
-        <v>913</v>
+        <v>535</v>
       </c>
       <c r="C187" t="s">
-        <v>914</v>
+        <v>903</v>
       </c>
       <c r="D187" t="s">
-        <v>575</v>
+        <v>564</v>
       </c>
       <c r="E187" s="2">
-        <v>9179355.8000000007</v>
+        <v>9529605</v>
       </c>
       <c r="F187">
         <v>0.04</v>
       </c>
       <c r="G187" s="2">
-        <v>297548</v>
+        <v>1058845</v>
       </c>
       <c r="H187">
-        <v>30.85</v>
+        <v>9</v>
       </c>
       <c r="I187" t="s">
         <v>559</v>
       </c>
       <c r="J187">
-        <v>0.92</v>
+        <v>2.23</v>
       </c>
     </row>
     <row r="188" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
-        <v>915</v>
+        <v>895</v>
       </c>
       <c r="B188" t="s">
-        <v>449</v>
+        <v>478</v>
       </c>
       <c r="C188" t="s">
-        <v>916</v>
+        <v>896</v>
       </c>
       <c r="D188" t="s">
-        <v>597</v>
+        <v>575</v>
       </c>
       <c r="E188" s="2">
-        <v>9167430.9600000009</v>
+        <v>9834467.5800000001</v>
       </c>
       <c r="F188">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="G188" s="2">
-        <v>324396</v>
+        <v>242109</v>
       </c>
       <c r="H188">
-        <v>28.26</v>
+        <v>40.619999999999997</v>
       </c>
       <c r="I188" t="s">
         <v>559</v>
       </c>
       <c r="J188">
-        <v>0.92</v>
+        <v>2.2000000000000002</v>
       </c>
     </row>
     <row r="189" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
-        <v>917</v>
+        <v>936</v>
       </c>
       <c r="B189" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="C189" t="s">
-        <v>918</v>
+        <v>937</v>
       </c>
       <c r="D189" t="s">
-        <v>564</v>
+        <v>718</v>
       </c>
       <c r="E189" s="2">
-        <v>8960696.5999999996</v>
+        <v>7986659.8399999999</v>
       </c>
       <c r="F189">
         <v>0.04</v>
       </c>
       <c r="G189" s="2">
-        <v>792982</v>
+        <v>510656</v>
       </c>
       <c r="H189">
-        <v>11.3</v>
+        <v>15.64</v>
       </c>
       <c r="I189" t="s">
         <v>559</v>
       </c>
       <c r="J189">
-        <v>0.9</v>
+        <v>2.16</v>
       </c>
     </row>
     <row r="190" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A190" t="s">
-        <v>919</v>
+        <v>945</v>
       </c>
       <c r="B190" t="s">
-        <v>364</v>
+        <v>426</v>
       </c>
       <c r="C190" t="s">
-        <v>920</v>
+        <v>946</v>
       </c>
       <c r="D190" t="s">
-        <v>594</v>
+        <v>558</v>
       </c>
       <c r="E190" s="2">
-        <v>8813408.6400000006</v>
+        <v>7509303.1200000001</v>
       </c>
       <c r="F190">
         <v>0.04</v>
       </c>
       <c r="G190" s="2">
-        <v>351552</v>
+        <v>59147</v>
       </c>
       <c r="H190">
-        <v>25.07</v>
+        <v>126.96</v>
       </c>
       <c r="I190" t="s">
         <v>559</v>
       </c>
       <c r="J190">
-        <v>0.88</v>
+        <v>2.09</v>
       </c>
     </row>
     <row r="191" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
-        <v>921</v>
+        <v>891</v>
       </c>
       <c r="B191" t="s">
-        <v>504</v>
+        <v>496</v>
       </c>
       <c r="C191" t="s">
-        <v>922</v>
+        <v>892</v>
       </c>
       <c r="D191" t="s">
-        <v>718</v>
+        <v>558</v>
       </c>
       <c r="E191" s="2">
-        <v>8782364.6699999999</v>
+        <v>9986070.0500000007</v>
       </c>
       <c r="F191">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="G191" s="2">
-        <v>664827</v>
+        <v>229829</v>
       </c>
       <c r="H191">
-        <v>13.21</v>
+        <v>43.45</v>
       </c>
       <c r="I191" t="s">
         <v>559</v>
       </c>
       <c r="J191">
-        <v>0.88</v>
+        <v>2.0499999999999998</v>
       </c>
     </row>
     <row r="192" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A192" t="s">
-        <v>923</v>
+        <v>912</v>
       </c>
       <c r="B192" t="s">
-        <v>924</v>
+        <v>913</v>
       </c>
       <c r="C192" t="s">
-        <v>925</v>
+        <v>914</v>
       </c>
       <c r="D192" t="s">
-        <v>558</v>
+        <v>575</v>
       </c>
       <c r="E192" s="2">
-        <v>8431031.9800000004</v>
+        <v>9179355.8000000007</v>
       </c>
       <c r="F192">
         <v>0.04</v>
       </c>
       <c r="G192" s="2">
-        <v>210934</v>
+        <v>297548</v>
       </c>
       <c r="H192">
-        <v>39.97</v>
+        <v>30.85</v>
       </c>
       <c r="I192" t="s">
         <v>559</v>
       </c>
       <c r="J192">
-        <v>0.84</v>
+        <v>2.04</v>
       </c>
     </row>
     <row r="193" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
-        <v>926</v>
+        <v>900</v>
       </c>
       <c r="B193" t="s">
-        <v>421</v>
+        <v>437</v>
       </c>
       <c r="C193" t="s">
-        <v>927</v>
+        <v>901</v>
       </c>
       <c r="D193" t="s">
-        <v>564</v>
+        <v>718</v>
       </c>
       <c r="E193" s="2">
-        <v>8379088.0599999996</v>
+        <v>9537194.9000000004</v>
       </c>
       <c r="F193">
         <v>0.04</v>
       </c>
       <c r="G193" s="2">
-        <v>358387</v>
+        <v>575570</v>
       </c>
       <c r="H193">
-        <v>23.38</v>
+        <v>16.57</v>
       </c>
       <c r="I193" t="s">
         <v>559</v>
       </c>
       <c r="J193">
-        <v>0.84</v>
+        <v>2.0299999999999998</v>
       </c>
     </row>
     <row r="194" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
-        <v>539</v>
+        <v>906</v>
       </c>
       <c r="B194" t="s">
-        <v>540</v>
+        <v>500</v>
       </c>
       <c r="C194" t="s">
-        <v>928</v>
+        <v>907</v>
       </c>
       <c r="D194" t="s">
         <v>564</v>
       </c>
       <c r="E194" s="2">
-        <v>8096135.9400000004</v>
+        <v>9316270.8000000007</v>
       </c>
       <c r="F194">
         <v>0.04</v>
       </c>
       <c r="G194" s="2">
-        <v>737353</v>
+        <v>1308465</v>
       </c>
       <c r="H194">
-        <v>10.98</v>
+        <v>7.12</v>
       </c>
       <c r="I194" t="s">
         <v>559</v>
       </c>
       <c r="J194">
-        <v>0.81</v>
+        <v>2.02</v>
       </c>
     </row>
     <row r="195" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
-        <v>929</v>
+        <v>910</v>
       </c>
       <c r="B195" t="s">
-        <v>401</v>
+        <v>522</v>
       </c>
       <c r="C195" t="s">
-        <v>930</v>
+        <v>911</v>
       </c>
       <c r="D195" t="s">
-        <v>718</v>
+        <v>754</v>
       </c>
       <c r="E195" s="2">
-        <v>8073383.7999999998</v>
+        <v>9233897.9700000007</v>
       </c>
       <c r="F195">
         <v>0.04</v>
       </c>
       <c r="G195" s="2">
-        <v>518855</v>
+        <v>437833</v>
       </c>
       <c r="H195">
-        <v>15.56</v>
+        <v>21.09</v>
       </c>
       <c r="I195" t="s">
         <v>559</v>
       </c>
       <c r="J195">
-        <v>0.81</v>
+        <v>1.98</v>
       </c>
     </row>
     <row r="196" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
-        <v>931</v>
+        <v>908</v>
       </c>
       <c r="B196" t="s">
-        <v>932</v>
+        <v>488</v>
       </c>
       <c r="C196" t="s">
-        <v>933</v>
+        <v>909</v>
       </c>
       <c r="D196" t="s">
-        <v>564</v>
+        <v>570</v>
       </c>
       <c r="E196" s="2">
-        <v>8064733.9500000002</v>
+        <v>9304154.3800000008</v>
       </c>
       <c r="F196">
         <v>0.04</v>
       </c>
       <c r="G196" s="2">
-        <v>459529</v>
+        <v>303958</v>
       </c>
       <c r="H196">
-        <v>17.55</v>
+        <v>30.61</v>
       </c>
       <c r="I196" t="s">
         <v>559</v>
       </c>
       <c r="J196">
-        <v>0.81</v>
+        <v>1.96</v>
       </c>
     </row>
     <row r="197" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
-        <v>934</v>
+        <v>917</v>
       </c>
       <c r="B197" t="s">
-        <v>508</v>
+        <v>492</v>
       </c>
       <c r="C197" t="s">
-        <v>935</v>
+        <v>918</v>
       </c>
       <c r="D197" t="s">
-        <v>570</v>
+        <v>564</v>
       </c>
       <c r="E197" s="2">
-        <v>8041114.1399999997</v>
+        <v>8960696.5999999996</v>
       </c>
       <c r="F197">
         <v>0.04</v>
       </c>
       <c r="G197" s="2">
-        <v>353611</v>
+        <v>792982</v>
       </c>
       <c r="H197">
-        <v>22.74</v>
+        <v>11.3</v>
       </c>
       <c r="I197" t="s">
         <v>559</v>
       </c>
       <c r="J197">
-        <v>0.8</v>
+        <v>1.94</v>
       </c>
     </row>
     <row r="198" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
-        <v>936</v>
+        <v>915</v>
       </c>
       <c r="B198" t="s">
-        <v>490</v>
+        <v>449</v>
       </c>
       <c r="C198" t="s">
-        <v>937</v>
+        <v>916</v>
       </c>
       <c r="D198" t="s">
-        <v>718</v>
+        <v>597</v>
       </c>
       <c r="E198" s="2">
-        <v>7986659.8399999999</v>
+        <v>9167430.9600000009</v>
       </c>
       <c r="F198">
         <v>0.04</v>
       </c>
       <c r="G198" s="2">
-        <v>510656</v>
+        <v>324396</v>
       </c>
       <c r="H198">
-        <v>15.64</v>
+        <v>28.26</v>
       </c>
       <c r="I198" t="s">
         <v>559</v>
       </c>
       <c r="J198">
-        <v>0.8</v>
+        <v>1.92</v>
       </c>
     </row>
     <row r="199" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
-        <v>938</v>
+        <v>934</v>
       </c>
       <c r="B199" t="s">
-        <v>447</v>
+        <v>508</v>
       </c>
       <c r="C199" t="s">
-        <v>939</v>
+        <v>935</v>
       </c>
       <c r="D199" t="s">
-        <v>718</v>
+        <v>570</v>
       </c>
       <c r="E199" s="2">
-        <v>7947426.0499999998</v>
+        <v>8041114.1399999997</v>
       </c>
       <c r="F199">
         <v>0.04</v>
       </c>
       <c r="G199" s="2">
-        <v>604367</v>
+        <v>353611</v>
       </c>
       <c r="H199">
-        <v>13.15</v>
+        <v>22.74</v>
       </c>
       <c r="I199" t="s">
         <v>559</v>
       </c>
       <c r="J199">
-        <v>0.79</v>
+        <v>1.91</v>
       </c>
     </row>
     <row r="200" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
-        <v>940</v>
+        <v>921</v>
       </c>
       <c r="B200" t="s">
-        <v>510</v>
+        <v>504</v>
       </c>
       <c r="C200" t="s">
-        <v>941</v>
+        <v>922</v>
       </c>
       <c r="D200" t="s">
-        <v>615</v>
+        <v>718</v>
       </c>
       <c r="E200" s="2">
-        <v>7662202.4000000004</v>
+        <v>8782364.6699999999</v>
       </c>
       <c r="F200">
         <v>0.04</v>
       </c>
       <c r="G200" s="2">
-        <v>1070140</v>
+        <v>664827</v>
       </c>
       <c r="H200">
-        <v>7.16</v>
+        <v>13.21</v>
       </c>
       <c r="I200" t="s">
         <v>559</v>
       </c>
       <c r="J200">
-        <v>0.77</v>
+        <v>1.88</v>
       </c>
     </row>
     <row r="201" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
-        <v>942</v>
+        <v>949</v>
       </c>
       <c r="B201" t="s">
-        <v>943</v>
+        <v>506</v>
       </c>
       <c r="C201" t="s">
-        <v>944</v>
+        <v>950</v>
       </c>
       <c r="D201" t="s">
         <v>575</v>
       </c>
       <c r="E201" s="2">
-        <v>7562773.75</v>
+        <v>6943008</v>
       </c>
       <c r="F201">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="G201" s="2">
-        <v>263053</v>
+        <v>447936</v>
       </c>
       <c r="H201">
-        <v>28.75</v>
+        <v>15.5</v>
       </c>
       <c r="I201" t="s">
         <v>559</v>
       </c>
       <c r="J201">
-        <v>0.76</v>
+        <v>1.86</v>
       </c>
     </row>
     <row r="202" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
-        <v>945</v>
+        <v>938</v>
       </c>
       <c r="B202" t="s">
-        <v>426</v>
+        <v>447</v>
       </c>
       <c r="C202" t="s">
-        <v>946</v>
+        <v>939</v>
       </c>
       <c r="D202" t="s">
-        <v>558</v>
+        <v>718</v>
       </c>
       <c r="E202" s="2">
-        <v>7509303.1200000001</v>
+        <v>7947426.0499999998</v>
       </c>
       <c r="F202">
         <v>0.04</v>
       </c>
       <c r="G202" s="2">
-        <v>59147</v>
+        <v>604367</v>
       </c>
       <c r="H202">
-        <v>126.96</v>
+        <v>13.15</v>
       </c>
       <c r="I202" t="s">
         <v>559</v>
       </c>
       <c r="J202">
-        <v>0.75</v>
+        <v>1.83</v>
       </c>
     </row>
     <row r="203" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A203" t="s">
-        <v>947</v>
+        <v>923</v>
       </c>
       <c r="B203" t="s">
-        <v>430</v>
+        <v>924</v>
       </c>
       <c r="C203" t="s">
-        <v>948</v>
+        <v>925</v>
       </c>
       <c r="D203" t="s">
-        <v>564</v>
+        <v>558</v>
       </c>
       <c r="E203" s="2">
-        <v>7437942.54</v>
+        <v>8431031.9800000004</v>
       </c>
       <c r="F203">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="G203" s="2">
-        <v>310691</v>
+        <v>210934</v>
       </c>
       <c r="H203">
-        <v>23.94</v>
+        <v>39.97</v>
       </c>
       <c r="I203" t="s">
         <v>559</v>
       </c>
       <c r="J203">
-        <v>0.74</v>
+        <v>1.79</v>
       </c>
     </row>
     <row r="204" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A204" t="s">
-        <v>949</v>
+        <v>931</v>
       </c>
       <c r="B204" t="s">
-        <v>506</v>
+        <v>932</v>
       </c>
       <c r="C204" t="s">
-        <v>950</v>
+        <v>933</v>
       </c>
       <c r="D204" t="s">
-        <v>575</v>
+        <v>564</v>
       </c>
       <c r="E204" s="2">
-        <v>6943008</v>
+        <v>8064733.9500000002</v>
       </c>
       <c r="F204">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="G204" s="2">
-        <v>447936</v>
+        <v>459529</v>
       </c>
       <c r="H204">
-        <v>15.5</v>
+        <v>17.55</v>
       </c>
       <c r="I204" t="s">
         <v>559</v>
       </c>
       <c r="J204">
-        <v>0.69</v>
+        <v>1.78</v>
       </c>
     </row>
     <row r="205" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A205" t="s">
-        <v>951</v>
+        <v>539</v>
       </c>
       <c r="B205" t="s">
-        <v>546</v>
+        <v>540</v>
       </c>
       <c r="C205" t="s">
-        <v>952</v>
+        <v>928</v>
       </c>
       <c r="D205" t="s">
-        <v>594</v>
+        <v>564</v>
       </c>
       <c r="E205" s="2">
-        <v>6516278.7300000004</v>
+        <v>8096135.9400000004</v>
       </c>
       <c r="F205">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="G205" s="2">
-        <v>198003</v>
+        <v>737353</v>
       </c>
       <c r="H205">
-        <v>32.909999999999997</v>
+        <v>10.98</v>
       </c>
       <c r="I205" t="s">
         <v>559</v>
       </c>
       <c r="J205">
-        <v>0.65</v>
+        <v>1.73</v>
       </c>
     </row>
     <row r="206" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
-        <v>953</v>
+        <v>942</v>
       </c>
       <c r="B206" t="s">
-        <v>954</v>
+        <v>943</v>
       </c>
       <c r="C206" t="s">
-        <v>955</v>
+        <v>944</v>
       </c>
       <c r="D206" t="s">
         <v>575</v>
       </c>
       <c r="E206" s="2">
-        <v>6292058.8600000003</v>
+        <v>7562773.75</v>
       </c>
       <c r="F206">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="G206" s="2">
-        <v>391054</v>
+        <v>263053</v>
       </c>
       <c r="H206">
-        <v>16.09</v>
+        <v>28.75</v>
       </c>
       <c r="I206" t="s">
         <v>559</v>
       </c>
       <c r="J206">
-        <v>0.63</v>
+        <v>1.61</v>
       </c>
     </row>
     <row r="207" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A207" t="s">
-        <v>956</v>
+        <v>940</v>
       </c>
       <c r="B207" t="s">
-        <v>353</v>
+        <v>510</v>
       </c>
       <c r="C207" t="s">
-        <v>957</v>
+        <v>941</v>
       </c>
       <c r="D207" t="s">
-        <v>718</v>
+        <v>615</v>
       </c>
       <c r="E207" s="2">
-        <v>5837298.0300000003</v>
+        <v>7662202.4000000004</v>
       </c>
       <c r="F207">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="G207" s="2">
-        <v>359661</v>
+        <v>1070140</v>
       </c>
       <c r="H207">
-        <v>16.23</v>
+        <v>7.16</v>
       </c>
       <c r="I207" t="s">
         <v>559</v>
       </c>
       <c r="J207">
-        <v>0.57999999999999996</v>
+        <v>1.58</v>
       </c>
     </row>
     <row r="208" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A208" t="s">
-        <v>958</v>
+        <v>962</v>
       </c>
       <c r="B208" t="s">
-        <v>399</v>
+        <v>963</v>
       </c>
       <c r="C208" t="s">
-        <v>959</v>
+        <v>964</v>
       </c>
       <c r="D208" t="s">
-        <v>570</v>
+        <v>564</v>
       </c>
       <c r="E208" s="2">
-        <v>5799869.9199999999</v>
+        <v>5731216.4000000004</v>
       </c>
       <c r="F208">
         <v>0.03</v>
       </c>
       <c r="G208" s="2">
-        <v>128089</v>
+        <v>787255</v>
       </c>
       <c r="H208">
-        <v>45.28</v>
+        <v>7.28</v>
       </c>
       <c r="I208" t="s">
         <v>559</v>
       </c>
       <c r="J208">
-        <v>0.57999999999999996</v>
+        <v>1.52</v>
       </c>
     </row>
     <row r="209" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A209" t="s">
-        <v>960</v>
+        <v>953</v>
       </c>
       <c r="B209" t="s">
-        <v>533</v>
+        <v>954</v>
       </c>
       <c r="C209" t="s">
-        <v>961</v>
+        <v>955</v>
       </c>
       <c r="D209" t="s">
         <v>575</v>
       </c>
       <c r="E209" s="2">
-        <v>5781437.0800000001</v>
+        <v>6292058.8600000003</v>
       </c>
       <c r="F209">
         <v>0.03</v>
       </c>
       <c r="G209" s="2">
-        <v>70964</v>
+        <v>391054</v>
       </c>
       <c r="H209">
-        <v>81.47</v>
+        <v>16.09</v>
       </c>
       <c r="I209" t="s">
         <v>559</v>
       </c>
       <c r="J209">
-        <v>0.57999999999999996</v>
+        <v>1.41</v>
       </c>
     </row>
     <row r="210" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A210" t="s">
-        <v>962</v>
+        <v>951</v>
       </c>
       <c r="B210" t="s">
-        <v>963</v>
+        <v>546</v>
       </c>
       <c r="C210" t="s">
-        <v>964</v>
+        <v>952</v>
       </c>
       <c r="D210" t="s">
-        <v>564</v>
+        <v>594</v>
       </c>
       <c r="E210" s="2">
-        <v>5731216.4000000004</v>
+        <v>6516278.7300000004</v>
       </c>
       <c r="F210">
         <v>0.03</v>
       </c>
       <c r="G210" s="2">
-        <v>787255</v>
+        <v>198003</v>
       </c>
       <c r="H210">
-        <v>7.28</v>
+        <v>32.909999999999997</v>
       </c>
       <c r="I210" t="s">
         <v>559</v>
       </c>
       <c r="J210">
-        <v>0.56999999999999995</v>
+        <v>1.38</v>
       </c>
     </row>
     <row r="211" spans="1:10" x14ac:dyDescent="0.3">
@@ -10611,7 +10612,7 @@
         <v>965</v>
       </c>
       <c r="B211" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="C211" t="s">
         <v>966</v>
@@ -10635,74 +10636,77 @@
         <v>559</v>
       </c>
       <c r="J211">
-        <v>0.54</v>
+        <v>1.28</v>
       </c>
     </row>
     <row r="212" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A212" t="s">
-        <v>967</v>
+        <v>960</v>
       </c>
       <c r="B212" t="s">
-        <v>968</v>
+        <v>533</v>
       </c>
       <c r="C212" t="s">
-        <v>969</v>
+        <v>961</v>
       </c>
       <c r="D212" t="s">
-        <v>594</v>
+        <v>575</v>
       </c>
       <c r="E212" s="2">
-        <v>1090876.8</v>
+        <v>5781437.0800000001</v>
       </c>
       <c r="F212">
-        <v>0.01</v>
+        <v>0.03</v>
       </c>
       <c r="G212" s="2">
-        <v>69928</v>
+        <v>70964</v>
       </c>
       <c r="H212">
-        <v>15.6</v>
+        <v>81.47</v>
       </c>
       <c r="I212" t="s">
         <v>559</v>
       </c>
       <c r="J212">
-        <v>0.11</v>
+        <v>1.27</v>
       </c>
     </row>
     <row r="213" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A213" t="s">
-        <v>830</v>
+        <v>967</v>
       </c>
       <c r="B213" t="s">
-        <v>831</v>
+        <v>968</v>
       </c>
       <c r="C213" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="D213" t="s">
-        <v>558</v>
+        <v>594</v>
       </c>
       <c r="E213" s="2">
-        <v>43912.800000000003</v>
+        <v>1090876.8</v>
       </c>
       <c r="F213">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="G213" s="2">
-        <v>146376</v>
+        <v>69928</v>
       </c>
       <c r="H213">
-        <v>0.3</v>
+        <v>15.6</v>
       </c>
       <c r="I213" t="s">
         <v>559</v>
       </c>
       <c r="J213">
-        <v>0</v>
+        <v>0.47</v>
       </c>
     </row>
   </sheetData>
+  <sortState ref="A2:K213">
+    <sortCondition descending="1" ref="J1"/>
+  </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/Tickers_Info.xlsx
+++ b/Tickers_Info.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="16392" windowHeight="5784" activeTab="3"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="16392" windowHeight="5784" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="Info" sheetId="3" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5205" uniqueCount="2028">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5207" uniqueCount="2028">
   <si>
     <t>Name</t>
   </si>
@@ -17744,7 +17744,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H102"/>
+  <dimension ref="A1:I102"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="37.44140625" bestFit="1" customWidth="1"/>
@@ -17752,9 +17752,10 @@
     <col min="5" max="5" width="13.5546875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="11.44140625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="14" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>4</v>
       </c>
@@ -17779,8 +17780,11 @@
       <c r="H1" t="s">
         <v>556</v>
       </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I1" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>990</v>
       </c>
@@ -17805,8 +17809,11 @@
       <c r="H2" t="s">
         <v>591</v>
       </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I2">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>992</v>
       </c>
@@ -17831,8 +17838,11 @@
       <c r="H3" t="s">
         <v>591</v>
       </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I3">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>994</v>
       </c>
@@ -17857,8 +17867,11 @@
       <c r="H4" t="s">
         <v>591</v>
       </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I4">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>996</v>
       </c>
@@ -17883,8 +17896,11 @@
       <c r="H5" t="s">
         <v>591</v>
       </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I5">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>998</v>
       </c>
@@ -17909,8 +17925,11 @@
       <c r="H6" t="s">
         <v>591</v>
       </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I6">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>1000</v>
       </c>
@@ -17935,8 +17954,11 @@
       <c r="H7" t="s">
         <v>591</v>
       </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I7">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>1002</v>
       </c>
@@ -17961,8 +17983,11 @@
       <c r="H8" t="s">
         <v>591</v>
       </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I8">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>1004</v>
       </c>
@@ -17987,8 +18012,11 @@
       <c r="H9" t="s">
         <v>591</v>
       </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I9">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>1006</v>
       </c>
@@ -18013,8 +18041,11 @@
       <c r="H10" t="s">
         <v>591</v>
       </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I10">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>1008</v>
       </c>
@@ -18039,8 +18070,11 @@
       <c r="H11" t="s">
         <v>591</v>
       </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I11">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>1010</v>
       </c>
@@ -18065,8 +18099,11 @@
       <c r="H12" t="s">
         <v>591</v>
       </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I12">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>1012</v>
       </c>
@@ -18091,8 +18128,11 @@
       <c r="H13" t="s">
         <v>591</v>
       </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I13">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>1014</v>
       </c>
@@ -18117,8 +18157,11 @@
       <c r="H14" t="s">
         <v>591</v>
       </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I14">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>1016</v>
       </c>
@@ -18143,8 +18186,11 @@
       <c r="H15" t="s">
         <v>591</v>
       </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I15">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>1018</v>
       </c>
@@ -18169,8 +18215,11 @@
       <c r="H16" t="s">
         <v>591</v>
       </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I16">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>1020</v>
       </c>
@@ -18195,8 +18244,11 @@
       <c r="H17" t="s">
         <v>591</v>
       </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I17">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>1022</v>
       </c>
@@ -18221,8 +18273,11 @@
       <c r="H18" t="s">
         <v>591</v>
       </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I18">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>1024</v>
       </c>
@@ -18247,8 +18302,11 @@
       <c r="H19" t="s">
         <v>591</v>
       </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I19">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>1026</v>
       </c>
@@ -18273,8 +18331,11 @@
       <c r="H20" t="s">
         <v>591</v>
       </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I20">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>9</v>
       </c>
@@ -18299,8 +18360,11 @@
       <c r="H21" t="s">
         <v>559</v>
       </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I21">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>1028</v>
       </c>
@@ -18325,8 +18389,11 @@
       <c r="H22" t="s">
         <v>591</v>
       </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I22">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>1030</v>
       </c>
@@ -18351,8 +18418,11 @@
       <c r="H23" t="s">
         <v>591</v>
       </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I23">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>1032</v>
       </c>
@@ -18377,8 +18447,11 @@
       <c r="H24" t="s">
         <v>591</v>
       </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I24">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>1034</v>
       </c>
@@ -18403,8 +18476,11 @@
       <c r="H25" t="s">
         <v>591</v>
       </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I25">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>1036</v>
       </c>
@@ -18429,8 +18505,11 @@
       <c r="H26" t="s">
         <v>591</v>
       </c>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I26">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>1038</v>
       </c>
@@ -18455,8 +18534,11 @@
       <c r="H27" t="s">
         <v>591</v>
       </c>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I27">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>1040</v>
       </c>
@@ -18481,8 +18563,11 @@
       <c r="H28" t="s">
         <v>591</v>
       </c>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I28">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>1042</v>
       </c>
@@ -18507,8 +18592,11 @@
       <c r="H29" t="s">
         <v>591</v>
       </c>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I29">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>1044</v>
       </c>
@@ -18533,8 +18621,11 @@
       <c r="H30" t="s">
         <v>591</v>
       </c>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I30">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>1046</v>
       </c>
@@ -18559,8 +18650,11 @@
       <c r="H31" t="s">
         <v>591</v>
       </c>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I31">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>1048</v>
       </c>
@@ -18585,8 +18679,11 @@
       <c r="H32" t="s">
         <v>591</v>
       </c>
-    </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I32">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>1050</v>
       </c>
@@ -18611,8 +18708,11 @@
       <c r="H33" t="s">
         <v>591</v>
       </c>
-    </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I33">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>1052</v>
       </c>
@@ -18637,8 +18737,11 @@
       <c r="H34" t="s">
         <v>591</v>
       </c>
-    </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I34">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>1054</v>
       </c>
@@ -18663,8 +18766,11 @@
       <c r="H35" t="s">
         <v>591</v>
       </c>
-    </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I35">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>1056</v>
       </c>
@@ -18689,8 +18795,11 @@
       <c r="H36" t="s">
         <v>591</v>
       </c>
-    </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I36">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>1058</v>
       </c>
@@ -18715,8 +18824,11 @@
       <c r="H37" t="s">
         <v>591</v>
       </c>
-    </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I37">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>1060</v>
       </c>
@@ -18741,8 +18853,11 @@
       <c r="H38" t="s">
         <v>591</v>
       </c>
-    </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I38">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>1062</v>
       </c>
@@ -18767,8 +18882,11 @@
       <c r="H39" t="s">
         <v>591</v>
       </c>
-    </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I39">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>1064</v>
       </c>
@@ -18793,8 +18911,11 @@
       <c r="H40" t="s">
         <v>591</v>
       </c>
-    </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I40">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>1066</v>
       </c>
@@ -18819,8 +18940,11 @@
       <c r="H41" t="s">
         <v>591</v>
       </c>
-    </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I41">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>1068</v>
       </c>
@@ -18845,8 +18969,11 @@
       <c r="H42" t="s">
         <v>591</v>
       </c>
-    </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I42">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>1070</v>
       </c>
@@ -18871,8 +18998,11 @@
       <c r="H43" t="s">
         <v>591</v>
       </c>
-    </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I43">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>1072</v>
       </c>
@@ -18897,8 +19027,11 @@
       <c r="H44" t="s">
         <v>591</v>
       </c>
-    </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I44">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>1074</v>
       </c>
@@ -18923,8 +19056,11 @@
       <c r="H45" t="s">
         <v>1076</v>
       </c>
-    </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I45">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>1077</v>
       </c>
@@ -18949,8 +19085,11 @@
       <c r="H46" t="s">
         <v>591</v>
       </c>
-    </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I46">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>1079</v>
       </c>
@@ -18975,8 +19114,11 @@
       <c r="H47" t="s">
         <v>591</v>
       </c>
-    </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I47">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>1081</v>
       </c>
@@ -19001,8 +19143,11 @@
       <c r="H48" t="s">
         <v>591</v>
       </c>
-    </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I48">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>1083</v>
       </c>
@@ -19027,8 +19172,11 @@
       <c r="H49" t="s">
         <v>591</v>
       </c>
-    </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I49">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>1085</v>
       </c>
@@ -19053,8 +19201,11 @@
       <c r="H50" t="s">
         <v>591</v>
       </c>
-    </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I50">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>1087</v>
       </c>
@@ -19079,8 +19230,11 @@
       <c r="H51" t="s">
         <v>1089</v>
       </c>
-    </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I51">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>1090</v>
       </c>
@@ -19105,8 +19259,11 @@
       <c r="H52" t="s">
         <v>591</v>
       </c>
-    </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I52">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>1092</v>
       </c>
@@ -19131,8 +19288,11 @@
       <c r="H53" t="s">
         <v>591</v>
       </c>
-    </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I53">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>1094</v>
       </c>
@@ -19157,8 +19317,11 @@
       <c r="H54" t="s">
         <v>591</v>
       </c>
-    </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I54">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>1096</v>
       </c>
@@ -19183,8 +19346,11 @@
       <c r="H55" t="s">
         <v>591</v>
       </c>
-    </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I55">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>1098</v>
       </c>
@@ -19209,8 +19375,11 @@
       <c r="H56" t="s">
         <v>591</v>
       </c>
-    </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I56">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>1100</v>
       </c>
@@ -19235,8 +19404,11 @@
       <c r="H57" t="s">
         <v>591</v>
       </c>
-    </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I57">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>1102</v>
       </c>
@@ -19261,8 +19433,11 @@
       <c r="H58" t="s">
         <v>591</v>
       </c>
-    </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I58">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>1104</v>
       </c>
@@ -19287,8 +19462,11 @@
       <c r="H59" t="s">
         <v>591</v>
       </c>
-    </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I59">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>1106</v>
       </c>
@@ -19313,8 +19491,11 @@
       <c r="H60" t="s">
         <v>591</v>
       </c>
-    </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I60">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>1108</v>
       </c>
@@ -19339,8 +19520,11 @@
       <c r="H61" t="s">
         <v>591</v>
       </c>
-    </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I61">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="62" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>1110</v>
       </c>
@@ -19365,8 +19549,11 @@
       <c r="H62" t="s">
         <v>591</v>
       </c>
-    </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I62">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="63" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>24</v>
       </c>
@@ -19391,8 +19578,11 @@
       <c r="H63" t="s">
         <v>559</v>
       </c>
-    </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I63">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="64" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>1112</v>
       </c>
@@ -19417,8 +19607,11 @@
       <c r="H64" t="s">
         <v>591</v>
       </c>
-    </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I64">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="65" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>1114</v>
       </c>
@@ -19443,8 +19636,11 @@
       <c r="H65" t="s">
         <v>591</v>
       </c>
-    </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I65">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="66" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>1116</v>
       </c>
@@ -19469,8 +19665,11 @@
       <c r="H66" t="s">
         <v>591</v>
       </c>
-    </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I66">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="67" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>1118</v>
       </c>
@@ -19495,8 +19694,11 @@
       <c r="H67" t="s">
         <v>591</v>
       </c>
-    </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I67">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="68" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>1120</v>
       </c>
@@ -19521,8 +19723,11 @@
       <c r="H68" t="s">
         <v>591</v>
       </c>
-    </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I68">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="69" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>1122</v>
       </c>
@@ -19547,8 +19752,11 @@
       <c r="H69" t="s">
         <v>591</v>
       </c>
-    </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I69">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="70" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>1124</v>
       </c>
@@ -19573,8 +19781,11 @@
       <c r="H70" t="s">
         <v>1126</v>
       </c>
-    </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I70">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="71" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>1127</v>
       </c>
@@ -19599,8 +19810,11 @@
       <c r="H71" t="s">
         <v>591</v>
       </c>
-    </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I71">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="72" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>1129</v>
       </c>
@@ -19625,8 +19839,11 @@
       <c r="H72" t="s">
         <v>591</v>
       </c>
-    </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I72">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="73" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>1131</v>
       </c>
@@ -19651,8 +19868,11 @@
       <c r="H73" t="s">
         <v>591</v>
       </c>
-    </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I73">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="74" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>1133</v>
       </c>
@@ -19677,8 +19897,11 @@
       <c r="H74" t="s">
         <v>1135</v>
       </c>
-    </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I74">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="75" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>1136</v>
       </c>
@@ -19703,8 +19926,11 @@
       <c r="H75" t="s">
         <v>591</v>
       </c>
-    </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I75">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="76" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>1138</v>
       </c>
@@ -19729,8 +19955,11 @@
       <c r="H76" t="s">
         <v>591</v>
       </c>
-    </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I76">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="77" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>1140</v>
       </c>
@@ -19755,8 +19984,11 @@
       <c r="H77" t="s">
         <v>591</v>
       </c>
-    </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I77">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="78" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>1142</v>
       </c>
@@ -19781,8 +20013,11 @@
       <c r="H78" t="s">
         <v>591</v>
       </c>
-    </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I78">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="79" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>1144</v>
       </c>
@@ -19807,8 +20042,11 @@
       <c r="H79" t="s">
         <v>591</v>
       </c>
-    </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I79">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="80" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>1146</v>
       </c>
@@ -19833,8 +20071,11 @@
       <c r="H80" t="s">
         <v>591</v>
       </c>
-    </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I80">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="81" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>1148</v>
       </c>
@@ -19859,8 +20100,11 @@
       <c r="H81" t="s">
         <v>591</v>
       </c>
-    </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I81">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="82" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>1150</v>
       </c>
@@ -19885,8 +20129,11 @@
       <c r="H82" t="s">
         <v>591</v>
       </c>
-    </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I82">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="83" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>1152</v>
       </c>
@@ -19911,8 +20158,11 @@
       <c r="H83" t="s">
         <v>591</v>
       </c>
-    </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I83">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="84" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>1154</v>
       </c>
@@ -19937,8 +20187,11 @@
       <c r="H84" t="s">
         <v>591</v>
       </c>
-    </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I84">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="85" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>1156</v>
       </c>
@@ -19963,8 +20216,11 @@
       <c r="H85" t="s">
         <v>1076</v>
       </c>
-    </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I85">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="86" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>1158</v>
       </c>
@@ -19989,8 +20245,11 @@
       <c r="H86" t="s">
         <v>591</v>
       </c>
-    </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I86">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="87" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>1160</v>
       </c>
@@ -20015,8 +20274,11 @@
       <c r="H87" t="s">
         <v>591</v>
       </c>
-    </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I87">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="88" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>1162</v>
       </c>
@@ -20041,8 +20303,11 @@
       <c r="H88" t="s">
         <v>591</v>
       </c>
-    </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I88">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="89" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>1164</v>
       </c>
@@ -20067,8 +20332,11 @@
       <c r="H89" t="s">
         <v>591</v>
       </c>
-    </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I89">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="90" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>1166</v>
       </c>
@@ -20093,8 +20361,11 @@
       <c r="H90" t="s">
         <v>591</v>
       </c>
-    </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I90">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="91" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>1168</v>
       </c>
@@ -20119,8 +20390,11 @@
       <c r="H91" t="s">
         <v>591</v>
       </c>
-    </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I91">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="92" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>1170</v>
       </c>
@@ -20145,8 +20419,11 @@
       <c r="H92" t="s">
         <v>591</v>
       </c>
-    </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I92">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="93" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>1172</v>
       </c>
@@ -20171,8 +20448,11 @@
       <c r="H93" t="s">
         <v>591</v>
       </c>
-    </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I93">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="94" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>1174</v>
       </c>
@@ -20197,8 +20477,11 @@
       <c r="H94" t="s">
         <v>591</v>
       </c>
-    </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I94">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="95" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>1176</v>
       </c>
@@ -20223,8 +20506,11 @@
       <c r="H95" t="s">
         <v>591</v>
       </c>
-    </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I95">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="96" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>1178</v>
       </c>
@@ -20249,8 +20535,11 @@
       <c r="H96" t="s">
         <v>591</v>
       </c>
-    </row>
-    <row r="97" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I96">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="97" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>1180</v>
       </c>
@@ -20275,8 +20564,11 @@
       <c r="H97" t="s">
         <v>591</v>
       </c>
-    </row>
-    <row r="98" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I97">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="98" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>1182</v>
       </c>
@@ -20301,8 +20593,11 @@
       <c r="H98" t="s">
         <v>591</v>
       </c>
-    </row>
-    <row r="99" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I98">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="99" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>1184</v>
       </c>
@@ -20327,8 +20622,11 @@
       <c r="H99" t="s">
         <v>591</v>
       </c>
-    </row>
-    <row r="100" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I99">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="100" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>1186</v>
       </c>
@@ -20353,8 +20651,11 @@
       <c r="H100" t="s">
         <v>591</v>
       </c>
-    </row>
-    <row r="101" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I100">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="101" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>1188</v>
       </c>
@@ -20379,8 +20680,11 @@
       <c r="H101" t="s">
         <v>591</v>
       </c>
-    </row>
-    <row r="102" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I101">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="102" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>1190</v>
       </c>
@@ -20404,6 +20708,9 @@
       </c>
       <c r="H102" t="s">
         <v>1126</v>
+      </c>
+      <c r="I102">
+        <v>1000</v>
       </c>
     </row>
   </sheetData>
@@ -20413,16 +20720,17 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J504"/>
+  <dimension ref="A1:K504"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="37.44140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="20.77734375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="16" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="13.5546875" style="4" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="25.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>4</v>
       </c>
@@ -20453,8 +20761,11 @@
       <c r="J1" t="s">
         <v>1195</v>
       </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K1" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>990</v>
       </c>
@@ -20485,8 +20796,11 @@
       <c r="J2" t="s">
         <v>1197</v>
       </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K2">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>992</v>
       </c>
@@ -20517,8 +20831,11 @@
       <c r="J3" t="s">
         <v>1197</v>
       </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K3">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>994</v>
       </c>
@@ -20549,8 +20866,11 @@
       <c r="J4" t="s">
         <v>1197</v>
       </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K4">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>996</v>
       </c>
@@ -20581,8 +20901,11 @@
       <c r="J5" t="s">
         <v>1197</v>
       </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K5">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>1002</v>
       </c>
@@ -20613,8 +20936,11 @@
       <c r="J6" t="s">
         <v>1197</v>
       </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K6">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>1006</v>
       </c>
@@ -20645,8 +20971,11 @@
       <c r="J7" t="s">
         <v>1197</v>
       </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K7">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>1004</v>
       </c>
@@ -20677,8 +21006,11 @@
       <c r="J8" t="s">
         <v>1197</v>
       </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K8">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>1000</v>
       </c>
@@ -20709,8 +21041,11 @@
       <c r="J9" t="s">
         <v>1197</v>
       </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K9">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>998</v>
       </c>
@@ -20741,8 +21076,11 @@
       <c r="J10" t="s">
         <v>1197</v>
       </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K10">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>1198</v>
       </c>
@@ -20773,8 +21111,11 @@
       <c r="J11" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K11">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>1201</v>
       </c>
@@ -20805,8 +21146,11 @@
       <c r="J12" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K12">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>1203</v>
       </c>
@@ -20837,8 +21181,11 @@
       <c r="J13" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K13">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>1205</v>
       </c>
@@ -20869,8 +21216,11 @@
       <c r="J14" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K14">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>1207</v>
       </c>
@@ -20901,8 +21251,11 @@
       <c r="J15" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K15">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>1209</v>
       </c>
@@ -20933,8 +21286,11 @@
       <c r="J16" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K16">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>1211</v>
       </c>
@@ -20965,8 +21321,11 @@
       <c r="J17" t="s">
         <v>1197</v>
       </c>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K17">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>1213</v>
       </c>
@@ -20997,8 +21356,11 @@
       <c r="J18" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K18">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>1008</v>
       </c>
@@ -21029,8 +21391,11 @@
       <c r="J19" t="s">
         <v>1197</v>
       </c>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K19">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>1215</v>
       </c>
@@ -21061,8 +21426,11 @@
       <c r="J20" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K20">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>1010</v>
       </c>
@@ -21093,8 +21461,11 @@
       <c r="J21" t="s">
         <v>1197</v>
       </c>
-    </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K21">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>1012</v>
       </c>
@@ -21125,8 +21496,11 @@
       <c r="J22" t="s">
         <v>1197</v>
       </c>
-    </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K22">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>1217</v>
       </c>
@@ -21157,8 +21531,11 @@
       <c r="J23" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K23">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>1014</v>
       </c>
@@ -21189,8 +21566,11 @@
       <c r="J24" t="s">
         <v>1197</v>
       </c>
-    </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K24">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>1219</v>
       </c>
@@ -21221,8 +21601,11 @@
       <c r="J25" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K25">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>1221</v>
       </c>
@@ -21253,8 +21636,11 @@
       <c r="J26" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K26">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>1223</v>
       </c>
@@ -21285,8 +21671,11 @@
       <c r="J27" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K27">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>1225</v>
       </c>
@@ -21317,8 +21706,11 @@
       <c r="J28" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K28">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>1016</v>
       </c>
@@ -21349,8 +21741,11 @@
       <c r="J29" t="s">
         <v>1197</v>
       </c>
-    </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K29">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>1018</v>
       </c>
@@ -21381,8 +21776,11 @@
       <c r="J30" t="s">
         <v>1197</v>
       </c>
-    </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K30">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>1227</v>
       </c>
@@ -21413,8 +21811,11 @@
       <c r="J31" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K31">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>1229</v>
       </c>
@@ -21445,8 +21846,11 @@
       <c r="J32" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K32">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>1231</v>
       </c>
@@ -21477,8 +21881,11 @@
       <c r="J33" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K33">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>1233</v>
       </c>
@@ -21509,8 +21916,11 @@
       <c r="J34" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K34">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>1235</v>
       </c>
@@ -21541,8 +21951,11 @@
       <c r="J35" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K35">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>1237</v>
       </c>
@@ -21573,8 +21986,11 @@
       <c r="J36" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K36">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>1239</v>
       </c>
@@ -21605,8 +22021,11 @@
       <c r="J37" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K37">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>1241</v>
       </c>
@@ -21637,8 +22056,11 @@
       <c r="J38" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K38">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>1243</v>
       </c>
@@ -21669,8 +22091,11 @@
       <c r="J39" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K39">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>1245</v>
       </c>
@@ -21701,8 +22126,11 @@
       <c r="J40" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K40">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>1247</v>
       </c>
@@ -21733,8 +22161,11 @@
       <c r="J41" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K41">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>1022</v>
       </c>
@@ -21765,8 +22196,11 @@
       <c r="J42" t="s">
         <v>1197</v>
       </c>
-    </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K42">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>1249</v>
       </c>
@@ -21797,8 +22231,11 @@
       <c r="J43" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K43">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>1251</v>
       </c>
@@ -21829,8 +22266,11 @@
       <c r="J44" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K44">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>1253</v>
       </c>
@@ -21861,8 +22301,11 @@
       <c r="J45" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K45">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="46" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>1255</v>
       </c>
@@ -21893,8 +22336,11 @@
       <c r="J46" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K46">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>1257</v>
       </c>
@@ -21925,8 +22371,11 @@
       <c r="J47" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K47">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>1026</v>
       </c>
@@ -21957,8 +22406,11 @@
       <c r="J48" t="s">
         <v>1197</v>
       </c>
-    </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K48">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="49" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>1028</v>
       </c>
@@ -21989,8 +22441,11 @@
       <c r="J49" t="s">
         <v>1197</v>
       </c>
-    </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K49">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="50" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>1259</v>
       </c>
@@ -22021,8 +22476,11 @@
       <c r="J50" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K50">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="51" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>1261</v>
       </c>
@@ -22053,8 +22511,11 @@
       <c r="J51" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K51">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="52" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>1030</v>
       </c>
@@ -22085,8 +22546,11 @@
       <c r="J52" t="s">
         <v>1197</v>
       </c>
-    </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K52">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="53" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>1032</v>
       </c>
@@ -22117,8 +22581,11 @@
       <c r="J53" t="s">
         <v>1197</v>
       </c>
-    </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K53">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="54" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>1024</v>
       </c>
@@ -22149,8 +22616,11 @@
       <c r="J54" t="s">
         <v>1197</v>
       </c>
-    </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K54">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="55" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>1034</v>
       </c>
@@ -22181,8 +22651,11 @@
       <c r="J55" t="s">
         <v>1197</v>
       </c>
-    </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K55">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="56" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>1036</v>
       </c>
@@ -22213,8 +22686,11 @@
       <c r="J56" t="s">
         <v>1197</v>
       </c>
-    </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K56">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="57" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>1263</v>
       </c>
@@ -22245,8 +22721,11 @@
       <c r="J57" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K57">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="58" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>1038</v>
       </c>
@@ -22277,8 +22756,11 @@
       <c r="J58" t="s">
         <v>1197</v>
       </c>
-    </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K58">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="59" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>1040</v>
       </c>
@@ -22309,8 +22791,11 @@
       <c r="J59" t="s">
         <v>1197</v>
       </c>
-    </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K59">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="60" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>1265</v>
       </c>
@@ -22341,8 +22826,11 @@
       <c r="J60" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K60">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="61" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>631</v>
       </c>
@@ -22373,8 +22861,11 @@
       <c r="J61" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K61">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="62" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>1268</v>
       </c>
@@ -22405,8 +22896,11 @@
       <c r="J62" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K62">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="63" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>1270</v>
       </c>
@@ -22437,8 +22931,11 @@
       <c r="J63" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K63">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="64" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>1272</v>
       </c>
@@ -22469,8 +22966,11 @@
       <c r="J64" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="65" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K64">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="65" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>1274</v>
       </c>
@@ -22501,8 +23001,11 @@
       <c r="J65" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="66" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K65">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="66" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>1276</v>
       </c>
@@ -22533,8 +23036,11 @@
       <c r="J66" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="67" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K66">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="67" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>1044</v>
       </c>
@@ -22565,8 +23071,11 @@
       <c r="J67" t="s">
         <v>1197</v>
       </c>
-    </row>
-    <row r="68" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K67">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="68" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>1278</v>
       </c>
@@ -22597,8 +23106,11 @@
       <c r="J68" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="69" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K68">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="69" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>1280</v>
       </c>
@@ -22629,8 +23141,11 @@
       <c r="J69" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="70" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K69">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="70" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>1282</v>
       </c>
@@ -22661,8 +23176,11 @@
       <c r="J70" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="71" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K70">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="71" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>1042</v>
       </c>
@@ -22693,8 +23211,11 @@
       <c r="J71" t="s">
         <v>1197</v>
       </c>
-    </row>
-    <row r="72" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K71">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="72" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>1046</v>
       </c>
@@ -22725,8 +23246,11 @@
       <c r="J72" t="s">
         <v>1197</v>
       </c>
-    </row>
-    <row r="73" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K72">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="73" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>1284</v>
       </c>
@@ -22757,8 +23281,11 @@
       <c r="J73" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="74" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K73">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="74" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>1286</v>
       </c>
@@ -22789,8 +23316,11 @@
       <c r="J74" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="75" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K74">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="75" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>1288</v>
       </c>
@@ -22821,8 +23351,11 @@
       <c r="J75" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="76" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K75">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="76" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>1048</v>
       </c>
@@ -22853,8 +23386,11 @@
       <c r="J76" t="s">
         <v>1197</v>
       </c>
-    </row>
-    <row r="77" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K76">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="77" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>1050</v>
       </c>
@@ -22885,8 +23421,11 @@
       <c r="J77" t="s">
         <v>1197</v>
       </c>
-    </row>
-    <row r="78" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K77">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="78" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>1290</v>
       </c>
@@ -22917,8 +23456,11 @@
       <c r="J78" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="79" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K78">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="79" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>1292</v>
       </c>
@@ -22949,8 +23491,11 @@
       <c r="J79" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="80" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K79">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="80" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>1294</v>
       </c>
@@ -22981,8 +23526,11 @@
       <c r="J80" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="81" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K80">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="81" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>1296</v>
       </c>
@@ -23013,8 +23561,11 @@
       <c r="J81" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="82" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K81">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="82" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>1298</v>
       </c>
@@ -23045,8 +23596,11 @@
       <c r="J82" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="83" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K82">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="83" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>1052</v>
       </c>
@@ -23077,8 +23631,11 @@
       <c r="J83" t="s">
         <v>1197</v>
       </c>
-    </row>
-    <row r="84" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K83">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="84" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>1300</v>
       </c>
@@ -23109,8 +23666,11 @@
       <c r="J84" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="85" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K84">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="85" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>1302</v>
       </c>
@@ -23141,8 +23701,11 @@
       <c r="J85" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="86" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K85">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="86" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>1304</v>
       </c>
@@ -23173,8 +23736,11 @@
       <c r="J86" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="87" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K86">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="87" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>1054</v>
       </c>
@@ -23205,8 +23771,11 @@
       <c r="J87" t="s">
         <v>1197</v>
       </c>
-    </row>
-    <row r="88" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K87">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="88" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>1056</v>
       </c>
@@ -23237,8 +23806,11 @@
       <c r="J88" t="s">
         <v>1197</v>
       </c>
-    </row>
-    <row r="89" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K88">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="89" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>1306</v>
       </c>
@@ -23269,8 +23841,11 @@
       <c r="J89" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="90" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K89">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="90" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>1308</v>
       </c>
@@ -23301,8 +23876,11 @@
       <c r="J90" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="91" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K90">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="91" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>1310</v>
       </c>
@@ -23333,8 +23911,11 @@
       <c r="J91" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="92" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K91">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="92" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>1058</v>
       </c>
@@ -23365,8 +23946,11 @@
       <c r="J92" t="s">
         <v>1197</v>
       </c>
-    </row>
-    <row r="93" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K92">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="93" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>1312</v>
       </c>
@@ -23397,8 +23981,11 @@
       <c r="J93" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="94" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K93">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="94" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>1314</v>
       </c>
@@ -23429,8 +24016,11 @@
       <c r="J94" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="95" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K94">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="95" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>1060</v>
       </c>
@@ -23461,8 +24051,11 @@
       <c r="J95" t="s">
         <v>1197</v>
       </c>
-    </row>
-    <row r="96" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K95">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="96" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>1316</v>
       </c>
@@ -23493,8 +24086,11 @@
       <c r="J96" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="97" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K96">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="97" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>1318</v>
       </c>
@@ -23525,8 +24121,11 @@
       <c r="J97" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="98" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K97">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="98" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>1320</v>
       </c>
@@ -23557,8 +24156,11 @@
       <c r="J98" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="99" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K98">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="99" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>1322</v>
       </c>
@@ -23589,8 +24191,11 @@
       <c r="J99" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="100" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K99">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="100" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>1062</v>
       </c>
@@ -23621,8 +24226,11 @@
       <c r="J100" t="s">
         <v>1197</v>
       </c>
-    </row>
-    <row r="101" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K100">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="101" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>1324</v>
       </c>
@@ -23653,8 +24261,11 @@
       <c r="J101" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="102" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K101">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="102" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>1326</v>
       </c>
@@ -23685,8 +24296,11 @@
       <c r="J102" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="103" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K102">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="103" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>1064</v>
       </c>
@@ -23717,8 +24331,11 @@
       <c r="J103" t="s">
         <v>1197</v>
       </c>
-    </row>
-    <row r="104" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K103">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="104" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>1066</v>
       </c>
@@ -23749,8 +24366,11 @@
       <c r="J104" t="s">
         <v>1197</v>
       </c>
-    </row>
-    <row r="105" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K104">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="105" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>1328</v>
       </c>
@@ -23781,8 +24401,11 @@
       <c r="J105" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="106" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K105">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="106" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>1330</v>
       </c>
@@ -23813,8 +24436,11 @@
       <c r="J106" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="107" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K106">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="107" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>1332</v>
       </c>
@@ -23845,8 +24471,11 @@
       <c r="J107" t="s">
         <v>1197</v>
       </c>
-    </row>
-    <row r="108" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K107">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="108" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>1334</v>
       </c>
@@ -23877,8 +24506,11 @@
       <c r="J108" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="109" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K108">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="109" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>1070</v>
       </c>
@@ -23909,8 +24541,11 @@
       <c r="J109" t="s">
         <v>1197</v>
       </c>
-    </row>
-    <row r="110" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K109">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="110" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>1336</v>
       </c>
@@ -23941,8 +24576,11 @@
       <c r="J110" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="111" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K110">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="111" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>1020</v>
       </c>
@@ -23973,8 +24611,11 @@
       <c r="J111" t="s">
         <v>1197</v>
       </c>
-    </row>
-    <row r="112" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K111">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="112" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>1338</v>
       </c>
@@ -24005,8 +24646,11 @@
       <c r="J112" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="113" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K112">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="113" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
         <v>1340</v>
       </c>
@@ -24037,8 +24681,11 @@
       <c r="J113" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="114" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K113">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="114" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
         <v>1342</v>
       </c>
@@ -24069,8 +24716,11 @@
       <c r="J114" t="s">
         <v>1197</v>
       </c>
-    </row>
-    <row r="115" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K114">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="115" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
         <v>1344</v>
       </c>
@@ -24101,8 +24751,11 @@
       <c r="J115" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="116" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K115">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="116" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
         <v>1346</v>
       </c>
@@ -24133,8 +24786,11 @@
       <c r="J116" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="117" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K116">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="117" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
         <v>1348</v>
       </c>
@@ -24165,8 +24821,11 @@
       <c r="J117" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="118" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K117">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="118" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
         <v>1077</v>
       </c>
@@ -24197,8 +24856,11 @@
       <c r="J118" t="s">
         <v>1197</v>
       </c>
-    </row>
-    <row r="119" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K118">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="119" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
         <v>1072</v>
       </c>
@@ -24229,8 +24891,11 @@
       <c r="J119" t="s">
         <v>1197</v>
       </c>
-    </row>
-    <row r="120" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K119">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="120" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
         <v>1350</v>
       </c>
@@ -24261,8 +24926,11 @@
       <c r="J120" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="121" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K120">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="121" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
         <v>1079</v>
       </c>
@@ -24293,8 +24961,11 @@
       <c r="J121" t="s">
         <v>1197</v>
       </c>
-    </row>
-    <row r="122" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K121">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="122" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
         <v>1352</v>
       </c>
@@ -24325,8 +24996,11 @@
       <c r="J122" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="123" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K122">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="123" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
         <v>1354</v>
       </c>
@@ -24357,8 +25031,11 @@
       <c r="J123" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="124" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K123">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="124" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
         <v>1356</v>
       </c>
@@ -24389,8 +25066,11 @@
       <c r="J124" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="125" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K124">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="125" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
         <v>1358</v>
       </c>
@@ -24421,8 +25101,11 @@
       <c r="J125" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="126" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K125">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="126" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
         <v>1360</v>
       </c>
@@ -24453,8 +25136,11 @@
       <c r="J126" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="127" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K126">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="127" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
         <v>1362</v>
       </c>
@@ -24485,8 +25171,11 @@
       <c r="J127" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="128" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K127">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="128" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
         <v>1364</v>
       </c>
@@ -24517,8 +25206,11 @@
       <c r="J128" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="129" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K128">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="129" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
         <v>1366</v>
       </c>
@@ -24549,8 +25241,11 @@
       <c r="J129" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="130" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K129">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="130" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
         <v>1368</v>
       </c>
@@ -24581,8 +25276,11 @@
       <c r="J130" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="131" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K130">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="131" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
         <v>1370</v>
       </c>
@@ -24613,8 +25311,11 @@
       <c r="J131" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="132" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K131">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="132" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
         <v>1083</v>
       </c>
@@ -24645,8 +25346,11 @@
       <c r="J132" t="s">
         <v>1197</v>
       </c>
-    </row>
-    <row r="133" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K132">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="133" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
         <v>1085</v>
       </c>
@@ -24677,8 +25381,11 @@
       <c r="J133" t="s">
         <v>1197</v>
       </c>
-    </row>
-    <row r="134" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K133">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="134" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
         <v>1372</v>
       </c>
@@ -24709,8 +25416,11 @@
       <c r="J134" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="135" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K134">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="135" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
         <v>1374</v>
       </c>
@@ -24741,8 +25451,11 @@
       <c r="J135" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="136" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K135">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="136" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
         <v>1376</v>
       </c>
@@ -24773,8 +25486,11 @@
       <c r="J136" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="137" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K136">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="137" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
         <v>1378</v>
       </c>
@@ -24805,8 +25521,11 @@
       <c r="J137" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="138" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K137">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="138" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
         <v>1380</v>
       </c>
@@ -24837,8 +25556,11 @@
       <c r="J138" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="139" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K138">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="139" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
         <v>1382</v>
       </c>
@@ -24869,8 +25591,11 @@
       <c r="J139" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="140" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K139">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="140" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
         <v>1384</v>
       </c>
@@ -24901,8 +25626,11 @@
       <c r="J140" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="141" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K140">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="141" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
         <v>1386</v>
       </c>
@@ -24933,8 +25661,11 @@
       <c r="J141" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="142" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K141">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="142" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
         <v>1388</v>
       </c>
@@ -24965,8 +25696,11 @@
       <c r="J142" t="s">
         <v>1197</v>
       </c>
-    </row>
-    <row r="143" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K142">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="143" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
         <v>1390</v>
       </c>
@@ -24997,8 +25731,11 @@
       <c r="J143" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="144" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K143">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="144" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
         <v>1392</v>
       </c>
@@ -25029,8 +25766,11 @@
       <c r="J144" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="145" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K144">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="145" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
         <v>1394</v>
       </c>
@@ -25061,8 +25801,11 @@
       <c r="J145" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="146" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K145">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="146" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
         <v>1396</v>
       </c>
@@ -25093,8 +25836,11 @@
       <c r="J146" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="147" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K146">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="147" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
         <v>1398</v>
       </c>
@@ -25125,8 +25871,11 @@
       <c r="J147" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="148" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K147">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="148" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
         <v>1400</v>
       </c>
@@ -25157,8 +25906,11 @@
       <c r="J148" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="149" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K148">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="149" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
         <v>1402</v>
       </c>
@@ -25189,8 +25941,11 @@
       <c r="J149" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="150" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K149">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="150" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
         <v>1404</v>
       </c>
@@ -25221,8 +25976,11 @@
       <c r="J150" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="151" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K150">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="151" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
         <v>1096</v>
       </c>
@@ -25253,8 +26011,11 @@
       <c r="J151" t="s">
         <v>1197</v>
       </c>
-    </row>
-    <row r="152" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K151">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="152" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
         <v>1098</v>
       </c>
@@ -25285,8 +26046,11 @@
       <c r="J152" t="s">
         <v>1197</v>
       </c>
-    </row>
-    <row r="153" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K152">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="153" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
         <v>1081</v>
       </c>
@@ -25317,8 +26081,11 @@
       <c r="J153" t="s">
         <v>1197</v>
       </c>
-    </row>
-    <row r="154" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K153">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="154" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
         <v>1406</v>
       </c>
@@ -25349,8 +26116,11 @@
       <c r="J154" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="155" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K154">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="155" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
         <v>1408</v>
       </c>
@@ -25381,8 +26151,11 @@
       <c r="J155" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="156" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K155">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="156" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
         <v>1410</v>
       </c>
@@ -25413,8 +26186,11 @@
       <c r="J156" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="157" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K156">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="157" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
         <v>1412</v>
       </c>
@@ -25445,8 +26221,11 @@
       <c r="J157" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="158" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K157">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="158" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
         <v>1100</v>
       </c>
@@ -25477,8 +26256,11 @@
       <c r="J158" t="s">
         <v>1197</v>
       </c>
-    </row>
-    <row r="159" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K158">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="159" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
         <v>1414</v>
       </c>
@@ -25509,8 +26291,11 @@
       <c r="J159" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="160" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K159">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="160" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
         <v>1416</v>
       </c>
@@ -25541,8 +26326,11 @@
       <c r="J160" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="161" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K160">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="161" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
         <v>1418</v>
       </c>
@@ -25573,8 +26361,11 @@
       <c r="J161" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="162" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K161">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="162" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
         <v>1420</v>
       </c>
@@ -25605,8 +26396,11 @@
       <c r="J162" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="163" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K162">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="163" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
         <v>1090</v>
       </c>
@@ -25637,8 +26431,11 @@
       <c r="J163" t="s">
         <v>1197</v>
       </c>
-    </row>
-    <row r="164" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K163">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="164" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
         <v>1422</v>
       </c>
@@ -25669,8 +26466,11 @@
       <c r="J164" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="165" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K164">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="165" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
         <v>1424</v>
       </c>
@@ -25701,8 +26501,11 @@
       <c r="J165" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="166" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K165">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="166" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
         <v>1426</v>
       </c>
@@ -25733,8 +26536,11 @@
       <c r="J166" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="167" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K166">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="167" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
         <v>1428</v>
       </c>
@@ -25765,8 +26571,11 @@
       <c r="J167" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="168" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K167">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="168" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
         <v>1430</v>
       </c>
@@ -25797,8 +26606,11 @@
       <c r="J168" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="169" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K168">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="169" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
         <v>1432</v>
       </c>
@@ -25829,8 +26641,11 @@
       <c r="J169" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="170" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K169">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="170" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
         <v>1102</v>
       </c>
@@ -25861,8 +26676,11 @@
       <c r="J170" t="s">
         <v>1197</v>
       </c>
-    </row>
-    <row r="171" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K170">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="171" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
         <v>1434</v>
       </c>
@@ -25893,8 +26711,11 @@
       <c r="J171" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="172" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K171">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="172" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
         <v>1108</v>
       </c>
@@ -25925,8 +26746,11 @@
       <c r="J172" t="s">
         <v>1197</v>
       </c>
-    </row>
-    <row r="173" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K172">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="173" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
         <v>1104</v>
       </c>
@@ -25957,8 +26781,11 @@
       <c r="J173" t="s">
         <v>1197</v>
       </c>
-    </row>
-    <row r="174" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K173">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="174" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
         <v>1436</v>
       </c>
@@ -25989,8 +26816,11 @@
       <c r="J174" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="175" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K174">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="175" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
         <v>1106</v>
       </c>
@@ -26021,8 +26851,11 @@
       <c r="J175" t="s">
         <v>1197</v>
       </c>
-    </row>
-    <row r="176" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K175">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="176" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
         <v>1438</v>
       </c>
@@ -26053,8 +26886,11 @@
       <c r="J176" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="177" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K176">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="177" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
         <v>1112</v>
       </c>
@@ -26085,8 +26921,11 @@
       <c r="J177" t="s">
         <v>1197</v>
       </c>
-    </row>
-    <row r="178" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K177">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="178" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
         <v>1114</v>
       </c>
@@ -26117,8 +26956,11 @@
       <c r="J178" t="s">
         <v>1197</v>
       </c>
-    </row>
-    <row r="179" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K178">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="179" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
         <v>1116</v>
       </c>
@@ -26149,8 +26991,11 @@
       <c r="J179" t="s">
         <v>1197</v>
       </c>
-    </row>
-    <row r="180" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K179">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="180" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
         <v>1440</v>
       </c>
@@ -26181,8 +27026,11 @@
       <c r="J180" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="181" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K180">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="181" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
         <v>1442</v>
       </c>
@@ -26213,8 +27061,11 @@
       <c r="J181" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="182" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K181">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="182" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
         <v>1444</v>
       </c>
@@ -26245,8 +27096,11 @@
       <c r="J182" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="183" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K182">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="183" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
         <v>1446</v>
       </c>
@@ -26277,8 +27131,11 @@
       <c r="J183" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="184" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K183">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="184" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
         <v>1448</v>
       </c>
@@ -26309,8 +27166,11 @@
       <c r="J184" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="185" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K184">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="185" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
         <v>1118</v>
       </c>
@@ -26341,8 +27201,11 @@
       <c r="J185" t="s">
         <v>1197</v>
       </c>
-    </row>
-    <row r="186" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K185">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="186" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
         <v>1120</v>
       </c>
@@ -26373,8 +27236,11 @@
       <c r="J186" t="s">
         <v>1197</v>
       </c>
-    </row>
-    <row r="187" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K186">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="187" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
         <v>1450</v>
       </c>
@@ -26405,8 +27271,11 @@
       <c r="J187" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="188" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K187">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="188" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
         <v>1452</v>
       </c>
@@ -26437,8 +27306,11 @@
       <c r="J188" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="189" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K188">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="189" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
         <v>1092</v>
       </c>
@@ -26469,8 +27341,11 @@
       <c r="J189" t="s">
         <v>1197</v>
       </c>
-    </row>
-    <row r="190" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K189">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="190" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A190" t="s">
         <v>1454</v>
       </c>
@@ -26501,8 +27376,11 @@
       <c r="J190" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="191" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K190">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="191" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
         <v>1122</v>
       </c>
@@ -26533,8 +27411,11 @@
       <c r="J191" t="s">
         <v>1197</v>
       </c>
-    </row>
-    <row r="192" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K191">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="192" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A192" t="s">
         <v>1456</v>
       </c>
@@ -26565,8 +27446,11 @@
       <c r="J192" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="193" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K192">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="193" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
         <v>1458</v>
       </c>
@@ -26597,8 +27481,11 @@
       <c r="J193" t="s">
         <v>1197</v>
       </c>
-    </row>
-    <row r="194" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K193">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="194" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
         <v>1460</v>
       </c>
@@ -26629,8 +27516,11 @@
       <c r="J194" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="195" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K194">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="195" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
         <v>1462</v>
       </c>
@@ -26661,8 +27551,11 @@
       <c r="J195" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="196" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K195">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="196" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
         <v>1464</v>
       </c>
@@ -26693,8 +27586,11 @@
       <c r="J196" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="197" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K196">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="197" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
         <v>1466</v>
       </c>
@@ -26725,8 +27621,11 @@
       <c r="J197" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="198" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K197">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="198" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
         <v>1468</v>
       </c>
@@ -26757,8 +27656,11 @@
       <c r="J198" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="199" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K198">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="199" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
         <v>1110</v>
       </c>
@@ -26789,8 +27691,11 @@
       <c r="J199" t="s">
         <v>1197</v>
       </c>
-    </row>
-    <row r="200" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K199">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="200" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
         <v>1470</v>
       </c>
@@ -26821,8 +27726,11 @@
       <c r="J200" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="201" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K200">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="201" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
         <v>1472</v>
       </c>
@@ -26853,8 +27761,11 @@
       <c r="J201" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="202" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K201">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="202" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
         <v>1474</v>
       </c>
@@ -26885,8 +27796,11 @@
       <c r="J202" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="203" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K202">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="203" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A203" t="s">
         <v>1476</v>
       </c>
@@ -26917,8 +27831,11 @@
       <c r="J203" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="204" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K203">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="204" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A204" t="s">
         <v>1478</v>
       </c>
@@ -26949,8 +27866,11 @@
       <c r="J204" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="205" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K204">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="205" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A205" t="s">
         <v>1480</v>
       </c>
@@ -26981,8 +27901,11 @@
       <c r="J205" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="206" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K205">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="206" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
         <v>1482</v>
       </c>
@@ -27013,8 +27936,11 @@
       <c r="J206" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="207" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K206">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="207" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A207" t="s">
         <v>1484</v>
       </c>
@@ -27045,8 +27971,11 @@
       <c r="J207" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="208" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K207">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="208" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A208" t="s">
         <v>1486</v>
       </c>
@@ -27077,8 +28006,11 @@
       <c r="J208" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="209" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K208">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="209" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A209" t="s">
         <v>1131</v>
       </c>
@@ -27109,8 +28041,11 @@
       <c r="J209" t="s">
         <v>1197</v>
       </c>
-    </row>
-    <row r="210" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K209">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="210" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A210" t="s">
         <v>1488</v>
       </c>
@@ -27141,8 +28076,11 @@
       <c r="J210" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="211" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K210">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="211" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A211" t="s">
         <v>1490</v>
       </c>
@@ -27173,8 +28111,11 @@
       <c r="J211" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="212" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K211">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="212" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A212" t="s">
         <v>1140</v>
       </c>
@@ -27205,8 +28146,11 @@
       <c r="J212" t="s">
         <v>1197</v>
       </c>
-    </row>
-    <row r="213" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K212">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="213" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A213" t="s">
         <v>1136</v>
       </c>
@@ -27237,8 +28181,11 @@
       <c r="J213" t="s">
         <v>1197</v>
       </c>
-    </row>
-    <row r="214" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K213">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="214" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A214" t="s">
         <v>1492</v>
       </c>
@@ -27269,8 +28216,11 @@
       <c r="J214" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="215" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K214">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="215" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A215" t="s">
         <v>1494</v>
       </c>
@@ -27301,8 +28251,11 @@
       <c r="J215" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="216" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K215">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="216" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A216" t="s">
         <v>1142</v>
       </c>
@@ -27333,8 +28286,11 @@
       <c r="J216" t="s">
         <v>1197</v>
       </c>
-    </row>
-    <row r="217" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K216">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="217" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A217" t="s">
         <v>1129</v>
       </c>
@@ -27365,8 +28321,11 @@
       <c r="J217" t="s">
         <v>1197</v>
       </c>
-    </row>
-    <row r="218" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K217">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="218" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A218" t="s">
         <v>1496</v>
       </c>
@@ -27397,8 +28356,11 @@
       <c r="J218" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="219" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K218">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="219" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A219" t="s">
         <v>1498</v>
       </c>
@@ -27429,8 +28391,11 @@
       <c r="J219" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="220" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K219">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="220" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A220" t="s">
         <v>1500</v>
       </c>
@@ -27461,8 +28426,11 @@
       <c r="J220" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="221" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K220">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="221" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A221" t="s">
         <v>1144</v>
       </c>
@@ -27493,8 +28461,11 @@
       <c r="J221" t="s">
         <v>1197</v>
       </c>
-    </row>
-    <row r="222" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K221">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="222" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A222" t="s">
         <v>1502</v>
       </c>
@@ -27525,8 +28496,11 @@
       <c r="J222" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="223" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K222">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="223" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A223" t="s">
         <v>1146</v>
       </c>
@@ -27557,8 +28531,11 @@
       <c r="J223" t="s">
         <v>1197</v>
       </c>
-    </row>
-    <row r="224" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K223">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="224" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A224" t="s">
         <v>1504</v>
       </c>
@@ -27589,8 +28566,11 @@
       <c r="J224" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="225" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K224">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="225" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A225" t="s">
         <v>1506</v>
       </c>
@@ -27621,8 +28601,11 @@
       <c r="J225" t="s">
         <v>1197</v>
       </c>
-    </row>
-    <row r="226" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K225">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="226" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A226" t="s">
         <v>1508</v>
       </c>
@@ -27653,8 +28636,11 @@
       <c r="J226" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="227" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K226">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="227" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A227" t="s">
         <v>1148</v>
       </c>
@@ -27685,8 +28671,11 @@
       <c r="J227" t="s">
         <v>1197</v>
       </c>
-    </row>
-    <row r="228" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K227">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="228" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A228" t="s">
         <v>1138</v>
       </c>
@@ -27717,8 +28706,11 @@
       <c r="J228" t="s">
         <v>1197</v>
       </c>
-    </row>
-    <row r="229" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K228">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="229" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A229" t="s">
         <v>1510</v>
       </c>
@@ -27749,8 +28741,11 @@
       <c r="J229" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="230" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K229">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="230" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A230" t="s">
         <v>1150</v>
       </c>
@@ -27781,8 +28776,11 @@
       <c r="J230" t="s">
         <v>1197</v>
       </c>
-    </row>
-    <row r="231" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K230">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="231" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A231" t="s">
         <v>1152</v>
       </c>
@@ -27813,8 +28811,11 @@
       <c r="J231" t="s">
         <v>1197</v>
       </c>
-    </row>
-    <row r="232" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K231">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="232" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A232" t="s">
         <v>1512</v>
       </c>
@@ -27845,8 +28846,11 @@
       <c r="J232" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="233" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K232">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="233" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A233" t="s">
         <v>1514</v>
       </c>
@@ -27877,8 +28881,11 @@
       <c r="J233" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="234" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K233">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="234" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A234" t="s">
         <v>1516</v>
       </c>
@@ -27909,8 +28916,11 @@
       <c r="J234" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="235" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K234">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="235" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A235" t="s">
         <v>1518</v>
       </c>
@@ -27941,8 +28951,11 @@
       <c r="J235" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="236" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K235">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="236" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A236" t="s">
         <v>1520</v>
       </c>
@@ -27973,8 +28986,11 @@
       <c r="J236" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="237" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K236">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="237" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A237" t="s">
         <v>1522</v>
       </c>
@@ -28005,8 +29021,11 @@
       <c r="J237" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="238" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K237">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="238" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A238" t="s">
         <v>1160</v>
       </c>
@@ -28037,8 +29056,11 @@
       <c r="J238" t="s">
         <v>1197</v>
       </c>
-    </row>
-    <row r="239" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K238">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="239" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A239" t="s">
         <v>1524</v>
       </c>
@@ -28069,8 +29091,11 @@
       <c r="J239" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="240" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K239">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="240" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A240" t="s">
         <v>1526</v>
       </c>
@@ -28101,8 +29126,11 @@
       <c r="J240" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="241" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K240">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="241" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A241" t="s">
         <v>1528</v>
       </c>
@@ -28133,8 +29161,11 @@
       <c r="J241" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="242" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K241">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="242" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A242" t="s">
         <v>1530</v>
       </c>
@@ -28165,8 +29196,11 @@
       <c r="J242" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="243" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K242">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="243" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A243" t="s">
         <v>1532</v>
       </c>
@@ -28197,8 +29231,11 @@
       <c r="J243" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="244" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K243">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="244" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A244" t="s">
         <v>1534</v>
       </c>
@@ -28229,8 +29266,11 @@
       <c r="J244" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="245" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K244">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="245" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A245" t="s">
         <v>1536</v>
       </c>
@@ -28261,8 +29301,11 @@
       <c r="J245" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="246" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K245">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="246" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A246" t="s">
         <v>1538</v>
       </c>
@@ -28293,8 +29336,11 @@
       <c r="J246" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="247" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K246">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="247" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A247" t="s">
         <v>1540</v>
       </c>
@@ -28325,8 +29371,11 @@
       <c r="J247" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="248" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K247">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="248" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A248" t="s">
         <v>1542</v>
       </c>
@@ -28357,8 +29406,11 @@
       <c r="J248" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="249" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K248">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="249" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A249" t="s">
         <v>1544</v>
       </c>
@@ -28389,8 +29441,11 @@
       <c r="J249" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="250" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K249">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="250" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A250" t="s">
         <v>1546</v>
       </c>
@@ -28421,8 +29476,11 @@
       <c r="J250" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="251" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K250">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="251" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A251" t="s">
         <v>1548</v>
       </c>
@@ -28453,8 +29511,11 @@
       <c r="J251" t="s">
         <v>1197</v>
       </c>
-    </row>
-    <row r="252" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K251">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="252" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A252" t="s">
         <v>1550</v>
       </c>
@@ -28485,8 +29546,11 @@
       <c r="J252" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="253" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K252">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="253" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A253" t="s">
         <v>1164</v>
       </c>
@@ -28517,8 +29581,11 @@
       <c r="J253" t="s">
         <v>1197</v>
       </c>
-    </row>
-    <row r="254" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K253">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="254" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A254" t="s">
         <v>1166</v>
       </c>
@@ -28549,8 +29616,11 @@
       <c r="J254" t="s">
         <v>1197</v>
       </c>
-    </row>
-    <row r="255" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K254">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="255" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A255" t="s">
         <v>1552</v>
       </c>
@@ -28581,8 +29651,11 @@
       <c r="J255" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="256" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K255">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="256" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A256" t="s">
         <v>1554</v>
       </c>
@@ -28613,8 +29686,11 @@
       <c r="J256" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="257" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K256">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="257" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A257" t="s">
         <v>1556</v>
       </c>
@@ -28645,8 +29721,11 @@
       <c r="J257" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="258" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K257">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="258" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A258" t="s">
         <v>1162</v>
       </c>
@@ -28677,8 +29756,11 @@
       <c r="J258" t="s">
         <v>1197</v>
       </c>
-    </row>
-    <row r="259" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K258">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="259" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A259" t="s">
         <v>1558</v>
       </c>
@@ -28709,8 +29791,11 @@
       <c r="J259" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="260" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K259">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="260" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A260" t="s">
         <v>1560</v>
       </c>
@@ -28741,8 +29826,11 @@
       <c r="J260" t="s">
         <v>1197</v>
       </c>
-    </row>
-    <row r="261" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K260">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="261" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A261" t="s">
         <v>1562</v>
       </c>
@@ -28773,8 +29861,11 @@
       <c r="J261" t="s">
         <v>1197</v>
       </c>
-    </row>
-    <row r="262" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K261">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="262" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A262" t="s">
         <v>1564</v>
       </c>
@@ -28805,8 +29896,11 @@
       <c r="J262" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="263" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K262">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="263" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A263" t="s">
         <v>1566</v>
       </c>
@@ -28837,8 +29931,11 @@
       <c r="J263" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="264" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K263">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="264" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A264" t="s">
         <v>1568</v>
       </c>
@@ -28869,8 +29966,11 @@
       <c r="J264" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="265" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K264">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="265" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A265" t="s">
         <v>1570</v>
       </c>
@@ -28901,8 +30001,11 @@
       <c r="J265" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="266" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K265">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="266" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A266" t="s">
         <v>1572</v>
       </c>
@@ -28933,8 +30036,11 @@
       <c r="J266" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="267" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K266">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="267" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A267" t="s">
         <v>1174</v>
       </c>
@@ -28965,8 +30071,11 @@
       <c r="J267" t="s">
         <v>1197</v>
       </c>
-    </row>
-    <row r="268" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K267">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="268" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A268" t="s">
         <v>1168</v>
       </c>
@@ -28997,8 +30106,11 @@
       <c r="J268" t="s">
         <v>1197</v>
       </c>
-    </row>
-    <row r="269" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K268">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="269" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A269" t="s">
         <v>1574</v>
       </c>
@@ -29029,8 +30141,11 @@
       <c r="J269" t="s">
         <v>1197</v>
       </c>
-    </row>
-    <row r="270" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K269">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="270" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A270" t="s">
         <v>1576</v>
       </c>
@@ -29061,8 +30176,11 @@
       <c r="J270" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="271" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K270">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="271" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A271" t="s">
         <v>1578</v>
       </c>
@@ -29093,8 +30211,11 @@
       <c r="J271" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="272" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K271">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="272" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A272" t="s">
         <v>1580</v>
       </c>
@@ -29125,8 +30246,11 @@
       <c r="J272" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="273" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K272">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="273" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A273" t="s">
         <v>1582</v>
       </c>
@@ -29157,8 +30281,11 @@
       <c r="J273" t="s">
         <v>1197</v>
       </c>
-    </row>
-    <row r="274" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K273">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="274" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A274" t="s">
         <v>1584</v>
       </c>
@@ -29189,8 +30316,11 @@
       <c r="J274" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="275" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K274">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="275" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A275" t="s">
         <v>1586</v>
       </c>
@@ -29221,8 +30351,11 @@
       <c r="J275" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="276" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K275">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="276" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A276" t="s">
         <v>1588</v>
       </c>
@@ -29253,8 +30386,11 @@
       <c r="J276" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="277" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K276">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="277" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A277" t="s">
         <v>1590</v>
       </c>
@@ -29285,8 +30421,11 @@
       <c r="J277" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="278" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K277">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="278" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A278" t="s">
         <v>1592</v>
       </c>
@@ -29317,8 +30456,11 @@
       <c r="J278" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="279" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K278">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="279" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A279" t="s">
         <v>1594</v>
       </c>
@@ -29349,8 +30491,11 @@
       <c r="J279" t="s">
         <v>1197</v>
       </c>
-    </row>
-    <row r="280" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K279">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="280" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A280" t="s">
         <v>1596</v>
       </c>
@@ -29381,8 +30526,11 @@
       <c r="J280" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="281" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K280">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="281" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A281" t="s">
         <v>1598</v>
       </c>
@@ -29413,8 +30561,11 @@
       <c r="J281" t="s">
         <v>1197</v>
       </c>
-    </row>
-    <row r="282" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K281">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="282" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A282" t="s">
         <v>1600</v>
       </c>
@@ -29445,8 +30596,11 @@
       <c r="J282" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="283" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K282">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="283" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A283" t="s">
         <v>1602</v>
       </c>
@@ -29477,8 +30631,11 @@
       <c r="J283" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="284" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K283">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="284" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A284" t="s">
         <v>1604</v>
       </c>
@@ -29509,8 +30666,11 @@
       <c r="J284" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="285" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K284">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="285" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A285" t="s">
         <v>1606</v>
       </c>
@@ -29541,8 +30701,11 @@
       <c r="J285" t="s">
         <v>1197</v>
       </c>
-    </row>
-    <row r="286" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K285">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="286" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A286" t="s">
         <v>1608</v>
       </c>
@@ -29573,8 +30736,11 @@
       <c r="J286" t="s">
         <v>1197</v>
       </c>
-    </row>
-    <row r="287" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K286">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="287" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A287" t="s">
         <v>1610</v>
       </c>
@@ -29605,8 +30771,11 @@
       <c r="J287" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="288" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K287">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="288" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A288" t="s">
         <v>1612</v>
       </c>
@@ -29637,8 +30806,11 @@
       <c r="J288" t="s">
         <v>1197</v>
       </c>
-    </row>
-    <row r="289" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K288">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="289" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A289" t="s">
         <v>1614</v>
       </c>
@@ -29669,8 +30841,11 @@
       <c r="J289" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="290" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K289">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="290" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A290" t="s">
         <v>1616</v>
       </c>
@@ -29701,8 +30876,11 @@
       <c r="J290" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="291" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K290">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="291" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A291" t="s">
         <v>1618</v>
       </c>
@@ -29733,8 +30911,11 @@
       <c r="J291" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="292" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K291">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="292" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A292" t="s">
         <v>1178</v>
       </c>
@@ -29765,8 +30946,11 @@
       <c r="J292" t="s">
         <v>1197</v>
       </c>
-    </row>
-    <row r="293" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K292">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="293" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A293" t="s">
         <v>1620</v>
       </c>
@@ -29797,8 +30981,11 @@
       <c r="J293" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="294" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K293">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="294" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A294" t="s">
         <v>1622</v>
       </c>
@@ -29829,8 +31016,11 @@
       <c r="J294" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="295" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K294">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="295" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A295" t="s">
         <v>1624</v>
       </c>
@@ -29861,8 +31051,11 @@
       <c r="J295" t="s">
         <v>1197</v>
       </c>
-    </row>
-    <row r="296" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K295">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="296" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A296" t="s">
         <v>1176</v>
       </c>
@@ -29893,8 +31086,11 @@
       <c r="J296" t="s">
         <v>1197</v>
       </c>
-    </row>
-    <row r="297" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K296">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="297" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A297" t="s">
         <v>1626</v>
       </c>
@@ -29925,8 +31121,11 @@
       <c r="J297" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="298" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K297">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="298" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A298" t="s">
         <v>1628</v>
       </c>
@@ -29957,8 +31156,11 @@
       <c r="J298" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="299" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K298">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="299" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A299" t="s">
         <v>1630</v>
       </c>
@@ -29989,8 +31191,11 @@
       <c r="J299" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="300" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K299">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="300" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A300" t="s">
         <v>1632</v>
       </c>
@@ -30021,8 +31226,11 @@
       <c r="J300" t="s">
         <v>1197</v>
       </c>
-    </row>
-    <row r="301" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K300">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="301" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A301" t="s">
         <v>1634</v>
       </c>
@@ -30053,8 +31261,11 @@
       <c r="J301" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="302" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K301">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="302" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A302" t="s">
         <v>1182</v>
       </c>
@@ -30085,8 +31296,11 @@
       <c r="J302" t="s">
         <v>1197</v>
       </c>
-    </row>
-    <row r="303" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K302">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="303" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A303" t="s">
         <v>1636</v>
       </c>
@@ -30117,8 +31331,11 @@
       <c r="J303" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="304" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K303">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="304" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A304" t="s">
         <v>1638</v>
       </c>
@@ -30149,8 +31366,11 @@
       <c r="J304" t="s">
         <v>1197</v>
       </c>
-    </row>
-    <row r="305" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K304">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="305" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A305" t="s">
         <v>1640</v>
       </c>
@@ -30181,8 +31401,11 @@
       <c r="J305" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="306" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K305">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="306" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A306" t="s">
         <v>1642</v>
       </c>
@@ -30213,8 +31436,11 @@
       <c r="J306" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="307" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K306">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="307" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A307" t="s">
         <v>1644</v>
       </c>
@@ -30245,8 +31471,11 @@
       <c r="J307" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="308" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K307">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="308" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A308" t="s">
         <v>1646</v>
       </c>
@@ -30277,8 +31506,11 @@
       <c r="J308" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="309" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K308">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="309" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A309" t="s">
         <v>1648</v>
       </c>
@@ -30309,8 +31541,11 @@
       <c r="J309" t="s">
         <v>1197</v>
       </c>
-    </row>
-    <row r="310" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K309">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="310" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A310" t="s">
         <v>1158</v>
       </c>
@@ -30341,8 +31576,11 @@
       <c r="J310" t="s">
         <v>1197</v>
       </c>
-    </row>
-    <row r="311" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K310">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="311" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A311" t="s">
         <v>871</v>
       </c>
@@ -30373,8 +31611,11 @@
       <c r="J311" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="312" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K311">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="312" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A312" t="s">
         <v>1651</v>
       </c>
@@ -30405,8 +31646,11 @@
       <c r="J312" t="s">
         <v>1197</v>
       </c>
-    </row>
-    <row r="313" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K312">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="313" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A313" t="s">
         <v>1653</v>
       </c>
@@ -30437,8 +31681,11 @@
       <c r="J313" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="314" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K313">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="314" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A314" t="s">
         <v>1655</v>
       </c>
@@ -30469,8 +31716,11 @@
       <c r="J314" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="315" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K314">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="315" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A315" t="s">
         <v>1657</v>
       </c>
@@ -30501,8 +31751,11 @@
       <c r="J315" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="316" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K315">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="316" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A316" t="s">
         <v>1659</v>
       </c>
@@ -30533,8 +31786,11 @@
       <c r="J316" t="s">
         <v>1661</v>
       </c>
-    </row>
-    <row r="317" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K316">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="317" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A317" t="s">
         <v>1662</v>
       </c>
@@ -30565,8 +31821,11 @@
       <c r="J317" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="318" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K317">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="318" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A318" t="s">
         <v>1664</v>
       </c>
@@ -30597,8 +31856,11 @@
       <c r="J318" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="319" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K318">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="319" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A319" t="s">
         <v>1666</v>
       </c>
@@ -30629,8 +31891,11 @@
       <c r="J319" t="s">
         <v>1197</v>
       </c>
-    </row>
-    <row r="320" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K319">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="320" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A320" t="s">
         <v>1668</v>
       </c>
@@ -30661,8 +31926,11 @@
       <c r="J320" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="321" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K320">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="321" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A321" t="s">
         <v>1188</v>
       </c>
@@ -30693,8 +31961,11 @@
       <c r="J321" t="s">
         <v>1197</v>
       </c>
-    </row>
-    <row r="322" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K321">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="322" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A322" t="s">
         <v>1670</v>
       </c>
@@ -30725,8 +31996,11 @@
       <c r="J322" t="s">
         <v>1197</v>
       </c>
-    </row>
-    <row r="323" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K322">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="323" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A323" t="s">
         <v>1672</v>
       </c>
@@ -30757,8 +32031,11 @@
       <c r="J323" t="s">
         <v>1197</v>
       </c>
-    </row>
-    <row r="324" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K323">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="324" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A324" t="s">
         <v>622</v>
       </c>
@@ -30789,8 +32066,11 @@
       <c r="J324" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="325" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K324">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="325" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A325" t="s">
         <v>1675</v>
       </c>
@@ -30821,8 +32101,11 @@
       <c r="J325" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="326" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K325">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="326" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A326" t="s">
         <v>1677</v>
       </c>
@@ -30853,8 +32136,11 @@
       <c r="J326" t="s">
         <v>1197</v>
       </c>
-    </row>
-    <row r="327" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K326">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="327" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A327" t="s">
         <v>1679</v>
       </c>
@@ -30885,8 +32171,11 @@
       <c r="J327" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="328" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K327">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="328" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A328" t="s">
         <v>1681</v>
       </c>
@@ -30917,8 +32206,11 @@
       <c r="J328" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="329" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K328">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="329" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A329" t="s">
         <v>1683</v>
       </c>
@@ -30949,8 +32241,11 @@
       <c r="J329" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="330" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K329">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="330" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A330" t="s">
         <v>1685</v>
       </c>
@@ -30981,8 +32276,11 @@
       <c r="J330" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="331" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K330">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="331" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A331" t="s">
         <v>1687</v>
       </c>
@@ -31013,8 +32311,11 @@
       <c r="J331" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="332" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K331">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="332" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A332" t="s">
         <v>1689</v>
       </c>
@@ -31045,8 +32346,11 @@
       <c r="J332" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="333" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K332">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="333" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A333" t="s">
         <v>1691</v>
       </c>
@@ -31077,8 +32381,11 @@
       <c r="J333" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="334" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K333">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="334" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A334" t="s">
         <v>1693</v>
       </c>
@@ -31109,8 +32416,11 @@
       <c r="J334" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="335" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K334">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="335" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A335" t="s">
         <v>1695</v>
       </c>
@@ -31141,8 +32451,11 @@
       <c r="J335" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="336" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K335">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="336" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A336" t="s">
         <v>1697</v>
       </c>
@@ -31173,8 +32486,11 @@
       <c r="J336" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="337" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K336">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="337" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A337" t="s">
         <v>1699</v>
       </c>
@@ -31205,8 +32521,11 @@
       <c r="J337" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="338" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K337">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="338" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A338" t="s">
         <v>1701</v>
       </c>
@@ -31237,8 +32556,11 @@
       <c r="J338" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="339" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K338">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="339" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A339" t="s">
         <v>1703</v>
       </c>
@@ -31269,8 +32591,11 @@
       <c r="J339" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="340" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K339">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="340" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A340" t="s">
         <v>1705</v>
       </c>
@@ -31301,8 +32626,11 @@
       <c r="J340" t="s">
         <v>1197</v>
       </c>
-    </row>
-    <row r="341" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K340">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="341" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A341" t="s">
         <v>1707</v>
       </c>
@@ -31333,8 +32661,11 @@
       <c r="J341" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="342" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K341">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="342" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A342" t="s">
         <v>1709</v>
       </c>
@@ -31365,8 +32696,11 @@
       <c r="J342" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="343" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K342">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="343" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A343" t="s">
         <v>1711</v>
       </c>
@@ -31397,8 +32731,11 @@
       <c r="J343" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="344" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K343">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="344" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A344" t="s">
         <v>1713</v>
       </c>
@@ -31429,8 +32766,11 @@
       <c r="J344" t="s">
         <v>1197</v>
       </c>
-    </row>
-    <row r="345" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K344">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="345" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A345" t="s">
         <v>1715</v>
       </c>
@@ -31461,8 +32801,11 @@
       <c r="J345" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="346" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K345">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="346" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A346" t="s">
         <v>1717</v>
       </c>
@@ -31493,8 +32836,11 @@
       <c r="J346" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="347" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K346">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="347" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A347" t="s">
         <v>1719</v>
       </c>
@@ -31525,8 +32871,11 @@
       <c r="J347" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="348" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K347">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="348" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A348" t="s">
         <v>1721</v>
       </c>
@@ -31557,8 +32906,11 @@
       <c r="J348" t="s">
         <v>1197</v>
       </c>
-    </row>
-    <row r="349" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K348">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="349" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A349" t="s">
         <v>1723</v>
       </c>
@@ -31589,8 +32941,11 @@
       <c r="J349" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="350" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K349">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="350" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A350" t="s">
         <v>1725</v>
       </c>
@@ -31621,8 +32976,11 @@
       <c r="J350" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="351" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K350">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="351" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A351" t="s">
         <v>1727</v>
       </c>
@@ -31653,8 +33011,11 @@
       <c r="J351" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="352" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K351">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="352" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A352" t="s">
         <v>1729</v>
       </c>
@@ -31685,8 +33046,11 @@
       <c r="J352" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="353" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K352">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="353" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A353" t="s">
         <v>1731</v>
       </c>
@@ -31717,8 +33081,11 @@
       <c r="J353" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="354" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K353">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="354" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A354" t="s">
         <v>1733</v>
       </c>
@@ -31749,8 +33116,11 @@
       <c r="J354" t="s">
         <v>1197</v>
       </c>
-    </row>
-    <row r="355" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K354">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="355" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A355" t="s">
         <v>1735</v>
       </c>
@@ -31781,8 +33151,11 @@
       <c r="J355" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="356" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K355">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="356" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A356" t="s">
         <v>1737</v>
       </c>
@@ -31813,8 +33186,11 @@
       <c r="J356" t="s">
         <v>1197</v>
       </c>
-    </row>
-    <row r="357" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K356">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="357" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A357" t="s">
         <v>1739</v>
       </c>
@@ -31845,8 +33221,11 @@
       <c r="J357" t="s">
         <v>1197</v>
       </c>
-    </row>
-    <row r="358" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K357">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="358" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A358" t="s">
         <v>1741</v>
       </c>
@@ -31877,8 +33256,11 @@
       <c r="J358" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="359" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K358">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="359" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A359" t="s">
         <v>1743</v>
       </c>
@@ -31909,8 +33291,11 @@
       <c r="J359" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="360" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K359">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="360" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A360" t="s">
         <v>1745</v>
       </c>
@@ -31941,8 +33326,11 @@
       <c r="J360" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="361" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K360">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="361" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A361" t="s">
         <v>1747</v>
       </c>
@@ -31973,8 +33361,11 @@
       <c r="J361" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="362" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K361">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="362" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A362" t="s">
         <v>1749</v>
       </c>
@@ -32005,8 +33396,11 @@
       <c r="J362" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="363" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K362">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="363" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A363" t="s">
         <v>1751</v>
       </c>
@@ -32037,8 +33431,11 @@
       <c r="J363" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="364" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K363">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="364" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A364" t="s">
         <v>1753</v>
       </c>
@@ -32069,8 +33466,11 @@
       <c r="J364" t="s">
         <v>1197</v>
       </c>
-    </row>
-    <row r="365" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K364">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="365" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A365" t="s">
         <v>1755</v>
       </c>
@@ -32101,8 +33501,11 @@
       <c r="J365" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="366" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K365">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="366" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A366" t="s">
         <v>1757</v>
       </c>
@@ -32133,8 +33536,11 @@
       <c r="J366" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="367" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K366">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="367" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A367" t="s">
         <v>1759</v>
       </c>
@@ -32165,8 +33571,11 @@
       <c r="J367" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="368" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K367">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="368" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A368" t="s">
         <v>1761</v>
       </c>
@@ -32197,8 +33606,11 @@
       <c r="J368" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="369" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K368">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="369" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A369" t="s">
         <v>1180</v>
       </c>
@@ -32229,8 +33641,11 @@
       <c r="J369" t="s">
         <v>1197</v>
       </c>
-    </row>
-    <row r="370" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K369">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="370" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A370" t="s">
         <v>1763</v>
       </c>
@@ -32261,8 +33676,11 @@
       <c r="J370" t="s">
         <v>1197</v>
       </c>
-    </row>
-    <row r="371" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K370">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="371" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A371" t="s">
         <v>1765</v>
       </c>
@@ -32293,8 +33711,11 @@
       <c r="J371" t="s">
         <v>1197</v>
       </c>
-    </row>
-    <row r="372" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K371">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="372" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A372" t="s">
         <v>1767</v>
       </c>
@@ -32325,8 +33746,11 @@
       <c r="J372" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="373" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K372">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="373" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A373" t="s">
         <v>1769</v>
       </c>
@@ -32357,8 +33781,11 @@
       <c r="J373" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="374" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K373">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="374" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A374" t="s">
         <v>1771</v>
       </c>
@@ -32389,8 +33816,11 @@
       <c r="J374" t="s">
         <v>1197</v>
       </c>
-    </row>
-    <row r="375" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K374">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="375" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A375" t="s">
         <v>1773</v>
       </c>
@@ -32421,8 +33851,11 @@
       <c r="J375" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="376" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K375">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="376" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A376" t="s">
         <v>1775</v>
       </c>
@@ -32453,8 +33886,11 @@
       <c r="J376" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="377" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K376">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="377" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A377" t="s">
         <v>1777</v>
       </c>
@@ -32485,8 +33921,11 @@
       <c r="J377" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="378" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K377">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="378" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A378" t="s">
         <v>1779</v>
       </c>
@@ -32517,8 +33956,11 @@
       <c r="J378" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="379" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K378">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="379" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A379" t="s">
         <v>1781</v>
       </c>
@@ -32549,8 +33991,11 @@
       <c r="J379" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="380" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K379">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="380" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A380" t="s">
         <v>704</v>
       </c>
@@ -32581,8 +34026,11 @@
       <c r="J380" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="381" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K380">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="381" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A381" t="s">
         <v>1784</v>
       </c>
@@ -32613,8 +34061,11 @@
       <c r="J381" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="382" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K381">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="382" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A382" t="s">
         <v>1786</v>
       </c>
@@ -32645,8 +34096,11 @@
       <c r="J382" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="383" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K382">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="383" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A383" t="s">
         <v>1788</v>
       </c>
@@ -32677,8 +34131,11 @@
       <c r="J383" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="384" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K383">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="384" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A384" t="s">
         <v>1790</v>
       </c>
@@ -32709,8 +34166,11 @@
       <c r="J384" t="s">
         <v>1197</v>
       </c>
-    </row>
-    <row r="385" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K384">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="385" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A385" t="s">
         <v>1792</v>
       </c>
@@ -32741,8 +34201,11 @@
       <c r="J385" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="386" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K385">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="386" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A386" t="s">
         <v>1794</v>
       </c>
@@ -32773,8 +34236,11 @@
       <c r="J386" t="s">
         <v>1197</v>
       </c>
-    </row>
-    <row r="387" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K386">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="387" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A387" t="s">
         <v>1796</v>
       </c>
@@ -32805,8 +34271,11 @@
       <c r="J387" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="388" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K387">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="388" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A388" t="s">
         <v>1798</v>
       </c>
@@ -32837,8 +34306,11 @@
       <c r="J388" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="389" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K388">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="389" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A389" t="s">
         <v>1800</v>
       </c>
@@ -32869,8 +34341,11 @@
       <c r="J389" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="390" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K389">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="390" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A390" t="s">
         <v>1802</v>
       </c>
@@ -32901,8 +34376,11 @@
       <c r="J390" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="391" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K390">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="391" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A391" t="s">
         <v>1186</v>
       </c>
@@ -32933,8 +34411,11 @@
       <c r="J391" t="s">
         <v>1197</v>
       </c>
-    </row>
-    <row r="392" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K391">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="392" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A392" t="s">
         <v>1804</v>
       </c>
@@ -32965,8 +34446,11 @@
       <c r="J392" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="393" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K392">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="393" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A393" t="s">
         <v>1806</v>
       </c>
@@ -32997,8 +34481,11 @@
       <c r="J393" t="s">
         <v>1197</v>
       </c>
-    </row>
-    <row r="394" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K393">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="394" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A394" t="s">
         <v>616</v>
       </c>
@@ -33029,8 +34516,11 @@
       <c r="J394" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="395" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K394">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="395" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A395" t="s">
         <v>1809</v>
       </c>
@@ -33061,8 +34551,11 @@
       <c r="J395" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="396" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K395">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="396" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A396" t="s">
         <v>1811</v>
       </c>
@@ -33093,8 +34586,11 @@
       <c r="J396" t="s">
         <v>1197</v>
       </c>
-    </row>
-    <row r="397" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K396">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="397" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A397" t="s">
         <v>1813</v>
       </c>
@@ -33125,8 +34621,11 @@
       <c r="J397" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="398" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K397">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="398" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A398" t="s">
         <v>1815</v>
       </c>
@@ -33157,8 +34656,11 @@
       <c r="J398" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="399" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K398">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="399" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A399" t="s">
         <v>1817</v>
       </c>
@@ -33189,8 +34691,11 @@
       <c r="J399" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="400" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K399">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="400" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A400" t="s">
         <v>1819</v>
       </c>
@@ -33221,8 +34726,11 @@
       <c r="J400" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="401" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K400">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="401" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A401" t="s">
         <v>1821</v>
       </c>
@@ -33253,8 +34761,11 @@
       <c r="J401" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="402" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K401">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="402" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A402" t="s">
         <v>1823</v>
       </c>
@@ -33285,8 +34796,11 @@
       <c r="J402" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="403" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K402">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="403" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A403" t="s">
         <v>1825</v>
       </c>
@@ -33317,8 +34831,11 @@
       <c r="J403" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="404" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K403">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="404" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A404" t="s">
         <v>1827</v>
       </c>
@@ -33349,8 +34866,11 @@
       <c r="J404" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="405" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K404">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="405" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A405" t="s">
         <v>1829</v>
       </c>
@@ -33381,8 +34901,11 @@
       <c r="J405" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="406" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K405">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="406" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A406" t="s">
         <v>1831</v>
       </c>
@@ -33413,8 +34936,11 @@
       <c r="J406" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="407" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K406">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="407" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A407" t="s">
         <v>1833</v>
       </c>
@@ -33445,8 +34971,11 @@
       <c r="J407" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="408" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K407">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="408" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A408" t="s">
         <v>1835</v>
       </c>
@@ -33477,8 +35006,11 @@
       <c r="J408" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="409" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K408">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="409" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A409" t="s">
         <v>1837</v>
       </c>
@@ -33509,8 +35041,11 @@
       <c r="J409" t="s">
         <v>1197</v>
       </c>
-    </row>
-    <row r="410" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K409">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="410" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A410" t="s">
         <v>1839</v>
       </c>
@@ -33541,8 +35076,11 @@
       <c r="J410" t="s">
         <v>1197</v>
       </c>
-    </row>
-    <row r="411" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K410">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="411" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A411" t="s">
         <v>1841</v>
       </c>
@@ -33573,8 +35111,11 @@
       <c r="J411" t="s">
         <v>1197</v>
       </c>
-    </row>
-    <row r="412" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K411">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="412" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A412" t="s">
         <v>1843</v>
       </c>
@@ -33605,8 +35146,11 @@
       <c r="J412" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="413" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K412">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="413" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A413" t="s">
         <v>1845</v>
       </c>
@@ -33637,8 +35181,11 @@
       <c r="J413" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="414" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K413">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="414" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A414" t="s">
         <v>1847</v>
       </c>
@@ -33669,8 +35216,11 @@
       <c r="J414" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="415" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K414">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="415" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A415" t="s">
         <v>1849</v>
       </c>
@@ -33701,8 +35251,11 @@
       <c r="J415" t="s">
         <v>1197</v>
       </c>
-    </row>
-    <row r="416" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K415">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="416" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A416" t="s">
         <v>1851</v>
       </c>
@@ -33733,8 +35286,11 @@
       <c r="J416" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="417" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K416">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="417" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A417" t="s">
         <v>1853</v>
       </c>
@@ -33765,8 +35321,11 @@
       <c r="J417" t="s">
         <v>1197</v>
       </c>
-    </row>
-    <row r="418" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K417">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="418" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A418" t="s">
         <v>1855</v>
       </c>
@@ -33797,8 +35356,11 @@
       <c r="J418" t="s">
         <v>1197</v>
       </c>
-    </row>
-    <row r="419" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K418">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="419" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A419" t="s">
         <v>1857</v>
       </c>
@@ -33829,8 +35391,11 @@
       <c r="J419" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="420" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K419">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="420" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A420" t="s">
         <v>1859</v>
       </c>
@@ -33861,8 +35426,11 @@
       <c r="J420" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="421" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K420">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="421" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A421" t="s">
         <v>1861</v>
       </c>
@@ -33893,8 +35461,11 @@
       <c r="J421" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="422" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K421">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="422" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A422" t="s">
         <v>1863</v>
       </c>
@@ -33925,8 +35496,11 @@
       <c r="J422" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="423" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K422">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="423" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A423" t="s">
         <v>1865</v>
       </c>
@@ -33957,8 +35531,11 @@
       <c r="J423" t="s">
         <v>1197</v>
       </c>
-    </row>
-    <row r="424" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K423">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="424" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A424" t="s">
         <v>1867</v>
       </c>
@@ -33989,8 +35566,11 @@
       <c r="J424" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="425" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K424">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="425" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A425" t="s">
         <v>1869</v>
       </c>
@@ -34021,8 +35601,11 @@
       <c r="J425" t="s">
         <v>1197</v>
       </c>
-    </row>
-    <row r="426" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K425">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="426" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A426" t="s">
         <v>1871</v>
       </c>
@@ -34053,8 +35636,11 @@
       <c r="J426" t="s">
         <v>1197</v>
       </c>
-    </row>
-    <row r="427" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K426">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="427" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A427" t="s">
         <v>1873</v>
       </c>
@@ -34085,8 +35671,11 @@
       <c r="J427" t="s">
         <v>1197</v>
       </c>
-    </row>
-    <row r="428" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K427">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="428" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A428" t="s">
         <v>1875</v>
       </c>
@@ -34117,8 +35706,11 @@
       <c r="J428" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="429" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K428">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="429" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A429" t="s">
         <v>1877</v>
       </c>
@@ -34149,8 +35741,11 @@
       <c r="J429" t="s">
         <v>1197</v>
       </c>
-    </row>
-    <row r="430" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K429">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="430" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A430" t="s">
         <v>1879</v>
       </c>
@@ -34181,8 +35776,11 @@
       <c r="J430" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="431" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K430">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="431" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A431" t="s">
         <v>1881</v>
       </c>
@@ -34213,8 +35811,11 @@
       <c r="J431" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="432" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K431">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="432" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A432" t="s">
         <v>1883</v>
       </c>
@@ -34245,8 +35846,11 @@
       <c r="J432" t="s">
         <v>1197</v>
       </c>
-    </row>
-    <row r="433" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K432">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="433" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A433" t="s">
         <v>1885</v>
       </c>
@@ -34277,8 +35881,11 @@
       <c r="J433" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="434" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K433">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="434" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A434" t="s">
         <v>1887</v>
       </c>
@@ -34309,8 +35916,11 @@
       <c r="J434" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="435" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K434">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="435" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A435" t="s">
         <v>1889</v>
       </c>
@@ -34341,8 +35951,11 @@
       <c r="J435" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="436" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K435">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="436" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A436" t="s">
         <v>1891</v>
       </c>
@@ -34373,8 +35986,11 @@
       <c r="J436" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="437" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K436">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="437" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A437" t="s">
         <v>1893</v>
       </c>
@@ -34405,8 +36021,11 @@
       <c r="J437" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="438" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K437">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="438" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A438" t="s">
         <v>1895</v>
       </c>
@@ -34437,8 +36056,11 @@
       <c r="J438" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="439" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K438">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="439" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A439" t="s">
         <v>1897</v>
       </c>
@@ -34469,8 +36091,11 @@
       <c r="J439" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="440" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K439">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="440" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A440" t="s">
         <v>1899</v>
       </c>
@@ -34501,8 +36126,11 @@
       <c r="J440" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="441" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K440">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="441" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A441" t="s">
         <v>1901</v>
       </c>
@@ -34533,8 +36161,11 @@
       <c r="J441" t="s">
         <v>1197</v>
       </c>
-    </row>
-    <row r="442" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K441">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="442" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A442" t="s">
         <v>1903</v>
       </c>
@@ -34565,8 +36196,11 @@
       <c r="J442" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="443" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K442">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="443" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A443" t="s">
         <v>1905</v>
       </c>
@@ -34597,8 +36231,11 @@
       <c r="J443" t="s">
         <v>1197</v>
       </c>
-    </row>
-    <row r="444" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K443">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="444" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A444" t="s">
         <v>1907</v>
       </c>
@@ -34629,8 +36266,11 @@
       <c r="J444" t="s">
         <v>1197</v>
       </c>
-    </row>
-    <row r="445" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K444">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="445" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A445" t="s">
         <v>1909</v>
       </c>
@@ -34661,8 +36301,11 @@
       <c r="J445" t="s">
         <v>1197</v>
       </c>
-    </row>
-    <row r="446" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K445">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="446" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A446" t="s">
         <v>1911</v>
       </c>
@@ -34693,8 +36336,11 @@
       <c r="J446" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="447" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K446">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="447" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A447" t="s">
         <v>1913</v>
       </c>
@@ -34725,8 +36371,11 @@
       <c r="J447" t="s">
         <v>1197</v>
       </c>
-    </row>
-    <row r="448" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K447">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="448" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A448" t="s">
         <v>1915</v>
       </c>
@@ -34757,8 +36406,11 @@
       <c r="J448" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="449" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K448">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="449" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A449" t="s">
         <v>1917</v>
       </c>
@@ -34789,8 +36441,11 @@
       <c r="J449" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="450" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K449">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="450" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A450" t="s">
         <v>1919</v>
       </c>
@@ -34821,8 +36476,11 @@
       <c r="J450" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="451" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K450">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="451" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A451" t="s">
         <v>1921</v>
       </c>
@@ -34853,8 +36511,11 @@
       <c r="J451" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="452" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K451">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="452" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A452" t="s">
         <v>1923</v>
       </c>
@@ -34885,8 +36546,11 @@
       <c r="J452" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="453" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K452">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="453" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A453" t="s">
         <v>1925</v>
       </c>
@@ -34917,8 +36581,11 @@
       <c r="J453" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="454" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K453">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="454" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A454" t="s">
         <v>1927</v>
       </c>
@@ -34949,8 +36616,11 @@
       <c r="J454" t="s">
         <v>1197</v>
       </c>
-    </row>
-    <row r="455" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K454">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="455" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A455" t="s">
         <v>1929</v>
       </c>
@@ -34981,8 +36651,11 @@
       <c r="J455" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="456" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K455">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="456" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A456" t="s">
         <v>1931</v>
       </c>
@@ -35013,8 +36686,11 @@
       <c r="J456" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="457" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K456">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="457" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A457" t="s">
         <v>1933</v>
       </c>
@@ -35045,8 +36721,11 @@
       <c r="J457" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="458" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K457">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="458" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A458" t="s">
         <v>1935</v>
       </c>
@@ -35077,8 +36756,11 @@
       <c r="J458" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="459" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K458">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="459" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A459" t="s">
         <v>1937</v>
       </c>
@@ -35109,8 +36791,11 @@
       <c r="J459" t="s">
         <v>1197</v>
       </c>
-    </row>
-    <row r="460" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K459">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="460" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A460" t="s">
         <v>1939</v>
       </c>
@@ -35141,8 +36826,11 @@
       <c r="J460" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="461" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K460">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="461" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A461" t="s">
         <v>1941</v>
       </c>
@@ -35173,8 +36861,11 @@
       <c r="J461" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="462" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K461">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="462" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A462" t="s">
         <v>1943</v>
       </c>
@@ -35205,8 +36896,11 @@
       <c r="J462" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="463" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K462">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="463" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A463" t="s">
         <v>1945</v>
       </c>
@@ -35237,8 +36931,11 @@
       <c r="J463" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="464" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K463">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="464" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A464" t="s">
         <v>1947</v>
       </c>
@@ -35269,8 +36966,11 @@
       <c r="J464" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="465" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K464">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="465" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A465" t="s">
         <v>1949</v>
       </c>
@@ -35301,8 +37001,11 @@
       <c r="J465" t="s">
         <v>1197</v>
       </c>
-    </row>
-    <row r="466" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K465">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="466" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A466" t="s">
         <v>1951</v>
       </c>
@@ -35333,8 +37036,11 @@
       <c r="J466" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="467" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K466">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="467" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A467" t="s">
         <v>1953</v>
       </c>
@@ -35365,8 +37071,11 @@
       <c r="J467" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="468" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K467">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="468" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A468" t="s">
         <v>1955</v>
       </c>
@@ -35397,8 +37106,11 @@
       <c r="J468" t="s">
         <v>1197</v>
       </c>
-    </row>
-    <row r="469" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K468">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="469" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A469" t="s">
         <v>1957</v>
       </c>
@@ -35429,8 +37141,11 @@
       <c r="J469" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="470" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K469">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="470" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A470" t="s">
         <v>1959</v>
       </c>
@@ -35461,8 +37176,11 @@
       <c r="J470" t="s">
         <v>1197</v>
       </c>
-    </row>
-    <row r="471" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K470">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="471" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A471" t="s">
         <v>1961</v>
       </c>
@@ -35493,8 +37211,11 @@
       <c r="J471" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="472" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K471">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="472" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A472" t="s">
         <v>1963</v>
       </c>
@@ -35525,8 +37246,11 @@
       <c r="J472" t="s">
         <v>1197</v>
       </c>
-    </row>
-    <row r="473" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K472">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="473" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A473" t="s">
         <v>1965</v>
       </c>
@@ -35557,8 +37281,11 @@
       <c r="J473" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="474" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K473">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="474" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A474" t="s">
         <v>1967</v>
       </c>
@@ -35589,8 +37316,11 @@
       <c r="J474" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="475" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K474">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="475" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A475" t="s">
         <v>1969</v>
       </c>
@@ -35621,8 +37351,11 @@
       <c r="J475" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="476" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K475">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="476" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A476" t="s">
         <v>1971</v>
       </c>
@@ -35653,8 +37386,11 @@
       <c r="J476" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="477" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K476">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="477" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A477" t="s">
         <v>1973</v>
       </c>
@@ -35685,8 +37421,11 @@
       <c r="J477" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="478" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K477">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="478" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A478" t="s">
         <v>1975</v>
       </c>
@@ -35717,8 +37456,11 @@
       <c r="J478" t="s">
         <v>1197</v>
       </c>
-    </row>
-    <row r="479" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K478">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="479" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A479" t="s">
         <v>1977</v>
       </c>
@@ -35749,8 +37491,11 @@
       <c r="J479" t="s">
         <v>1197</v>
       </c>
-    </row>
-    <row r="480" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K479">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="480" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A480" t="s">
         <v>1979</v>
       </c>
@@ -35781,8 +37526,11 @@
       <c r="J480" t="s">
         <v>1197</v>
       </c>
-    </row>
-    <row r="481" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K480">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="481" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A481" t="s">
         <v>1981</v>
       </c>
@@ -35813,8 +37561,11 @@
       <c r="J481" t="s">
         <v>1197</v>
       </c>
-    </row>
-    <row r="482" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K481">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="482" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A482" t="s">
         <v>1983</v>
       </c>
@@ -35845,8 +37596,11 @@
       <c r="J482" t="s">
         <v>1197</v>
       </c>
-    </row>
-    <row r="483" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K482">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="483" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A483" t="s">
         <v>1985</v>
       </c>
@@ -35877,8 +37631,11 @@
       <c r="J483" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="484" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K483">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="484" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A484" t="s">
         <v>1987</v>
       </c>
@@ -35909,8 +37666,11 @@
       <c r="J484" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="485" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K484">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="485" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A485" t="s">
         <v>1989</v>
       </c>
@@ -35941,8 +37701,11 @@
       <c r="J485" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="486" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K485">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="486" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A486" t="s">
         <v>1991</v>
       </c>
@@ -35973,8 +37736,11 @@
       <c r="J486" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="487" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K486">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="487" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A487" t="s">
         <v>1993</v>
       </c>
@@ -36005,8 +37771,11 @@
       <c r="J487" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="488" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K487">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="488" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A488" t="s">
         <v>1995</v>
       </c>
@@ -36037,8 +37806,11 @@
       <c r="J488" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="489" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K488">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="489" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A489" t="s">
         <v>1997</v>
       </c>
@@ -36069,8 +37841,11 @@
       <c r="J489" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="490" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K489">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="490" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A490" t="s">
         <v>1999</v>
       </c>
@@ -36101,8 +37876,11 @@
       <c r="J490" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="491" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K490">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="491" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A491" t="s">
         <v>2001</v>
       </c>
@@ -36133,8 +37911,11 @@
       <c r="J491" t="s">
         <v>1197</v>
       </c>
-    </row>
-    <row r="492" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K491">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="492" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A492" t="s">
         <v>2003</v>
       </c>
@@ -36165,8 +37946,11 @@
       <c r="J492" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="493" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K492">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="493" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A493" t="s">
         <v>2005</v>
       </c>
@@ -36197,8 +37981,11 @@
       <c r="J493" t="s">
         <v>1197</v>
       </c>
-    </row>
-    <row r="494" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K493">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="494" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A494" t="s">
         <v>2007</v>
       </c>
@@ -36229,8 +38016,11 @@
       <c r="J494" t="s">
         <v>1197</v>
       </c>
-    </row>
-    <row r="495" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K494">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="495" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A495" t="s">
         <v>912</v>
       </c>
@@ -36261,8 +38051,11 @@
       <c r="J495" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="496" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K495">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="496" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A496" t="s">
         <v>2010</v>
       </c>
@@ -36293,8 +38086,11 @@
       <c r="J496" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="497" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K496">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="497" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A497" t="s">
         <v>2012</v>
       </c>
@@ -36325,8 +38121,11 @@
       <c r="J497" t="s">
         <v>1197</v>
       </c>
-    </row>
-    <row r="498" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K497">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="498" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A498" t="s">
         <v>2014</v>
       </c>
@@ -36357,8 +38156,11 @@
       <c r="J498" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="499" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K498">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="499" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A499" t="s">
         <v>2016</v>
       </c>
@@ -36389,8 +38191,11 @@
       <c r="J499" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="500" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K499">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="500" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A500" t="s">
         <v>2018</v>
       </c>
@@ -36421,8 +38226,11 @@
       <c r="J500" t="s">
         <v>1197</v>
       </c>
-    </row>
-    <row r="501" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K500">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="501" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A501" t="s">
         <v>2020</v>
       </c>
@@ -36453,8 +38261,11 @@
       <c r="J501" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="502" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K501">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="502" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A502" t="s">
         <v>2022</v>
       </c>
@@ -36485,8 +38296,11 @@
       <c r="J502" t="s">
         <v>1197</v>
       </c>
-    </row>
-    <row r="503" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K502">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="503" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A503" t="s">
         <v>2024</v>
       </c>
@@ -36517,8 +38331,11 @@
       <c r="J503" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="504" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K503">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="504" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A504" t="s">
         <v>2026</v>
       </c>
@@ -36548,6 +38365,9 @@
       </c>
       <c r="J504" t="s">
         <v>1197</v>
+      </c>
+      <c r="K504">
+        <v>1000</v>
       </c>
     </row>
   </sheetData>
